--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027A8171-92AD-4BFD-8EE0-3F0BE7308AA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D7316E-A721-4229-A79E-6313E9314401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="204">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -635,6 +635,30 @@
   </si>
   <si>
     <t>فل عدد 2 الحبه 0.750</t>
+  </si>
+  <si>
+    <t>Inv-53</t>
+  </si>
+  <si>
+    <t>Inv-54</t>
+  </si>
+  <si>
+    <t>Inv-55</t>
+  </si>
+  <si>
+    <t>Inv-56</t>
+  </si>
+  <si>
+    <t>فل عدد 24 الحبه .750</t>
+  </si>
+  <si>
+    <t>دارسينا خضراء عدد 1 الحبه 2</t>
+  </si>
+  <si>
+    <t>افوبيا عدد 2 الحبه .750</t>
+  </si>
+  <si>
+    <t>دارسينا سوداء عدد 3 الحبه 1</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1958,7 @@
       <c r="B3" s="139"/>
       <c r="C3" s="3">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>349.75</v>
+        <v>374.35</v>
       </c>
       <c r="D3" s="140" t="s">
         <v>4</v>
@@ -3052,7 +3076,7 @@
       </c>
       <c r="E41" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(37,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F41" s="9" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(37,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -3095,28 +3119,28 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(39,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B43" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(39,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-53</v>
       </c>
       <c r="C43" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(39,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>فل عدد 24 الحبه .750</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="8" t="str">
+      <c r="E43" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(39,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="F43" s="9" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(39,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G43" s="10"/>
       <c r="H43" s="1" t="str">
@@ -3125,28 +3149,28 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1">
-      <c r="A44" s="11" t="str">
+      <c r="A44" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(40,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B44" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(40,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-54</v>
       </c>
       <c r="C44" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(40,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>دارسينا خضراء عدد 1 الحبه 2</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="15" t="str">
+      <c r="E44" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(40,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F44" s="16" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(40,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G44" s="17"/>
       <c r="H44" s="1" t="str">
@@ -3155,28 +3179,28 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1">
-      <c r="A45" s="4" t="str">
+      <c r="A45" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(41,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B45" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(41,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-55</v>
       </c>
       <c r="C45" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(41,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>افوبيا عدد 2 الحبه .750</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E45" s="8" t="str">
+      <c r="E45" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(41,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="F45" s="9" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(41,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="1" t="str">
@@ -3185,28 +3209,28 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1">
-      <c r="A46" s="11" t="str">
+      <c r="A46" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(42,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B46" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(42,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-56</v>
       </c>
       <c r="C46" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(42,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>دارسينا سوداء عدد 3 الحبه 1</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E46" s="15" t="str">
+      <c r="E46" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(42,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F46" s="16" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(42,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G46" s="17"/>
       <c r="H46" s="1" t="str">
@@ -4963,7 +4987,7 @@
       <c r="D105" s="131"/>
       <c r="E105" s="18">
         <f>SUM(E5:E104)</f>
-        <v>502</v>
+        <v>526.6</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
@@ -7996,7 +8020,7 @@
       <c r="C208" s="134"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>349.75</v>
+        <v>374.35</v>
       </c>
       <c r="E208" s="135" t="s">
         <v>11</v>
@@ -9666,9 +9690,9 @@
         <f>IF(AND(D4&gt;0,G4="المحفظة"),COUNTIFS($D$4:D4,"&gt;"&amp;0,$G$4:G4,"المحفظة"),"")</f>
         <v>1</v>
       </c>
-      <c r="N4" s="1" t="str">
+      <c r="N4" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A4)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A4)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A4&lt;&gt;""),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O4" s="1" t="str">
         <f>IF(AND(D4&gt;0,F4="أحد الشركاء"),1,"")</f>
@@ -9710,9 +9734,9 @@
         <f>IF(AND(D5&gt;0,G5="المحفظة"),COUNTIFS($D$4:D5,"&gt;"&amp;0,$G$4:G5,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N5" s="1" t="str">
+      <c r="N5" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A5)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A5)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A5&lt;&gt;""),IFERROR(MAX($N$4:N4),0)+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O5" s="1" t="str">
         <f>IF(AND(D5&gt;0,F5="أحد الشركاء"),COUNTIFS($D$4:D5,"&gt;"&amp;0,$F$4:F5,"أحد الشركاء"),"")</f>
@@ -9758,9 +9782,9 @@
         <f>IF(AND(D6&gt;0,G6="المحفظة"),COUNTIFS($D$4:D6,"&gt;"&amp;0,$G$4:G6,"المحفظة"),"")</f>
         <v>2</v>
       </c>
-      <c r="N6" s="1" t="str">
+      <c r="N6" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A6)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A6)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A6&lt;&gt;""),IFERROR(MAX($N$4:N5),0)+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="O6" s="1" t="str">
         <f>IF(AND(D6&gt;0,F6="أحد الشركاء"),COUNTIFS($D$4:D6,"&gt;"&amp;0,$F$4:F6,"أحد الشركاء"),"")</f>
@@ -9804,9 +9828,9 @@
         <f>IF(AND(D7&gt;0,G7="المحفظة"),COUNTIFS($D$4:D7,"&gt;"&amp;0,$G$4:G7,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N7" s="1" t="str">
+      <c r="N7" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A7)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A7)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A7&lt;&gt;""),IFERROR(MAX($N$4:N6),0)+1,"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="O7" s="1">
         <f>IF(AND(D7&gt;0,F7="أحد الشركاء"),COUNTIFS($D$4:D7,"&gt;"&amp;0,$F$4:F7,"أحد الشركاء"),"")</f>
@@ -9852,9 +9876,9 @@
         <f>IF(AND(D8&gt;0,G8="المحفظة"),COUNTIFS($D$4:D8,"&gt;"&amp;0,$G$4:G8,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N8" s="1" t="str">
+      <c r="N8" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A8)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A8)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A8&lt;&gt;""),IFERROR(MAX($N$4:N7),0)+1,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O8" s="1">
         <f>IF(AND(D8&gt;0,F8="أحد الشركاء"),COUNTIFS($D$4:D8,"&gt;"&amp;0,$F$4:F8,"أحد الشركاء"),"")</f>
@@ -9898,9 +9922,9 @@
         <f>IF(AND(D9&gt;0,G9="المحفظة"),COUNTIFS($D$4:D9,"&gt;"&amp;0,$G$4:G9,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N9" s="1" t="str">
+      <c r="N9" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A9)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A9)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A9&lt;&gt;""),IFERROR(MAX($N$4:N8),0)+1,"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="O9" s="1">
         <f>IF(AND(D9&gt;0,F9="أحد الشركاء"),COUNTIFS($D$4:D9,"&gt;"&amp;0,$F$4:F9,"أحد الشركاء"),"")</f>
@@ -9948,9 +9972,9 @@
         <f>IF(AND(D10&gt;0,G10="المحفظة"),COUNTIFS($D$4:D10,"&gt;"&amp;0,$G$4:G10,"المحفظة"),"")</f>
         <v>3</v>
       </c>
-      <c r="N10" s="1" t="str">
+      <c r="N10" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A10)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A10)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A10&lt;&gt;""),IFERROR(MAX($N$4:N9),0)+1,"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O10" s="1" t="str">
         <f>IF(AND(D10&gt;0,F10="أحد الشركاء"),COUNTIFS($D$4:D10,"&gt;"&amp;0,$F$4:F10,"أحد الشركاء"),"")</f>
@@ -9996,9 +10020,9 @@
         <f>IF(AND(D11&gt;0,G11="المحفظة"),COUNTIFS($D$4:D11,"&gt;"&amp;0,$G$4:G11,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N11" s="1" t="str">
+      <c r="N11" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A11)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A11)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A11&lt;&gt;""),IFERROR(MAX($N$4:N10),0)+1,"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="O11" s="1">
         <f>IF(AND(D11&gt;0,F11="أحد الشركاء"),COUNTIFS($D$4:D11,"&gt;"&amp;0,$F$4:F11,"أحد الشركاء"),"")</f>
@@ -10034,9 +10058,9 @@
         <f>IF(AND(D12&gt;0,G12="المحفظة"),COUNTIFS($D$4:D12,"&gt;"&amp;0,$G$4:G12,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N12" s="1" t="str">
+      <c r="N12" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A12)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A12)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A12&lt;&gt;""),IFERROR(MAX($N$4:N11),0)+1,"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="O12" s="1" t="str">
         <f>IF(AND(D12&gt;0,F12="أحد الشركاء"),COUNTIFS($D$4:D12,"&gt;"&amp;0,$F$4:F12,"أحد الشركاء"),"")</f>
@@ -10082,9 +10106,9 @@
         <f>IF(AND(D13&gt;0,G13="المحفظة"),COUNTIFS($D$4:D13,"&gt;"&amp;0,$G$4:G13,"المحفظة"),"")</f>
         <v>4</v>
       </c>
-      <c r="N13" s="1" t="str">
+      <c r="N13" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A13)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A13)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A13&lt;&gt;""),IFERROR(MAX($N$4:N12),0)+1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O13" s="1" t="str">
         <f>IF(AND(D13&gt;0,F13="أحد الشركاء"),COUNTIFS($D$4:D13,"&gt;"&amp;0,$F$4:F13,"أحد الشركاء"),"")</f>
@@ -10130,9 +10154,9 @@
         <f>IF(AND(D14&gt;0,G14="المحفظة"),COUNTIFS($D$4:D14,"&gt;"&amp;0,$G$4:G14,"المحفظة"),"")</f>
         <v>5</v>
       </c>
-      <c r="N14" s="1" t="str">
+      <c r="N14" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A14)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A14)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A14&lt;&gt;""),IFERROR(MAX($N$4:N13),0)+1,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(AND(D14&gt;0,F14="أحد الشركاء"),COUNTIFS($D$4:D14,"&gt;"&amp;0,$F$4:F14,"أحد الشركاء"),"")</f>
@@ -10176,7 +10200,7 @@
       </c>
       <c r="N15" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A15)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A15)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A15&lt;&gt;""),IFERROR(MAX($N$4:N14),0)+1,"")</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O15" s="1" t="str">
         <f>IF(AND(D15&gt;0,F15="أحد الشركاء"),COUNTIFS($D$4:D15,"&gt;"&amp;0,$F$4:F15,"أحد الشركاء"),"")</f>
@@ -10222,7 +10246,7 @@
       </c>
       <c r="N16" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A16)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A16)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A16&lt;&gt;""),IFERROR(MAX($N$4:N15),0)+1,"")</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O16" s="1" t="str">
         <f>IF(AND(D16&gt;0,F16="أحد الشركاء"),COUNTIFS($D$4:D16,"&gt;"&amp;0,$F$4:F16,"أحد الشركاء"),"")</f>
@@ -10270,7 +10294,7 @@
       </c>
       <c r="N17" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A17)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A17)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A17&lt;&gt;""),IFERROR(MAX($N$4:N16),0)+1,"")</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1">
         <f>IF(AND(D17&gt;0,F17="أحد الشركاء"),COUNTIFS($D$4:D17,"&gt;"&amp;0,$F$4:F17,"أحد الشركاء"),"")</f>
@@ -10312,7 +10336,7 @@
       </c>
       <c r="N18" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A18)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A18)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A18&lt;&gt;""),IFERROR(MAX($N$4:N17),0)+1,"")</f>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1" t="str">
         <f>IF(AND(D18&gt;0,F18="أحد الشركاء"),COUNTIFS($D$4:D18,"&gt;"&amp;0,$F$4:F18,"أحد الشركاء"),"")</f>
@@ -10354,7 +10378,7 @@
       </c>
       <c r="N19" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A19)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A19)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A19&lt;&gt;""),IFERROR(MAX($N$4:N18),0)+1,"")</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="str">
         <f>IF(AND(D19&gt;0,F19="أحد الشركاء"),COUNTIFS($D$4:D19,"&gt;"&amp;0,$F$4:F19,"أحد الشركاء"),"")</f>
@@ -10396,7 +10420,7 @@
       </c>
       <c r="N20" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A20)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A20)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A20&lt;&gt;""),IFERROR(MAX($N$4:N19),0)+1,"")</f>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O20" s="1" t="str">
         <f>IF(AND(D20&gt;0,F20="أحد الشركاء"),COUNTIFS($D$4:D20,"&gt;"&amp;0,$F$4:F20,"أحد الشركاء"),"")</f>
@@ -10438,7 +10462,7 @@
       </c>
       <c r="N21" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A21)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A21)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A21&lt;&gt;""),IFERROR(MAX($N$4:N20),0)+1,"")</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="O21" s="1" t="str">
         <f>IF(AND(D21&gt;0,F21="أحد الشركاء"),COUNTIFS($D$4:D21,"&gt;"&amp;0,$F$4:F21,"أحد الشركاء"),"")</f>
@@ -10480,7 +10504,7 @@
       </c>
       <c r="N22" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A22)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A22)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A22&lt;&gt;""),IFERROR(MAX($N$4:N21),0)+1,"")</f>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O22" s="1" t="str">
         <f>IF(AND(D22&gt;0,F22="أحد الشركاء"),COUNTIFS($D$4:D22,"&gt;"&amp;0,$F$4:F22,"أحد الشركاء"),"")</f>
@@ -10522,7 +10546,7 @@
       </c>
       <c r="N23" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A23)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A23)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A23&lt;&gt;""),IFERROR(MAX($N$4:N22),0)+1,"")</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O23" s="1" t="str">
         <f>IF(AND(D23&gt;0,F23="أحد الشركاء"),COUNTIFS($D$4:D23,"&gt;"&amp;0,$F$4:F23,"أحد الشركاء"),"")</f>
@@ -10564,7 +10588,7 @@
       </c>
       <c r="N24" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A24)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A24)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A24&lt;&gt;""),IFERROR(MAX($N$4:N23),0)+1,"")</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O24" s="1" t="str">
         <f>IF(AND(D24&gt;0,F24="أحد الشركاء"),COUNTIFS($D$4:D24,"&gt;"&amp;0,$F$4:F24,"أحد الشركاء"),"")</f>
@@ -10608,7 +10632,7 @@
       </c>
       <c r="N25" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A25)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A25)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A25&lt;&gt;""),IFERROR(MAX($N$4:N24),0)+1,"")</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(AND(D25&gt;0,F25="أحد الشركاء"),COUNTIFS($D$4:D25,"&gt;"&amp;0,$F$4:F25,"أحد الشركاء"),"")</f>
@@ -10650,7 +10674,7 @@
       </c>
       <c r="N26" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A26)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A26)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A26&lt;&gt;""),IFERROR(MAX($N$4:N25),0)+1,"")</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O26" s="1" t="str">
         <f>IF(AND(D26&gt;0,F26="أحد الشركاء"),COUNTIFS($D$4:D26,"&gt;"&amp;0,$F$4:F26,"أحد الشركاء"),"")</f>
@@ -10692,7 +10716,7 @@
       </c>
       <c r="N27" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A27)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A27)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A27&lt;&gt;""),IFERROR(MAX($N$4:N26),0)+1,"")</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="O27" s="1" t="str">
         <f>IF(AND(D27&gt;0,F27="أحد الشركاء"),COUNTIFS($D$4:D27,"&gt;"&amp;0,$F$4:F27,"أحد الشركاء"),"")</f>
@@ -10734,7 +10758,7 @@
       </c>
       <c r="N28" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A28)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A28)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A28&lt;&gt;""),IFERROR(MAX($N$4:N27),0)+1,"")</f>
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O28" s="1" t="str">
         <f>IF(AND(D28&gt;0,F28="أحد الشركاء"),COUNTIFS($D$4:D28,"&gt;"&amp;0,$F$4:F28,"أحد الشركاء"),"")</f>
@@ -10776,7 +10800,7 @@
       </c>
       <c r="N29" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A29)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A29)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A29&lt;&gt;""),IFERROR(MAX($N$4:N28),0)+1,"")</f>
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O29" s="1" t="str">
         <f>IF(AND(D29&gt;0,F29="أحد الشركاء"),COUNTIFS($D$4:D29,"&gt;"&amp;0,$F$4:F29,"أحد الشركاء"),"")</f>
@@ -10818,7 +10842,7 @@
       </c>
       <c r="N30" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A30)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A30)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A30&lt;&gt;""),IFERROR(MAX($N$4:N29),0)+1,"")</f>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="str">
         <f>IF(AND(D30&gt;0,F30="أحد الشركاء"),COUNTIFS($D$4:D30,"&gt;"&amp;0,$F$4:F30,"أحد الشركاء"),"")</f>
@@ -10860,7 +10884,7 @@
       </c>
       <c r="N31" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A31)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A31)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A31&lt;&gt;""),IFERROR(MAX($N$4:N30),0)+1,"")</f>
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="O31" s="1" t="str">
         <f>IF(AND(D31&gt;0,F31="أحد الشركاء"),COUNTIFS($D$4:D31,"&gt;"&amp;0,$F$4:F31,"أحد الشركاء"),"")</f>
@@ -10902,7 +10926,7 @@
       </c>
       <c r="N32" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A32)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A32)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A32&lt;&gt;""),IFERROR(MAX($N$4:N31),0)+1,"")</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="O32" s="1" t="str">
         <f>IF(AND(D32&gt;0,F32="أحد الشركاء"),COUNTIFS($D$4:D32,"&gt;"&amp;0,$F$4:F32,"أحد الشركاء"),"")</f>
@@ -10950,7 +10974,7 @@
       </c>
       <c r="N33" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A33)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A33)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A33&lt;&gt;""),IFERROR(MAX($N$4:N32),0)+1,"")</f>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="O33" s="1" t="str">
         <f>IF(AND(D33&gt;0,F33="أحد الشركاء"),COUNTIFS($D$4:D33,"&gt;"&amp;0,$F$4:F33,"أحد الشركاء"),"")</f>
@@ -10992,7 +11016,7 @@
       </c>
       <c r="N34" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A34)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A34)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A34&lt;&gt;""),IFERROR(MAX($N$4:N33),0)+1,"")</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O34" s="1" t="str">
         <f>IF(AND(D34&gt;0,F34="أحد الشركاء"),COUNTIFS($D$4:D34,"&gt;"&amp;0,$F$4:F34,"أحد الشركاء"),"")</f>
@@ -11034,7 +11058,7 @@
       </c>
       <c r="N35" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A35)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A35)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A35&lt;&gt;""),IFERROR(MAX($N$4:N34),0)+1,"")</f>
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="O35" s="1" t="str">
         <f>IF(AND(D35&gt;0,F35="أحد الشركاء"),COUNTIFS($D$4:D35,"&gt;"&amp;0,$F$4:F35,"أحد الشركاء"),"")</f>
@@ -11076,7 +11100,7 @@
       </c>
       <c r="N36" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A36)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A36)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A36&lt;&gt;""),IFERROR(MAX($N$4:N35),0)+1,"")</f>
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O36" s="1" t="str">
         <f>IF(AND(D36&gt;0,F36="أحد الشركاء"),COUNTIFS($D$4:D36,"&gt;"&amp;0,$F$4:F36,"أحد الشركاء"),"")</f>
@@ -11118,7 +11142,7 @@
       </c>
       <c r="N37" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A37)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A37)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A37&lt;&gt;""),IFERROR(MAX($N$4:N36),0)+1,"")</f>
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O37" s="1" t="str">
         <f>IF(AND(D37&gt;0,F37="أحد الشركاء"),COUNTIFS($D$4:D37,"&gt;"&amp;0,$F$4:F37,"أحد الشركاء"),"")</f>
@@ -11160,7 +11184,7 @@
       </c>
       <c r="N38" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A38)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A38)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A38&lt;&gt;""),IFERROR(MAX($N$4:N37),0)+1,"")</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="O38" s="1" t="str">
         <f>IF(AND(D38&gt;0,F38="أحد الشركاء"),COUNTIFS($D$4:D38,"&gt;"&amp;0,$F$4:F38,"أحد الشركاء"),"")</f>
@@ -11202,7 +11226,7 @@
       </c>
       <c r="N39" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A39)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A39)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A39&lt;&gt;""),IFERROR(MAX($N$4:N38),0)+1,"")</f>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O39" s="1" t="str">
         <f>IF(AND(D39&gt;0,F39="أحد الشركاء"),COUNTIFS($D$4:D39,"&gt;"&amp;0,$F$4:F39,"أحد الشركاء"),"")</f>
@@ -11244,7 +11268,7 @@
       </c>
       <c r="N40" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A40)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A40)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A40&lt;&gt;""),IFERROR(MAX($N$4:N39),0)+1,"")</f>
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="O40" s="1" t="str">
         <f>IF(AND(D40&gt;0,F40="أحد الشركاء"),COUNTIFS($D$4:D40,"&gt;"&amp;0,$F$4:F40,"أحد الشركاء"),"")</f>
@@ -11286,7 +11310,7 @@
       </c>
       <c r="N41" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A41)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A41)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A41&lt;&gt;""),IFERROR(MAX($N$4:N40),0)+1,"")</f>
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O41" s="1" t="str">
         <f>IF(AND(D41&gt;0,F41="أحد الشركاء"),COUNTIFS($D$4:D41,"&gt;"&amp;0,$F$4:F41,"أحد الشركاء"),"")</f>
@@ -11328,7 +11352,7 @@
       </c>
       <c r="N42" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A42)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A42)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A42&lt;&gt;""),IFERROR(MAX($N$4:N41),0)+1,"")</f>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="O42" s="1" t="str">
         <f>IF(AND(D42&gt;0,F42="أحد الشركاء"),COUNTIFS($D$4:D42,"&gt;"&amp;0,$F$4:F42,"أحد الشركاء"),"")</f>
@@ -11370,7 +11394,7 @@
       </c>
       <c r="N43" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A43)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A43)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A43&lt;&gt;""),IFERROR(MAX($N$4:N42),0)+1,"")</f>
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O43" s="1" t="str">
         <f>IF(AND(D43&gt;0,F43="أحد الشركاء"),COUNTIFS($D$4:D43,"&gt;"&amp;0,$F$4:F43,"أحد الشركاء"),"")</f>
@@ -11414,7 +11438,7 @@
       </c>
       <c r="N44" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A44)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A44)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A44&lt;&gt;""),IFERROR(MAX($N$4:N43),0)+1,"")</f>
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O44" s="1">
         <f>IF(AND(D44&gt;0,F44="أحد الشركاء"),COUNTIFS($D$4:D44,"&gt;"&amp;0,$F$4:F44,"أحد الشركاء"),"")</f>
@@ -11460,7 +11484,7 @@
       </c>
       <c r="N45" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A45)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A45)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A45&lt;&gt;""),IFERROR(MAX($N$4:N44),0)+1,"")</f>
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O45" s="1">
         <f>IF(AND(D45&gt;0,F45="أحد الشركاء"),COUNTIFS($D$4:D45,"&gt;"&amp;0,$F$4:F45,"أحد الشركاء"),"")</f>
@@ -11506,7 +11530,7 @@
       </c>
       <c r="N46" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A46)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A46)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A46&lt;&gt;""),IFERROR(MAX($N$4:N45),0)+1,"")</f>
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="O46" s="1">
         <f>IF(AND(D46&gt;0,F46="أحد الشركاء"),COUNTIFS($D$4:D46,"&gt;"&amp;0,$F$4:F46,"أحد الشركاء"),"")</f>
@@ -11550,7 +11574,7 @@
       </c>
       <c r="N47" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A47)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A47)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A47&lt;&gt;""),IFERROR(MAX($N$4:N46),0)+1,"")</f>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="O47" s="1" t="str">
         <f>IF(AND(D47&gt;0,F47="أحد الشركاء"),COUNTIFS($D$4:D47,"&gt;"&amp;0,$F$4:F47,"أحد الشركاء"),"")</f>
@@ -11594,7 +11618,7 @@
       </c>
       <c r="N48" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A48)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A48)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A48&lt;&gt;""),IFERROR(MAX($N$4:N47),0)+1,"")</f>
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O48" s="1" t="str">
         <f>IF(AND(D48&gt;0,F48="أحد الشركاء"),COUNTIFS($D$4:D48,"&gt;"&amp;0,$F$4:F48,"أحد الشركاء"),"")</f>
@@ -11638,7 +11662,7 @@
       </c>
       <c r="N49" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A49)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A49)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A49&lt;&gt;""),IFERROR(MAX($N$4:N48),0)+1,"")</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O49" s="1" t="str">
         <f>IF(AND(D49&gt;0,F49="أحد الشركاء"),COUNTIFS($D$4:D49,"&gt;"&amp;0,$F$4:F49,"أحد الشركاء"),"")</f>
@@ -11682,7 +11706,7 @@
       </c>
       <c r="N50" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A50)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A50)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A50&lt;&gt;""),IFERROR(MAX($N$4:N49),0)+1,"")</f>
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="O50" s="1" t="str">
         <f>IF(AND(D50&gt;0,F50="أحد الشركاء"),COUNTIFS($D$4:D50,"&gt;"&amp;0,$F$4:F50,"أحد الشركاء"),"")</f>
@@ -11726,7 +11750,7 @@
       </c>
       <c r="N51" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A51)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A51)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A51&lt;&gt;""),IFERROR(MAX($N$4:N50),0)+1,"")</f>
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="O51" s="1" t="str">
         <f>IF(AND(D51&gt;0,F51="أحد الشركاء"),COUNTIFS($D$4:D51,"&gt;"&amp;0,$F$4:F51,"أحد الشركاء"),"")</f>
@@ -11770,7 +11794,7 @@
       </c>
       <c r="N52" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A52)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A52)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A52&lt;&gt;""),IFERROR(MAX($N$4:N51),0)+1,"")</f>
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="O52" s="1" t="str">
         <f>IF(AND(D52&gt;0,F52="أحد الشركاء"),COUNTIFS($D$4:D52,"&gt;"&amp;0,$F$4:F52,"أحد الشركاء"),"")</f>
@@ -11814,7 +11838,7 @@
       </c>
       <c r="N53" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A53)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A53)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A53&lt;&gt;""),IFERROR(MAX($N$4:N52),0)+1,"")</f>
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="O53" s="1" t="str">
         <f>IF(AND(D53&gt;0,F53="أحد الشركاء"),COUNTIFS($D$4:D53,"&gt;"&amp;0,$F$4:F53,"أحد الشركاء"),"")</f>
@@ -11833,7 +11857,7 @@
       </c>
       <c r="D54" s="48"/>
       <c r="E54" s="49">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>42</v>
@@ -11845,7 +11869,7 @@
       <c r="I54" s="53"/>
       <c r="J54" s="54">
         <f>IF(AND(D54="",E54="",A54="",B54="",C54=""),"", IFERROR(IF(J53="",D2,J53),D2)+IF(E54="",0,E54)-IF(D54="",0,D54))</f>
-        <v>-532</v>
+        <v>-531.9</v>
       </c>
       <c r="K54" s="55"/>
       <c r="L54" s="1">
@@ -11858,7 +11882,7 @@
       </c>
       <c r="N54" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A54)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A54)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A54&lt;&gt;""),IFERROR(MAX($N$4:N53),0)+1,"")</f>
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O54" s="1" t="str">
         <f>IF(AND(D54&gt;0,F54="أحد الشركاء"),COUNTIFS($D$4:D54,"&gt;"&amp;0,$F$4:F54,"أحد الشركاء"),"")</f>
@@ -11889,7 +11913,7 @@
       <c r="I55" s="64"/>
       <c r="J55" s="65">
         <f>IF(AND(D55="",E55="",A55="",B55="",C55=""),"", IFERROR(IF(J54="",D2,J54),D2)+IF(E55="",0,E55)-IF(D55="",0,D55))</f>
-        <v>-529</v>
+        <v>-528.9</v>
       </c>
       <c r="K55" s="66"/>
       <c r="L55" s="1">
@@ -11902,7 +11926,7 @@
       </c>
       <c r="N55" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A55)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A55)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A55&lt;&gt;""),IFERROR(MAX($N$4:N54),0)+1,"")</f>
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="O55" s="1" t="str">
         <f>IF(AND(D55&gt;0,F55="أحد الشركاء"),COUNTIFS($D$4:D55,"&gt;"&amp;0,$F$4:F55,"أحد الشركاء"),"")</f>
@@ -11933,7 +11957,7 @@
       <c r="I56" s="53"/>
       <c r="J56" s="54">
         <f>IF(AND(D56="",E56="",A56="",B56="",C56=""),"", IFERROR(IF(J55="",D2,J55),D2)+IF(E56="",0,E56)-IF(D56="",0,D56))</f>
-        <v>-531.75</v>
+        <v>-531.65</v>
       </c>
       <c r="K56" s="55"/>
       <c r="L56" s="1" t="str">
@@ -11946,7 +11970,7 @@
       </c>
       <c r="N56" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A56)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A56)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A56&lt;&gt;""),IFERROR(MAX($N$4:N55),0)+1,"")</f>
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="O56" s="1" t="str">
         <f>IF(AND(D56&gt;0,F56="أحد الشركاء"),COUNTIFS($D$4:D56,"&gt;"&amp;0,$F$4:F56,"أحد الشركاء"),"")</f>
@@ -11954,31 +11978,43 @@
       </c>
     </row>
     <row r="57" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A57" s="56"/>
-      <c r="B57" s="57"/>
-      <c r="C57" s="58"/>
+      <c r="A57" s="56">
+        <v>46175</v>
+      </c>
+      <c r="B57" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" s="58" t="s">
+        <v>200</v>
+      </c>
       <c r="D57" s="59"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="61"/>
+      <c r="E57" s="60">
+        <v>18</v>
+      </c>
+      <c r="F57" s="61" t="s">
+        <v>42</v>
+      </c>
       <c r="G57" s="62"/>
-      <c r="H57" s="63"/>
+      <c r="H57" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I57" s="64"/>
-      <c r="J57" s="65" t="str">
+      <c r="J57" s="65">
         <f>IF(AND(D57="",E57="",A57="",B57="",C57=""),"", IFERROR(IF(J56="",D2,J56),D2)+IF(E57="",0,E57)-IF(D57="",0,D57))</f>
-        <v/>
+        <v>-513.65</v>
       </c>
       <c r="K57" s="66"/>
-      <c r="L57" s="1" t="str">
+      <c r="L57" s="1">
         <f>IF(E57&gt;0,COUNTIF($E$4:E57,"&gt;0"),"")</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="M57" s="1" t="str">
         <f>IF(AND(D57&gt;0,G57="المحفظة"),COUNTIFS($D$4:D57,"&gt;"&amp;0,$G$4:G57,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N57" s="1" t="str">
+      <c r="N57" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A57)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A57)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A57&lt;&gt;""),IFERROR(MAX($N$4:N56),0)+1,"")</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="O57" s="1" t="str">
         <f>IF(AND(D57&gt;0,F57="أحد الشركاء"),COUNTIFS($D$4:D57,"&gt;"&amp;0,$F$4:F57,"أحد الشركاء"),"")</f>
@@ -11986,31 +12022,43 @@
       </c>
     </row>
     <row r="58" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A58" s="45"/>
-      <c r="B58" s="46"/>
-      <c r="C58" s="47"/>
+      <c r="A58" s="56">
+        <v>46175</v>
+      </c>
+      <c r="B58" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="47" t="s">
+        <v>201</v>
+      </c>
       <c r="D58" s="48"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="50"/>
+      <c r="E58" s="49">
+        <v>2</v>
+      </c>
+      <c r="F58" s="50" t="s">
+        <v>42</v>
+      </c>
       <c r="G58" s="51"/>
-      <c r="H58" s="52"/>
+      <c r="H58" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I58" s="53"/>
-      <c r="J58" s="54" t="str">
+      <c r="J58" s="54">
         <f>IF(AND(D58="",E58="",A58="",B58="",C58=""),"", IFERROR(IF(J57="",D2,J57),D2)+IF(E58="",0,E58)-IF(D58="",0,D58))</f>
-        <v/>
+        <v>-511.65</v>
       </c>
       <c r="K58" s="55"/>
-      <c r="L58" s="1" t="str">
+      <c r="L58" s="1">
         <f>IF(E58&gt;0,COUNTIF($E$4:E58,"&gt;0"),"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="M58" s="1" t="str">
         <f>IF(AND(D58&gt;0,G58="المحفظة"),COUNTIFS($D$4:D58,"&gt;"&amp;0,$G$4:G58,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N58" s="1" t="str">
+      <c r="N58" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A58)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A58)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A58&lt;&gt;""),IFERROR(MAX($N$4:N57),0)+1,"")</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="O58" s="1" t="str">
         <f>IF(AND(D58&gt;0,F58="أحد الشركاء"),COUNTIFS($D$4:D58,"&gt;"&amp;0,$F$4:F58,"أحد الشركاء"),"")</f>
@@ -12018,31 +12066,43 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A59" s="56"/>
-      <c r="B59" s="57"/>
-      <c r="C59" s="58"/>
+      <c r="A59" s="56">
+        <v>46175</v>
+      </c>
+      <c r="B59" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>202</v>
+      </c>
       <c r="D59" s="59"/>
-      <c r="E59" s="60"/>
-      <c r="F59" s="61"/>
+      <c r="E59" s="60">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="61" t="s">
+        <v>42</v>
+      </c>
       <c r="G59" s="62"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I59" s="64"/>
-      <c r="J59" s="65" t="str">
+      <c r="J59" s="65">
         <f>IF(AND(D59="",E59="",A59="",B59="",C59=""),"", IFERROR(IF(J58="",D2,J58),D2)+IF(E59="",0,E59)-IF(D59="",0,D59))</f>
-        <v/>
+        <v>-510.15</v>
       </c>
       <c r="K59" s="66"/>
-      <c r="L59" s="1" t="str">
+      <c r="L59" s="1">
         <f>IF(E59&gt;0,COUNTIF($E$4:E59,"&gt;0"),"")</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="M59" s="1" t="str">
         <f>IF(AND(D59&gt;0,G59="المحفظة"),COUNTIFS($D$4:D59,"&gt;"&amp;0,$G$4:G59,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N59" s="1" t="str">
+      <c r="N59" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A59)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A59)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A59&lt;&gt;""),IFERROR(MAX($N$4:N58),0)+1,"")</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="O59" s="1" t="str">
         <f>IF(AND(D59&gt;0,F59="أحد الشركاء"),COUNTIFS($D$4:D59,"&gt;"&amp;0,$F$4:F59,"أحد الشركاء"),"")</f>
@@ -12050,31 +12110,43 @@
       </c>
     </row>
     <row r="60" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A60" s="45"/>
-      <c r="B60" s="46"/>
-      <c r="C60" s="47"/>
+      <c r="A60" s="56">
+        <v>46175</v>
+      </c>
+      <c r="B60" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="47" t="s">
+        <v>203</v>
+      </c>
       <c r="D60" s="48"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="50"/>
+      <c r="E60" s="49">
+        <v>3</v>
+      </c>
+      <c r="F60" s="50" t="s">
+        <v>42</v>
+      </c>
       <c r="G60" s="51"/>
-      <c r="H60" s="52"/>
+      <c r="H60" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I60" s="53"/>
-      <c r="J60" s="54" t="str">
+      <c r="J60" s="54">
         <f>IF(AND(D60="",E60="",A60="",B60="",C60=""),"", IFERROR(IF(J59="",D2,J59),D2)+IF(E60="",0,E60)-IF(D60="",0,D60))</f>
-        <v/>
+        <v>-507.15</v>
       </c>
       <c r="K60" s="55"/>
-      <c r="L60" s="1" t="str">
+      <c r="L60" s="1">
         <f>IF(E60&gt;0,COUNTIF($E$4:E60,"&gt;0"),"")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="M60" s="1" t="str">
         <f>IF(AND(D60&gt;0,G60="المحفظة"),COUNTIFS($D$4:D60,"&gt;"&amp;0,$G$4:G60,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N60" s="1" t="str">
+      <c r="N60" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A60)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A60)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A60&lt;&gt;""),IFERROR(MAX($N$4:N59),0)+1,"")</f>
-        <v/>
+        <v>57</v>
       </c>
       <c r="O60" s="1" t="str">
         <f>IF(AND(D60&gt;0,F60="أحد الشركاء"),COUNTIFS($D$4:D60,"&gt;"&amp;0,$F$4:F60,"أحد الشركاء"),"")</f>
@@ -16669,7 +16741,7 @@
       </c>
       <c r="E204" s="67">
         <f>SUM(E4:E203)</f>
-        <v>502</v>
+        <v>526.6</v>
       </c>
       <c r="F204" s="141">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -16679,7 +16751,7 @@
       <c r="H204" s="141"/>
       <c r="J204" s="67">
         <f>$D$2+E204-D204</f>
-        <v>-495.25</v>
+        <v>-470.65</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="15.75" customHeight="1">
@@ -17075,12 +17147,10 @@
       <c r="K1" s="136"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="146">
-        <v>5</v>
-      </c>
+      <c r="A2" s="146"/>
       <c r="B2" s="146"/>
       <c r="C2" s="77" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D2" s="146">
         <v>2026</v>
@@ -17146,43 +17216,43 @@
     <row r="5" spans="1:11" ht="16.5" customHeight="1">
       <c r="A5" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46151</v>
+        <v>46117</v>
       </c>
       <c r="B5" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-013</v>
+        <v>82869</v>
       </c>
       <c r="C5" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 21 سعر الحبه .0.750</v>
+        <v>مبيدات الاتحاد الكويتي للمزارعين</v>
       </c>
       <c r="D5" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="F5" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G5" s="80">
+      <c r="G5" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H5" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>تم الدفع</v>
       </c>
-      <c r="I5" s="80">
+      <c r="I5" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مبيدات وأسمدة</v>
       </c>
       <c r="J5" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-248.75</v>
+        <v>-4.5</v>
       </c>
       <c r="K5" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17192,15 +17262,15 @@
     <row r="6" spans="1:11" ht="16.5" customHeight="1">
       <c r="A6" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46151</v>
+        <v>46121</v>
       </c>
       <c r="B6" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-013</v>
+        <v>Inv-001</v>
       </c>
       <c r="C6" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>برازيليا عدد 25 سعر الحبه .500</v>
+        <v>بيع عدد١ اناناس</v>
       </c>
       <c r="D6" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17208,15 +17278,15 @@
       </c>
       <c r="E6" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="F6" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G6" s="82" t="str">
+      <c r="G6" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H6" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17228,7 +17298,7 @@
       </c>
       <c r="J6" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-236.25</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17238,19 +17308,19 @@
     <row r="7" spans="1:11" ht="16.5" customHeight="1">
       <c r="A7" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46151</v>
-      </c>
-      <c r="B7" s="80">
+        <v>46124</v>
+      </c>
+      <c r="B7" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>18213</v>
+        <v>242</v>
       </c>
       <c r="C7" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>شراء دريل</v>
+        <v>احواض حجم 18سم عدد 2000</v>
       </c>
       <c r="D7" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="E7" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17258,15 +17328,15 @@
       </c>
       <c r="F7" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v>نقداً</v>
       </c>
       <c r="G7" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
+        <v>المحفظة</v>
       </c>
       <c r="H7" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
+        <v>تم الدفع</v>
       </c>
       <c r="I7" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17274,7 +17344,7 @@
       </c>
       <c r="J7" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-245.25</v>
+        <v>-89.5</v>
       </c>
       <c r="K7" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17284,43 +17354,43 @@
     <row r="8" spans="1:11" ht="16.5" customHeight="1">
       <c r="A8" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46152</v>
-      </c>
-      <c r="B8" s="82" t="str">
+        <v>46131</v>
+      </c>
+      <c r="B8" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-016</v>
+        <v>0</v>
       </c>
       <c r="C8" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه عدد 3 الحبه 0.750</v>
+        <v>تبديل كمبرسيور ثلاجة العمال</v>
       </c>
       <c r="D8" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E8" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="F8" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G8" s="82">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G8" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="82">
+        <v>أبو اسحاق</v>
+      </c>
+      <c r="H8" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="82">
+        <v>معلق</v>
+      </c>
+      <c r="I8" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>صيانة المعدات</v>
       </c>
       <c r="J8" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-243</v>
+        <v>-134.5</v>
       </c>
       <c r="K8" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17330,43 +17400,43 @@
     <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="A9" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
+        <v>46134</v>
       </c>
       <c r="B9" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-017</v>
+        <v>11300</v>
       </c>
       <c r="C9" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 10 الحبه 0.750</v>
+        <v>فلاتر كيميكال لمحطة التحلية</v>
       </c>
       <c r="D9" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E9" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G9" s="80">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G9" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="80">
+        <v>أبو اسحاق</v>
+      </c>
+      <c r="H9" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="80">
+        <v>معلق</v>
+      </c>
+      <c r="I9" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>وقود ومحروقات</v>
       </c>
       <c r="J9" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-235.5</v>
+        <v>-189.5</v>
       </c>
       <c r="K9" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17376,43 +17446,43 @@
     <row r="10" spans="1:11" ht="16.5" customHeight="1">
       <c r="A10" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
-      </c>
-      <c r="B10" s="82" t="str">
+        <v>46134</v>
+      </c>
+      <c r="B10" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-18</v>
+        <v>0</v>
       </c>
       <c r="C10" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل 4 حبات الحبه 1.500</v>
+        <v>ديزل لمكينة الكهرباء</v>
       </c>
       <c r="D10" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E10" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F10" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G10" s="82">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G10" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="82">
+        <v>أبو اسحاق</v>
+      </c>
+      <c r="H10" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="82">
+        <v>معلق</v>
+      </c>
+      <c r="I10" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>وقود ومحروقات</v>
       </c>
       <c r="J10" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-229.5</v>
+        <v>-209.5</v>
       </c>
       <c r="K10" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17422,89 +17492,89 @@
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
       <c r="A11" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46156</v>
+        <v>46134</v>
       </c>
       <c r="B11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-18</v>
+        <v>8127</v>
       </c>
       <c r="C11" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه 8 حبات الحبه 1</v>
+        <v>تاير لعربة الرش</v>
       </c>
       <c r="D11" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G11" s="80">
+      <c r="G11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="80">
+        <v>المحفظة</v>
+      </c>
+      <c r="H11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="80">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مستلزمات زراعية</v>
       </c>
       <c r="J11" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-221.5</v>
-      </c>
-      <c r="K11" s="80">
+        <v>-212.5</v>
+      </c>
+      <c r="K11" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>تم الصرف</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1">
       <c r="A12" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46158</v>
+        <v>46134</v>
       </c>
       <c r="B12" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-19</v>
+        <v>242</v>
       </c>
       <c r="C12" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 2 الحبه 0.750</v>
+        <v>احواض حجم25سم عدد 2000</v>
       </c>
       <c r="D12" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E12" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G12" s="82">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G12" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="82">
+        <v>أبو آدم</v>
+      </c>
+      <c r="H12" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="82">
+        <v>معلق</v>
+      </c>
+      <c r="I12" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>أحواض وأدوات</v>
       </c>
       <c r="J12" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-220</v>
+        <v>-402.5</v>
       </c>
       <c r="K12" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17514,15 +17584,15 @@
     <row r="13" spans="1:11" ht="16.5" customHeight="1">
       <c r="A13" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46158</v>
-      </c>
-      <c r="B13" s="80" t="str">
+        <v>46142</v>
+      </c>
+      <c r="B13" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-20</v>
+        <v>0</v>
       </c>
       <c r="C13" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>صبار اوليفيرا عدد 3 الحبه 0.750</v>
+        <v>مدخول شهر ابريل</v>
       </c>
       <c r="D13" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17530,11 +17600,11 @@
       </c>
       <c r="E13" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.25</v>
-      </c>
-      <c r="F13" s="80" t="str">
+        <v>181</v>
+      </c>
+      <c r="F13" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>0</v>
       </c>
       <c r="G13" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17550,7 +17620,7 @@
       </c>
       <c r="J13" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-217.75</v>
+        <v>-221.5</v>
       </c>
       <c r="K13" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17560,43 +17630,43 @@
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="A14" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46158</v>
-      </c>
-      <c r="B14" s="82" t="str">
+        <v>46142</v>
+      </c>
+      <c r="B14" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-21</v>
+        <v>40505</v>
       </c>
       <c r="C14" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 الحبه 2.500</v>
+        <v>احواض حجم 14سم عدد 2000</v>
       </c>
       <c r="D14" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E14" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="82">
+        <v>المحفظة</v>
+      </c>
+      <c r="H14" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="82">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I14" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>أحواض وأدوات</v>
       </c>
       <c r="J14" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-215.25</v>
+        <v>-261.5</v>
       </c>
       <c r="K14" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17606,61 +17676,61 @@
     <row r="15" spans="1:11" ht="16.5" customHeight="1">
       <c r="A15" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46159</v>
-      </c>
-      <c r="B15" s="80" t="str">
+        <v>46142</v>
+      </c>
+      <c r="B15" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-22</v>
+        <v>5370</v>
       </c>
       <c r="C15" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 30 الحبه 0.750</v>
+        <v>جبس لتغطيه المحميه</v>
       </c>
       <c r="D15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G15" s="80">
+      <c r="G15" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="80">
+        <v>المحفظة</v>
+      </c>
+      <c r="H15" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="80">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I15" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مبيدات وأسمدة</v>
       </c>
       <c r="J15" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-192.75</v>
-      </c>
-      <c r="K15" s="80" t="str">
+        <v>-264.5</v>
+      </c>
+      <c r="K15" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم إعطاء 1 حبه هديه الإجمالي 31 حبه</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1">
       <c r="A16" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46159</v>
+        <v>46151</v>
       </c>
       <c r="B16" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-23</v>
+        <v>Inv-013</v>
       </c>
       <c r="C16" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>برازيليا عدد 16 الحبه 0.500</v>
+        <v>فل عدد 21 سعر الحبه .0.750</v>
       </c>
       <c r="D16" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17668,7 +17738,7 @@
       </c>
       <c r="E16" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8</v>
+        <v>15.75</v>
       </c>
       <c r="F16" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17678,9 +17748,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H16" s="82">
+      <c r="H16" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>تم الدفع</v>
       </c>
       <c r="I16" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17688,7 +17758,7 @@
       </c>
       <c r="J16" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-184.75</v>
+        <v>-248.75</v>
       </c>
       <c r="K16" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17698,15 +17768,15 @@
     <row r="17" spans="1:11" ht="16.5" customHeight="1">
       <c r="A17" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46151</v>
       </c>
       <c r="B17" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-24</v>
+        <v>Inv-013</v>
       </c>
       <c r="C17" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد10 الحبه 0.750</v>
+        <v>برازيليا عدد 25 سعر الحبه .500</v>
       </c>
       <c r="D17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17714,19 +17784,19 @@
       </c>
       <c r="E17" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G17" s="80">
+      <c r="G17" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="80">
+        <v>المحفظة</v>
+      </c>
+      <c r="H17" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>تم الدفع</v>
       </c>
       <c r="I17" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17734,7 +17804,7 @@
       </c>
       <c r="J17" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-185.25</v>
+        <v>-236.25</v>
       </c>
       <c r="K17" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17744,43 +17814,43 @@
     <row r="18" spans="1:11" ht="16.5" customHeight="1">
       <c r="A18" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
-      </c>
-      <c r="B18" s="82" t="str">
+        <v>46151</v>
+      </c>
+      <c r="B18" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-25</v>
+        <v>18213</v>
       </c>
       <c r="C18" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسيناحمراء عدد 1</v>
+        <v>شراء دريل</v>
       </c>
       <c r="D18" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E18" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G18" s="82">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G18" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="82">
+        <v>أبو اسحاق</v>
+      </c>
+      <c r="H18" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="82">
+        <v>معلق</v>
+      </c>
+      <c r="I18" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مستلزمات زراعية</v>
       </c>
       <c r="J18" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-187.75</v>
+        <v>-245.25</v>
       </c>
       <c r="K18" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17790,15 +17860,15 @@
     <row r="19" spans="1:11" ht="16.5" customHeight="1">
       <c r="A19" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46152</v>
       </c>
       <c r="B19" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-26</v>
+        <v>Inv-016</v>
       </c>
       <c r="C19" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا خضراء عدد 2 الحبه 1.500</v>
+        <v>ودليه عدد 3 الحبه 0.750</v>
       </c>
       <c r="D19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17806,7 +17876,7 @@
       </c>
       <c r="E19" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="F19" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17826,7 +17896,7 @@
       </c>
       <c r="J19" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-189.75</v>
+        <v>-243</v>
       </c>
       <c r="K19" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17836,15 +17906,15 @@
     <row r="20" spans="1:11" ht="16.5" customHeight="1">
       <c r="A20" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B20" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-27</v>
+        <v>Inv-017</v>
       </c>
       <c r="C20" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد 2 الحبه 1.500</v>
+        <v>فل عدد 10 الحبه 0.750</v>
       </c>
       <c r="D20" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17852,7 +17922,7 @@
       </c>
       <c r="E20" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="F20" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17872,7 +17942,7 @@
       </c>
       <c r="J20" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-189.75</v>
+        <v>-235.5</v>
       </c>
       <c r="K20" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17882,15 +17952,15 @@
     <row r="21" spans="1:11" ht="16.5" customHeight="1">
       <c r="A21" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B21" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-28</v>
+        <v>Inv-18</v>
       </c>
       <c r="C21" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا حمراء عدد2 الحبه 2.500</v>
+        <v>ربل 4 حبات الحبه 1.500</v>
       </c>
       <c r="D21" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17898,7 +17968,7 @@
       </c>
       <c r="E21" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17918,7 +17988,7 @@
       </c>
       <c r="J21" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-187.75</v>
+        <v>-229.5</v>
       </c>
       <c r="K21" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17928,15 +17998,15 @@
     <row r="22" spans="1:11" ht="16.5" customHeight="1">
       <c r="A22" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B22" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-29</v>
+        <v>Inv-18</v>
       </c>
       <c r="C22" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>برازيليا عدد 10 الحبه 0.500</v>
+        <v>ودليه 8 حبات الحبه 1</v>
       </c>
       <c r="D22" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17944,7 +18014,7 @@
       </c>
       <c r="E22" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F22" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17964,7 +18034,7 @@
       </c>
       <c r="J22" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-187.75</v>
+        <v>-221.5</v>
       </c>
       <c r="K22" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17974,43 +18044,43 @@
     <row r="23" spans="1:11" ht="16.5" customHeight="1">
       <c r="A23" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="B23" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>85164</v>
+        <v>Inv-19</v>
       </c>
       <c r="C23" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>مبيد اسيتبلان عدد 1</v>
+        <v>فل عدد 2 الحبه 0.750</v>
       </c>
       <c r="D23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E23" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F23" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G23" s="80" t="str">
+      <c r="G23" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
-      </c>
-      <c r="H23" s="80" t="str">
+        <v>0</v>
+      </c>
+      <c r="H23" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I23" s="80" t="str">
+        <v>0</v>
+      </c>
+      <c r="I23" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>مبيدات وأسمدة</v>
+        <v>0</v>
       </c>
       <c r="J23" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-201.75</v>
+        <v>-220</v>
       </c>
       <c r="K23" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18020,15 +18090,15 @@
     <row r="24" spans="1:11" ht="16.5" customHeight="1">
       <c r="A24" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46161</v>
+        <v>46158</v>
       </c>
       <c r="B24" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-30</v>
+        <v>Inv-20</v>
       </c>
       <c r="C24" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 30 الحبه 0.750</v>
+        <v>صبار اوليفيرا عدد 3 الحبه 0.750</v>
       </c>
       <c r="D24" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18036,7 +18106,7 @@
       </c>
       <c r="E24" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22.5</v>
+        <v>2.25</v>
       </c>
       <c r="F24" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18056,7 +18126,7 @@
       </c>
       <c r="J24" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-179.25</v>
+        <v>-217.75</v>
       </c>
       <c r="K24" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18066,15 +18136,15 @@
     <row r="25" spans="1:11" ht="16.5" customHeight="1">
       <c r="A25" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46162</v>
+        <v>46158</v>
       </c>
       <c r="B25" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-31</v>
+        <v>Inv-21</v>
       </c>
       <c r="C25" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد30 الحبه 0.750</v>
+        <v>دارسينا عدد 1 الحبه 2.500</v>
       </c>
       <c r="D25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18082,7 +18152,7 @@
       </c>
       <c r="E25" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="F25" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18102,7 +18172,7 @@
       </c>
       <c r="J25" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-156.75</v>
+        <v>-215.25</v>
       </c>
       <c r="K25" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18112,15 +18182,15 @@
     <row r="26" spans="1:11" ht="16.5" customHeight="1">
       <c r="A26" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46162</v>
+        <v>46159</v>
       </c>
       <c r="B26" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-32</v>
+        <v>Inv-22</v>
       </c>
       <c r="C26" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>برازيليا عدد 50 الحبه0.500</v>
+        <v>فل عدد 30 الحبه 0.750</v>
       </c>
       <c r="D26" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18128,7 +18198,7 @@
       </c>
       <c r="E26" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="F26" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18148,25 +18218,25 @@
       </c>
       <c r="J26" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-131.75</v>
-      </c>
-      <c r="K26" s="82">
+        <v>-192.75</v>
+      </c>
+      <c r="K26" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>تم إعطاء 1 حبه هديه الإجمالي 31 حبه</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="16.5" customHeight="1">
       <c r="A27" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46163</v>
+        <v>46159</v>
       </c>
       <c r="B27" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-33</v>
+        <v>Inv-23</v>
       </c>
       <c r="C27" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>برازيليا عدد 75 الحبه 0.500</v>
+        <v>برازيليا عدد 16 الحبه 0.500</v>
       </c>
       <c r="D27" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18174,7 +18244,7 @@
       </c>
       <c r="E27" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>37.5</v>
+        <v>8</v>
       </c>
       <c r="F27" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18194,7 +18264,7 @@
       </c>
       <c r="J27" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-94.25</v>
+        <v>-184.75</v>
       </c>
       <c r="K27" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18204,15 +18274,15 @@
     <row r="28" spans="1:11" ht="16.5" customHeight="1">
       <c r="A28" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B28" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-34</v>
+        <v>Inv-24</v>
       </c>
       <c r="C28" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينيا احمر عدد1 حبه 2.500</v>
+        <v>فل عدد10 الحبه 0.750</v>
       </c>
       <c r="D28" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18220,7 +18290,7 @@
       </c>
       <c r="E28" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F28" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18240,7 +18310,7 @@
       </c>
       <c r="J28" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-91.75</v>
+        <v>-185.25</v>
       </c>
       <c r="K28" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18250,15 +18320,15 @@
     <row r="29" spans="1:11" ht="16.5" customHeight="1">
       <c r="A29" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B29" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-35</v>
+        <v>Inv-25</v>
       </c>
       <c r="C29" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا حمراء عدد 6 الحبه 2,500</v>
+        <v>دارسيناحمراء عدد 1</v>
       </c>
       <c r="D29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18266,7 +18336,7 @@
       </c>
       <c r="E29" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F29" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18286,7 +18356,7 @@
       </c>
       <c r="J29" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-76.75</v>
+        <v>-187.75</v>
       </c>
       <c r="K29" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18296,15 +18366,15 @@
     <row r="30" spans="1:11" ht="16.5" customHeight="1">
       <c r="A30" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B30" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-36</v>
+        <v>Inv-26</v>
       </c>
       <c r="C30" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد4 الحبه 1.500</v>
+        <v>دارسينا خضراء عدد 2 الحبه 1.500</v>
       </c>
       <c r="D30" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18312,7 +18382,7 @@
       </c>
       <c r="E30" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18332,7 +18402,7 @@
       </c>
       <c r="J30" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-70.75</v>
+        <v>-189.75</v>
       </c>
       <c r="K30" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18342,15 +18412,15 @@
     <row r="31" spans="1:11" ht="16.5" customHeight="1">
       <c r="A31" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="B31" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-37</v>
+        <v>Inv-27</v>
       </c>
       <c r="C31" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عطره عدد 10 الحبه 0.750</v>
+        <v>ربل عدد 2 الحبه 1.500</v>
       </c>
       <c r="D31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18358,7 +18428,7 @@
       </c>
       <c r="E31" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18378,7 +18448,7 @@
       </c>
       <c r="J31" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-63.25</v>
+        <v>-189.75</v>
       </c>
       <c r="K31" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18388,15 +18458,15 @@
     <row r="32" spans="1:11" ht="16.5" customHeight="1">
       <c r="A32" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="B32" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-38</v>
+        <v>Inv-28</v>
       </c>
       <c r="C32" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه عدد 2 الحبه 1</v>
+        <v>دارسينا حمراء عدد2 الحبه 2.500</v>
       </c>
       <c r="D32" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18404,7 +18474,7 @@
       </c>
       <c r="E32" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F32" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18424,7 +18494,7 @@
       </c>
       <c r="J32" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-61.25</v>
+        <v>-187.75</v>
       </c>
       <c r="K32" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18434,15 +18504,15 @@
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
       <c r="A33" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="B33" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-39</v>
+        <v>Inv-29</v>
       </c>
       <c r="C33" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>داراسينا حمراء عدد4 الحبه 1</v>
+        <v>برازيليا عدد 10 الحبه 0.500</v>
       </c>
       <c r="D33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18450,7 +18520,7 @@
       </c>
       <c r="E33" s="81">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18470,7 +18540,7 @@
       </c>
       <c r="J33" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-57.25</v>
+        <v>-187.75</v>
       </c>
       <c r="K33" s="80">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18480,19 +18550,19 @@
     <row r="34" spans="1:11" ht="16.5" customHeight="1">
       <c r="A34" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
-      </c>
-      <c r="B34" s="82">
+        <v>46160</v>
+      </c>
+      <c r="B34" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>85164</v>
       </c>
       <c r="C34" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>يزل ماكينه كهرباء</v>
+        <v>مبيد اسيتبلان عدد 1</v>
       </c>
       <c r="D34" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E34" s="83">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18500,23 +18570,23 @@
       </c>
       <c r="F34" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v>نقداً</v>
       </c>
       <c r="G34" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
+        <v>المحفظة</v>
       </c>
       <c r="H34" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
-      </c>
-      <c r="I34" s="82">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I34" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مبيدات وأسمدة</v>
       </c>
       <c r="J34" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-83.25</v>
+        <v>-201.75</v>
       </c>
       <c r="K34" s="82">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18526,43 +18596,43 @@
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
-      </c>
-      <c r="B35" s="85">
+        <v>46161</v>
+      </c>
+      <c r="B35" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-30</v>
       </c>
       <c r="C35" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>راتب عماله مايو 2025</v>
+        <v>فل عدد 30 الحبه 0.750</v>
       </c>
       <c r="D35" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E35" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F35" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
-      </c>
-      <c r="G35" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G35" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو آدم</v>
-      </c>
-      <c r="H35" s="85" t="str">
+        <v>0</v>
+      </c>
+      <c r="H35" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
-      </c>
-      <c r="I35" s="85" t="str">
+        <v>0</v>
+      </c>
+      <c r="I35" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>رواتب العمال</v>
+        <v>0</v>
       </c>
       <c r="J35" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-333.25</v>
+        <v>-179.25</v>
       </c>
       <c r="K35" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18572,43 +18642,43 @@
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46167</v>
-      </c>
-      <c r="B36" s="91">
+        <v>46162</v>
+      </c>
+      <c r="B36" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-31</v>
       </c>
       <c r="C36" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>راتب عماله مايو 2025</v>
+        <v>فل عدد30 الحبه 0.750</v>
       </c>
       <c r="D36" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E36" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F36" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
-      </c>
-      <c r="G36" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G36" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
-      </c>
-      <c r="H36" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="H36" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
-      </c>
-      <c r="I36" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="I36" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>رواتب العمال</v>
+        <v>0</v>
       </c>
       <c r="J36" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-583.25</v>
+        <v>-156.75</v>
       </c>
       <c r="K36" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18618,15 +18688,15 @@
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="B37" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-40</v>
+        <v>Inv-32</v>
       </c>
       <c r="C37" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>برازيليا عدد 50 الحبه0.500</v>
       </c>
       <c r="D37" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18634,7 +18704,7 @@
       </c>
       <c r="E37" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F37" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18644,9 +18714,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H37" s="85" t="str">
+      <c r="H37" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I37" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18654,7 +18724,7 @@
       </c>
       <c r="J37" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-574.25</v>
+        <v>-131.75</v>
       </c>
       <c r="K37" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18664,15 +18734,15 @@
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46146</v>
+        <v>46163</v>
       </c>
       <c r="B38" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-41</v>
+        <v>Inv-33</v>
       </c>
       <c r="C38" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>برازيليا عدد 75 الحبه 0.500</v>
       </c>
       <c r="D38" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18680,7 +18750,7 @@
       </c>
       <c r="E38" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v>37.5</v>
       </c>
       <c r="F38" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18690,9 +18760,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H38" s="91" t="str">
+      <c r="H38" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I38" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18700,7 +18770,7 @@
       </c>
       <c r="J38" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-565.25</v>
+        <v>-94.25</v>
       </c>
       <c r="K38" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18710,15 +18780,15 @@
     <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46146</v>
+        <v>46163</v>
       </c>
       <c r="B39" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-42</v>
+        <v>Inv-34</v>
       </c>
       <c r="C39" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>دارسينيا احمر عدد1 حبه 2.500</v>
       </c>
       <c r="D39" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18726,7 +18796,7 @@
       </c>
       <c r="E39" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F39" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18736,9 +18806,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H39" s="85" t="str">
+      <c r="H39" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I39" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18746,7 +18816,7 @@
       </c>
       <c r="J39" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-563.25</v>
+        <v>-91.75</v>
       </c>
       <c r="K39" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18756,15 +18826,15 @@
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46147</v>
+        <v>46164</v>
       </c>
       <c r="B40" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-43</v>
+        <v>Inv-35</v>
       </c>
       <c r="C40" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>دارسينا حمراء عدد 6 الحبه 2,500</v>
       </c>
       <c r="D40" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18772,7 +18842,7 @@
       </c>
       <c r="E40" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="F40" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18782,9 +18852,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H40" s="91" t="str">
+      <c r="H40" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I40" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18792,7 +18862,7 @@
       </c>
       <c r="J40" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-559.5</v>
+        <v>-76.75</v>
       </c>
       <c r="K40" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18802,15 +18872,15 @@
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46149</v>
+        <v>46164</v>
       </c>
       <c r="B41" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-44</v>
+        <v>Inv-36</v>
       </c>
       <c r="C41" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>ربل عدد4 الحبه 1.500</v>
       </c>
       <c r="D41" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18818,7 +18888,7 @@
       </c>
       <c r="E41" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18828,9 +18898,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="85" t="str">
+      <c r="H41" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I41" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18838,7 +18908,7 @@
       </c>
       <c r="J41" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-554.5</v>
+        <v>-70.75</v>
       </c>
       <c r="K41" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18848,15 +18918,15 @@
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B42" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-44</v>
+        <v>Inv-37</v>
       </c>
       <c r="C42" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>عطره عدد 10 الحبه 0.750</v>
       </c>
       <c r="D42" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18864,7 +18934,7 @@
       </c>
       <c r="E42" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="F42" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18874,9 +18944,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H42" s="91" t="str">
+      <c r="H42" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I42" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18884,7 +18954,7 @@
       </c>
       <c r="J42" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-539.5</v>
+        <v>-63.25</v>
       </c>
       <c r="K42" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18894,15 +18964,15 @@
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B43" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-45</v>
+        <v>Inv-38</v>
       </c>
       <c r="C43" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>ودليه عدد 2 الحبه 1</v>
       </c>
       <c r="D43" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18910,7 +18980,7 @@
       </c>
       <c r="E43" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18920,9 +18990,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H43" s="85" t="str">
+      <c r="H43" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I43" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18930,7 +19000,7 @@
       </c>
       <c r="J43" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-535.5</v>
+        <v>-61.25</v>
       </c>
       <c r="K43" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18940,15 +19010,15 @@
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B44" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-46</v>
+        <v>Inv-39</v>
       </c>
       <c r="C44" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>داراسينا حمراء عدد4 الحبه 1</v>
       </c>
       <c r="D44" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18956,7 +19026,7 @@
       </c>
       <c r="E44" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18966,9 +19036,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H44" s="91" t="str">
+      <c r="H44" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>0</v>
       </c>
       <c r="I44" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18976,7 +19046,7 @@
       </c>
       <c r="J44" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-532</v>
+        <v>-57.25</v>
       </c>
       <c r="K44" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18986,35 +19056,35 @@
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46158</v>
-      </c>
-      <c r="B45" s="85" t="str">
+        <v>46167</v>
+      </c>
+      <c r="B45" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-47</v>
+        <v>0</v>
       </c>
       <c r="C45" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>other</v>
+        <v>يزل ماكينه كهرباء</v>
       </c>
       <c r="D45" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E45" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G45" s="85">
+        <v>أحد الشركاء</v>
+      </c>
+      <c r="G45" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>أبو اسحاق</v>
       </c>
       <c r="H45" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
+        <v>معلق</v>
       </c>
       <c r="I45" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19022,7 +19092,7 @@
       </c>
       <c r="J45" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-529</v>
+        <v>-83.25</v>
       </c>
       <c r="K45" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19032,7 +19102,7 @@
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B46" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19040,11 +19110,11 @@
       </c>
       <c r="C46" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>جبس لتغطيه المحميه</v>
+        <v>راتب عماله مايو 2025</v>
       </c>
       <c r="D46" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.75</v>
+        <v>250</v>
       </c>
       <c r="E46" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19052,23 +19122,23 @@
       </c>
       <c r="F46" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G46" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>أبو آدم</v>
       </c>
       <c r="H46" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I46" s="91">
+        <v>معلق</v>
+      </c>
+      <c r="I46" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>رواتب العمال</v>
       </c>
       <c r="J46" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>-531.75</v>
+        <v>-333.25</v>
       </c>
       <c r="K46" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19076,693 +19146,693 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
-      <c r="A47" s="84" t="str">
+      <c r="A47" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="85" t="str">
+        <v>46167</v>
+      </c>
+      <c r="B47" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C47" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="87" t="str">
+        <v>راتب عماله مايو 2025</v>
+      </c>
+      <c r="D47" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="88" t="str">
+        <v>250</v>
+      </c>
+      <c r="E47" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G47" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="H47" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>معلق</v>
       </c>
       <c r="I47" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="89" t="str">
+        <v>رواتب العمال</v>
+      </c>
+      <c r="J47" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="85" t="str">
+        <v>-583.25</v>
+      </c>
+      <c r="K47" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A48" s="90" t="str">
+      <c r="A48" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="B48" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-40</v>
       </c>
       <c r="C48" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="93" t="str">
+        <v>other</v>
+      </c>
+      <c r="D48" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E48" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F48" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G48" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I48" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J48" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="91" t="str">
+        <v>-574.25</v>
+      </c>
+      <c r="K48" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A49" s="84" t="str">
+      <c r="A49" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="B49" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-41</v>
       </c>
       <c r="C49" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="87" t="str">
+        <v>other</v>
+      </c>
+      <c r="D49" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E49" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F49" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G49" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I49" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J49" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="85" t="str">
+        <v>-565.25</v>
+      </c>
+      <c r="K49" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(45,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A50" s="90" t="str">
+      <c r="A50" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="B50" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-42</v>
       </c>
       <c r="C50" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="93" t="str">
+        <v>other</v>
+      </c>
+      <c r="D50" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E50" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F50" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G50" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I50" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J50" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="91" t="str">
+        <v>-563.25</v>
+      </c>
+      <c r="K50" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(46,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A51" s="84" t="str">
+      <c r="A51" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46147</v>
       </c>
       <c r="B51" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-43</v>
       </c>
       <c r="C51" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="87" t="str">
+        <v>other</v>
+      </c>
+      <c r="D51" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E51" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3.75</v>
       </c>
       <c r="F51" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G51" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I51" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J51" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K51" s="85" t="str">
+        <v>-559.5</v>
+      </c>
+      <c r="K51" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(47,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A52" s="90" t="str">
+      <c r="A52" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46149</v>
       </c>
       <c r="B52" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-44</v>
       </c>
       <c r="C52" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="93" t="str">
+        <v>other</v>
+      </c>
+      <c r="D52" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E52" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F52" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G52" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H52" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I52" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J52" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="91" t="str">
+        <v>-554.5</v>
+      </c>
+      <c r="K52" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A53" s="84" t="str">
+      <c r="A53" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46155</v>
       </c>
       <c r="B53" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-44</v>
       </c>
       <c r="C53" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="87" t="str">
+        <v>other</v>
+      </c>
+      <c r="D53" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E53" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F53" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G53" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I53" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="85" t="str">
+        <v>-539.5</v>
+      </c>
+      <c r="K53" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(49,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A54" s="90" t="str">
+      <c r="A54" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46155</v>
       </c>
       <c r="B54" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-45</v>
       </c>
       <c r="C54" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="93" t="str">
+        <v>other</v>
+      </c>
+      <c r="D54" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E54" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F54" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G54" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G54" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I54" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K54" s="91" t="str">
+        <v>-535.5</v>
+      </c>
+      <c r="K54" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(50,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A55" s="84" t="str">
+      <c r="A55" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46155</v>
       </c>
       <c r="B55" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-46</v>
       </c>
       <c r="C55" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="87" t="str">
+        <v>other</v>
+      </c>
+      <c r="D55" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E55" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3.6</v>
       </c>
       <c r="F55" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G55" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G55" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I55" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="85" t="str">
+        <v>-531.9</v>
+      </c>
+      <c r="K55" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(51,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A56" s="90" t="str">
+      <c r="A56" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46158</v>
       </c>
       <c r="B56" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-47</v>
       </c>
       <c r="C56" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="93" t="str">
+        <v>other</v>
+      </c>
+      <c r="D56" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E56" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F56" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G56" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I56" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K56" s="91" t="str">
+        <v>-528.9</v>
+      </c>
+      <c r="K56" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(52,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A57" s="84" t="str">
+      <c r="A57" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B57" s="85" t="str">
+        <v>46155</v>
+      </c>
+      <c r="B57" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C57" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="87" t="str">
+        <v>جبس لتغطيه المحميه</v>
+      </c>
+      <c r="D57" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="88" t="str">
+        <v>2.75</v>
+      </c>
+      <c r="E57" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F57" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G57" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H57" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I57" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K57" s="85" t="str">
+        <v>-531.65</v>
+      </c>
+      <c r="K57" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(53,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A58" s="90" t="str">
+      <c r="A58" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B58" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-53</v>
       </c>
       <c r="C58" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="93" t="str">
+        <v>فل عدد 24 الحبه .750</v>
+      </c>
+      <c r="D58" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E58" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="F58" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G58" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H58" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I58" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K58" s="91" t="str">
+        <v>-513.65</v>
+      </c>
+      <c r="K58" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(54,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A59" s="84" t="str">
+      <c r="A59" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B59" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-54</v>
       </c>
       <c r="C59" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="87" t="str">
+        <v>دارسينا خضراء عدد 1 الحبه 2</v>
+      </c>
+      <c r="D59" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E59" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F59" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G59" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G59" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H59" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I59" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J59" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K59" s="85" t="str">
+        <v>-511.65</v>
+      </c>
+      <c r="K59" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(55,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A60" s="90" t="str">
+      <c r="A60" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B60" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-55</v>
       </c>
       <c r="C60" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="93" t="str">
+        <v>افوبيا عدد 2 الحبه .750</v>
+      </c>
+      <c r="D60" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E60" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E60" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="F60" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G60" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G60" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H60" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I60" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J60" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K60" s="91" t="str">
+        <v>-510.15</v>
+      </c>
+      <c r="K60" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(56,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A61" s="84" t="str">
+      <c r="A61" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46175</v>
       </c>
       <c r="B61" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-56</v>
       </c>
       <c r="C61" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="87" t="str">
+        <v>دارسينا سوداء عدد 3 الحبه 1</v>
+      </c>
+      <c r="D61" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E61" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="E61" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F61" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G61" s="85" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G61" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H61" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I61" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I61" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J61" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J61" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K61" s="85" t="str">
+        <v>-507.15</v>
+      </c>
+      <c r="K61" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(57,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1">
@@ -24051,22 +24121,22 @@
       <c r="C155" s="145"/>
       <c r="D155" s="96">
         <f>SUM(D5:D154)</f>
-        <v>546.75</v>
+        <v>997.25</v>
       </c>
       <c r="E155" s="96">
         <f>SUM(E5:E154)</f>
-        <v>316</v>
+        <v>526.6</v>
       </c>
       <c r="F155" s="141">
         <f>COUNTIF(H5:H154,"معلق")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G155" s="141"/>
       <c r="H155" s="141"/>
       <c r="I155" s="97"/>
       <c r="J155" s="96">
         <f>E155-D155</f>
-        <v>-230.75</v>
+        <v>-470.65</v>
       </c>
       <c r="K155" s="97"/>
     </row>
@@ -24186,7 +24256,7 @@
       <c r="E3" s="148"/>
       <c r="F3" s="99">
         <f>المحفظة!$C$3</f>
-        <v>349.75</v>
+        <v>374.35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
@@ -25102,7 +25172,7 @@
       </c>
       <c r="E39" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F39" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -25509,7 +25579,7 @@
       <c r="D55" s="131"/>
       <c r="E55" s="114">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
-        <v>316</v>
+        <v>316.10000000000002</v>
       </c>
       <c r="F55" s="97"/>
       <c r="G55" s="97"/>
@@ -26847,11 +26917,11 @@
       <c r="C108" s="145"/>
       <c r="D108" s="96">
         <f>E55-D107</f>
-        <v>304.25</v>
+        <v>304.35000000000002</v>
       </c>
       <c r="E108" s="149">
         <f>SUM(E5:E107)</f>
-        <v>632</v>
+        <v>632.20000000000005</v>
       </c>
       <c r="F108" s="149"/>
       <c r="G108" s="149"/>

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D7316E-A721-4229-A79E-6313E9314401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1C0B0-99DD-49CB-9FEC-4349778CB742}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="207">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -659,6 +659,15 @@
   </si>
   <si>
     <t>دارسينا سوداء عدد 3 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-44a</t>
+  </si>
+  <si>
+    <t>Inv-013a</t>
+  </si>
+  <si>
+    <t>Inv-18a</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2084,7 @@
       </c>
       <c r="B8" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(4,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>Inv-013</v>
+        <v>Inv-013a</v>
       </c>
       <c r="C8" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(4,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -2165,7 +2174,7 @@
       </c>
       <c r="B11" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(7,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>Inv-18</v>
+        <v>Inv-18a</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(7,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -2975,7 +2984,7 @@
       </c>
       <c r="B38" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(34,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>Inv-44</v>
+        <v>Inv-44a</v>
       </c>
       <c r="C38" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(34,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -10212,7 +10221,7 @@
         <v>46151</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="C16" s="47" t="s">
         <v>71</v>
@@ -10390,7 +10399,7 @@
         <v>46155</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="C20" s="47" t="s">
         <v>78</v>
@@ -11718,7 +11727,7 @@
         <v>46149</v>
       </c>
       <c r="B51" s="57" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="C51" s="58" t="s">
         <v>127</v>
@@ -17772,7 +17781,7 @@
       </c>
       <c r="B17" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-013</v>
+        <v>Inv-013a</v>
       </c>
       <c r="C17" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -17956,7 +17965,7 @@
       </c>
       <c r="B21" s="80" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-18</v>
+        <v>Inv-18a</v>
       </c>
       <c r="C21" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -19382,7 +19391,7 @@
       </c>
       <c r="B52" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-44</v>
+        <v>Inv-44a</v>
       </c>
       <c r="C52" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(48,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -24303,7 +24312,7 @@
       </c>
       <c r="B6" s="12" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>Inv-013</v>
+        <v>Inv-013a</v>
       </c>
       <c r="C6" s="102" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -24381,7 +24390,7 @@
       </c>
       <c r="B9" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>Inv-18</v>
+        <v>Inv-18a</v>
       </c>
       <c r="C9" s="100" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -25083,7 +25092,7 @@
       </c>
       <c r="B36" s="105" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>Inv-44</v>
+        <v>Inv-44a</v>
       </c>
       <c r="C36" s="106" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0))),"")</f>

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1C0B0-99DD-49CB-9FEC-4349778CB742}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF0E68F-B2AE-4CA4-95BF-A30A84A78316}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="211">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -668,6 +668,18 @@
   </si>
   <si>
     <t>Inv-18a</t>
+  </si>
+  <si>
+    <t>inv-57</t>
+  </si>
+  <si>
+    <t>فوزير عدد1 قيمه 1</t>
+  </si>
+  <si>
+    <t>سماد</t>
+  </si>
+  <si>
+    <t>حفاره خلط السماد</t>
   </si>
 </sst>
 </file>
@@ -1547,6 +1559,21 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1563,21 +1590,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1935,57 +1947,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="139"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="3">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>374.35</v>
-      </c>
-      <c r="D3" s="140" t="s">
+        <v>350.1</v>
+      </c>
+      <c r="D3" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="130" t="s">
+      <c r="A4" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="4">
@@ -3248,28 +3260,28 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1">
-      <c r="A47" s="4" t="str">
+      <c r="A47" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(43,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46177</v>
       </c>
       <c r="B47" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(43,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>inv-57</v>
       </c>
       <c r="C47" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(43,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>فوزير عدد1 قيمه 1</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E47" s="8" t="str">
+      <c r="E47" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(43,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="9" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(43,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G47" s="10"/>
       <c r="H47" s="1" t="str">
@@ -4988,27 +5000,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="131" t="s">
+      <c r="A105" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="131"/>
-      <c r="C105" s="131"/>
-      <c r="D105" s="131"/>
+      <c r="B105" s="136"/>
+      <c r="C105" s="136"/>
+      <c r="D105" s="136"/>
       <c r="E105" s="18">
         <f>SUM(E5:E104)</f>
-        <v>526.6</v>
+        <v>527.6</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="132" t="s">
+      <c r="A106" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="132"/>
-      <c r="C106" s="132"/>
-      <c r="D106" s="132"/>
-      <c r="E106" s="132"/>
-      <c r="F106" s="132"/>
-      <c r="G106" s="132"/>
+      <c r="B106" s="137"/>
+      <c r="C106" s="137"/>
+      <c r="D106" s="137"/>
+      <c r="E106" s="137"/>
+      <c r="F106" s="137"/>
+      <c r="G106" s="137"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="19">
@@ -5221,28 +5233,28 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="18" customHeight="1">
-      <c r="A114" s="26" t="str">
+      <c r="A114" s="26">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(8,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B114" s="27" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B114" s="27">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(8,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C114" s="28" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(8,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D114" s="29" t="str">
+        <v>سماد</v>
+      </c>
+      <c r="D114" s="29">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(8,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E114" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F114" s="31" t="str">
+      <c r="F114" s="31">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(8,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="1" t="str">
@@ -5251,28 +5263,28 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="18" customHeight="1">
-      <c r="A115" s="19" t="str">
+      <c r="A115" s="19">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(9,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B115" s="20" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B115" s="20">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(9,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C115" s="21" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(9,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D115" s="22" t="str">
+        <v>تاير لعربة الرش</v>
+      </c>
+      <c r="D115" s="22">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(9,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>3.25</v>
       </c>
       <c r="E115" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="24" t="str">
+      <c r="F115" s="24">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(9,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G115" s="25"/>
       <c r="H115" s="1" t="str">
@@ -5281,28 +5293,28 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="18" customHeight="1">
-      <c r="A116" s="26" t="str">
+      <c r="A116" s="26">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(10,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B116" s="27" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B116" s="27">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(10,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C116" s="28" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(10,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D116" s="29" t="str">
+        <v>حفاره خلط السماد</v>
+      </c>
+      <c r="D116" s="29">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(10,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="E116" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F116" s="31" t="str">
+      <c r="F116" s="31">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(10,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G116" s="32"/>
       <c r="H116" s="1" t="str">
@@ -8011,31 +8023,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="133" t="s">
+      <c r="A207" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="133"/>
-      <c r="C207" s="133"/>
+      <c r="B207" s="138"/>
+      <c r="C207" s="138"/>
       <c r="D207" s="33">
         <f>SUM(D107:D206)</f>
-        <v>152.25</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="134" t="s">
+      <c r="A208" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="134"/>
-      <c r="C208" s="134"/>
+      <c r="B208" s="139"/>
+      <c r="C208" s="139"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>374.35</v>
-      </c>
-      <c r="E208" s="135" t="s">
+        <v>350.1</v>
+      </c>
+      <c r="E208" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="135"/>
-      <c r="G208" s="135"/>
+      <c r="F208" s="140"/>
+      <c r="G208" s="140"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9544,17 +9556,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9580,38 +9592,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -12163,31 +12175,43 @@
       </c>
     </row>
     <row r="61" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A61" s="56"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="58"/>
+      <c r="A61" s="56">
+        <v>46177</v>
+      </c>
+      <c r="B61" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="58" t="s">
+        <v>208</v>
+      </c>
       <c r="D61" s="59"/>
-      <c r="E61" s="60"/>
-      <c r="F61" s="61"/>
+      <c r="E61" s="60">
+        <v>1</v>
+      </c>
+      <c r="F61" s="61" t="s">
+        <v>42</v>
+      </c>
       <c r="G61" s="62"/>
-      <c r="H61" s="63"/>
+      <c r="H61" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I61" s="64"/>
-      <c r="J61" s="65" t="str">
+      <c r="J61" s="65">
         <f>IF(AND(D61="",E61="",A61="",B61="",C61=""),"", IFERROR(IF(J60="",D2,J60),D2)+IF(E61="",0,E61)-IF(D61="",0,D61))</f>
-        <v/>
+        <v>-506.15</v>
       </c>
       <c r="K61" s="66"/>
-      <c r="L61" s="1" t="str">
+      <c r="L61" s="1">
         <f>IF(E61&gt;0,COUNTIF($E$4:E61,"&gt;0"),"")</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="M61" s="1" t="str">
         <f>IF(AND(D61&gt;0,G61="المحفظة"),COUNTIFS($D$4:D61,"&gt;"&amp;0,$G$4:G61,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N61" s="1" t="str">
+      <c r="N61" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A61)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A61)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A61&lt;&gt;""),IFERROR(MAX($N$4:N60),0)+1,"")</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="O61" s="1" t="str">
         <f>IF(AND(D61&gt;0,F61="أحد الشركاء"),COUNTIFS($D$4:D61,"&gt;"&amp;0,$F$4:F61,"أحد الشركاء"),"")</f>
@@ -12195,31 +12219,43 @@
       </c>
     </row>
     <row r="62" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A62" s="45"/>
+      <c r="A62" s="56">
+        <v>46177</v>
+      </c>
       <c r="B62" s="46"/>
-      <c r="C62" s="47"/>
-      <c r="D62" s="48"/>
+      <c r="C62" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="D62" s="48">
+        <v>10</v>
+      </c>
       <c r="E62" s="49"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="52"/>
+      <c r="F62" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I62" s="53"/>
-      <c r="J62" s="54" t="str">
+      <c r="J62" s="54">
         <f>IF(AND(D62="",E62="",A62="",B62="",C62=""),"", IFERROR(IF(J61="",D2,J61),D2)+IF(E62="",0,E62)-IF(D62="",0,D62))</f>
-        <v/>
+        <v>-516.15</v>
       </c>
       <c r="K62" s="55"/>
       <c r="L62" s="1" t="str">
         <f>IF(E62&gt;0,COUNTIF($E$4:E62,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M62" s="1" t="str">
+      <c r="M62" s="1">
         <f>IF(AND(D62&gt;0,G62="المحفظة"),COUNTIFS($D$4:D62,"&gt;"&amp;0,$G$4:G62,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N62" s="1" t="str">
+        <v>8</v>
+      </c>
+      <c r="N62" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A62)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A62)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A62&lt;&gt;""),IFERROR(MAX($N$4:N61),0)+1,"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="O62" s="1" t="str">
         <f>IF(AND(D62&gt;0,F62="أحد الشركاء"),COUNTIFS($D$4:D62,"&gt;"&amp;0,$F$4:F62,"أحد الشركاء"),"")</f>
@@ -12227,31 +12263,43 @@
       </c>
     </row>
     <row r="63" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A63" s="56"/>
+      <c r="A63" s="56">
+        <v>46177</v>
+      </c>
       <c r="B63" s="57"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="59"/>
+      <c r="C63" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" s="59">
+        <v>3.25</v>
+      </c>
       <c r="E63" s="60"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="62"/>
-      <c r="H63" s="63"/>
+      <c r="F63" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I63" s="64"/>
-      <c r="J63" s="65" t="str">
+      <c r="J63" s="65">
         <f>IF(AND(D63="",E63="",A63="",B63="",C63=""),"", IFERROR(IF(J62="",D2,J62),D2)+IF(E63="",0,E63)-IF(D63="",0,D63))</f>
-        <v/>
+        <v>-519.4</v>
       </c>
       <c r="K63" s="66"/>
       <c r="L63" s="1" t="str">
         <f>IF(E63&gt;0,COUNTIF($E$4:E63,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M63" s="1" t="str">
+      <c r="M63" s="1">
         <f>IF(AND(D63&gt;0,G63="المحفظة"),COUNTIFS($D$4:D63,"&gt;"&amp;0,$G$4:G63,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N63" s="1" t="str">
+        <v>9</v>
+      </c>
+      <c r="N63" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A63)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A63)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A63&lt;&gt;""),IFERROR(MAX($N$4:N62),0)+1,"")</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="O63" s="1" t="str">
         <f>IF(AND(D63&gt;0,F63="أحد الشركاء"),COUNTIFS($D$4:D63,"&gt;"&amp;0,$F$4:F63,"أحد الشركاء"),"")</f>
@@ -12259,31 +12307,43 @@
       </c>
     </row>
     <row r="64" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A64" s="45"/>
+      <c r="A64" s="56">
+        <v>46177</v>
+      </c>
       <c r="B64" s="46"/>
-      <c r="C64" s="47"/>
-      <c r="D64" s="48"/>
+      <c r="C64" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D64" s="48">
+        <v>12</v>
+      </c>
       <c r="E64" s="49"/>
-      <c r="F64" s="50"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="52"/>
+      <c r="F64" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I64" s="53"/>
-      <c r="J64" s="54" t="str">
+      <c r="J64" s="54">
         <f>IF(AND(D64="",E64="",A64="",B64="",C64=""),"", IFERROR(IF(J63="",D2,J63),D2)+IF(E64="",0,E64)-IF(D64="",0,D64))</f>
-        <v/>
+        <v>-531.4</v>
       </c>
       <c r="K64" s="55"/>
       <c r="L64" s="1" t="str">
         <f>IF(E64&gt;0,COUNTIF($E$4:E64,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M64" s="1" t="str">
+      <c r="M64" s="1">
         <f>IF(AND(D64&gt;0,G64="المحفظة"),COUNTIFS($D$4:D64,"&gt;"&amp;0,$G$4:G64,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N64" s="1" t="str">
+        <v>10</v>
+      </c>
+      <c r="N64" s="1">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A64)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A64)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A64&lt;&gt;""),IFERROR(MAX($N$4:N63),0)+1,"")</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="O64" s="1" t="str">
         <f>IF(AND(D64&gt;0,F64="أحد الشركاء"),COUNTIFS($D$4:D64,"&gt;"&amp;0,$F$4:F64,"أحد الشركاء"),"")</f>
@@ -16739,18 +16799,18 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="134" t="s">
+      <c r="A204" s="139" t="s">
         <v>135</v>
       </c>
-      <c r="B204" s="134"/>
-      <c r="C204" s="134"/>
+      <c r="B204" s="139"/>
+      <c r="C204" s="139"/>
       <c r="D204" s="67">
         <f>SUM(D4:D203)</f>
-        <v>997.25</v>
+        <v>1022.5</v>
       </c>
       <c r="E204" s="67">
         <f>SUM(E4:E203)</f>
-        <v>526.6</v>
+        <v>527.6</v>
       </c>
       <c r="F204" s="141">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -16760,7 +16820,7 @@
       <c r="H204" s="141"/>
       <c r="J204" s="67">
         <f>$D$2+E204-D204</f>
-        <v>-470.65</v>
+        <v>-494.9</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="15.75" customHeight="1">
@@ -17141,19 +17201,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
       <c r="A2" s="146"/>
@@ -19845,187 +19905,187 @@
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A62" s="90" t="str">
+      <c r="A62" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46177</v>
       </c>
       <c r="B62" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>inv-57</v>
       </c>
       <c r="C62" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="93" t="str">
+        <v>فوزير عدد1 قيمه 1</v>
+      </c>
+      <c r="D62" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E62" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E62" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F62" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G62" s="91" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G62" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H62" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I62" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I62" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J62" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J62" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K62" s="91" t="str">
+        <v>-506.15</v>
+      </c>
+      <c r="K62" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(58,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A63" s="84" t="str">
+      <c r="A63" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B63" s="85" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B63" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C63" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="87" t="str">
+        <v>سماد</v>
+      </c>
+      <c r="D63" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E63" s="88" t="str">
+        <v>10</v>
+      </c>
+      <c r="E63" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F63" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G63" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H63" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I63" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I63" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J63" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K63" s="85" t="str">
+        <v>-516.15</v>
+      </c>
+      <c r="K63" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(59,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A64" s="90" t="str">
+      <c r="A64" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B64" s="91" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B64" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C64" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="93" t="str">
+        <v>تاير لعربة الرش</v>
+      </c>
+      <c r="D64" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E64" s="94" t="str">
+        <v>3.25</v>
+      </c>
+      <c r="E64" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F64" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G64" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H64" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I64" s="91" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I64" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J64" s="95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J64" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K64" s="91" t="str">
+        <v>-519.4</v>
+      </c>
+      <c r="K64" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(60,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A65" s="84" t="str">
+      <c r="A65" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B65" s="85" t="str">
+        <v>46177</v>
+      </c>
+      <c r="B65" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C65" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="87" t="str">
+        <v>حفاره خلط السماد</v>
+      </c>
+      <c r="D65" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E65" s="88" t="str">
+        <v>12</v>
+      </c>
+      <c r="E65" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F65" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G65" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H65" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I65" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J65" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K65" s="85" t="str">
+        <v>-531.4</v>
+      </c>
+      <c r="K65" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(61,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" hidden="1" customHeight="1">
@@ -24130,11 +24190,11 @@
       <c r="C155" s="145"/>
       <c r="D155" s="96">
         <f>SUM(D5:D154)</f>
-        <v>997.25</v>
+        <v>1022.5</v>
       </c>
       <c r="E155" s="96">
         <f>SUM(E5:E154)</f>
-        <v>526.6</v>
+        <v>527.6</v>
       </c>
       <c r="F155" s="141">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -24145,7 +24205,7 @@
       <c r="I155" s="97"/>
       <c r="J155" s="96">
         <f>E155-D155</f>
-        <v>-470.65</v>
+        <v>-494.9</v>
       </c>
       <c r="K155" s="97"/>
     </row>
@@ -24224,15 +24284,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
       <c r="A2" s="146" t="s">
@@ -24265,19 +24325,19 @@
       <c r="E3" s="148"/>
       <c r="F3" s="99">
         <f>المحفظة!$C$3</f>
-        <v>374.35</v>
+        <v>350.1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="136" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="4">
@@ -25580,12 +25640,12 @@
       <c r="G54" s="17"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="131" t="s">
+      <c r="A55" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="131"/>
-      <c r="C55" s="131"/>
-      <c r="D55" s="131"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="136"/>
       <c r="E55" s="114">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>316.10000000000002</v>
@@ -25594,15 +25654,15 @@
       <c r="G55" s="97"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="138" t="s">
         <v>192</v>
       </c>
-      <c r="B56" s="133"/>
-      <c r="C56" s="133"/>
-      <c r="D56" s="133"/>
-      <c r="E56" s="133"/>
-      <c r="F56" s="133"/>
-      <c r="G56" s="133"/>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="138"/>
+      <c r="E56" s="138"/>
+      <c r="F56" s="138"/>
+      <c r="G56" s="138"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="19">
@@ -26905,11 +26965,11 @@
       <c r="G106" s="32"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="133" t="s">
+      <c r="A107" s="138" t="s">
         <v>193</v>
       </c>
-      <c r="B107" s="133"/>
-      <c r="C107" s="133"/>
+      <c r="B107" s="138"/>
+      <c r="C107" s="138"/>
       <c r="D107" s="129">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>11.75</v>
@@ -26937,17 +26997,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="E108:G108"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73525CB2-A8C1-4A44-8D59-545568D1851A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F1D91B-83B4-4596-93A7-690C77B76FEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="224">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -263,9 +263,6 @@
     <t>فل عدد 21 سعر الحبه .0.750</t>
   </si>
   <si>
-    <t>Inv-013a</t>
-  </si>
-  <si>
     <t>برازيليا عدد 25 سعر الحبه .500</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
   </si>
   <si>
     <t>فل عدد 10 الحبه 0.750</t>
-  </si>
-  <si>
-    <t>Inv-18a</t>
   </si>
   <si>
     <t>ربل 4 حبات الحبه 1.500</t>
@@ -699,6 +693,27 @@
   </si>
   <si>
     <t>دارسينا حمراء عدد 1 بقيمه 3</t>
+  </si>
+  <si>
+    <t>Inv-61</t>
+  </si>
+  <si>
+    <t>فل عدد 20 بقيمه 0.750</t>
+  </si>
+  <si>
+    <t>اسمنت اسود للمحميه الصغيره الجديده</t>
+  </si>
+  <si>
+    <t>حديد اسود للمحميه الصغيره الجديده</t>
+  </si>
+  <si>
+    <t>Inv-62</t>
+  </si>
+  <si>
+    <t>Inv-013A</t>
+  </si>
+  <si>
+    <t>Inv-18A</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1612,17 +1627,16 @@
     <xf numFmtId="14" fontId="23" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1646,6 +1660,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2021,7 +2042,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="137"/>
@@ -2032,7 +2053,7 @@
       <c r="G1" s="137"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="145" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="137"/>
@@ -2040,22 +2061,22 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="144" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="3">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>308.35000000000002</v>
-      </c>
-      <c r="D3" s="139" t="s">
+        <v>286.60000000000002</v>
+      </c>
+      <c r="D3" s="138" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="137"/>
@@ -2063,7 +2084,7 @@
       <c r="G3" s="137"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="143" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="137"/>
@@ -2140,7 +2161,7 @@
       </c>
       <c r="B7" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(3,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>Inv-013a</v>
+        <v>Inv-013A</v>
       </c>
       <c r="C7" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(3,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -2230,7 +2251,7 @@
       </c>
       <c r="B10" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(6,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>Inv-18a</v>
+        <v>Inv-18A</v>
       </c>
       <c r="C10" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(6,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
@@ -3426,26 +3447,26 @@
     <row r="50" spans="1:8" ht="18" customHeight="1">
       <c r="A50" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(46,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B50" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B50" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(46,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="13">
+        <v>Inv-61</v>
+      </c>
+      <c r="C50" s="13" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(46,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>فل عدد 20 بقيمه 0.750</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>6</v>
       </c>
       <c r="E50" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(46,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="16">
+        <v>15</v>
+      </c>
+      <c r="F50" s="16" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(46,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>نقداً</v>
       </c>
       <c r="G50" s="17"/>
       <c r="H50" t="str">
@@ -3454,28 +3475,28 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1">
-      <c r="A51" s="4" t="str">
+      <c r="A51" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(47,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B51" s="5" t="str">
+        <v>46181</v>
+      </c>
+      <c r="B51" s="5">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(47,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C51" s="6" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(47,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>اسمنت اسود للمحميه الصغيره الجديده</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(47,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="9" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(47,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" t="str">
@@ -3484,28 +3505,28 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="18" customHeight="1">
-      <c r="A52" s="11" t="str">
+      <c r="A52" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(48,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B52" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="B52" s="12">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(48,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="C52" s="13">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(48,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E52" s="15" t="str">
+      <c r="E52" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(48,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="16" t="str">
+        <v>10</v>
+      </c>
+      <c r="F52" s="16">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(48,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G52" s="17"/>
       <c r="H52" t="str">
@@ -3514,28 +3535,28 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="18" customHeight="1">
-      <c r="A53" s="4" t="str">
+      <c r="A53" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(49,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B53" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="B53" s="5">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(49,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="C53" s="6">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(49,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E53" s="8" t="str">
+      <c r="E53" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(49,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(49,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" t="str">
@@ -5074,7 +5095,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="140" t="s">
+      <c r="A105" s="139" t="s">
         <v>7</v>
       </c>
       <c r="B105" s="137"/>
@@ -5082,11 +5103,11 @@
       <c r="D105" s="137"/>
       <c r="E105" s="18">
         <f>SUM(E5:E104)</f>
-        <v>464.1</v>
+        <v>489.1</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="141" t="s">
+      <c r="A106" s="140" t="s">
         <v>8</v>
       </c>
       <c r="B106" s="137"/>
@@ -5427,28 +5448,28 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="18" customHeight="1">
-      <c r="A118" s="26" t="str">
+      <c r="A118" s="26">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(12,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B118" s="27" t="str">
+        <v>46181</v>
+      </c>
+      <c r="B118" s="27">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(12,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C118" s="28" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(12,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D118" s="29" t="str">
+        <v>حديد اسود للمحميه الصغيره الجديده</v>
+      </c>
+      <c r="D118" s="29">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(12,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>46.75</v>
       </c>
       <c r="E118" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F118" s="31" t="str">
+      <c r="F118" s="31">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(12,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G118" s="32"/>
       <c r="H118" t="str">
@@ -5457,28 +5478,28 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="18" customHeight="1">
-      <c r="A119" s="19" t="str">
+      <c r="A119" s="19">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(13,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>46182</v>
       </c>
       <c r="B119" s="20" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(13,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>Inv-62</v>
       </c>
       <c r="C119" s="21" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(13,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D119" s="22" t="str">
+        <v>فل عدد 30 الحبه 0.750</v>
+      </c>
+      <c r="D119" s="22">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(13,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E119" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F119" s="24" t="str">
+      <c r="F119" s="24">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(13,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G119" s="25"/>
       <c r="H119" t="str">
@@ -8097,27 +8118,27 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="136" t="s">
+      <c r="A207" s="148" t="s">
         <v>9</v>
       </c>
       <c r="B207" s="137"/>
       <c r="C207" s="137"/>
       <c r="D207" s="33">
         <f>SUM(D107:D206)</f>
-        <v>155.75</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="142" t="s">
+      <c r="A208" s="141" t="s">
         <v>10</v>
       </c>
       <c r="B208" s="137"/>
       <c r="C208" s="137"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>308.35000000000002</v>
-      </c>
-      <c r="E208" s="143" t="s">
+        <v>286.60000000000002</v>
+      </c>
+      <c r="E208" s="142" t="s">
         <v>11</v>
       </c>
       <c r="F208" s="137"/>
@@ -9630,6 +9651,10 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A106:G106"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
     <mergeCell ref="A4:G4"/>
@@ -9637,10 +9662,6 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A106:G106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9666,7 +9687,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="136" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="137"/>
@@ -9681,7 +9702,7 @@
       <c r="K1" s="137"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="145" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="137"/>
@@ -9689,15 +9710,15 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -10342,10 +10363,10 @@
         <v>46151</v>
       </c>
       <c r="B17" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="47" t="s">
         <v>73</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>74</v>
       </c>
       <c r="D17" s="48"/>
       <c r="E17" s="49">
@@ -10391,7 +10412,7 @@
         <v>18213</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="59">
         <v>9</v>
@@ -10436,10 +10457,10 @@
         <v>46152</v>
       </c>
       <c r="B19" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="47" t="s">
         <v>76</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>77</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="49">
@@ -10478,10 +10499,10 @@
         <v>46155</v>
       </c>
       <c r="B20" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="58" t="s">
         <v>78</v>
-      </c>
-      <c r="C20" s="58" t="s">
-        <v>79</v>
       </c>
       <c r="D20" s="59"/>
       <c r="E20" s="60">
@@ -10520,10 +10541,10 @@
         <v>46155</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D21" s="48"/>
       <c r="E21" s="49">
@@ -10562,10 +10583,10 @@
         <v>46156</v>
       </c>
       <c r="B22" s="57" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D22" s="59"/>
       <c r="E22" s="60">
@@ -10604,10 +10625,10 @@
         <v>46158</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D23" s="48"/>
       <c r="E23" s="49">
@@ -10646,10 +10667,10 @@
         <v>46158</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D24" s="59"/>
       <c r="E24" s="60">
@@ -10688,10 +10709,10 @@
         <v>46158</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="49">
@@ -10730,10 +10751,10 @@
         <v>46159</v>
       </c>
       <c r="B26" s="57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D26" s="59"/>
       <c r="E26" s="60">
@@ -10750,7 +10771,7 @@
         <v>80.75</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L26">
         <f>IF(E25&gt;0,COUNTIF($E$4:E25,"&gt;0"),"")</f>
@@ -10774,10 +10795,10 @@
         <v>46159</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D27" s="48"/>
       <c r="E27" s="49">
@@ -10816,10 +10837,10 @@
         <v>46160</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D28" s="48"/>
       <c r="E28" s="49">
@@ -10858,10 +10879,10 @@
         <v>46160</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D29" s="48"/>
       <c r="E29" s="49">
@@ -10900,10 +10921,10 @@
         <v>46160</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" s="48"/>
       <c r="E30" s="49">
@@ -10942,10 +10963,10 @@
         <v>46160</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D31" s="48"/>
       <c r="E31" s="49">
@@ -10984,10 +11005,10 @@
         <v>46160</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="49">
@@ -11026,10 +11047,10 @@
         <v>46160</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="49">
@@ -11068,10 +11089,10 @@
         <v>46160</v>
       </c>
       <c r="B34" s="46" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D34" s="48">
         <v>9</v>
@@ -11116,10 +11137,10 @@
         <v>46161</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="48"/>
       <c r="E35" s="49">
@@ -11158,10 +11179,10 @@
         <v>46162</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D36" s="59"/>
       <c r="E36" s="60">
@@ -11200,10 +11221,10 @@
         <v>46162</v>
       </c>
       <c r="B37" s="46" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D37" s="48"/>
       <c r="E37" s="49">
@@ -11242,10 +11263,10 @@
         <v>46163</v>
       </c>
       <c r="B38" s="57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D38" s="59"/>
       <c r="E38" s="60">
@@ -11284,10 +11305,10 @@
         <v>46163</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D39" s="48"/>
       <c r="E39" s="49">
@@ -11326,10 +11347,10 @@
         <v>46164</v>
       </c>
       <c r="B40" s="57" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D40" s="59"/>
       <c r="E40" s="60">
@@ -11368,10 +11389,10 @@
         <v>46164</v>
       </c>
       <c r="B41" s="46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="49">
@@ -11410,10 +11431,10 @@
         <v>46167</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C42" s="58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D42" s="59"/>
       <c r="E42" s="60">
@@ -11452,10 +11473,10 @@
         <v>46167</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D43" s="48"/>
       <c r="E43" s="49">
@@ -11494,10 +11515,10 @@
         <v>46167</v>
       </c>
       <c r="B44" s="57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C44" s="58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D44" s="59"/>
       <c r="E44" s="60">
@@ -11537,7 +11558,7 @@
       </c>
       <c r="B45" s="46"/>
       <c r="C45" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D45" s="48">
         <v>26</v>
@@ -11581,7 +11602,7 @@
       </c>
       <c r="B46" s="57"/>
       <c r="C46" s="58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D46" s="59">
         <v>250</v>
@@ -11597,7 +11618,7 @@
         <v>54</v>
       </c>
       <c r="I46" s="64" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J46" s="65">
         <f>IF(AND(D46="",E46="",A46="",B46="",C46=""),"", IFERROR(IF(J45="",D2,J45),D2)+IF(E46="",0,E46)-IF(OR(G46="أبو اسحاق",G46="أبو آدم",G46="أبو اسحاق ",G46="أبو آدم "),0,IF(D46="",0,D46)))</f>
@@ -11627,7 +11648,7 @@
       </c>
       <c r="B47" s="46"/>
       <c r="C47" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D47" s="48">
         <v>250</v>
@@ -11643,7 +11664,7 @@
         <v>54</v>
       </c>
       <c r="I47" s="53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J47" s="54">
         <f>IF(AND(D47="",E47="",A47="",B47="",C47=""),"", IFERROR(IF(J46="",D2,J46),D2)+IF(E47="",0,E47)-IF(OR(G47="أبو اسحاق",G47="أبو آدم",G47="أبو اسحاق ",G47="أبو آدم "),0,IF(D47="",0,D47)))</f>
@@ -11672,10 +11693,10 @@
         <v>46146</v>
       </c>
       <c r="B48" s="57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C48" s="58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D48" s="59"/>
       <c r="E48" s="60">
@@ -11716,10 +11737,10 @@
         <v>46146</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D49" s="48"/>
       <c r="E49" s="49">
@@ -11760,10 +11781,10 @@
         <v>46146</v>
       </c>
       <c r="B50" s="57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D50" s="59"/>
       <c r="E50" s="60">
@@ -11804,10 +11825,10 @@
         <v>46147</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D51" s="48"/>
       <c r="E51" s="49">
@@ -11848,10 +11869,10 @@
         <v>46149</v>
       </c>
       <c r="B52" s="57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C52" s="58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D52" s="59"/>
       <c r="E52" s="60">
@@ -11892,10 +11913,10 @@
         <v>46155</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D53" s="48"/>
       <c r="E53" s="49">
@@ -11936,10 +11957,10 @@
         <v>46155</v>
       </c>
       <c r="B54" s="57" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C54" s="58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D54" s="59"/>
       <c r="E54" s="60">
@@ -11980,10 +12001,10 @@
         <v>46155</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D55" s="48"/>
       <c r="E55" s="49">
@@ -12024,10 +12045,10 @@
         <v>46158</v>
       </c>
       <c r="B56" s="57" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C56" s="58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D56" s="59"/>
       <c r="E56" s="60">
@@ -12112,10 +12133,10 @@
         <v>46175</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C58" s="58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D58" s="59"/>
       <c r="E58" s="60">
@@ -12156,10 +12177,10 @@
         <v>46175</v>
       </c>
       <c r="B59" s="57" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D59" s="48"/>
       <c r="E59" s="49">
@@ -12200,10 +12221,10 @@
         <v>46175</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C60" s="58" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D60" s="59"/>
       <c r="E60" s="60">
@@ -12244,10 +12265,10 @@
         <v>46175</v>
       </c>
       <c r="B61" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D61" s="48"/>
       <c r="E61" s="49">
@@ -12288,10 +12309,10 @@
         <v>46177</v>
       </c>
       <c r="B62" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C62" s="58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D62" s="59"/>
       <c r="E62" s="60">
@@ -12333,7 +12354,7 @@
       </c>
       <c r="B63" s="46"/>
       <c r="C63" s="47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D63" s="48">
         <v>10</v>
@@ -12421,7 +12442,7 @@
       </c>
       <c r="B65" s="46"/>
       <c r="C65" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D65" s="48">
         <v>12</v>
@@ -12464,10 +12485,10 @@
         <v>46179</v>
       </c>
       <c r="B66" s="57" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D66" s="59"/>
       <c r="E66" s="60">
@@ -12508,10 +12529,10 @@
         <v>46179</v>
       </c>
       <c r="B67" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" s="47" t="s">
         <v>215</v>
-      </c>
-      <c r="C67" s="47" t="s">
-        <v>217</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="49">
@@ -12552,10 +12573,10 @@
         <v>46179</v>
       </c>
       <c r="B68" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="58" t="s">
         <v>216</v>
-      </c>
-      <c r="C68" s="58" t="s">
-        <v>218</v>
       </c>
       <c r="D68" s="59"/>
       <c r="E68" s="60">
@@ -12592,14 +12613,26 @@
       </c>
     </row>
     <row r="69" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A69" s="45"/>
-      <c r="B69" s="46"/>
-      <c r="C69" s="47"/>
+      <c r="A69" s="45">
+        <v>46181</v>
+      </c>
+      <c r="B69" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" s="47" t="s">
+        <v>218</v>
+      </c>
       <c r="D69" s="48"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="50"/>
+      <c r="E69" s="49">
+        <v>15</v>
+      </c>
+      <c r="F69" s="50" t="s">
+        <v>42</v>
+      </c>
       <c r="G69" s="51"/>
-      <c r="H69" s="52"/>
+      <c r="H69" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I69" s="53"/>
       <c r="J69" s="54">
         <f>IF(AND(D68="",E68="",A68="",B68="",C68=""),"", IFERROR(IF(J67="",D2,J67),D2)+IF(E68="",0,E68)-IF(D68="",0,D68))</f>
@@ -12624,31 +12657,42 @@
       </c>
     </row>
     <row r="70" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A70" s="56"/>
-      <c r="B70" s="57"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="59"/>
+      <c r="A70" s="56">
+        <v>46181</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" s="59">
+        <v>2.8</v>
+      </c>
       <c r="E70" s="60"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="62"/>
-      <c r="H70" s="63"/>
+      <c r="F70" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I70" s="64"/>
-      <c r="J70" s="65" t="str">
+      <c r="J70" s="65">
         <f>IF(AND(D69="",E69="",A69="",B69="",C69=""),"", IFERROR(IF(J68="",D2,J68),D2)+IF(E69="",0,E69)-IF(D69="",0,D69))</f>
-        <v/>
+        <v>320.60000000000002</v>
       </c>
       <c r="K70" s="66"/>
-      <c r="L70" t="str">
+      <c r="L70">
         <f>IF(E69&gt;0,COUNTIF($E$4:E69,"&gt;0"),"")</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="M70" t="str">
         <f>IF(AND(D69&gt;0,G69="المحفظة"),COUNTIFS($D$4:D69,"&gt;"&amp;0,$G$4:G69,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N70" t="str">
+      <c r="N70">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A69)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A69)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A69&lt;&gt;""),IFERROR(MAX($N$4:N68),0)+1,"")</f>
-        <v/>
+        <v>64</v>
       </c>
       <c r="O70" t="str">
         <f>IF(AND(D69&gt;0,F69="أحد الشركاء"),COUNTIFS($D$4:D69,"&gt;"&amp;0,$F$4:F69,"أحد الشركاء"),"")</f>
@@ -12656,31 +12700,42 @@
       </c>
     </row>
     <row r="71" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A71" s="45"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="48"/>
+      <c r="A71" s="134">
+        <v>46181</v>
+      </c>
+      <c r="C71" s="135" t="s">
+        <v>220</v>
+      </c>
+      <c r="D71" s="48">
+        <v>46.75</v>
+      </c>
       <c r="E71" s="49"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="52"/>
+      <c r="F71" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H71" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I71" s="53"/>
-      <c r="J71" s="54" t="str">
-        <f>IF(AND(D70="",E70="",A70="",B70="",C70=""),"", IFERROR(IF(J69="",D2,J69),D2)+IF(E70="",0,E70)-IF(D70="",0,D70))</f>
-        <v/>
+      <c r="J71" s="54">
+        <f>IF(AND(D70="",E70="",A70="",B72="",C70=""),"", IFERROR(IF(J69="",D2,J69),D2)+IF(E70="",0,E70)-IF(D70="",0,D70))</f>
+        <v>307.8</v>
       </c>
       <c r="K71" s="55"/>
       <c r="L71" t="str">
         <f>IF(E70&gt;0,COUNTIF($E$4:E70,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M71" t="str">
+      <c r="M71">
         <f>IF(AND(D70&gt;0,G70="المحفظة"),COUNTIFS($D$4:D70,"&gt;"&amp;0,$G$4:G70,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N71" t="str">
+        <v>12</v>
+      </c>
+      <c r="N71">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A70)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A70)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A70&lt;&gt;""),IFERROR(MAX($N$4:N69),0)+1,"")</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="O71" t="str">
         <f>IF(AND(D70&gt;0,F70="أحد الشركاء"),COUNTIFS($D$4:D70,"&gt;"&amp;0,$F$4:F70,"أحد الشركاء"),"")</f>
@@ -12688,31 +12743,43 @@
       </c>
     </row>
     <row r="72" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A72" s="56"/>
-      <c r="B72" s="57"/>
-      <c r="C72" s="58"/>
+      <c r="A72" s="56">
+        <v>46182</v>
+      </c>
+      <c r="B72" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="58" t="s">
+        <v>89</v>
+      </c>
       <c r="D72" s="59"/>
-      <c r="E72" s="60"/>
-      <c r="F72" s="61"/>
+      <c r="E72" s="60">
+        <v>22.5</v>
+      </c>
+      <c r="F72" s="61" t="s">
+        <v>42</v>
+      </c>
       <c r="G72" s="62"/>
-      <c r="H72" s="63"/>
+      <c r="H72" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I72" s="64"/>
-      <c r="J72" s="65" t="str">
-        <f>IF(AND(D71="",E71="",A71="",B71="",C71=""),"", IFERROR(IF(J70="",D2,J70),D2)+IF(E71="",0,E71)-IF(D71="",0,D71))</f>
-        <v/>
+      <c r="J72" s="65" t="e">
+        <f>IF(AND(D71="",E71="",A71="",#REF!="",C71=""),"", IFERROR(IF(J70="",D2,J70),D2)+IF(E71="",0,E71)-IF(D71="",0,D71))</f>
+        <v>#REF!</v>
       </c>
       <c r="K72" s="66"/>
       <c r="L72" t="str">
         <f>IF(E71&gt;0,COUNTIF($E$4:E71,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M72" t="str">
+      <c r="M72">
         <f>IF(AND(D71&gt;0,G71="المحفظة"),COUNTIFS($D$4:D71,"&gt;"&amp;0,$G$4:G71,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N72" t="str">
+        <v>13</v>
+      </c>
+      <c r="N72">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A71)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A71)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A71&lt;&gt;""),IFERROR(MAX($N$4:N70),0)+1,"")</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="O72" t="str">
         <f>IF(AND(D71&gt;0,F71="أحد الشركاء"),COUNTIFS($D$4:D71,"&gt;"&amp;0,$F$4:F71,"أحد الشركاء"),"")</f>
@@ -12724,27 +12791,29 @@
       <c r="B73" s="46"/>
       <c r="C73" s="47"/>
       <c r="D73" s="48"/>
-      <c r="E73" s="49"/>
+      <c r="E73" s="49">
+        <v>10</v>
+      </c>
       <c r="F73" s="50"/>
       <c r="G73" s="51"/>
       <c r="H73" s="52"/>
       <c r="I73" s="53"/>
-      <c r="J73" s="54" t="str">
-        <f>IF(AND(D72="",E72="",A72="",B72="",C72=""),"", IFERROR(IF(J71="",D2,J71),D2)+IF(E72="",0,E72)-IF(D72="",0,D72))</f>
-        <v/>
+      <c r="J73" s="54" t="e">
+        <f>IF(AND(D72="",E72="",A72="",#REF!="",C72=""),"", IFERROR(IF(J71="",D2,J71),D2)+IF(E72="",0,E72)-IF(D72="",0,D72))</f>
+        <v>#REF!</v>
       </c>
       <c r="K73" s="55"/>
-      <c r="L73" t="str">
+      <c r="L73">
         <f>IF(E72&gt;0,COUNTIF($E$4:E72,"&gt;0"),"")</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="M73" t="str">
         <f>IF(AND(D72&gt;0,G72="المحفظة"),COUNTIFS($D$4:D72,"&gt;"&amp;0,$G$4:G72,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N73" t="str">
+      <c r="N73">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A72)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A72)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A72&lt;&gt;""),IFERROR(MAX($N$4:N71),0)+1,"")</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="O73" t="str">
         <f>IF(AND(D72&gt;0,F72="أحد الشركاء"),COUNTIFS($D$4:D72,"&gt;"&amp;0,$F$4:F72,"أحد الشركاء"),"")</f>
@@ -12761,14 +12830,14 @@
       <c r="G74" s="62"/>
       <c r="H74" s="63"/>
       <c r="I74" s="64"/>
-      <c r="J74" s="65" t="str">
+      <c r="J74" s="65">
         <f>IF(AND(D73="",E73="",A73="",B73="",C73=""),"", IFERROR(IF(J72="",D2,J72),D2)+IF(E73="",0,E73)-IF(D73="",0,D73))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K74" s="66"/>
-      <c r="L74" t="str">
+      <c r="L74">
         <f>IF(E73&gt;0,COUNTIF($E$4:E73,"&gt;0"),"")</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="M74" t="str">
         <f>IF(AND(D73&gt;0,G73="المحفظة"),COUNTIFS($D$4:D73,"&gt;"&amp;0,$G$4:G73,"المحفظة"),"")</f>
@@ -16912,14 +16981,14 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="150"/>
-      <c r="B204" s="151"/>
-      <c r="C204" s="152"/>
+      <c r="A204" s="152"/>
+      <c r="B204" s="153"/>
+      <c r="C204" s="154"/>
       <c r="D204" s="59"/>
       <c r="E204" s="60"/>
-      <c r="F204" s="147"/>
-      <c r="G204" s="148"/>
-      <c r="H204" s="149"/>
+      <c r="F204" s="149"/>
+      <c r="G204" s="150"/>
+      <c r="H204" s="151"/>
       <c r="I204" s="64"/>
       <c r="J204" s="65" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -16945,17 +17014,17 @@
     </row>
     <row r="205" spans="1:15" ht="15.75" customHeight="1">
       <c r="A205" s="129" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B205" s="132"/>
       <c r="C205" s="132"/>
       <c r="D205" s="67">
         <f>SUM(D4:D203)</f>
-        <v>1027.5</v>
+        <v>1077.05</v>
       </c>
       <c r="E205" s="67">
         <f>SUM(E4:E203)</f>
-        <v>534.6</v>
+        <v>582.1</v>
       </c>
       <c r="F205" s="130">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -16974,16 +17043,16 @@
     </row>
     <row r="206" spans="1:15">
       <c r="D206" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="E206" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="F206" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="E206" s="69" t="s">
+      <c r="J206" s="71" t="s">
         <v>155</v>
-      </c>
-      <c r="F206" s="70" t="s">
-        <v>156</v>
-      </c>
-      <c r="J206" s="71" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -17046,8 +17115,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A1" s="153" t="s">
-        <v>158</v>
+      <c r="A1" s="155" t="s">
+        <v>156</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -17057,15 +17126,15 @@
         <v>17</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
       <c r="A3" s="73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B3" s="73"/>
       <c r="C3" s="46"/>
@@ -17093,14 +17162,14 @@
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
       <c r="A7" s="73" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B7" s="73"/>
       <c r="C7" s="46"/>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
       <c r="A8" s="74" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B8" s="74"/>
       <c r="C8" s="57"/>
@@ -17121,70 +17190,70 @@
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1">
       <c r="A11" s="73" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B11" s="73"/>
       <c r="C11" s="46"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1">
       <c r="A12" s="74" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B12" s="74"/>
       <c r="C12" s="57"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1">
       <c r="A13" s="73" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B13" s="73"/>
       <c r="C13" s="46"/>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1">
       <c r="A14" s="74" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" s="74"/>
       <c r="C14" s="57"/>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1">
       <c r="A15" s="73" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" s="73"/>
       <c r="C15" s="46"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1">
       <c r="A16" s="74" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B16" s="74"/>
       <c r="C16" s="57"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1">
       <c r="A17" s="73" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B17" s="73"/>
       <c r="C17" s="46"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1">
       <c r="A18" s="74" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B18" s="74"/>
       <c r="C18" s="57"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1">
       <c r="A19" s="73" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B19" s="73"/>
       <c r="C19" s="46"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1">
       <c r="A20" s="74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B20" s="74"/>
       <c r="C20" s="57"/>
@@ -17208,115 +17277,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="155" t="s">
-        <v>173</v>
+      <c r="A1" s="157" t="s">
+        <v>171</v>
       </c>
       <c r="B1" s="137"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A2" s="154" t="s">
-        <v>174</v>
+      <c r="A2" s="156" t="s">
+        <v>172</v>
       </c>
       <c r="B2" s="137"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="75" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.5" customHeight="1">
       <c r="A4" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="21.75" customHeight="1">
+      <c r="A5" s="156" t="s">
         <v>177</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A5" s="154" t="s">
-        <v>179</v>
       </c>
       <c r="B5" s="137"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="76" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="19.5" customHeight="1">
       <c r="A7" s="75" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="19.5" customHeight="1">
       <c r="A8" s="76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="19.5" customHeight="1">
       <c r="A9" s="75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19.5" customHeight="1">
       <c r="A10" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="21.75" customHeight="1">
+      <c r="A11" s="156" t="s">
         <v>186</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A11" s="154" t="s">
-        <v>188</v>
       </c>
       <c r="B11" s="137"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1">
       <c r="A12" s="76" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="19.5" customHeight="1">
       <c r="A13" s="75" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="19.5" customHeight="1">
       <c r="A14" s="76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="19.5" customHeight="1">
       <c r="A15" s="75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -17350,7 +17419,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="136" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="137"/>
@@ -17365,29 +17434,29 @@
       <c r="K1" s="137"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="156"/>
+      <c r="A2" s="158"/>
       <c r="B2" s="137"/>
       <c r="C2" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="156">
+        <v>191</v>
+      </c>
+      <c r="D2" s="158">
         <v>2026</v>
       </c>
       <c r="E2" s="137"/>
       <c r="F2" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="161" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A3" s="162" t="s">
         <v>193</v>
-      </c>
-      <c r="G2" s="159" t="s">
-        <v>194</v>
-      </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-    </row>
-    <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A3" s="160" t="s">
-        <v>195</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="137"/>
@@ -17407,28 +17476,28 @@
         <v>15</v>
       </c>
       <c r="D4" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="G4" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="H4" s="79" t="s">
         <v>198</v>
-      </c>
-      <c r="G4" s="79" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="79" t="s">
-        <v>200</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="79" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K4" s="79" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.5" customHeight="1">
@@ -18036,7 +18105,7 @@
       </c>
       <c r="B18" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-013a</v>
+        <v>Inv-013A</v>
       </c>
       <c r="C18" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18220,7 +18289,7 @@
       </c>
       <c r="B22" s="82" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-18a</v>
+        <v>Inv-18A</v>
       </c>
       <c r="C22" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20332,15 +20401,15 @@
     <row r="68" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A68" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B68" s="91">
+        <v>46181</v>
+      </c>
+      <c r="B68" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="92">
+        <v>Inv-61</v>
+      </c>
+      <c r="C68" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>فل عدد 20 بقيمه 0.750</v>
       </c>
       <c r="D68" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20348,19 +20417,19 @@
       </c>
       <c r="E68" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="91">
+        <v>15</v>
+      </c>
+      <c r="F68" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>نقداً</v>
       </c>
       <c r="G68" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>0</v>
       </c>
-      <c r="H68" s="91">
+      <c r="H68" s="91" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>تم الدفع</v>
       </c>
       <c r="I68" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(64,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20376,95 +20445,95 @@
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A69" s="84" t="str">
+      <c r="A69" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B69" s="85" t="str">
+        <v>46181</v>
+      </c>
+      <c r="B69" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C69" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D69" s="87" t="str">
+        <v>حديد اسود للمحميه الصغيره الجديده</v>
+      </c>
+      <c r="D69" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E69" s="88" t="str">
+        <v>46.75</v>
+      </c>
+      <c r="E69" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F69" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G69" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H69" s="85" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I69" s="85" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I69" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J69" s="89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J69" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K69" s="85" t="str">
+        <v>307.8</v>
+      </c>
+      <c r="K69" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(65,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A70" s="90" t="str">
+      <c r="A70" s="90">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B70" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="B70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="C70" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="C70" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D70" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="D70" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E70" s="94" t="str">
+        <v>0</v>
+      </c>
+      <c r="E70" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="F70" s="91" t="str">
+        <v>10</v>
+      </c>
+      <c r="F70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="G70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="H70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I70" s="91" t="str">
+        <v>0</v>
+      </c>
+      <c r="I70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J70" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v/>
       </c>
-      <c r="K70" s="91" t="str">
+      <c r="K70" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(66,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="15" hidden="1" customHeight="1">
@@ -24332,20 +24401,20 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A155" s="157" t="s">
-        <v>202</v>
+      <c r="A155" s="159" t="s">
+        <v>200</v>
       </c>
       <c r="B155" s="137"/>
       <c r="C155" s="137"/>
       <c r="D155" s="96">
         <f>SUM(D5:D154)</f>
-        <v>1027.5</v>
+        <v>1074.25</v>
       </c>
       <c r="E155" s="96">
         <f>SUM(E5:E154)</f>
-        <v>528.6</v>
-      </c>
-      <c r="F155" s="158">
+        <v>553.6</v>
+      </c>
+      <c r="F155" s="160">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>8</v>
       </c>
@@ -24354,7 +24423,7 @@
       <c r="I155" s="97"/>
       <c r="J155" s="96">
         <f>E155-D155</f>
-        <v>-498.9</v>
+        <v>-520.65</v>
       </c>
       <c r="K155" s="97"/>
     </row>
@@ -24363,19 +24432,19 @@
       <c r="B156" s="98"/>
       <c r="C156" s="98"/>
       <c r="D156" s="68" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E156" s="69" t="s">
         <v>7</v>
       </c>
       <c r="F156" s="70" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G156" s="98"/>
       <c r="H156" s="98"/>
       <c r="I156" s="98"/>
       <c r="J156" s="71" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K156" s="98"/>
     </row>
@@ -24433,7 +24502,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="137"/>
@@ -24444,15 +24513,15 @@
       <c r="G1" s="137"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="156" t="s">
-        <v>204</v>
+      <c r="A2" s="158" t="s">
+        <v>202</v>
       </c>
       <c r="B2" s="137"/>
       <c r="C2" s="77" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="156" t="s">
-        <v>206</v>
+        <v>203</v>
+      </c>
+      <c r="D2" s="158" t="s">
+        <v>204</v>
       </c>
       <c r="E2" s="137"/>
       <c r="F2" s="77">
@@ -24460,26 +24529,26 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="160" t="s">
-        <v>207</v>
+      <c r="A3" s="162" t="s">
+        <v>205</v>
       </c>
       <c r="B3" s="137"/>
       <c r="C3" s="78">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="160" t="s">
-        <v>208</v>
+      <c r="D3" s="162" t="s">
+        <v>206</v>
       </c>
       <c r="E3" s="137"/>
       <c r="F3" s="99">
         <f>المحفظة!$C$3</f>
-        <v>308.35000000000002</v>
+        <v>286.60000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="140" t="s">
-        <v>209</v>
+      <c r="A4" s="139" t="s">
+        <v>207</v>
       </c>
       <c r="B4" s="137"/>
       <c r="C4" s="137"/>
@@ -24495,7 +24564,7 @@
       </c>
       <c r="B5" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>Inv-013a</v>
+        <v>Inv-013A</v>
       </c>
       <c r="C5" s="100" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -24573,7 +24642,7 @@
       </c>
       <c r="B8" s="12" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>Inv-18a</v>
+        <v>Inv-18A</v>
       </c>
       <c r="C8" s="102" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -25789,7 +25858,7 @@
       <c r="G54" s="17"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="140" t="s">
+      <c r="A55" s="139" t="s">
         <v>7</v>
       </c>
       <c r="B55" s="137"/>
@@ -25803,8 +25872,8 @@
       <c r="G55" s="97"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="136" t="s">
-        <v>210</v>
+      <c r="A56" s="148" t="s">
+        <v>208</v>
       </c>
       <c r="B56" s="137"/>
       <c r="C56" s="137"/>
@@ -27114,8 +27183,8 @@
       <c r="G106" s="32"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="136" t="s">
-        <v>211</v>
+      <c r="A107" s="148" t="s">
+        <v>209</v>
       </c>
       <c r="B107" s="137"/>
       <c r="C107" s="137"/>
@@ -27128,8 +27197,8 @@
       <c r="G107" s="97"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A108" s="157" t="s">
-        <v>212</v>
+      <c r="A108" s="159" t="s">
+        <v>210</v>
       </c>
       <c r="B108" s="137"/>
       <c r="C108" s="137"/>
@@ -27137,12 +27206,12 @@
         <f>E55-D107</f>
         <v>266.60000000000002</v>
       </c>
-      <c r="E108" s="161">
+      <c r="E108" s="163">
         <f>SUM(E5:E107)</f>
         <v>533.20000000000005</v>
       </c>
       <c r="F108" s="137"/>
-      <c r="G108" s="162"/>
+      <c r="G108" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76999E5-8F8D-47D4-B089-0979F972C35E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B426ED14-548D-4F7A-9BE1-640F1749EDD4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="245">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -771,6 +771,18 @@
   <si>
     <t>يونيو</t>
   </si>
+  <si>
+    <t>Inv-70</t>
+  </si>
+  <si>
+    <t>افوبياعدد 1 الحبه .0.750</t>
+  </si>
+  <si>
+    <t>Inv-71</t>
+  </si>
+  <si>
+    <t>دارسينا عدد 1 الحبه 1.500</t>
+  </si>
 </sst>
 </file>
 
@@ -1306,7 +1318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1671,20 +1683,8 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1702,6 +1702,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2065,57 +2080,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="136" t="s">
+      <c r="E2" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="137"/>
+      <c r="B3" s="144"/>
       <c r="C3" s="2">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
         <v>316.60000000000002</v>
       </c>
-      <c r="D3" s="138" t="s">
+      <c r="D3" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="3">
@@ -3759,7 +3774,7 @@
       </c>
       <c r="F59" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(55,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59">
@@ -3768,28 +3783,28 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="18" customHeight="1">
-      <c r="A60" s="10" t="str">
+      <c r="A60" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B60" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="B60" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="C60" s="12">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E60" s="14" t="str">
+      <c r="E60" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="15" t="str">
+        <v>0</v>
+      </c>
+      <c r="F60" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G60" s="16"/>
       <c r="H60" t="str">
@@ -5118,27 +5133,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="140" t="s">
+      <c r="A105" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="140"/>
-      <c r="C105" s="140"/>
-      <c r="D105" s="140"/>
+      <c r="B105" s="136"/>
+      <c r="C105" s="136"/>
+      <c r="D105" s="136"/>
       <c r="E105" s="17">
         <f>SUM(E5:E104)</f>
         <v>519.1</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="141" t="s">
+      <c r="A106" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="141"/>
-      <c r="C106" s="141"/>
-      <c r="D106" s="141"/>
-      <c r="E106" s="141"/>
-      <c r="F106" s="141"/>
-      <c r="G106" s="141"/>
+      <c r="B106" s="137"/>
+      <c r="C106" s="137"/>
+      <c r="D106" s="137"/>
+      <c r="E106" s="137"/>
+      <c r="F106" s="137"/>
+      <c r="G106" s="137"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="18">
@@ -5593,15 +5608,15 @@
     <row r="122" spans="1:8" ht="18" customHeight="1">
       <c r="A122" s="25">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(16,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B122" s="26">
+        <v>46190</v>
+      </c>
+      <c r="B122" s="26" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(16,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="27">
+        <v>Inv-70</v>
+      </c>
+      <c r="C122" s="27" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(16,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
+        <v>افوبياعدد 1 الحبه .0.750</v>
       </c>
       <c r="D122" s="28">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(16,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
@@ -5615,9 +5630,9 @@
         <v>0</v>
       </c>
       <c r="G122" s="31"/>
-      <c r="H122" t="str">
+      <c r="H122">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A122),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A122),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A122&lt;&gt;""),IFERROR(MAX($H$107:H121),0)+1,"")</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="18" customHeight="1">
@@ -8141,31 +8156,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="142" t="s">
+      <c r="A207" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="142"/>
-      <c r="C207" s="142"/>
+      <c r="B207" s="138"/>
+      <c r="C207" s="138"/>
       <c r="D207" s="32">
         <f>SUM(D107:D206)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="143" t="s">
+      <c r="A208" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="143"/>
-      <c r="C208" s="143"/>
+      <c r="B208" s="139"/>
+      <c r="C208" s="139"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
         <v>316.60000000000002</v>
       </c>
-      <c r="E208" s="144" t="s">
+      <c r="E208" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="144"/>
-      <c r="G208" s="144"/>
+      <c r="F208" s="140"/>
+      <c r="G208" s="140"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9674,17 +9689,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9710,38 +9725,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="136" t="s">
+      <c r="E2" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -13262,7 +13277,7 @@
       </c>
       <c r="E83" s="49"/>
       <c r="F83" s="50" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="G83" s="51" t="s">
         <v>43</v>
@@ -13294,18 +13309,28 @@
       </c>
     </row>
     <row r="84" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A84" s="56"/>
-      <c r="B84" s="57"/>
-      <c r="C84" s="58"/>
+      <c r="A84" s="56">
+        <v>46190</v>
+      </c>
+      <c r="B84" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="C84" s="58" t="s">
+        <v>242</v>
+      </c>
       <c r="D84" s="59"/>
       <c r="E84" s="60"/>
-      <c r="F84" s="61"/>
+      <c r="F84" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G84" s="62"/>
-      <c r="H84" s="63"/>
+      <c r="H84" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I84" s="64"/>
-      <c r="J84" s="65" t="str">
+      <c r="J84" s="65">
         <f>IF(AND(D84="",E84="",A84="",B84="",C84=""),"", IFERROR(IF(J83="",D2,J83),D2)+IF(E84="",0,E84)-IF(OR(G84="أبو اسحاق",G84="أبو آدم",G84="أبو اسحاق ",G84="أبو آدم "),0,IF(D84="",0,D84)))</f>
-        <v/>
+        <v>349.05</v>
       </c>
       <c r="K84" s="66"/>
       <c r="L84" t="str">
@@ -13316,9 +13341,9 @@
         <f>IF(AND(D83&gt;0,G83="المحفظة"),COUNTIFS($D$4:D83,"&gt;"&amp;0,$G$4:G83,"المحفظة"),"")</f>
         <v>16</v>
       </c>
-      <c r="N84" t="str">
+      <c r="N84">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A84)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A84)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A84&lt;&gt;""),IFERROR(MAX($N$4:N83),0)+1,"")</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="O84" t="str">
         <f>IF(AND(D83&gt;0,F83="أحد الشركاء"),COUNTIFS($D$4:D83,"&gt;"&amp;0,$F$4:F83,"أحد الشركاء"),"")</f>
@@ -13326,18 +13351,30 @@
       </c>
     </row>
     <row r="85" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A85" s="45"/>
-      <c r="B85" s="46"/>
-      <c r="C85" s="47"/>
+      <c r="A85" s="134">
+        <v>46190</v>
+      </c>
+      <c r="B85" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C85" s="47" t="s">
+        <v>244</v>
+      </c>
       <c r="D85" s="48"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="50"/>
+      <c r="E85" s="49">
+        <v>1.5</v>
+      </c>
+      <c r="F85" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G85" s="51"/>
-      <c r="H85" s="52"/>
+      <c r="H85" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I85" s="53"/>
-      <c r="J85" s="54" t="str">
+      <c r="J85" s="54">
         <f>IF(AND(D85="",E85="",A85="",B85="",C85=""),"", IFERROR(IF(J84="",D2,J84),D2)+IF(E85="",0,E85)-IF(OR(G85="أبو اسحاق",G85="أبو آدم",G85="أبو اسحاق ",G85="أبو آدم "),0,IF(D85="",0,D85)))</f>
-        <v/>
+        <v>350.55</v>
       </c>
       <c r="K85" s="55"/>
       <c r="L85" t="str">
@@ -13348,9 +13385,9 @@
         <f>IF(AND(D84&gt;0,G84="المحفظة"),COUNTIFS($D$4:D84,"&gt;"&amp;0,$G$4:G84,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N85" t="str">
+      <c r="N85">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A85)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A85)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A85&lt;&gt;""),IFERROR(MAX($N$4:N84),0)+1,"")</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="O85" t="str">
         <f>IF(AND(D84&gt;0,F84="أحد الشركاء"),COUNTIFS($D$4:D84,"&gt;"&amp;0,$F$4:F84,"أحد الشركاء"),"")</f>
@@ -13372,9 +13409,9 @@
         <v/>
       </c>
       <c r="K86" s="66"/>
-      <c r="L86" t="str">
+      <c r="L86">
         <f>IF(E85&gt;0,COUNTIF($E$4:E85,"&gt;0"),"")</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="M86" t="str">
         <f>IF(AND(D85&gt;0,G85="المحفظة"),COUNTIFS($D$4:D85,"&gt;"&amp;0,$G$4:G85,"المحفظة"),"")</f>
@@ -17134,14 +17171,14 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="145"/>
-      <c r="B204" s="145"/>
-      <c r="C204" s="145"/>
+      <c r="A204" s="146"/>
+      <c r="B204" s="146"/>
+      <c r="C204" s="146"/>
       <c r="D204" s="59"/>
       <c r="E204" s="60"/>
-      <c r="F204" s="146"/>
-      <c r="G204" s="146"/>
-      <c r="H204" s="146"/>
+      <c r="F204" s="147"/>
+      <c r="G204" s="147"/>
+      <c r="H204" s="147"/>
       <c r="I204" s="64"/>
       <c r="J204" s="65" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -17177,7 +17214,7 @@
       </c>
       <c r="E205" s="70">
         <f>SUM(E4:E203)</f>
-        <v>652.1</v>
+        <v>653.6</v>
       </c>
       <c r="F205" s="71">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -17268,11 +17305,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -17430,16 +17467,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="148"/>
+      <c r="B1" s="149"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="150" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="149"/>
+      <c r="B2" s="150"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -17458,10 +17495,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="150" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="149"/>
+      <c r="B5" s="150"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="80" t="s">
@@ -17504,10 +17541,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A11" s="149" t="s">
+      <c r="A11" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="149"/>
+      <c r="B11" s="150"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1">
       <c r="A12" s="80" t="s">
@@ -17572,47 +17609,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="152"/>
-      <c r="B2" s="152"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="152">
+      <c r="D2" s="153">
         <v>2026</v>
       </c>
-      <c r="E2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="154" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="153"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A3" s="154" t="s">
+      <c r="A3" s="155" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="154"/>
-      <c r="C3" s="154"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
       <c r="D3" s="82">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -18826,7 +18863,7 @@
       </c>
       <c r="F30" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G30" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18850,95 +18887,95 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A31" s="56" t="str">
+      <c r="A31" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46190</v>
       </c>
       <c r="B31" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-70</v>
       </c>
       <c r="C31" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="59" t="str">
+        <v>افوبياعدد 1 الحبه .0.750</v>
+      </c>
+      <c r="D31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="85" t="str">
+        <v>0</v>
+      </c>
+      <c r="E31" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F31" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="84" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G31" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H31" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="84" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I31" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="65" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="84" t="str">
+        <v>349.05</v>
+      </c>
+      <c r="K31" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A32" s="45" t="str">
+      <c r="A32" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46190</v>
       </c>
       <c r="B32" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-71</v>
       </c>
       <c r="C32" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="48" t="str">
+        <v>دارسينا عدد 1 الحبه 1.500</v>
+      </c>
+      <c r="D32" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="87" t="str">
+        <v>0</v>
+      </c>
+      <c r="E32" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="F32" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="86" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G32" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H32" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="86" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I32" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J32" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="86" t="str">
+        <v>350.55</v>
+      </c>
+      <c r="K32" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
@@ -24554,29 +24591,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A155" s="150" t="s">
+      <c r="A155" s="151" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="150"/>
-      <c r="C155" s="150"/>
+      <c r="B155" s="151"/>
+      <c r="C155" s="151"/>
       <c r="D155" s="100">
         <f>SUM(D5:D154)</f>
         <v>212.8</v>
       </c>
       <c r="E155" s="100">
         <f>SUM(E5:E154)</f>
-        <v>150</v>
-      </c>
-      <c r="F155" s="151">
+        <v>151.5</v>
+      </c>
+      <c r="F155" s="152">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="151"/>
-      <c r="H155" s="151"/>
+      <c r="G155" s="152"/>
+      <c r="H155" s="152"/>
       <c r="I155" s="101"/>
       <c r="J155" s="100">
         <f>E155-D155</f>
-        <v>-62.800000000000011</v>
+        <v>-61.300000000000011</v>
       </c>
       <c r="K155" s="101"/>
     </row>
@@ -24655,60 +24692,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="153" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="152" t="s">
+      <c r="D2" s="153" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="81">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="154" t="s">
+      <c r="A3" s="155" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="154"/>
+      <c r="B3" s="155"/>
       <c r="C3" s="82">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="154" t="s">
+      <c r="D3" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="154"/>
+      <c r="E3" s="155"/>
       <c r="F3" s="103">
         <f>المحفظة!$C$3</f>
         <v>316.60000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="3">
@@ -25148,7 +25185,7 @@
       </c>
       <c r="F21" s="4" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(17,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G21" s="105"/>
     </row>
@@ -26011,12 +26048,12 @@
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="140" t="s">
+      <c r="A55" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="140"/>
-      <c r="C55" s="140"/>
-      <c r="D55" s="140"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="136"/>
       <c r="E55" s="118">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>66.5</v>
@@ -26025,15 +26062,15 @@
       <c r="G55" s="101"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="142" t="s">
+      <c r="A56" s="138" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="142"/>
-      <c r="D56" s="142"/>
-      <c r="E56" s="142"/>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="138"/>
+      <c r="E56" s="138"/>
+      <c r="F56" s="138"/>
+      <c r="G56" s="138"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="18">
@@ -26244,28 +26281,28 @@
       <c r="G64" s="31"/>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
-      <c r="A65" s="123" t="str">
+      <c r="A65" s="123">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$A$107:$A$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>46190</v>
       </c>
       <c r="B65" s="124" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$B$107:$B$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>Inv-70</v>
       </c>
       <c r="C65" s="125" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$C$107:$C$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="126" t="str">
+        <v>افوبياعدد 1 الحبه .0.750</v>
+      </c>
+      <c r="D65" s="126">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$D$107:$D$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E65" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="F65" s="124" t="str">
+      <c r="F65" s="124">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G65" s="24"/>
     </row>
@@ -27336,11 +27373,11 @@
       <c r="G106" s="31"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="142" t="s">
+      <c r="A107" s="138" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="142"/>
-      <c r="C107" s="142"/>
+      <c r="B107" s="138"/>
+      <c r="C107" s="138"/>
       <c r="D107" s="133">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>62</v>
@@ -27350,35 +27387,35 @@
       <c r="G107" s="101"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A108" s="150" t="s">
+      <c r="A108" s="151" t="s">
         <v>229</v>
       </c>
-      <c r="B108" s="150"/>
-      <c r="C108" s="150"/>
+      <c r="B108" s="151"/>
+      <c r="C108" s="151"/>
       <c r="D108" s="100">
         <f>E55-D107</f>
         <v>4.5</v>
       </c>
-      <c r="E108" s="155">
+      <c r="E108" s="156">
         <f>SUM(E5:E107)</f>
         <v>133</v>
       </c>
-      <c r="F108" s="155"/>
-      <c r="G108" s="155"/>
+      <c r="F108" s="156"/>
+      <c r="G108" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="E108:G108"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B426ED14-548D-4F7A-9BE1-640F1749EDD4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAAC48C-C889-41E4-A3D4-8FCECB4DEDAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="249">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -783,6 +783,18 @@
   <si>
     <t>دارسينا عدد 1 الحبه 1.500</t>
   </si>
+  <si>
+    <t>Inv-72</t>
+  </si>
+  <si>
+    <t>Inv-73</t>
+  </si>
+  <si>
+    <t>فل عدد 1 الحبه 0.750</t>
+  </si>
+  <si>
+    <t>ودليه عدد 3 الحبه 1</t>
+  </si>
 </sst>
 </file>
 
@@ -1318,7 +1330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1686,6 +1698,24 @@
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1702,21 +1732,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2080,57 +2095,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="143" t="s">
+      <c r="E2" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="144" t="s">
+      <c r="A3" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="144"/>
+      <c r="B3" s="139"/>
       <c r="C3" s="2">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>316.60000000000002</v>
-      </c>
-      <c r="D3" s="145" t="s">
+        <v>321.85000000000002</v>
+      </c>
+      <c r="D3" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="135" t="s">
+      <c r="A4" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="3">
@@ -3785,116 +3800,116 @@
     <row r="60" spans="1:8" ht="18" customHeight="1">
       <c r="A60" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B60" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B60" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C60" s="12">
+        <v>Inv-71</v>
+      </c>
+      <c r="C60" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>دارسينا عدد 1 الحبه 1.500</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>6</v>
       </c>
       <c r="E60" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="F60" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(56,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>أون لاين</v>
       </c>
       <c r="G60" s="16"/>
-      <c r="H60" t="str">
+      <c r="H60">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A60),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A60),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A60&lt;&gt;""),IFERROR(MAX($H$5:H59),0)+1,"")</f>
-        <v/>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="18" customHeight="1">
-      <c r="A61" s="3" t="str">
+      <c r="A61" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(57,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B61" s="4" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(57,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-72</v>
       </c>
       <c r="C61" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(57,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>فل عدد 1 الحبه 0.750</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E61" s="7" t="str">
+      <c r="E61" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(57,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="F61" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(57,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G61" s="9"/>
-      <c r="H61" t="str">
+      <c r="H61">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A61),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A61),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A61&lt;&gt;""),IFERROR(MAX($H$5:H60),0)+1,"")</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="18" customHeight="1">
-      <c r="A62" s="10" t="str">
+      <c r="A62" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(58,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B62" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(58,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-73</v>
       </c>
       <c r="C62" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(58,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>ودليه عدد 3 الحبه 1</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E62" s="14" t="str">
+      <c r="E62" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(58,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F62" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(58,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G62" s="16"/>
-      <c r="H62" t="str">
+      <c r="H62">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A62),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A62),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A62&lt;&gt;""),IFERROR(MAX($H$5:H61),0)+1,"")</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="18" customHeight="1">
-      <c r="A63" s="3" t="str">
+      <c r="A63" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B63" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="B63" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C63" s="5" t="str">
+        <v>0</v>
+      </c>
+      <c r="C63" s="5">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E63" s="7" t="str">
+      <c r="E63" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F63" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" t="str">
@@ -5133,27 +5148,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="136" t="s">
+      <c r="A105" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="136"/>
-      <c r="C105" s="136"/>
-      <c r="D105" s="136"/>
+      <c r="B105" s="142"/>
+      <c r="C105" s="142"/>
+      <c r="D105" s="142"/>
       <c r="E105" s="17">
         <f>SUM(E5:E104)</f>
-        <v>519.1</v>
+        <v>524.35</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="137" t="s">
+      <c r="A106" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="137"/>
-      <c r="C106" s="137"/>
-      <c r="D106" s="137"/>
-      <c r="E106" s="137"/>
-      <c r="F106" s="137"/>
-      <c r="G106" s="137"/>
+      <c r="B106" s="143"/>
+      <c r="C106" s="143"/>
+      <c r="D106" s="143"/>
+      <c r="E106" s="143"/>
+      <c r="F106" s="143"/>
+      <c r="G106" s="143"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="18">
@@ -8156,31 +8171,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="138" t="s">
+      <c r="A207" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="138"/>
-      <c r="C207" s="138"/>
+      <c r="B207" s="144"/>
+      <c r="C207" s="144"/>
       <c r="D207" s="32">
         <f>SUM(D107:D206)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="139" t="s">
+      <c r="A208" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="139"/>
-      <c r="C208" s="139"/>
+      <c r="B208" s="145"/>
+      <c r="C208" s="145"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>316.60000000000002</v>
-      </c>
-      <c r="E208" s="140" t="s">
+        <v>321.85000000000002</v>
+      </c>
+      <c r="E208" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="140"/>
-      <c r="G208" s="140"/>
+      <c r="F208" s="146"/>
+      <c r="G208" s="146"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9689,17 +9704,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9725,38 +9740,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="143" t="s">
+      <c r="E2" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -13319,7 +13334,9 @@
         <v>242</v>
       </c>
       <c r="D84" s="59"/>
-      <c r="E84" s="60"/>
+      <c r="E84" s="60">
+        <v>0.75</v>
+      </c>
       <c r="F84" s="61" t="s">
         <v>233</v>
       </c>
@@ -13330,7 +13347,7 @@
       <c r="I84" s="64"/>
       <c r="J84" s="65">
         <f>IF(AND(D84="",E84="",A84="",B84="",C84=""),"", IFERROR(IF(J83="",D2,J83),D2)+IF(E84="",0,E84)-IF(OR(G84="أبو اسحاق",G84="أبو آدم",G84="أبو اسحاق ",G84="أبو آدم "),0,IF(D84="",0,D84)))</f>
-        <v>349.05</v>
+        <v>349.8</v>
       </c>
       <c r="K84" s="66"/>
       <c r="L84" t="str">
@@ -13374,12 +13391,12 @@
       <c r="I85" s="53"/>
       <c r="J85" s="54">
         <f>IF(AND(D85="",E85="",A85="",B85="",C85=""),"", IFERROR(IF(J84="",D2,J84),D2)+IF(E85="",0,E85)-IF(OR(G85="أبو اسحاق",G85="أبو آدم",G85="أبو اسحاق ",G85="أبو آدم "),0,IF(D85="",0,D85)))</f>
-        <v>350.55</v>
+        <v>351.3</v>
       </c>
       <c r="K85" s="55"/>
-      <c r="L85" t="str">
+      <c r="L85">
         <f>IF(E84&gt;0,COUNTIF($E$4:E84,"&gt;0"),"")</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="M85" t="str">
         <f>IF(AND(D84&gt;0,G84="المحفظة"),COUNTIFS($D$4:D84,"&gt;"&amp;0,$G$4:G84,"المحفظة"),"")</f>
@@ -13395,31 +13412,43 @@
       </c>
     </row>
     <row r="86" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A86" s="56"/>
-      <c r="B86" s="57"/>
-      <c r="C86" s="58"/>
+      <c r="A86" s="56">
+        <v>46191</v>
+      </c>
+      <c r="B86" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="C86" s="58" t="s">
+        <v>247</v>
+      </c>
       <c r="D86" s="59"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="61"/>
+      <c r="E86" s="60">
+        <v>0.75</v>
+      </c>
+      <c r="F86" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G86" s="62"/>
-      <c r="H86" s="63"/>
+      <c r="H86" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I86" s="64"/>
-      <c r="J86" s="65" t="str">
+      <c r="J86" s="65">
         <f>IF(AND(D86="",E86="",A86="",B86="",C86=""),"", IFERROR(IF(J85="",D2,J85),D2)+IF(E86="",0,E86)-IF(OR(G86="أبو اسحاق",G86="أبو آدم",G86="أبو اسحاق ",G86="أبو آدم "),0,IF(D86="",0,D86)))</f>
-        <v/>
+        <v>352.05</v>
       </c>
       <c r="K86" s="66"/>
       <c r="L86">
         <f>IF(E85&gt;0,COUNTIF($E$4:E85,"&gt;0"),"")</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M86" t="str">
         <f>IF(AND(D85&gt;0,G85="المحفظة"),COUNTIFS($D$4:D85,"&gt;"&amp;0,$G$4:G85,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N86" t="str">
+      <c r="N86">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A86)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A86)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A86&lt;&gt;""),IFERROR(MAX($N$4:N85),0)+1,"")</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="O86" t="str">
         <f>IF(AND(D85&gt;0,F85="أحد الشركاء"),COUNTIFS($D$4:D85,"&gt;"&amp;0,$F$4:F85,"أحد الشركاء"),"")</f>
@@ -13427,31 +13456,43 @@
       </c>
     </row>
     <row r="87" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A87" s="45"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="47"/>
+      <c r="A87" s="135">
+        <v>46191</v>
+      </c>
+      <c r="B87" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="C87" s="47" t="s">
+        <v>248</v>
+      </c>
       <c r="D87" s="48"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="50"/>
+      <c r="E87" s="49">
+        <v>3</v>
+      </c>
+      <c r="F87" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G87" s="51"/>
-      <c r="H87" s="52"/>
+      <c r="H87" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I87" s="53"/>
-      <c r="J87" s="54" t="str">
+      <c r="J87" s="54">
         <f>IF(AND(D87="",E87="",A87="",B87="",C87=""),"", IFERROR(IF(J86="",D2,J86),D2)+IF(E87="",0,E87)-IF(OR(G87="أبو اسحاق",G87="أبو آدم",G87="أبو اسحاق ",G87="أبو آدم "),0,IF(D87="",0,D87)))</f>
-        <v/>
+        <v>355.05</v>
       </c>
       <c r="K87" s="55"/>
-      <c r="L87" t="str">
+      <c r="L87">
         <f>IF(E86&gt;0,COUNTIF($E$4:E86,"&gt;0"),"")</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="M87" t="str">
         <f>IF(AND(D86&gt;0,G86="المحفظة"),COUNTIFS($D$4:D86,"&gt;"&amp;0,$G$4:G86,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N87" t="str">
+      <c r="N87">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A87)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A87)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A87&lt;&gt;""),IFERROR(MAX($N$4:N86),0)+1,"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="O87" t="str">
         <f>IF(AND(D86&gt;0,F86="أحد الشركاء"),COUNTIFS($D$4:D86,"&gt;"&amp;0,$F$4:F86,"أحد الشركاء"),"")</f>
@@ -13473,9 +13514,9 @@
         <v/>
       </c>
       <c r="K88" s="66"/>
-      <c r="L88" t="str">
+      <c r="L88">
         <f>IF(E87&gt;0,COUNTIF($E$4:E87,"&gt;0"),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="M88" t="str">
         <f>IF(AND(D87&gt;0,G87="المحفظة"),COUNTIFS($D$4:D87,"&gt;"&amp;0,$G$4:G87,"المحفظة"),"")</f>
@@ -17171,14 +17212,14 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="146"/>
-      <c r="B204" s="146"/>
-      <c r="C204" s="146"/>
+      <c r="A204" s="147"/>
+      <c r="B204" s="147"/>
+      <c r="C204" s="147"/>
       <c r="D204" s="59"/>
       <c r="E204" s="60"/>
-      <c r="F204" s="147"/>
-      <c r="G204" s="147"/>
-      <c r="H204" s="147"/>
+      <c r="F204" s="148"/>
+      <c r="G204" s="148"/>
+      <c r="H204" s="148"/>
       <c r="I204" s="64"/>
       <c r="J204" s="65" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -17214,7 +17255,7 @@
       </c>
       <c r="E205" s="70">
         <f>SUM(E4:E203)</f>
-        <v>653.6</v>
+        <v>658.1</v>
       </c>
       <c r="F205" s="71">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -17305,11 +17346,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -17467,16 +17508,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="150" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="149"/>
+      <c r="B1" s="150"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="151" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="150"/>
+      <c r="B2" s="151"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -17495,10 +17536,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="151" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="150"/>
+      <c r="B5" s="151"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="80" t="s">
@@ -17541,10 +17582,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A11" s="150" t="s">
+      <c r="A11" s="151" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="150"/>
+      <c r="B11" s="151"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1">
       <c r="A12" s="80" t="s">
@@ -17609,47 +17650,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="153"/>
-      <c r="B2" s="153"/>
+      <c r="A2" s="154"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="153">
+      <c r="D2" s="154">
         <v>2026</v>
       </c>
-      <c r="E2" s="153"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="154" t="s">
+      <c r="G2" s="155" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="156" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
       <c r="D3" s="82">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -18905,7 +18946,7 @@
       </c>
       <c r="E31" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F31" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18925,7 +18966,7 @@
       </c>
       <c r="J31" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>349.05</v>
+        <v>349.8</v>
       </c>
       <c r="K31" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18971,7 +19012,7 @@
       </c>
       <c r="J32" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>350.55</v>
+        <v>351.3</v>
       </c>
       <c r="K32" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -18979,95 +19020,95 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A33" s="56" t="str">
+      <c r="A33" s="56">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B33" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-72</v>
       </c>
       <c r="C33" s="58" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="59" t="str">
+        <v>فل عدد 1 الحبه 0.750</v>
+      </c>
+      <c r="D33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="85" t="str">
+        <v>0</v>
+      </c>
+      <c r="E33" s="85">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="F33" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="84" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G33" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H33" s="84" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="84" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I33" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="65" t="str">
+        <v>0</v>
+      </c>
+      <c r="J33" s="65">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="84" t="str">
+        <v>352.05</v>
+      </c>
+      <c r="K33" s="84">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A34" s="45" t="str">
+      <c r="A34" s="45">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B34" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-73</v>
       </c>
       <c r="C34" s="47" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="48" t="str">
+        <v>ودليه عدد 3 الحبه 1</v>
+      </c>
+      <c r="D34" s="48">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="87" t="str">
+        <v>0</v>
+      </c>
+      <c r="E34" s="87">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F34" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="86" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G34" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H34" s="86" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="86" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I34" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J34" s="54">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="86" t="str">
+        <v>355.05</v>
+      </c>
+      <c r="K34" s="86">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
@@ -24591,29 +24632,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A155" s="151" t="s">
+      <c r="A155" s="152" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="151"/>
-      <c r="C155" s="151"/>
+      <c r="B155" s="152"/>
+      <c r="C155" s="152"/>
       <c r="D155" s="100">
         <f>SUM(D5:D154)</f>
         <v>212.8</v>
       </c>
       <c r="E155" s="100">
         <f>SUM(E5:E154)</f>
-        <v>151.5</v>
-      </c>
-      <c r="F155" s="152">
+        <v>156</v>
+      </c>
+      <c r="F155" s="153">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="152"/>
-      <c r="H155" s="152"/>
+      <c r="G155" s="153"/>
+      <c r="H155" s="153"/>
       <c r="I155" s="101"/>
       <c r="J155" s="100">
         <f>E155-D155</f>
-        <v>-61.300000000000011</v>
+        <v>-56.800000000000011</v>
       </c>
       <c r="K155" s="101"/>
     </row>
@@ -24692,60 +24733,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="153" t="s">
+      <c r="D2" s="154" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="153"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="81">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="156" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="155"/>
+      <c r="B3" s="156"/>
       <c r="C3" s="82">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="155" t="s">
+      <c r="D3" s="156" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="155"/>
+      <c r="E3" s="156"/>
       <c r="F3" s="103">
         <f>المحفظة!$C$3</f>
-        <v>316.60000000000002</v>
+        <v>321.85000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="142" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="136"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="3">
@@ -25190,80 +25231,80 @@
       <c r="G21" s="105"/>
     </row>
     <row r="22" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A22" s="10" t="str">
+      <c r="A22" s="10">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46190</v>
       </c>
       <c r="B22" s="11" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-71</v>
       </c>
       <c r="C22" s="106" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>دارسينا عدد 1 الحبه 1.500</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="14" t="str">
+      <c r="E22" s="14">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="F22" s="11" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G22" s="107"/>
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A23" s="3" t="str">
+      <c r="A23" s="3">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B23" s="4" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-72</v>
       </c>
       <c r="C23" s="104" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>فل عدد 1 الحبه 0.750</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="7" t="str">
+      <c r="E23" s="7">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="F23" s="4" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G23" s="105"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
-      <c r="A24" s="108" t="str">
+      <c r="A24" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46191</v>
       </c>
       <c r="B24" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-73</v>
       </c>
       <c r="C24" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>ودليه عدد 3 الحبه 1</v>
       </c>
       <c r="D24" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="112" t="str">
+      <c r="E24" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F24" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G24" s="16"/>
     </row>
@@ -26048,29 +26089,29 @@
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="136" t="s">
+      <c r="A55" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="136"/>
-      <c r="C55" s="136"/>
-      <c r="D55" s="136"/>
+      <c r="B55" s="142"/>
+      <c r="C55" s="142"/>
+      <c r="D55" s="142"/>
       <c r="E55" s="118">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
-        <v>66.5</v>
+        <v>71.75</v>
       </c>
       <c r="F55" s="101"/>
       <c r="G55" s="101"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="138" t="s">
+      <c r="A56" s="144" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
-      <c r="D56" s="138"/>
-      <c r="E56" s="138"/>
-      <c r="F56" s="138"/>
-      <c r="G56" s="138"/>
+      <c r="B56" s="144"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="144"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="18">
@@ -27373,11 +27414,11 @@
       <c r="G106" s="31"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="138" t="s">
+      <c r="A107" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="138"/>
-      <c r="C107" s="138"/>
+      <c r="B107" s="144"/>
+      <c r="C107" s="144"/>
       <c r="D107" s="133">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>62</v>
@@ -27387,35 +27428,35 @@
       <c r="G107" s="101"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A108" s="151" t="s">
+      <c r="A108" s="152" t="s">
         <v>229</v>
       </c>
-      <c r="B108" s="151"/>
-      <c r="C108" s="151"/>
+      <c r="B108" s="152"/>
+      <c r="C108" s="152"/>
       <c r="D108" s="100">
         <f>E55-D107</f>
-        <v>4.5</v>
-      </c>
-      <c r="E108" s="156">
+        <v>9.75</v>
+      </c>
+      <c r="E108" s="157">
         <f>SUM(E5:E107)</f>
-        <v>133</v>
-      </c>
-      <c r="F108" s="156"/>
-      <c r="G108" s="156"/>
+        <v>143.5</v>
+      </c>
+      <c r="F108" s="157"/>
+      <c r="G108" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="E108:G108"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAAC48C-C889-41E4-A3D4-8FCECB4DEDAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9575711-9FD1-4EAA-8554-F141498771B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="254">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -795,6 +795,21 @@
   <si>
     <t>ودليه عدد 3 الحبه 1</t>
   </si>
+  <si>
+    <t>Inv-74</t>
+  </si>
+  <si>
+    <t>Inv-75</t>
+  </si>
+  <si>
+    <t>ربل عدد 11 الحبه 2</t>
+  </si>
+  <si>
+    <t>شوفليرا عدد6 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>nbk 18-18-18</t>
+  </si>
 </sst>
 </file>
 
@@ -1330,7 +1345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1701,20 +1716,8 @@
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1732,6 +1735,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2095,57 +2113,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="139"/>
+      <c r="B3" s="146"/>
       <c r="C3" s="2">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>321.85000000000002</v>
-      </c>
-      <c r="D3" s="140" t="s">
+        <v>352.85</v>
+      </c>
+      <c r="D3" s="147" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="141" t="s">
+      <c r="A4" s="137" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="3">
@@ -3890,91 +3908,91 @@
     <row r="63" spans="1:8" ht="18" customHeight="1">
       <c r="A63" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B63" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B63" s="4" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C63" s="5">
+        <v>Inv-74</v>
+      </c>
+      <c r="C63" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>ربل عدد 11 الحبه 2</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E63" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F63" s="8">
+        <v>22</v>
+      </c>
+      <c r="F63" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(59,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>أون لاين</v>
       </c>
       <c r="G63" s="9"/>
-      <c r="H63" t="str">
+      <c r="H63">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A63),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A63),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A63&lt;&gt;""),IFERROR(MAX($H$5:H62),0)+1,"")</f>
-        <v/>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="18" customHeight="1">
-      <c r="A64" s="10" t="str">
+      <c r="A64" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(60,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46199</v>
       </c>
       <c r="B64" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(60,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-75</v>
       </c>
       <c r="C64" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(60,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>شوفليرا عدد6 الحبه 1.500</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E64" s="14" t="str">
+      <c r="E64" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(60,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F64" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(60,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G64" s="16"/>
-      <c r="H64" t="str">
+      <c r="H64">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A64),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A64),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A64&lt;&gt;""),IFERROR(MAX($H$5:H63),0)+1,"")</f>
-        <v/>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="18" customHeight="1">
-      <c r="A65" s="3" t="str">
+      <c r="A65" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(61,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B65" s="4" t="str">
+        <v>46197</v>
+      </c>
+      <c r="B65" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(61,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C65" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(61,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>nbk 18-18-18</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E65" s="7" t="str">
+      <c r="E65" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(61,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F65" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(61,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G65" s="9"/>
-      <c r="H65" t="str">
+      <c r="H65">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A65),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A65),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A65&lt;&gt;""),IFERROR(MAX($H$5:H64),0)+1,"")</f>
-        <v/>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="18" customHeight="1">
@@ -5148,27 +5166,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="142" t="s">
+      <c r="A105" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="142"/>
-      <c r="C105" s="142"/>
-      <c r="D105" s="142"/>
+      <c r="B105" s="138"/>
+      <c r="C105" s="138"/>
+      <c r="D105" s="138"/>
       <c r="E105" s="17">
         <f>SUM(E5:E104)</f>
-        <v>524.35</v>
+        <v>555.35</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="143" t="s">
+      <c r="A106" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="143"/>
-      <c r="C106" s="143"/>
-      <c r="D106" s="143"/>
-      <c r="E106" s="143"/>
-      <c r="F106" s="143"/>
-      <c r="G106" s="143"/>
+      <c r="B106" s="139"/>
+      <c r="C106" s="139"/>
+      <c r="D106" s="139"/>
+      <c r="E106" s="139"/>
+      <c r="F106" s="139"/>
+      <c r="G106" s="139"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="18">
@@ -5651,28 +5669,28 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="18" customHeight="1">
-      <c r="A123" s="18" t="str">
+      <c r="A123" s="18">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B123" s="19" t="str">
+        <v>0</v>
+      </c>
+      <c r="B123" s="19">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C123" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="C123" s="20">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D123" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="D123" s="21">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E123" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F123" s="23" t="str">
+      <c r="F123" s="23">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G123" s="24"/>
       <c r="H123" t="str">
@@ -8171,31 +8189,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="144" t="s">
+      <c r="A207" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="144"/>
-      <c r="C207" s="144"/>
+      <c r="B207" s="140"/>
+      <c r="C207" s="140"/>
       <c r="D207" s="32">
         <f>SUM(D107:D206)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="145" t="s">
+      <c r="A208" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="145"/>
-      <c r="C208" s="145"/>
+      <c r="B208" s="141"/>
+      <c r="C208" s="141"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>321.85000000000002</v>
-      </c>
-      <c r="E208" s="146" t="s">
+        <v>352.85</v>
+      </c>
+      <c r="E208" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="146"/>
-      <c r="G208" s="146"/>
+      <c r="F208" s="142"/>
+      <c r="G208" s="142"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9704,17 +9722,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9740,38 +9758,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -13500,18 +13518,30 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A88" s="56"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="58"/>
+      <c r="A88" s="56">
+        <v>46199</v>
+      </c>
+      <c r="B88" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="C88" s="58" t="s">
+        <v>251</v>
+      </c>
       <c r="D88" s="59"/>
-      <c r="E88" s="60"/>
-      <c r="F88" s="61"/>
+      <c r="E88" s="60">
+        <v>22</v>
+      </c>
+      <c r="F88" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G88" s="62"/>
-      <c r="H88" s="63"/>
+      <c r="H88" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I88" s="64"/>
-      <c r="J88" s="65" t="str">
+      <c r="J88" s="65">
         <f>IF(AND(D88="",E88="",A88="",B88="",C88=""),"", IFERROR(IF(J87="",D2,J87),D2)+IF(E88="",0,E88)-IF(OR(G88="أبو اسحاق",G88="أبو آدم",G88="أبو اسحاق ",G88="أبو آدم "),0,IF(D88="",0,D88)))</f>
-        <v/>
+        <v>377.05</v>
       </c>
       <c r="K88" s="66"/>
       <c r="L88">
@@ -13522,9 +13552,9 @@
         <f>IF(AND(D87&gt;0,G87="المحفظة"),COUNTIFS($D$4:D87,"&gt;"&amp;0,$G$4:G87,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N88" t="str">
+      <c r="N88">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A88)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A88)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A88&lt;&gt;""),IFERROR(MAX($N$4:N87),0)+1,"")</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="O88" t="str">
         <f>IF(AND(D87&gt;0,F87="أحد الشركاء"),COUNTIFS($D$4:D87,"&gt;"&amp;0,$F$4:F87,"أحد الشركاء"),"")</f>
@@ -13532,31 +13562,43 @@
       </c>
     </row>
     <row r="89" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A89" s="45"/>
-      <c r="B89" s="46"/>
-      <c r="C89" s="47"/>
+      <c r="A89" s="136">
+        <v>46199</v>
+      </c>
+      <c r="B89" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="C89" s="47" t="s">
+        <v>252</v>
+      </c>
       <c r="D89" s="48"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="50"/>
+      <c r="E89" s="49">
+        <v>9</v>
+      </c>
+      <c r="F89" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G89" s="51"/>
-      <c r="H89" s="52"/>
+      <c r="H89" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I89" s="53"/>
-      <c r="J89" s="54" t="str">
+      <c r="J89" s="54">
         <f>IF(AND(D89="",E89="",A89="",B89="",C89=""),"", IFERROR(IF(J88="",D2,J88),D2)+IF(E89="",0,E89)-IF(OR(G89="أبو اسحاق",G89="أبو آدم",G89="أبو اسحاق ",G89="أبو آدم "),0,IF(D89="",0,D89)))</f>
-        <v/>
+        <v>386.05</v>
       </c>
       <c r="K89" s="55"/>
-      <c r="L89" t="str">
+      <c r="L89">
         <f>IF(E88&gt;0,COUNTIF($E$4:E88,"&gt;0"),"")</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="M89" t="str">
         <f>IF(AND(D88&gt;0,G88="المحفظة"),COUNTIFS($D$4:D88,"&gt;"&amp;0,$G$4:G88,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N89" t="str">
+      <c r="N89">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A89)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A89)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A89&lt;&gt;""),IFERROR(MAX($N$4:N88),0)+1,"")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="O89" t="str">
         <f>IF(AND(D88&gt;0,F88="أحد الشركاء"),COUNTIFS($D$4:D88,"&gt;"&amp;0,$F$4:F88,"أحد الشركاء"),"")</f>
@@ -13564,31 +13606,43 @@
       </c>
     </row>
     <row r="90" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A90" s="56"/>
+      <c r="A90" s="56">
+        <v>46197</v>
+      </c>
       <c r="B90" s="57"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="59"/>
+      <c r="C90" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" s="59">
+        <v>12</v>
+      </c>
       <c r="E90" s="60"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="62"/>
-      <c r="H90" s="63"/>
+      <c r="F90" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G90" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I90" s="64"/>
-      <c r="J90" s="65" t="str">
+      <c r="J90" s="65">
         <f>IF(AND(D90="",E90="",A90="",B90="",C90=""),"", IFERROR(IF(J89="",D2,J89),D2)+IF(E90="",0,E90)-IF(OR(G90="أبو اسحاق",G90="أبو آدم",G90="أبو اسحاق ",G90="أبو آدم "),0,IF(D90="",0,D90)))</f>
-        <v/>
+        <v>374.05</v>
       </c>
       <c r="K90" s="66"/>
-      <c r="L90" t="str">
+      <c r="L90">
         <f>IF(E89&gt;0,COUNTIF($E$4:E89,"&gt;0"),"")</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="M90" t="str">
         <f>IF(AND(D89&gt;0,G89="المحفظة"),COUNTIFS($D$4:D89,"&gt;"&amp;0,$G$4:G89,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N90" t="str">
+      <c r="N90">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A90)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A90)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A90&lt;&gt;""),IFERROR(MAX($N$4:N89),0)+1,"")</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="O90" t="str">
         <f>IF(AND(D89&gt;0,F89="أحد الشركاء"),COUNTIFS($D$4:D89,"&gt;"&amp;0,$F$4:F89,"أحد الشركاء"),"")</f>
@@ -13614,9 +13668,9 @@
         <f>IF(E90&gt;0,COUNTIF($E$4:E90,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M91" t="str">
+      <c r="M91">
         <f>IF(AND(D90&gt;0,G90="المحفظة"),COUNTIFS($D$4:D90,"&gt;"&amp;0,$G$4:G90,"المحفظة"),"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="N91" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A91)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A91)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A91&lt;&gt;""),IFERROR(MAX($N$4:N90),0)+1,"")</f>
@@ -17212,14 +17266,14 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="147"/>
-      <c r="B204" s="147"/>
-      <c r="C204" s="147"/>
+      <c r="A204" s="148"/>
+      <c r="B204" s="148"/>
+      <c r="C204" s="148"/>
       <c r="D204" s="59"/>
       <c r="E204" s="60"/>
-      <c r="F204" s="148"/>
-      <c r="G204" s="148"/>
-      <c r="H204" s="148"/>
+      <c r="F204" s="149"/>
+      <c r="G204" s="149"/>
+      <c r="H204" s="149"/>
       <c r="I204" s="64"/>
       <c r="J204" s="65" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -17251,11 +17305,11 @@
       <c r="C205" s="69"/>
       <c r="D205" s="70">
         <f>SUM(D4:D203)</f>
-        <v>1215.05</v>
+        <v>1227.05</v>
       </c>
       <c r="E205" s="70">
         <f>SUM(E4:E203)</f>
-        <v>658.1</v>
+        <v>689.1</v>
       </c>
       <c r="F205" s="71">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -17346,11 +17400,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="150" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -17508,16 +17562,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="151" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="150"/>
+      <c r="B1" s="151"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="151"/>
+      <c r="B2" s="152"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -17536,10 +17590,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="152" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="151"/>
+      <c r="B5" s="152"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="80" t="s">
@@ -17582,10 +17636,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A11" s="151" t="s">
+      <c r="A11" s="152" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="151"/>
+      <c r="B11" s="152"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1">
       <c r="A12" s="80" t="s">
@@ -17650,47 +17704,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="154"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="155"/>
+      <c r="B2" s="155"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="154">
+      <c r="D2" s="155">
         <v>2026</v>
       </c>
-      <c r="E2" s="154"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="156" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="157" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
       <c r="D3" s="82">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -19112,141 +19166,141 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
-      <c r="A35" s="88" t="str">
+      <c r="A35" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46199</v>
       </c>
       <c r="B35" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-74</v>
       </c>
       <c r="C35" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="91" t="str">
+        <v>ربل عدد 11 الحبه 2</v>
+      </c>
+      <c r="D35" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="E35" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="F35" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="89" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G35" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H35" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I35" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J35" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="89" t="str">
+        <v>377.05</v>
+      </c>
+      <c r="K35" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
-      <c r="A36" s="94" t="str">
+      <c r="A36" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46199</v>
       </c>
       <c r="B36" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-75</v>
       </c>
       <c r="C36" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="97" t="str">
+        <v>شوفليرا عدد6 الحبه 1.500</v>
+      </c>
+      <c r="D36" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="98" t="str">
+        <v>0</v>
+      </c>
+      <c r="E36" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F36" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="95" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G36" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H36" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I36" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J36" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="95" t="str">
+        <v>386.05</v>
+      </c>
+      <c r="K36" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
-      <c r="A37" s="88" t="str">
+      <c r="A37" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="89" t="str">
+        <v>46197</v>
+      </c>
+      <c r="B37" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C37" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="91" t="str">
+        <v>nbk 18-18-18</v>
+      </c>
+      <c r="D37" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="92" t="str">
+        <v>12</v>
+      </c>
+      <c r="E37" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F37" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G37" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H37" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I37" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J37" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="89" t="str">
+        <v>374.05</v>
+      </c>
+      <c r="K37" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
@@ -24632,29 +24686,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A155" s="152" t="s">
+      <c r="A155" s="153" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="152"/>
-      <c r="C155" s="152"/>
+      <c r="B155" s="153"/>
+      <c r="C155" s="153"/>
       <c r="D155" s="100">
         <f>SUM(D5:D154)</f>
-        <v>212.8</v>
+        <v>224.8</v>
       </c>
       <c r="E155" s="100">
         <f>SUM(E5:E154)</f>
-        <v>156</v>
-      </c>
-      <c r="F155" s="153">
+        <v>187</v>
+      </c>
+      <c r="F155" s="154">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="153"/>
-      <c r="H155" s="153"/>
+      <c r="G155" s="154"/>
+      <c r="H155" s="154"/>
       <c r="I155" s="101"/>
       <c r="J155" s="100">
         <f>E155-D155</f>
-        <v>-56.800000000000011</v>
+        <v>-37.800000000000011</v>
       </c>
       <c r="K155" s="101"/>
     </row>
@@ -24733,60 +24787,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="155" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="154"/>
+      <c r="B2" s="155"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="154" t="s">
+      <c r="D2" s="155" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="154"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="81">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="157" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="156"/>
+      <c r="B3" s="157"/>
       <c r="C3" s="82">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="156" t="s">
+      <c r="D3" s="157" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="156"/>
+      <c r="E3" s="157"/>
       <c r="F3" s="103">
         <f>المحفظة!$C$3</f>
-        <v>321.85000000000002</v>
+        <v>352.85</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="138" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="3">
@@ -25309,80 +25363,80 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
-      <c r="A25" s="113" t="str">
+      <c r="A25" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46199</v>
       </c>
       <c r="B25" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-74</v>
       </c>
       <c r="C25" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>ربل عدد 11 الحبه 2</v>
       </c>
       <c r="D25" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="117" t="str">
+      <c r="E25" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="F25" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
-      <c r="A26" s="108" t="str">
+      <c r="A26" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46199</v>
       </c>
       <c r="B26" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-75</v>
       </c>
       <c r="C26" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>شوفليرا عدد6 الحبه 1.500</v>
       </c>
       <c r="D26" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="112" t="str">
+      <c r="E26" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F26" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
-      <c r="A27" s="113" t="str">
+      <c r="A27" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B27" s="114" t="str">
+        <v>46197</v>
+      </c>
+      <c r="B27" s="114">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C27" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>nbk 18-18-18</v>
       </c>
       <c r="D27" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="117" t="str">
+      <c r="E27" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F27" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G27" s="9"/>
     </row>
@@ -26089,29 +26143,29 @@
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="142" t="s">
+      <c r="A55" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="142"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
+      <c r="B55" s="138"/>
+      <c r="C55" s="138"/>
+      <c r="D55" s="138"/>
       <c r="E55" s="118">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
-        <v>71.75</v>
+        <v>102.75</v>
       </c>
       <c r="F55" s="101"/>
       <c r="G55" s="101"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="140" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="144"/>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="144"/>
+      <c r="B56" s="140"/>
+      <c r="C56" s="140"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="18">
@@ -27414,11 +27468,11 @@
       <c r="G106" s="31"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="144" t="s">
+      <c r="A107" s="140" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="144"/>
-      <c r="C107" s="144"/>
+      <c r="B107" s="140"/>
+      <c r="C107" s="140"/>
       <c r="D107" s="133">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>62</v>
@@ -27428,35 +27482,35 @@
       <c r="G107" s="101"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A108" s="152" t="s">
+      <c r="A108" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="B108" s="152"/>
-      <c r="C108" s="152"/>
+      <c r="B108" s="153"/>
+      <c r="C108" s="153"/>
       <c r="D108" s="100">
         <f>E55-D107</f>
-        <v>9.75</v>
-      </c>
-      <c r="E108" s="157">
+        <v>40.75</v>
+      </c>
+      <c r="E108" s="158">
         <f>SUM(E5:E107)</f>
-        <v>143.5</v>
-      </c>
-      <c r="F108" s="157"/>
-      <c r="G108" s="157"/>
+        <v>205.5</v>
+      </c>
+      <c r="F108" s="158"/>
+      <c r="G108" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="E108:G108"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9575711-9FD1-4EAA-8554-F141498771B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D004450-B1C7-4396-BC35-9BA81B2D963A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="256">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -809,6 +809,12 @@
   </si>
   <si>
     <t>nbk 18-18-18</t>
+  </si>
+  <si>
+    <t>Inv-76</t>
+  </si>
+  <si>
+    <t>فل عدد 11 الحبه 0.750</t>
   </si>
 </sst>
 </file>
@@ -1719,6 +1725,21 @@
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1735,21 +1756,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2113,57 +2119,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="145" t="s">
+      <c r="E2" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="146"/>
+      <c r="B3" s="140"/>
       <c r="C3" s="2">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
         <v>352.85</v>
       </c>
-      <c r="D3" s="147" t="s">
+      <c r="D3" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="3">
@@ -3996,28 +4002,28 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="18" customHeight="1">
-      <c r="A66" s="10" t="str">
+      <c r="A66" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B66" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="B66" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C66" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="C66" s="12">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E66" s="14" t="str">
+      <c r="E66" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F66" s="15" t="str">
+        <v>0</v>
+      </c>
+      <c r="F66" s="15">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G66" s="16"/>
       <c r="H66" t="str">
@@ -5166,27 +5172,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="138" t="s">
+      <c r="A105" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="138"/>
-      <c r="C105" s="138"/>
-      <c r="D105" s="138"/>
+      <c r="B105" s="143"/>
+      <c r="C105" s="143"/>
+      <c r="D105" s="143"/>
       <c r="E105" s="17">
         <f>SUM(E5:E104)</f>
         <v>555.35</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="139" t="s">
+      <c r="A106" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="139"/>
-      <c r="C106" s="139"/>
-      <c r="D106" s="139"/>
-      <c r="E106" s="139"/>
-      <c r="F106" s="139"/>
-      <c r="G106" s="139"/>
+      <c r="B106" s="144"/>
+      <c r="C106" s="144"/>
+      <c r="D106" s="144"/>
+      <c r="E106" s="144"/>
+      <c r="F106" s="144"/>
+      <c r="G106" s="144"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="18">
@@ -5671,15 +5677,15 @@
     <row r="123" spans="1:8" ht="18" customHeight="1">
       <c r="A123" s="18">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B123" s="19">
+        <v>46201</v>
+      </c>
+      <c r="B123" s="19" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C123" s="20">
+        <v>Inv-76</v>
+      </c>
+      <c r="C123" s="20" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v>0</v>
+        <v>فل عدد 11 الحبه 0.750</v>
       </c>
       <c r="D123" s="21">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(17,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
@@ -5693,9 +5699,9 @@
         <v>0</v>
       </c>
       <c r="G123" s="24"/>
-      <c r="H123" t="str">
+      <c r="H123">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A123),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A123),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A123&lt;&gt;""),IFERROR(MAX($H$107:H122),0)+1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="18" customHeight="1">
@@ -8189,31 +8195,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="140" t="s">
+      <c r="A207" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="140"/>
-      <c r="C207" s="140"/>
+      <c r="B207" s="145"/>
+      <c r="C207" s="145"/>
       <c r="D207" s="32">
         <f>SUM(D107:D206)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="141" t="s">
+      <c r="A208" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="141"/>
-      <c r="C208" s="141"/>
+      <c r="B208" s="146"/>
+      <c r="C208" s="146"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
         <v>352.85</v>
       </c>
-      <c r="E208" s="142" t="s">
+      <c r="E208" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="142"/>
-      <c r="G208" s="142"/>
+      <c r="F208" s="147"/>
+      <c r="G208" s="147"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9722,17 +9728,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="E208:G208"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9758,38 +9764,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="145" t="s">
+      <c r="E2" s="139" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -13650,18 +13656,30 @@
       </c>
     </row>
     <row r="91" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A91" s="45"/>
-      <c r="B91" s="46"/>
-      <c r="C91" s="47"/>
+      <c r="A91" s="45">
+        <v>46201</v>
+      </c>
+      <c r="B91" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="C91" s="47" t="s">
+        <v>255</v>
+      </c>
       <c r="D91" s="48"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="50"/>
+      <c r="E91" s="49">
+        <v>8.25</v>
+      </c>
+      <c r="F91" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G91" s="51"/>
-      <c r="H91" s="52"/>
+      <c r="H91" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I91" s="53"/>
-      <c r="J91" s="54" t="str">
+      <c r="J91" s="54">
         <f>IF(AND(D91="",E91="",A91="",B91="",C91=""),"", IFERROR(IF(J90="",D2,J90),D2)+IF(E91="",0,E91)-IF(OR(G91="أبو اسحاق",G91="أبو آدم",G91="أبو اسحاق ",G91="أبو آدم "),0,IF(D91="",0,D91)))</f>
-        <v/>
+        <v>382.3</v>
       </c>
       <c r="K91" s="55"/>
       <c r="L91" t="str">
@@ -13672,9 +13690,9 @@
         <f>IF(AND(D90&gt;0,G90="المحفظة"),COUNTIFS($D$4:D90,"&gt;"&amp;0,$G$4:G90,"المحفظة"),"")</f>
         <v>17</v>
       </c>
-      <c r="N91" t="str">
+      <c r="N91">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A91)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A91)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A91&lt;&gt;""),IFERROR(MAX($N$4:N90),0)+1,"")</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="O91" t="str">
         <f>IF(AND(D90&gt;0,F90="أحد الشركاء"),COUNTIFS($D$4:D90,"&gt;"&amp;0,$F$4:F90,"أحد الشركاء"),"")</f>
@@ -13696,9 +13714,9 @@
         <v/>
       </c>
       <c r="K92" s="66"/>
-      <c r="L92" t="str">
+      <c r="L92">
         <f>IF(E91&gt;0,COUNTIF($E$4:E91,"&gt;0"),"")</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="M92" t="str">
         <f>IF(AND(D91&gt;0,G91="المحفظة"),COUNTIFS($D$4:D91,"&gt;"&amp;0,$G$4:G91,"المحفظة"),"")</f>
@@ -17309,7 +17327,7 @@
       </c>
       <c r="E205" s="70">
         <f>SUM(E4:E203)</f>
-        <v>689.1</v>
+        <v>697.35</v>
       </c>
       <c r="F205" s="71">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -17704,19 +17722,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
       <c r="A2" s="155"/>
@@ -19304,49 +19322,49 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
-      <c r="A38" s="94" t="str">
+      <c r="A38" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46201</v>
       </c>
       <c r="B38" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-76</v>
       </c>
       <c r="C38" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="97" t="str">
+        <v>فل عدد 11 الحبه 0.750</v>
+      </c>
+      <c r="D38" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="98" t="str">
+        <v>0</v>
+      </c>
+      <c r="E38" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>8.25</v>
       </c>
       <c r="F38" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="95" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G38" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I38" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J38" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="95" t="str">
+        <v>382.3</v>
+      </c>
+      <c r="K38" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
@@ -24697,7 +24715,7 @@
       </c>
       <c r="E155" s="100">
         <f>SUM(E5:E154)</f>
-        <v>187</v>
+        <v>195.25</v>
       </c>
       <c r="F155" s="154">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -24708,7 +24726,7 @@
       <c r="I155" s="101"/>
       <c r="J155" s="100">
         <f>E155-D155</f>
-        <v>-37.800000000000011</v>
+        <v>-29.550000000000011</v>
       </c>
       <c r="K155" s="101"/>
     </row>
@@ -24787,15 +24805,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
       <c r="A2" s="155" t="s">
@@ -24832,15 +24850,15 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="143" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="3">
@@ -26143,12 +26161,12 @@
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="138" t="s">
+      <c r="A55" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="138"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="138"/>
+      <c r="B55" s="143"/>
+      <c r="C55" s="143"/>
+      <c r="D55" s="143"/>
       <c r="E55" s="118">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>102.75</v>
@@ -26157,15 +26175,15 @@
       <c r="G55" s="101"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="140" t="s">
+      <c r="A56" s="145" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="140"/>
-      <c r="C56" s="140"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="140"/>
+      <c r="B56" s="145"/>
+      <c r="C56" s="145"/>
+      <c r="D56" s="145"/>
+      <c r="E56" s="145"/>
+      <c r="F56" s="145"/>
+      <c r="G56" s="145"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="18">
@@ -26402,28 +26420,28 @@
       <c r="G65" s="24"/>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
-      <c r="A66" s="128" t="str">
+      <c r="A66" s="128">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$A$107:$A$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>46201</v>
       </c>
       <c r="B66" s="129" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$B$107:$B$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>Inv-76</v>
       </c>
       <c r="C66" s="130" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$C$107:$C$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="131" t="str">
+        <v>فل عدد 11 الحبه 0.750</v>
+      </c>
+      <c r="D66" s="131">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$D$107:$D$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E66" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="129" t="str">
+      <c r="F66" s="129">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G66" s="31"/>
     </row>
@@ -27468,11 +27486,11 @@
       <c r="G106" s="31"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="140" t="s">
+      <c r="A107" s="145" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="140"/>
-      <c r="C107" s="140"/>
+      <c r="B107" s="145"/>
+      <c r="C107" s="145"/>
       <c r="D107" s="133">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>62</v>
@@ -27500,17 +27518,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="E108:G108"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D004450-B1C7-4396-BC35-9BA81B2D963A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CDE5C5-47CE-47BD-A836-0F4CB1698E48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="270">
   <si>
     <t>💰  المحفظة  —  Farm Wallet</t>
   </si>
@@ -816,6 +816,48 @@
   <si>
     <t>فل عدد 11 الحبه 0.750</t>
   </si>
+  <si>
+    <t>Inv-77</t>
+  </si>
+  <si>
+    <t>عطره عدد 3 الحبه 0.750</t>
+  </si>
+  <si>
+    <t>Inv-78</t>
+  </si>
+  <si>
+    <t>معلقات عدد 3 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-79</t>
+  </si>
+  <si>
+    <t>معلقات عدد 4 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-80</t>
+  </si>
+  <si>
+    <t>معلقات عدد4 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-81</t>
+  </si>
+  <si>
+    <t>افوبيا عدد 2 الحبه 1</t>
+  </si>
+  <si>
+    <t>رواتب عماله شهر يونيو 2026</t>
+  </si>
+  <si>
+    <t>تكمله رواتب يونيو 2026 ابوادم</t>
+  </si>
+  <si>
+    <t>تكمله رواتب يونيو 2026 ابواسحاق</t>
+  </si>
+  <si>
+    <t>احواض عدد 1000 مقاس 25 سم</t>
+  </si>
 </sst>
 </file>
 
@@ -1351,7 +1393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1715,6 +1757,12 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2119,57 +2167,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A1" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="A1" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="139" t="s">
+      <c r="E2" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="140" t="s">
+      <c r="A3" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="140"/>
+      <c r="B3" s="142"/>
       <c r="C3" s="2">
         <f>$D$2+SUM(E5:E104)-SUM(D106:D205)</f>
-        <v>352.85</v>
-      </c>
-      <c r="D3" s="141" t="s">
+        <v>418.1</v>
+      </c>
+      <c r="D3" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="3">
@@ -4004,241 +4052,241 @@
     <row r="66" spans="1:8" ht="18" customHeight="1">
       <c r="A66" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="B66" s="11">
+        <v>46202</v>
+      </c>
+      <c r="B66" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="12">
+        <v>Inv-77</v>
+      </c>
+      <c r="C66" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>عطره عدد 3 الحبه 0.750</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>6</v>
       </c>
       <c r="E66" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="15">
+        <v>2.25</v>
+      </c>
+      <c r="F66" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(62,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v>0</v>
+        <v>أون لاين</v>
       </c>
       <c r="G66" s="16"/>
-      <c r="H66" t="str">
+      <c r="H66">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A66),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A66),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A66&lt;&gt;""),IFERROR(MAX($H$5:H65),0)+1,"")</f>
-        <v/>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="18" customHeight="1">
-      <c r="A67" s="3" t="str">
+      <c r="A67" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(63,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46202</v>
       </c>
       <c r="B67" s="4" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(63,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-78</v>
       </c>
       <c r="C67" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(63,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>معلقات عدد 3 الحبه 1</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E67" s="7" t="str">
+      <c r="E67" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(63,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F67" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(63,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G67" s="9"/>
-      <c r="H67" t="str">
+      <c r="H67">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A67),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A67),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A67&lt;&gt;""),IFERROR(MAX($H$5:H66),0)+1,"")</f>
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="18" customHeight="1">
-      <c r="A68" s="10" t="str">
+      <c r="A68" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(64,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B68" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(64,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-79</v>
       </c>
       <c r="C68" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(64,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>معلقات عدد 4 الحبه 1</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E68" s="14" t="str">
+      <c r="E68" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(64,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F68" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(64,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G68" s="16"/>
-      <c r="H68" t="str">
+      <c r="H68">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A68),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A68),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A68&lt;&gt;""),IFERROR(MAX($H$5:H67),0)+1,"")</f>
-        <v/>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="18" customHeight="1">
-      <c r="A69" s="3" t="str">
+      <c r="A69" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(65,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B69" s="4" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(65,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-80</v>
       </c>
       <c r="C69" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(65,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>معلقات عدد4 الحبه 1</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E69" s="7" t="str">
+      <c r="E69" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(65,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F69" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(65,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G69" s="9"/>
-      <c r="H69" t="str">
+      <c r="H69">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A69),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A69),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A69&lt;&gt;""),IFERROR(MAX($H$5:H68),0)+1,"")</f>
-        <v/>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="18" customHeight="1">
-      <c r="A70" s="10" t="str">
+      <c r="A70" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(66,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B70" s="11" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(66,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>Inv-81</v>
       </c>
       <c r="C70" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(66,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>افوبيا عدد 2 الحبه 1</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E70" s="14" t="str">
+      <c r="E70" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(66,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F70" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(66,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G70" s="16"/>
-      <c r="H70" t="str">
+      <c r="H70">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A70),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A70),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A70&lt;&gt;""),IFERROR(MAX($H$5:H69),0)+1,"")</f>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1">
-      <c r="A71" s="3" t="str">
+      <c r="A71" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(67,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B71" s="4" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B71" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(67,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C71" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(67,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>رواتب عماله شهر يونيو 2026</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E71" s="7" t="str">
+      <c r="E71" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(67,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F71" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(67,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G71" s="9"/>
-      <c r="H71" t="str">
+      <c r="H71">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A71),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A71),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A71&lt;&gt;""),IFERROR(MAX($H$5:H70),0)+1,"")</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="18" customHeight="1">
-      <c r="A72" s="10" t="str">
+      <c r="A72" s="10">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(68,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B72" s="11" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B72" s="11">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(68,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C72" s="12" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(68,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>تكمله رواتب يونيو 2026 ابواسحاق</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E72" s="14" t="str">
+      <c r="E72" s="14">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(68,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="F72" s="15" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(68,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G72" s="16"/>
-      <c r="H72" t="str">
+      <c r="H72">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A72),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A72),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A72&lt;&gt;""),IFERROR(MAX($H$5:H71),0)+1,"")</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="18" customHeight="1">
-      <c r="A73" s="3" t="str">
+      <c r="A73" s="3">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(69,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B73" s="4" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B73" s="4">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(69,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C73" s="5" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(69,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>احواض عدد 1000 مقاس 25 سم</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E73" s="7" t="str">
+      <c r="E73" s="7">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$203,MATCH(69,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F73" s="8" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$F$4:$F$203,MATCH(69,'كشف الحساب'!$L$4:$L$203,0)),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G73" s="9"/>
-      <c r="H73" t="str">
+      <c r="H73">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A73),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A73),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A73&lt;&gt;""),IFERROR(MAX($H$5:H72),0)+1,"")</f>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="18" customHeight="1">
@@ -5172,27 +5220,27 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A105" s="143" t="s">
+      <c r="A105" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="143"/>
-      <c r="C105" s="143"/>
-      <c r="D105" s="143"/>
+      <c r="B105" s="145"/>
+      <c r="C105" s="145"/>
+      <c r="D105" s="145"/>
       <c r="E105" s="17">
         <f>SUM(E5:E104)</f>
-        <v>555.35</v>
+        <v>620.6</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A106" s="144" t="s">
+      <c r="A106" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="144"/>
-      <c r="C106" s="144"/>
-      <c r="D106" s="144"/>
-      <c r="E106" s="144"/>
-      <c r="F106" s="144"/>
-      <c r="G106" s="144"/>
+      <c r="B106" s="146"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="146"/>
+      <c r="E106" s="146"/>
+      <c r="F106" s="146"/>
+      <c r="G106" s="146"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
       <c r="A107" s="18">
@@ -5705,58 +5753,58 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="18" customHeight="1">
-      <c r="A124" s="25" t="str">
+      <c r="A124" s="25">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(18,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B124" s="26" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B124" s="26">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(18,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C124" s="27" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(18,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D124" s="28" t="str">
+        <v>تكمله رواتب يونيو 2026 ابوادم</v>
+      </c>
+      <c r="D124" s="28">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(18,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E124" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="F124" s="30" t="str">
+      <c r="F124" s="30">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(18,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G124" s="31"/>
-      <c r="H124" t="str">
+      <c r="H124">
         <f>IF(AND(OR('طباعة المحفظة'!$C$2="الكل",IFERROR(MONTH(A124),0)=IFERROR(MATCH('طباعة المحفظة'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة المحفظة'!$F$2="الكل",IFERROR(YEAR(A124),0)=IFERROR(VALUE('طباعة المحفظة'!$F$2),0)),A124&lt;&gt;""),IFERROR(MAX($H$107:H123),0)+1,"")</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="18" customHeight="1">
-      <c r="A125" s="18" t="str">
+      <c r="A125" s="18">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$203,MATCH(19,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B125" s="19" t="str">
+        <v>0</v>
+      </c>
+      <c r="B125" s="19">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$203,MATCH(19,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C125" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="C125" s="20">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$203,MATCH(19,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D125" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="D125" s="21">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$203,MATCH(19,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E125" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F125" s="23" t="str">
+      <c r="F125" s="23">
         <f>IFERROR(INDEX('كشف الحساب'!$I$4:$I$203,MATCH(19,'كشف الحساب'!$M$4:$M$203,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G125" s="24"/>
       <c r="H125" t="str">
@@ -8195,31 +8243,31 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A207" s="145" t="s">
+      <c r="A207" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="145"/>
-      <c r="C207" s="145"/>
+      <c r="B207" s="147"/>
+      <c r="C207" s="147"/>
       <c r="D207" s="32">
         <f>SUM(D107:D206)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A208" s="146" t="s">
+      <c r="A208" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="146"/>
-      <c r="C208" s="146"/>
+      <c r="B208" s="148"/>
+      <c r="C208" s="148"/>
       <c r="D208" s="34">
         <f>$D$2+E105-D207</f>
-        <v>352.85</v>
-      </c>
-      <c r="E208" s="147" t="s">
+        <v>418.1</v>
+      </c>
+      <c r="E208" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="F208" s="147"/>
-      <c r="G208" s="147"/>
+      <c r="F208" s="149"/>
+      <c r="G208" s="149"/>
     </row>
     <row r="210" spans="1:7" ht="15" customHeight="1">
       <c r="A210" s="35" t="s">
@@ -9764,38 +9812,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="139" t="s">
+      <c r="E2" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1">
       <c r="A3" s="42" t="s">
@@ -13700,18 +13748,30 @@
       </c>
     </row>
     <row r="92" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A92" s="56"/>
-      <c r="B92" s="57"/>
-      <c r="C92" s="58"/>
+      <c r="A92" s="56">
+        <v>46202</v>
+      </c>
+      <c r="B92" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C92" s="58" t="s">
+        <v>257</v>
+      </c>
       <c r="D92" s="59"/>
-      <c r="E92" s="60"/>
-      <c r="F92" s="61"/>
+      <c r="E92" s="60">
+        <v>2.25</v>
+      </c>
+      <c r="F92" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G92" s="62"/>
-      <c r="H92" s="63"/>
+      <c r="H92" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I92" s="64"/>
-      <c r="J92" s="65" t="str">
+      <c r="J92" s="65">
         <f>IF(AND(D92="",E92="",A92="",B92="",C92=""),"", IFERROR(IF(J91="",D2,J91),D2)+IF(E92="",0,E92)-IF(OR(G92="أبو اسحاق",G92="أبو آدم",G92="أبو اسحاق ",G92="أبو آدم "),0,IF(D92="",0,D92)))</f>
-        <v/>
+        <v>384.55</v>
       </c>
       <c r="K92" s="66"/>
       <c r="L92">
@@ -13722,9 +13782,9 @@
         <f>IF(AND(D91&gt;0,G91="المحفظة"),COUNTIFS($D$4:D91,"&gt;"&amp;0,$G$4:G91,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N92" t="str">
+      <c r="N92">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A92)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A92)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A92&lt;&gt;""),IFERROR(MAX($N$4:N91),0)+1,"")</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="O92" t="str">
         <f>IF(AND(D91&gt;0,F91="أحد الشركاء"),COUNTIFS($D$4:D91,"&gt;"&amp;0,$F$4:F91,"أحد الشركاء"),"")</f>
@@ -13732,31 +13792,43 @@
       </c>
     </row>
     <row r="93" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A93" s="45"/>
-      <c r="B93" s="46"/>
-      <c r="C93" s="47"/>
+      <c r="A93" s="137">
+        <v>46202</v>
+      </c>
+      <c r="B93" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="C93" s="47" t="s">
+        <v>259</v>
+      </c>
       <c r="D93" s="48"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="50"/>
+      <c r="E93" s="49">
+        <v>3</v>
+      </c>
+      <c r="F93" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G93" s="51"/>
-      <c r="H93" s="52"/>
+      <c r="H93" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I93" s="53"/>
-      <c r="J93" s="54" t="str">
+      <c r="J93" s="54">
         <f>IF(AND(D93="",E93="",A93="",B93="",C93=""),"", IFERROR(IF(J92="",D2,J92),D2)+IF(E93="",0,E93)-IF(OR(G93="أبو اسحاق",G93="أبو آدم",G93="أبو اسحاق ",G93="أبو آدم "),0,IF(D93="",0,D93)))</f>
-        <v/>
+        <v>387.55</v>
       </c>
       <c r="K93" s="55"/>
-      <c r="L93" t="str">
+      <c r="L93">
         <f>IF(E92&gt;0,COUNTIF($E$4:E92,"&gt;0"),"")</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="M93" t="str">
         <f>IF(AND(D92&gt;0,G92="المحفظة"),COUNTIFS($D$4:D92,"&gt;"&amp;0,$G$4:G92,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N93" t="str">
+      <c r="N93">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A93)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A93)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A93&lt;&gt;""),IFERROR(MAX($N$4:N92),0)+1,"")</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="O93" t="str">
         <f>IF(AND(D92&gt;0,F92="أحد الشركاء"),COUNTIFS($D$4:D92,"&gt;"&amp;0,$F$4:F92,"أحد الشركاء"),"")</f>
@@ -13764,31 +13836,43 @@
       </c>
     </row>
     <row r="94" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A94" s="56"/>
-      <c r="B94" s="57"/>
-      <c r="C94" s="58"/>
+      <c r="A94" s="56">
+        <v>46203</v>
+      </c>
+      <c r="B94" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="C94" s="58" t="s">
+        <v>261</v>
+      </c>
       <c r="D94" s="59"/>
-      <c r="E94" s="60"/>
-      <c r="F94" s="61"/>
+      <c r="E94" s="60">
+        <v>4</v>
+      </c>
+      <c r="F94" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G94" s="62"/>
-      <c r="H94" s="63"/>
+      <c r="H94" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I94" s="64"/>
-      <c r="J94" s="65" t="str">
+      <c r="J94" s="65">
         <f>IF(AND(D94="",E94="",A94="",B94="",C94=""),"", IFERROR(IF(J93="",D2,J93),D2)+IF(E94="",0,E94)-IF(OR(G94="أبو اسحاق",G94="أبو آدم",G94="أبو اسحاق ",G94="أبو آدم "),0,IF(D94="",0,D94)))</f>
-        <v/>
+        <v>391.55</v>
       </c>
       <c r="K94" s="66"/>
-      <c r="L94" t="str">
+      <c r="L94">
         <f>IF(E93&gt;0,COUNTIF($E$4:E93,"&gt;0"),"")</f>
-        <v/>
+        <v>64</v>
       </c>
       <c r="M94" t="str">
         <f>IF(AND(D93&gt;0,G93="المحفظة"),COUNTIFS($D$4:D93,"&gt;"&amp;0,$G$4:G93,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N94" t="str">
+      <c r="N94">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A94)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A94)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A94&lt;&gt;""),IFERROR(MAX($N$4:N93),0)+1,"")</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="O94" t="str">
         <f>IF(AND(D93&gt;0,F93="أحد الشركاء"),COUNTIFS($D$4:D93,"&gt;"&amp;0,$F$4:F93,"أحد الشركاء"),"")</f>
@@ -13796,31 +13880,43 @@
       </c>
     </row>
     <row r="95" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A95" s="45"/>
-      <c r="B95" s="46"/>
-      <c r="C95" s="47"/>
+      <c r="A95" s="138">
+        <v>46203</v>
+      </c>
+      <c r="B95" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C95" s="47" t="s">
+        <v>263</v>
+      </c>
       <c r="D95" s="48"/>
-      <c r="E95" s="49"/>
-      <c r="F95" s="50"/>
+      <c r="E95" s="49">
+        <v>4</v>
+      </c>
+      <c r="F95" s="50" t="s">
+        <v>233</v>
+      </c>
       <c r="G95" s="51"/>
-      <c r="H95" s="52"/>
+      <c r="H95" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I95" s="53"/>
-      <c r="J95" s="54" t="str">
+      <c r="J95" s="54">
         <f>IF(AND(D95="",E95="",A95="",B95="",C95=""),"", IFERROR(IF(J94="",D2,J94),D2)+IF(E95="",0,E95)-IF(OR(G95="أبو اسحاق",G95="أبو آدم",G95="أبو اسحاق ",G95="أبو آدم "),0,IF(D95="",0,D95)))</f>
-        <v/>
+        <v>395.55</v>
       </c>
       <c r="K95" s="55"/>
-      <c r="L95" t="str">
+      <c r="L95">
         <f>IF(E94&gt;0,COUNTIF($E$4:E94,"&gt;0"),"")</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="M95" t="str">
         <f>IF(AND(D94&gt;0,G94="المحفظة"),COUNTIFS($D$4:D94,"&gt;"&amp;0,$G$4:G94,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N95" t="str">
+      <c r="N95">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A95)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A95)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A95&lt;&gt;""),IFERROR(MAX($N$4:N94),0)+1,"")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="O95" t="str">
         <f>IF(AND(D94&gt;0,F94="أحد الشركاء"),COUNTIFS($D$4:D94,"&gt;"&amp;0,$F$4:F94,"أحد الشركاء"),"")</f>
@@ -13828,31 +13924,43 @@
       </c>
     </row>
     <row r="96" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A96" s="56"/>
-      <c r="B96" s="57"/>
-      <c r="C96" s="58"/>
+      <c r="A96" s="138">
+        <v>46203</v>
+      </c>
+      <c r="B96" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="C96" s="58" t="s">
+        <v>265</v>
+      </c>
       <c r="D96" s="59"/>
-      <c r="E96" s="60"/>
-      <c r="F96" s="61"/>
+      <c r="E96" s="60">
+        <v>2</v>
+      </c>
+      <c r="F96" s="61" t="s">
+        <v>233</v>
+      </c>
       <c r="G96" s="62"/>
-      <c r="H96" s="63"/>
+      <c r="H96" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I96" s="64"/>
-      <c r="J96" s="65" t="str">
+      <c r="J96" s="65">
         <f>IF(AND(D96="",E96="",A96="",B96="",C96=""),"", IFERROR(IF(J95="",D2,J95),D2)+IF(E96="",0,E96)-IF(OR(G96="أبو اسحاق",G96="أبو آدم",G96="أبو اسحاق ",G96="أبو آدم "),0,IF(D96="",0,D96)))</f>
-        <v/>
+        <v>397.55</v>
       </c>
       <c r="K96" s="66"/>
-      <c r="L96" t="str">
+      <c r="L96">
         <f>IF(E95&gt;0,COUNTIF($E$4:E95,"&gt;0"),"")</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="M96" t="str">
         <f>IF(AND(D95&gt;0,G95="المحفظة"),COUNTIFS($D$4:D95,"&gt;"&amp;0,$G$4:G95,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N96" t="str">
+      <c r="N96">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A96)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A96)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A96&lt;&gt;""),IFERROR(MAX($N$4:N95),0)+1,"")</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="O96" t="str">
         <f>IF(AND(D95&gt;0,F95="أحد الشركاء"),COUNTIFS($D$4:D95,"&gt;"&amp;0,$F$4:F95,"أحد الشركاء"),"")</f>
@@ -13860,31 +13968,43 @@
       </c>
     </row>
     <row r="97" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A97" s="45"/>
+      <c r="A97" s="138">
+        <v>46203</v>
+      </c>
       <c r="B97" s="46"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="48"/>
+      <c r="C97" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="D97" s="48">
+        <v>380</v>
+      </c>
       <c r="E97" s="49"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="52"/>
+      <c r="F97" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I97" s="53"/>
-      <c r="J97" s="54" t="str">
+      <c r="J97" s="54">
         <f>IF(AND(D97="",E97="",A97="",B97="",C97=""),"", IFERROR(IF(J96="",D2,J96),D2)+IF(E97="",0,E97)-IF(OR(G97="أبو اسحاق",G97="أبو آدم",G97="أبو اسحاق ",G97="أبو آدم "),0,IF(D97="",0,D97)))</f>
-        <v/>
+        <v>17.550000000000011</v>
       </c>
       <c r="K97" s="55"/>
-      <c r="L97" t="str">
+      <c r="L97">
         <f>IF(E96&gt;0,COUNTIF($E$4:E96,"&gt;0"),"")</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="M97" t="str">
         <f>IF(AND(D96&gt;0,G96="المحفظة"),COUNTIFS($D$4:D96,"&gt;"&amp;0,$G$4:G96,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N97" t="str">
+      <c r="N97">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A97)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A97)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A97&lt;&gt;""),IFERROR(MAX($N$4:N96),0)+1,"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="O97" t="str">
         <f>IF(AND(D96&gt;0,F96="أحد الشركاء"),COUNTIFS($D$4:D96,"&gt;"&amp;0,$F$4:F96,"أحد الشركاء"),"")</f>
@@ -13892,31 +14012,43 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A98" s="56"/>
+      <c r="A98" s="138">
+        <v>46203</v>
+      </c>
       <c r="B98" s="57"/>
-      <c r="C98" s="58"/>
+      <c r="C98" s="58" t="s">
+        <v>267</v>
+      </c>
       <c r="D98" s="59"/>
-      <c r="E98" s="60"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="62"/>
-      <c r="H98" s="63"/>
+      <c r="E98" s="60">
+        <v>50</v>
+      </c>
+      <c r="F98" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="H98" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I98" s="64"/>
-      <c r="J98" s="65" t="str">
+      <c r="J98" s="65">
         <f>IF(AND(D98="",E98="",A98="",B98="",C98=""),"", IFERROR(IF(J97="",D2,J97),D2)+IF(E98="",0,E98)-IF(OR(G98="أبو اسحاق",G98="أبو آدم",G98="أبو اسحاق ",G98="أبو آدم "),0,IF(D98="",0,D98)))</f>
-        <v/>
+        <v>67.550000000000011</v>
       </c>
       <c r="K98" s="66"/>
       <c r="L98" t="str">
         <f>IF(E97&gt;0,COUNTIF($E$4:E97,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M98" t="str">
+      <c r="M98">
         <f>IF(AND(D97&gt;0,G97="المحفظة"),COUNTIFS($D$4:D97,"&gt;"&amp;0,$G$4:G97,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N98" t="str">
+        <v>18</v>
+      </c>
+      <c r="N98">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A98)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A98)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A98&lt;&gt;""),IFERROR(MAX($N$4:N97),0)+1,"")</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="O98" t="str">
         <f>IF(AND(D97&gt;0,F97="أحد الشركاء"),COUNTIFS($D$4:D97,"&gt;"&amp;0,$F$4:F97,"أحد الشركاء"),"")</f>
@@ -13924,31 +14056,43 @@
       </c>
     </row>
     <row r="99" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A99" s="45"/>
+      <c r="A99" s="138">
+        <v>46203</v>
+      </c>
       <c r="B99" s="46"/>
-      <c r="C99" s="47"/>
+      <c r="C99" s="58" t="s">
+        <v>268</v>
+      </c>
       <c r="D99" s="48"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="52"/>
+      <c r="E99" s="49">
+        <v>50</v>
+      </c>
+      <c r="F99" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="G99" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" s="52" t="s">
+        <v>44</v>
+      </c>
       <c r="I99" s="53"/>
-      <c r="J99" s="54" t="str">
+      <c r="J99" s="54">
         <f>IF(AND(D99="",E99="",A99="",B99="",C99=""),"", IFERROR(IF(J98="",D2,J98),D2)+IF(E99="",0,E99)-IF(OR(G99="أبو اسحاق",G99="أبو آدم",G99="أبو اسحاق ",G99="أبو آدم "),0,IF(D99="",0,D99)))</f>
-        <v/>
+        <v>117.55000000000001</v>
       </c>
       <c r="K99" s="55"/>
-      <c r="L99" t="str">
+      <c r="L99">
         <f>IF(E98&gt;0,COUNTIF($E$4:E98,"&gt;0"),"")</f>
-        <v/>
+        <v>68</v>
       </c>
       <c r="M99" t="str">
         <f>IF(AND(D98&gt;0,G98="المحفظة"),COUNTIFS($D$4:D98,"&gt;"&amp;0,$G$4:G98,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N99" t="str">
+      <c r="N99">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A99)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A99)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A99&lt;&gt;""),IFERROR(MAX($N$4:N98),0)+1,"")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="O99" t="str">
         <f>IF(AND(D98&gt;0,F98="أحد الشركاء"),COUNTIFS($D$4:D98,"&gt;"&amp;0,$F$4:F98,"أحد الشركاء"),"")</f>
@@ -13956,31 +14100,43 @@
       </c>
     </row>
     <row r="100" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A100" s="56"/>
+      <c r="A100" s="138">
+        <v>46203</v>
+      </c>
       <c r="B100" s="57"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="59"/>
+      <c r="C100" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="D100" s="59">
+        <v>80</v>
+      </c>
       <c r="E100" s="60"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="62"/>
-      <c r="H100" s="63"/>
+      <c r="F100" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H100" s="63" t="s">
+        <v>44</v>
+      </c>
       <c r="I100" s="64"/>
-      <c r="J100" s="65" t="str">
+      <c r="J100" s="65">
         <f>IF(AND(D100="",E100="",A100="",B100="",C100=""),"", IFERROR(IF(J99="",D2,J99),D2)+IF(E100="",0,E100)-IF(OR(G100="أبو اسحاق",G100="أبو آدم",G100="أبو اسحاق ",G100="أبو آدم "),0,IF(D100="",0,D100)))</f>
-        <v/>
+        <v>37.550000000000011</v>
       </c>
       <c r="K100" s="66"/>
-      <c r="L100" t="str">
+      <c r="L100">
         <f>IF(E99&gt;0,COUNTIF($E$4:E99,"&gt;0"),"")</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="M100" t="str">
         <f>IF(AND(D99&gt;0,G99="المحفظة"),COUNTIFS($D$4:D99,"&gt;"&amp;0,$G$4:G99,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N100" t="str">
+      <c r="N100">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A100)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A100)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A100&lt;&gt;""),IFERROR(MAX($N$4:N99),0)+1,"")</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="O100" t="str">
         <f>IF(AND(D99&gt;0,F99="أحد الشركاء"),COUNTIFS($D$4:D99,"&gt;"&amp;0,$F$4:F99,"أحد الشركاء"),"")</f>
@@ -14006,9 +14162,9 @@
         <f>IF(E100&gt;0,COUNTIF($E$4:E100,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M101" t="str">
+      <c r="M101">
         <f>IF(AND(D100&gt;0,G100="المحفظة"),COUNTIFS($D$4:D100,"&gt;"&amp;0,$G$4:G100,"المحفظة"),"")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="N101" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A101)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A101)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A101&lt;&gt;""),IFERROR(MAX($N$4:N100),0)+1,"")</f>
@@ -17284,14 +17440,14 @@
       </c>
     </row>
     <row r="204" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A204" s="148"/>
-      <c r="B204" s="148"/>
-      <c r="C204" s="148"/>
+      <c r="A204" s="150"/>
+      <c r="B204" s="150"/>
+      <c r="C204" s="150"/>
       <c r="D204" s="59"/>
       <c r="E204" s="60"/>
-      <c r="F204" s="149"/>
-      <c r="G204" s="149"/>
-      <c r="H204" s="149"/>
+      <c r="F204" s="151"/>
+      <c r="G204" s="151"/>
+      <c r="H204" s="151"/>
       <c r="I204" s="64"/>
       <c r="J204" s="65" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -17323,11 +17479,11 @@
       <c r="C205" s="69"/>
       <c r="D205" s="70">
         <f>SUM(D4:D203)</f>
-        <v>1227.05</v>
+        <v>1687.05</v>
       </c>
       <c r="E205" s="70">
         <f>SUM(E4:E203)</f>
-        <v>697.35</v>
+        <v>812.6</v>
       </c>
       <c r="F205" s="71">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -17418,11 +17574,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="152" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -17580,16 +17736,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="153" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="151"/>
+      <c r="B1" s="153"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="154" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="152"/>
+      <c r="B2" s="154"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -17608,10 +17764,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="152"/>
+      <c r="B5" s="154"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="80" t="s">
@@ -17654,10 +17810,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A11" s="152" t="s">
+      <c r="A11" s="154" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="152"/>
+      <c r="B11" s="154"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1">
       <c r="A12" s="80" t="s">
@@ -17722,47 +17878,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="155">
+      <c r="D2" s="157">
         <v>2026</v>
       </c>
-      <c r="E2" s="155"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="156" t="s">
+      <c r="G2" s="158" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="159" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
       <c r="D3" s="82">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -19368,417 +19524,417 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
-      <c r="A39" s="88" t="str">
+      <c r="A39" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46202</v>
       </c>
       <c r="B39" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-77</v>
       </c>
       <c r="C39" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="91" t="str">
+        <v>عطره عدد 3 الحبه 0.750</v>
+      </c>
+      <c r="D39" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="E39" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2.25</v>
       </c>
       <c r="F39" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="89" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G39" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I39" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J39" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="89" t="str">
+        <v>384.55</v>
+      </c>
+      <c r="K39" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
-      <c r="A40" s="94" t="str">
+      <c r="A40" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46202</v>
       </c>
       <c r="B40" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-78</v>
       </c>
       <c r="C40" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="97" t="str">
+        <v>معلقات عدد 3 الحبه 1</v>
+      </c>
+      <c r="D40" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="98" t="str">
+        <v>0</v>
+      </c>
+      <c r="E40" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F40" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="95" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G40" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I40" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J40" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="95" t="str">
+        <v>387.55</v>
+      </c>
+      <c r="K40" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
-      <c r="A41" s="88" t="str">
+      <c r="A41" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B41" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-79</v>
       </c>
       <c r="C41" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="91" t="str">
+        <v>معلقات عدد 4 الحبه 1</v>
+      </c>
+      <c r="D41" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="E41" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F41" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="89" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G41" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I41" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J41" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="89" t="str">
+        <v>391.55</v>
+      </c>
+      <c r="K41" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
-      <c r="A42" s="94" t="str">
+      <c r="A42" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B42" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-80</v>
       </c>
       <c r="C42" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="97" t="str">
+        <v>معلقات عدد4 الحبه 1</v>
+      </c>
+      <c r="D42" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="98" t="str">
+        <v>0</v>
+      </c>
+      <c r="E42" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F42" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="95" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G42" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I42" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J42" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="95" t="str">
+        <v>395.55</v>
+      </c>
+      <c r="K42" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
-      <c r="A43" s="88" t="str">
+      <c r="A43" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B43" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-81</v>
       </c>
       <c r="C43" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="91" t="str">
+        <v>افوبيا عدد 2 الحبه 1</v>
+      </c>
+      <c r="D43" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="E43" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F43" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="89" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G43" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I43" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J43" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="89" t="str">
+        <v>397.55</v>
+      </c>
+      <c r="K43" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
-      <c r="A44" s="94" t="str">
+      <c r="A44" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B44" s="95" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B44" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C44" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="97" t="str">
+        <v>رواتب عماله شهر يونيو 2026</v>
+      </c>
+      <c r="D44" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="98" t="str">
+        <v>380</v>
+      </c>
+      <c r="E44" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F44" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G44" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H44" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I44" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J44" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="95" t="str">
+        <v>17.550000000000011</v>
+      </c>
+      <c r="K44" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
-      <c r="A45" s="88" t="str">
+      <c r="A45" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B45" s="89" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B45" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C45" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="91" t="str">
+        <v>تكمله رواتب يونيو 2026 ابوادم</v>
+      </c>
+      <c r="D45" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="E45" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="F45" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G45" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو آدم</v>
       </c>
       <c r="H45" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I45" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J45" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="89" t="str">
+        <v>67.550000000000011</v>
+      </c>
+      <c r="K45" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
-      <c r="A46" s="94" t="str">
+      <c r="A46" s="94">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B46" s="95" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B46" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C46" s="96" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="97" t="str">
+        <v>تكمله رواتب يونيو 2026 ابواسحاق</v>
+      </c>
+      <c r="D46" s="97">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="98" t="str">
+        <v>0</v>
+      </c>
+      <c r="E46" s="98">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="F46" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G46" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="H46" s="95" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="95" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I46" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J46" s="99">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="95" t="str">
+        <v>117.55000000000001</v>
+      </c>
+      <c r="K46" s="95">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
-      <c r="A47" s="88" t="str">
+      <c r="A47" s="88">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="89" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B47" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C47" s="90" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="91" t="str">
+        <v>احواض عدد 1000 مقاس 25 سم</v>
+      </c>
+      <c r="D47" s="91">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="92" t="str">
+        <v>80</v>
+      </c>
+      <c r="E47" s="92">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G47" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H47" s="89" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="89" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I47" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J47" s="93">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="89" t="str">
+        <v>37.550000000000011</v>
+      </c>
+      <c r="K47" s="89">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
@@ -24704,29 +24860,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A155" s="153" t="s">
+      <c r="A155" s="155" t="s">
         <v>220</v>
       </c>
-      <c r="B155" s="153"/>
-      <c r="C155" s="153"/>
+      <c r="B155" s="155"/>
+      <c r="C155" s="155"/>
       <c r="D155" s="100">
         <f>SUM(D5:D154)</f>
-        <v>224.8</v>
+        <v>684.8</v>
       </c>
       <c r="E155" s="100">
         <f>SUM(E5:E154)</f>
-        <v>195.25</v>
-      </c>
-      <c r="F155" s="154">
+        <v>310.5</v>
+      </c>
+      <c r="F155" s="156">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="154"/>
-      <c r="H155" s="154"/>
+      <c r="G155" s="156"/>
+      <c r="H155" s="156"/>
       <c r="I155" s="101"/>
       <c r="J155" s="100">
         <f>E155-D155</f>
-        <v>-29.550000000000011</v>
+        <v>-374.29999999999995</v>
       </c>
       <c r="K155" s="101"/>
     </row>
@@ -24805,60 +24961,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="A1" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="157" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="155"/>
+      <c r="B2" s="157"/>
       <c r="C2" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="157" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="155"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="81">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="159" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="157"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="82">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="157" t="s">
+      <c r="D3" s="159" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="157"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="103">
         <f>المحفظة!$C$3</f>
-        <v>352.85</v>
+        <v>418.1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="145" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1">
       <c r="A5" s="3">
@@ -25459,210 +25615,210 @@
       <c r="G27" s="9"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
-      <c r="A28" s="108" t="str">
+      <c r="A28" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46202</v>
       </c>
       <c r="B28" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-77</v>
       </c>
       <c r="C28" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>عطره عدد 3 الحبه 0.750</v>
       </c>
       <c r="D28" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="112" t="str">
+      <c r="E28" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>2.25</v>
       </c>
       <c r="F28" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
-      <c r="A29" s="113" t="str">
+      <c r="A29" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46202</v>
       </c>
       <c r="B29" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-78</v>
       </c>
       <c r="C29" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>معلقات عدد 3 الحبه 1</v>
       </c>
       <c r="D29" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E29" s="117" t="str">
+      <c r="E29" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F29" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G29" s="9"/>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
-      <c r="A30" s="108" t="str">
+      <c r="A30" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B30" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-79</v>
       </c>
       <c r="C30" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>معلقات عدد 4 الحبه 1</v>
       </c>
       <c r="D30" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="112" t="str">
+      <c r="E30" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F30" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
-      <c r="A31" s="113" t="str">
+      <c r="A31" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B31" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-80</v>
       </c>
       <c r="C31" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>معلقات عدد4 الحبه 1</v>
       </c>
       <c r="D31" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="117" t="str">
+      <c r="E31" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F31" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G31" s="9"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
-      <c r="A32" s="108" t="str">
+      <c r="A32" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="B32" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>Inv-81</v>
       </c>
       <c r="C32" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>افوبيا عدد 2 الحبه 1</v>
       </c>
       <c r="D32" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="112" t="str">
+      <c r="E32" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F32" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>أون لاين</v>
       </c>
       <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
-      <c r="A33" s="113" t="str">
+      <c r="A33" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="114" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B33" s="114">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C33" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>رواتب عماله شهر يونيو 2026</v>
       </c>
       <c r="D33" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="117" t="str">
+      <c r="E33" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F33" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G33" s="9"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
-      <c r="A34" s="108" t="str">
+      <c r="A34" s="108">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="109" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B34" s="109">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C34" s="110" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>تكمله رواتب يونيو 2026 ابواسحاق</v>
       </c>
       <c r="D34" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="112" t="str">
+      <c r="E34" s="112">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="F34" s="109" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
-      <c r="A35" s="113" t="str">
+      <c r="A35" s="113">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$A$5:$A$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="114" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B35" s="114">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$B$5:$B$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C35" s="115" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$C$5:$C$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>احواض عدد 1000 مقاس 25 سم</v>
       </c>
       <c r="D35" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="117" t="str">
+      <c r="E35" s="117">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F35" s="114" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$F$5:$F$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G35" s="9"/>
     </row>
@@ -26161,29 +26317,29 @@
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A55" s="143" t="s">
+      <c r="A55" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="143"/>
-      <c r="C55" s="143"/>
-      <c r="D55" s="143"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="145"/>
+      <c r="D55" s="145"/>
       <c r="E55" s="118">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
-        <v>102.75</v>
+        <v>168</v>
       </c>
       <c r="F55" s="101"/>
       <c r="G55" s="101"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="145" t="s">
+      <c r="A56" s="147" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="145"/>
-      <c r="C56" s="145"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="145"/>
-      <c r="F56" s="145"/>
-      <c r="G56" s="145"/>
+      <c r="B56" s="147"/>
+      <c r="C56" s="147"/>
+      <c r="D56" s="147"/>
+      <c r="E56" s="147"/>
+      <c r="F56" s="147"/>
+      <c r="G56" s="147"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="18">
@@ -26446,28 +26602,28 @@
       <c r="G66" s="31"/>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
-      <c r="A67" s="123" t="str">
+      <c r="A67" s="123">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$A$107:$A$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B67" s="124" t="str">
+        <v>46203</v>
+      </c>
+      <c r="B67" s="124">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$B$107:$B$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C67" s="125" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$C$107:$C$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="126" t="str">
+        <v>تكمله رواتب يونيو 2026 ابوادم</v>
+      </c>
+      <c r="D67" s="126">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$D$107:$D$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E67" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="F67" s="124" t="str">
+      <c r="F67" s="124">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G67" s="24"/>
     </row>
@@ -27486,11 +27642,11 @@
       <c r="G106" s="31"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A107" s="145" t="s">
+      <c r="A107" s="147" t="s">
         <v>228</v>
       </c>
-      <c r="B107" s="145"/>
-      <c r="C107" s="145"/>
+      <c r="B107" s="147"/>
+      <c r="C107" s="147"/>
       <c r="D107" s="133">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>62</v>
@@ -27500,21 +27656,21 @@
       <c r="G107" s="101"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A108" s="153" t="s">
+      <c r="A108" s="155" t="s">
         <v>229</v>
       </c>
-      <c r="B108" s="153"/>
-      <c r="C108" s="153"/>
+      <c r="B108" s="155"/>
+      <c r="C108" s="155"/>
       <c r="D108" s="100">
         <f>E55-D107</f>
-        <v>40.75</v>
-      </c>
-      <c r="E108" s="158">
+        <v>106</v>
+      </c>
+      <c r="E108" s="160">
         <f>SUM(E5:E107)</f>
-        <v>205.5</v>
-      </c>
-      <c r="F108" s="158"/>
-      <c r="G108" s="158"/>
+        <v>336</v>
+      </c>
+      <c r="F108" s="160"/>
+      <c r="G108" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E867B1-A9F1-49D7-8E84-F813923C115C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB60B08C-BBDC-4606-96B7-4820436BAB65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -884,9 +884,6 @@
     <t>Inv-85</t>
   </si>
   <si>
-    <t>عطريات عدد8 الحبه 0.800</t>
-  </si>
-  <si>
     <t>Inv-86</t>
   </si>
   <si>
@@ -924,6 +921,9 @@
   </si>
   <si>
     <t>عطريات عدد 1 الفحبه 1</t>
+  </si>
+  <si>
+    <t>عطريات عدد8 الحبه 1</t>
   </si>
 </sst>
 </file>
@@ -2095,14 +2095,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C90" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(85,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>عطريات عدد8 الحبه 0.800</v>
+        <v>عطريات عدد8 الحبه 1</v>
       </c>
       <c r="D90" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(85,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -15453,7 +15453,7 @@
         <v>279</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="D105" s="28"/>
       <c r="E105" s="29">
@@ -15502,10 +15502,10 @@
         <v>46211</v>
       </c>
       <c r="B106" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C106" s="37" t="s">
         <v>281</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>282</v>
       </c>
       <c r="D106" s="38"/>
       <c r="E106" s="39">
@@ -15554,10 +15554,10 @@
         <v>46211</v>
       </c>
       <c r="B107" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="27" t="s">
         <v>283</v>
-      </c>
-      <c r="C107" s="27" t="s">
-        <v>284</v>
       </c>
       <c r="D107" s="28"/>
       <c r="E107" s="29">
@@ -15606,10 +15606,10 @@
         <v>46212</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="39">
@@ -15658,10 +15658,10 @@
         <v>46212</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D109" s="28"/>
       <c r="E109" s="29">
@@ -15710,7 +15710,7 @@
         <v>46212</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C110" s="37" t="s">
         <v>182</v>
@@ -15762,10 +15762,10 @@
         <v>46212</v>
       </c>
       <c r="B111" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C111" s="27" t="s">
         <v>290</v>
-      </c>
-      <c r="C111" s="27" t="s">
-        <v>291</v>
       </c>
       <c r="D111" s="28"/>
       <c r="E111" s="29">
@@ -15814,10 +15814,10 @@
         <v>46212</v>
       </c>
       <c r="B112" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="C112" s="37" t="s">
         <v>292</v>
-      </c>
-      <c r="C112" s="37" t="s">
-        <v>293</v>
       </c>
       <c r="D112" s="38"/>
       <c r="E112" s="39">
@@ -27076,7 +27076,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="168" t="s">
+      <c r="A4" s="169" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="153"/>
@@ -28387,7 +28387,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="168" t="s">
+      <c r="A55" s="169" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="153"/>
@@ -28401,7 +28401,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="170" t="s">
+      <c r="A56" s="168" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="153"/>
@@ -29712,7 +29712,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="170" t="s">
+      <c r="A107" s="168" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="153"/>
@@ -29735,7 +29735,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="169">
+      <c r="E108" s="170">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -29744,17 +29744,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB60B08C-BBDC-4606-96B7-4820436BAB65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D40B88-F5D5-49BB-98B1-43C5E4637B0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="308">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -924,6 +924,48 @@
   </si>
   <si>
     <t>عطريات عدد8 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-93</t>
+  </si>
+  <si>
+    <t>Inv-94</t>
+  </si>
+  <si>
+    <t>متنوع عدد 2 الحبه 2.500</t>
+  </si>
+  <si>
+    <t>متنوع عدد 12 الحبه 2</t>
+  </si>
+  <si>
+    <t>حبل تعليق</t>
+  </si>
+  <si>
+    <t>Inv-95</t>
+  </si>
+  <si>
+    <t>ربل عدد 1 الحبه 2</t>
+  </si>
+  <si>
+    <t>مهندس عامر</t>
+  </si>
+  <si>
+    <t>Inv-96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دارسينا عدد 1 الحبه 2 </t>
+  </si>
+  <si>
+    <t>افوبيا عدد 1 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-97</t>
+  </si>
+  <si>
+    <t>Inv-98</t>
+  </si>
+  <si>
+    <t>دارسينا عدد 1 الحبه 2</t>
   </si>
 </sst>
 </file>
@@ -1628,7 +1670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2032,6 +2074,9 @@
     </xf>
     <xf numFmtId="168" fontId="41" fillId="48" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2446,45 +2491,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="147"/>
+      <c r="A1" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="148" t="s">
+      <c r="A2" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="147"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="148"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>77.550000000000011</v>
+        <v>111.62500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="151"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="147"/>
+      <c r="A3" s="152"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="148"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="147"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -4899,185 +4944,185 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="142" t="str">
+      <c r="A98" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(93,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46217</v>
       </c>
       <c r="B98" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(93,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-93</v>
       </c>
       <c r="C98" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(93,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="123" t="str">
+        <v>متنوع عدد 2 الحبه 2.500</v>
+      </c>
+      <c r="D98" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(93,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="124" t="str">
+        <v>5</v>
+      </c>
+      <c r="E98" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(93,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F98" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>82.550000000000011</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="142" t="str">
+      <c r="A99" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(94,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46217</v>
       </c>
       <c r="B99" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(94,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-94</v>
       </c>
       <c r="C99" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(94,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D99" s="123" t="str">
+        <v>متنوع عدد 12 الحبه 2</v>
+      </c>
+      <c r="D99" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(94,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E99" s="124" t="str">
+        <v>24</v>
+      </c>
+      <c r="E99" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(94,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F99" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>106.55000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="142" t="str">
+      <c r="A100" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(95,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B100" s="122" t="str">
+        <v>46217</v>
+      </c>
+      <c r="B100" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(95,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C100" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(95,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D100" s="123" t="str">
+        <v>حبل تعليق</v>
+      </c>
+      <c r="D100" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(95,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E100" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E100" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(95,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F100" s="125" t="str">
+        <v>1.925</v>
+      </c>
+      <c r="F100" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>104.62500000000001</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="142" t="str">
+      <c r="A101" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(96,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46219</v>
       </c>
       <c r="B101" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(96,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-95</v>
       </c>
       <c r="C101" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(96,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D101" s="123" t="str">
+        <v>ربل عدد 1 الحبه 2</v>
+      </c>
+      <c r="D101" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(96,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E101" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E101" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(96,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F101" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F101" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>106.62500000000001</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="142" t="str">
+      <c r="A102" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(97,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46219</v>
       </c>
       <c r="B102" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(97,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-96</v>
       </c>
       <c r="C102" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(97,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D102" s="123" t="str">
+        <v xml:space="preserve">دارسينا عدد 1 الحبه 2 </v>
+      </c>
+      <c r="D102" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(97,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E102" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E102" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(97,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F102" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F102" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>108.62500000000001</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="142" t="str">
+      <c r="A103" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(98,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46221</v>
       </c>
       <c r="B103" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(98,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-97</v>
       </c>
       <c r="C103" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(98,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D103" s="123" t="str">
+        <v>افوبيا عدد 1 الحبه 1</v>
+      </c>
+      <c r="D103" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(98,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E103" s="124" t="str">
+        <v>1</v>
+      </c>
+      <c r="E103" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(98,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F103" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F103" s="125">
         <f t="shared" ref="F103:F134" si="3">IF($A103="","",IF($F102="",0,$F102)+IF($D103="",0,$D103)-IF($E103="",0,$E103))</f>
-        <v/>
+        <v>109.62500000000001</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="142" t="str">
+      <c r="A104" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(99,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46221</v>
       </c>
       <c r="B104" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(99,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-98</v>
       </c>
       <c r="C104" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(99,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D104" s="123" t="str">
+        <v>دارسينا عدد 1 الحبه 2</v>
+      </c>
+      <c r="D104" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(99,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E104" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E104" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(99,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F104" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F104" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>111.62500000000001</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7714,26 +7759,26 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>629.6</v>
+        <v>665.6</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>552.04999999999995</v>
+        <v>553.97499999999991</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>77.550000000000011</v>
+        <v>111.62500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="145" t="s">
+      <c r="A208" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="146"/>
-      <c r="C208" s="146"/>
-      <c r="D208" s="146"/>
-      <c r="E208" s="146"/>
-      <c r="F208" s="147"/>
+      <c r="B208" s="147"/>
+      <c r="C208" s="147"/>
+      <c r="D208" s="147"/>
+      <c r="E208" s="147"/>
+      <c r="F208" s="148"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10131,38 +10176,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="156" t="s">
+      <c r="E2" s="157" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -15862,18 +15907,30 @@
       </c>
     </row>
     <row r="113" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="25"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="27"/>
+      <c r="A113" s="25">
+        <v>46217</v>
+      </c>
+      <c r="B113" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>296</v>
+      </c>
       <c r="D113" s="28"/>
-      <c r="E113" s="29"/>
-      <c r="F113" s="30"/>
+      <c r="E113" s="29">
+        <v>5</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G113" s="31"/>
-      <c r="H113" s="32"/>
+      <c r="H113" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I113" s="33"/>
-      <c r="J113" s="34" t="str">
+      <c r="J113" s="34">
         <f>IF(AND(D113="",E113="",A113="",B113="",C113=""),"", IFERROR(IF(J112="",D2,J112),D2)+IF(E113="",0,E113)-IF(OR(G113="أبو اسحاق",G113="أبو آدم",G113="أبو اسحاق ",G113="أبو آدم "),0,IF(D113="",0,D113)))</f>
-        <v/>
+        <v>82.550000000000011</v>
       </c>
       <c r="K113" s="35"/>
       <c r="L113">
@@ -15892,9 +15949,9 @@
         <f>IF(AND(D112&gt;0,F112="أحد الشركاء"),COUNTIFS($D$4:D112,"&gt;"&amp;0,$F$4:F112,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P113" t="str">
+      <c r="P113">
         <f>IF(OR($A113="",$F113="أحد الشركاء",AND($D113="",$E113="")),"",SUMPRODUCT(($A$4:$A113&lt;&gt;"")*($F$4:$F113&lt;&gt;"أحد الشركاء")*((($D$4:$D113&lt;&gt;"")+($E$4:$E113&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="Q113" t="str">
         <f>IF(OR($A113="",$F113&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A113,"&lt;&gt;",$F$4:F113,"أحد الشركاء"))</f>
@@ -15902,23 +15959,35 @@
       </c>
     </row>
     <row r="114" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="139"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="37"/>
+      <c r="A114" s="139">
+        <v>46217</v>
+      </c>
+      <c r="B114" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="C114" s="37" t="s">
+        <v>297</v>
+      </c>
       <c r="D114" s="38"/>
-      <c r="E114" s="39"/>
-      <c r="F114" s="136"/>
+      <c r="E114" s="39">
+        <v>24</v>
+      </c>
+      <c r="F114" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G114" s="40"/>
-      <c r="H114" s="41"/>
+      <c r="H114" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I114" s="42"/>
-      <c r="J114" s="43" t="str">
+      <c r="J114" s="43">
         <f>IF(AND(D114="",E114="",A114="",B114="",C114=""),"", IFERROR(IF(J113="",D2,J113),D2)+IF(E114="",0,E114)-IF(OR(G114="أبو اسحاق",G114="أبو آدم",G114="أبو اسحاق ",G114="أبو آدم "),0,IF(D114="",0,D114)))</f>
-        <v/>
+        <v>106.55000000000001</v>
       </c>
       <c r="K114" s="44"/>
-      <c r="L114" t="str">
+      <c r="L114">
         <f>IF(E113&gt;0,COUNTIF($E$4:E113,"&gt;0"),"")</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="M114" t="str">
         <f>IF(AND(D113&gt;0,G113="المحفظة"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$G$4:G113,"المحفظة"),"")</f>
@@ -15932,9 +16001,9 @@
         <f>IF(AND(D113&gt;0,F113="أحد الشركاء"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$F$4:F113,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P114" t="str">
+      <c r="P114">
         <f>IF(OR($A114="",$F114="أحد الشركاء",AND($D114="",$E114="")),"",SUMPRODUCT(($A$4:$A114&lt;&gt;"")*($F$4:$F114&lt;&gt;"أحد الشركاء")*((($D$4:$D114&lt;&gt;"")+($E$4:$E114&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="Q114" t="str">
         <f>IF(OR($A114="",$F114&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A114,"&lt;&gt;",$F$4:F114,"أحد الشركاء"))</f>
@@ -15942,23 +16011,35 @@
       </c>
     </row>
     <row r="115" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="25"/>
+      <c r="A115" s="25">
+        <v>46217</v>
+      </c>
       <c r="B115" s="26"/>
-      <c r="C115" s="27"/>
-      <c r="D115" s="28"/>
+      <c r="C115" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D115" s="28">
+        <v>1.925</v>
+      </c>
       <c r="E115" s="29"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="31"/>
-      <c r="H115" s="32"/>
+      <c r="F115" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I115" s="33"/>
-      <c r="J115" s="34" t="str">
+      <c r="J115" s="34">
         <f>IF(AND(D115="",E115="",A115="",B115="",C115=""),"", IFERROR(IF(J114="",D2,J114),D2)+IF(E115="",0,E115)-IF(OR(G115="أبو اسحاق",G115="أبو آدم",G115="أبو اسحاق ",G115="أبو آدم "),0,IF(D115="",0,D115)))</f>
-        <v/>
+        <v>104.62500000000001</v>
       </c>
       <c r="K115" s="35"/>
-      <c r="L115" t="str">
+      <c r="L115">
         <f>IF(E114&gt;0,COUNTIF($E$4:E114,"&gt;0"),"")</f>
-        <v/>
+        <v>79</v>
       </c>
       <c r="M115" t="str">
         <f>IF(AND(D114&gt;0,G114="المحفظة"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$G$4:G114,"المحفظة"),"")</f>
@@ -15972,9 +16053,9 @@
         <f>IF(AND(D114&gt;0,F114="أحد الشركاء"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$F$4:F114,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P115" t="str">
+      <c r="P115">
         <f>IF(OR($A115="",$F115="أحد الشركاء",AND($D115="",$E115="")),"",SUMPRODUCT(($A$4:$A115&lt;&gt;"")*($F$4:$F115&lt;&gt;"أحد الشركاء")*((($D$4:$D115&lt;&gt;"")+($E$4:$E115&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="Q115" t="str">
         <f>IF(OR($A115="",$F115&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A115,"&lt;&gt;",$F$4:F115,"أحد الشركاء"))</f>
@@ -15982,27 +16063,41 @@
       </c>
     </row>
     <row r="116" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="139"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="37"/>
+      <c r="A116" s="139">
+        <v>46219</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="C116" s="37" t="s">
+        <v>300</v>
+      </c>
       <c r="D116" s="38"/>
-      <c r="E116" s="39"/>
-      <c r="F116" s="136"/>
+      <c r="E116" s="39">
+        <v>2</v>
+      </c>
+      <c r="F116" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G116" s="40"/>
-      <c r="H116" s="41"/>
+      <c r="H116" s="41" t="s">
+        <v>50</v>
+      </c>
       <c r="I116" s="42"/>
-      <c r="J116" s="43" t="str">
+      <c r="J116" s="43">
         <f>IF(AND(D116="",E116="",A116="",B116="",C116=""),"", IFERROR(IF(J115="",D2,J115),D2)+IF(E116="",0,E116)-IF(OR(G116="أبو اسحاق",G116="أبو آدم",G116="أبو اسحاق ",G116="أبو آدم "),0,IF(D116="",0,D116)))</f>
-        <v/>
-      </c>
-      <c r="K116" s="44"/>
+        <v>106.62500000000001</v>
+      </c>
+      <c r="K116" s="44" t="s">
+        <v>301</v>
+      </c>
       <c r="L116" t="str">
         <f>IF(E115&gt;0,COUNTIF($E$4:E115,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M116" t="str">
+      <c r="M116">
         <f>IF(AND(D115&gt;0,G115="المحفظة"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$G$4:G115,"المحفظة"),"")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="N116" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A116)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A116)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A116&lt;&gt;""),IFERROR(MAX($N$4:N115),0)+1,"")</f>
@@ -16012,9 +16107,9 @@
         <f>IF(AND(D115&gt;0,F115="أحد الشركاء"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$F$4:F115,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P116" t="str">
+      <c r="P116">
         <f>IF(OR($A116="",$F116="أحد الشركاء",AND($D116="",$E116="")),"",SUMPRODUCT(($A$4:$A116&lt;&gt;"")*($F$4:$F116&lt;&gt;"أحد الشركاء")*((($D$4:$D116&lt;&gt;"")+($E$4:$E116&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="Q116" t="str">
         <f>IF(OR($A116="",$F116&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A116,"&lt;&gt;",$F$4:F116,"أحد الشركاء"))</f>
@@ -16022,23 +16117,37 @@
       </c>
     </row>
     <row r="117" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="25"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="145">
+        <v>46219</v>
+      </c>
+      <c r="B117" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>303</v>
+      </c>
       <c r="D117" s="28"/>
-      <c r="E117" s="29"/>
-      <c r="F117" s="30"/>
+      <c r="E117" s="29">
+        <v>2</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G117" s="31"/>
-      <c r="H117" s="32"/>
+      <c r="H117" s="32" t="s">
+        <v>50</v>
+      </c>
       <c r="I117" s="33"/>
-      <c r="J117" s="34" t="str">
+      <c r="J117" s="34">
         <f>IF(AND(D117="",E117="",A117="",B117="",C117=""),"", IFERROR(IF(J116="",D2,J116),D2)+IF(E117="",0,E117)-IF(OR(G117="أبو اسحاق",G117="أبو آدم",G117="أبو اسحاق ",G117="أبو آدم "),0,IF(D117="",0,D117)))</f>
-        <v/>
-      </c>
-      <c r="K117" s="35"/>
-      <c r="L117" t="str">
+        <v>108.62500000000001</v>
+      </c>
+      <c r="K117" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="L117">
         <f>IF(E116&gt;0,COUNTIF($E$4:E116,"&gt;0"),"")</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="M117" t="str">
         <f>IF(AND(D116&gt;0,G116="المحفظة"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$G$4:G116,"المحفظة"),"")</f>
@@ -16052,9 +16161,9 @@
         <f>IF(AND(D116&gt;0,F116="أحد الشركاء"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$F$4:F116,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P117" t="str">
+      <c r="P117">
         <f>IF(OR($A117="",$F117="أحد الشركاء",AND($D117="",$E117="")),"",SUMPRODUCT(($A$4:$A117&lt;&gt;"")*($F$4:$F117&lt;&gt;"أحد الشركاء")*((($D$4:$D117&lt;&gt;"")+($E$4:$E117&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="Q117" t="str">
         <f>IF(OR($A117="",$F117&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A117,"&lt;&gt;",$F$4:F117,"أحد الشركاء"))</f>
@@ -16062,23 +16171,35 @@
       </c>
     </row>
     <row r="118" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="139"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="37"/>
+      <c r="A118" s="139">
+        <v>46221</v>
+      </c>
+      <c r="B118" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="C118" s="37" t="s">
+        <v>304</v>
+      </c>
       <c r="D118" s="38"/>
-      <c r="E118" s="39"/>
-      <c r="F118" s="136"/>
+      <c r="E118" s="39">
+        <v>1</v>
+      </c>
+      <c r="F118" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G118" s="40"/>
-      <c r="H118" s="41"/>
+      <c r="H118" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I118" s="42"/>
-      <c r="J118" s="43" t="str">
+      <c r="J118" s="43">
         <f>IF(AND(D118="",E118="",A118="",B118="",C118=""),"", IFERROR(IF(J117="",D2,J117),D2)+IF(E118="",0,E118)-IF(OR(G118="أبو اسحاق",G118="أبو آدم",G118="أبو اسحاق ",G118="أبو آدم "),0,IF(D118="",0,D118)))</f>
-        <v/>
+        <v>109.62500000000001</v>
       </c>
       <c r="K118" s="44"/>
-      <c r="L118" t="str">
+      <c r="L118">
         <f>IF(E117&gt;0,COUNTIF($E$4:E117,"&gt;0"),"")</f>
-        <v/>
+        <v>81</v>
       </c>
       <c r="M118" t="str">
         <f>IF(AND(D117&gt;0,G117="المحفظة"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$G$4:G117,"المحفظة"),"")</f>
@@ -16092,9 +16213,9 @@
         <f>IF(AND(D117&gt;0,F117="أحد الشركاء"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$F$4:F117,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P118" t="str">
+      <c r="P118">
         <f>IF(OR($A118="",$F118="أحد الشركاء",AND($D118="",$E118="")),"",SUMPRODUCT(($A$4:$A118&lt;&gt;"")*($F$4:$F118&lt;&gt;"أحد الشركاء")*((($D$4:$D118&lt;&gt;"")+($E$4:$E118&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="Q118" t="str">
         <f>IF(OR($A118="",$F118&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A118,"&lt;&gt;",$F$4:F118,"أحد الشركاء"))</f>
@@ -16102,23 +16223,35 @@
       </c>
     </row>
     <row r="119" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="25"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="145">
+        <v>46221</v>
+      </c>
+      <c r="B119" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>307</v>
+      </c>
       <c r="D119" s="28"/>
-      <c r="E119" s="29"/>
-      <c r="F119" s="30"/>
+      <c r="E119" s="29">
+        <v>2</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G119" s="31"/>
-      <c r="H119" s="32"/>
+      <c r="H119" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I119" s="33"/>
-      <c r="J119" s="34" t="str">
+      <c r="J119" s="34">
         <f>IF(AND(D119="",E119="",A119="",B119="",C119=""),"", IFERROR(IF(J118="",D2,J118),D2)+IF(E119="",0,E119)-IF(OR(G119="أبو اسحاق",G119="أبو آدم",G119="أبو اسحاق ",G119="أبو آدم "),0,IF(D119="",0,D119)))</f>
-        <v/>
+        <v>111.62500000000001</v>
       </c>
       <c r="K119" s="35"/>
-      <c r="L119" t="str">
+      <c r="L119">
         <f>IF(E118&gt;0,COUNTIF($E$4:E118,"&gt;0"),"")</f>
-        <v/>
+        <v>82</v>
       </c>
       <c r="M119" t="str">
         <f>IF(AND(D118&gt;0,G118="المحفظة"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$G$4:G118,"المحفظة"),"")</f>
@@ -16132,9 +16265,9 @@
         <f>IF(AND(D118&gt;0,F118="أحد الشركاء"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$F$4:F118,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P119" t="str">
+      <c r="P119">
         <f>IF(OR($A119="",$F119="أحد الشركاء",AND($D119="",$E119="")),"",SUMPRODUCT(($A$4:$A119&lt;&gt;"")*($F$4:$F119&lt;&gt;"أحد الشركاء")*((($D$4:$D119&lt;&gt;"")+($E$4:$E119&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="Q119" t="str">
         <f>IF(OR($A119="",$F119&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A119,"&lt;&gt;",$F$4:F119,"أحد الشركاء"))</f>
@@ -16156,9 +16289,9 @@
         <v/>
       </c>
       <c r="K120" s="44"/>
-      <c r="L120" t="str">
+      <c r="L120">
         <f>IF(E119&gt;0,COUNTIF($E$4:E119,"&gt;0"),"")</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="M120" t="str">
         <f>IF(AND(D119&gt;0,G119="المحفظة"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$G$4:G119,"المحفظة"),"")</f>
@@ -19502,14 +19635,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="159"/>
-      <c r="B204" s="153"/>
-      <c r="C204" s="154"/>
+      <c r="A204" s="160"/>
+      <c r="B204" s="154"/>
+      <c r="C204" s="155"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="152"/>
-      <c r="G204" s="153"/>
-      <c r="H204" s="154"/>
+      <c r="F204" s="153"/>
+      <c r="G204" s="154"/>
+      <c r="H204" s="155"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -19549,15 +19682,15 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>1574.55</v>
+        <v>1576.4749999999999</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>629.6</v>
+        <v>665.6</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G205" s="137"/>
       <c r="H205" s="137"/>
@@ -19644,11 +19777,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="161" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -19806,16 +19939,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="153"/>
+      <c r="B1" s="154"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="162" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="153"/>
+      <c r="B2" s="154"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -19834,10 +19967,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="162" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="153"/>
+      <c r="B5" s="154"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -19880,10 +20013,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="161" t="s">
+      <c r="A11" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="153"/>
+      <c r="B11" s="154"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -19948,47 +20081,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163"/>
-      <c r="B2" s="153"/>
+      <c r="A2" s="164"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="163">
+      <c r="D2" s="164">
         <v>2026</v>
       </c>
-      <c r="E2" s="153"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="166" t="s">
+      <c r="G2" s="167" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="168" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="154"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -26930,11 +27063,11 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="164" t="s">
+      <c r="A155" s="165" t="s">
         <v>266</v>
       </c>
-      <c r="B155" s="153"/>
-      <c r="C155" s="153"/>
+      <c r="B155" s="154"/>
+      <c r="C155" s="154"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
         <v>724.8</v>
@@ -26943,12 +27076,12 @@
         <f>SUM(E5:E154)</f>
         <v>195.5</v>
       </c>
-      <c r="F155" s="165">
+      <c r="F155" s="166">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>3</v>
       </c>
-      <c r="G155" s="153"/>
-      <c r="H155" s="153"/>
+      <c r="G155" s="154"/>
+      <c r="H155" s="154"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
@@ -27031,60 +27164,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="164" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="163" t="s">
+      <c r="D2" s="164" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="153"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="168" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="153"/>
+      <c r="B3" s="154"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="167" t="s">
+      <c r="D3" s="168" t="s">
         <v>273</v>
       </c>
-      <c r="E3" s="153"/>
+      <c r="E3" s="154"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="169" t="s">
+      <c r="A4" s="170" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -28387,12 +28520,12 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="169" t="s">
+      <c r="A55" s="170" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="153"/>
-      <c r="C55" s="153"/>
-      <c r="D55" s="153"/>
+      <c r="B55" s="154"/>
+      <c r="C55" s="154"/>
+      <c r="D55" s="154"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -28401,15 +28534,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="168" t="s">
+      <c r="A56" s="169" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="153"/>
-      <c r="C56" s="153"/>
-      <c r="D56" s="153"/>
-      <c r="E56" s="153"/>
-      <c r="F56" s="153"/>
-      <c r="G56" s="153"/>
+      <c r="B56" s="154"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="154"/>
+      <c r="E56" s="154"/>
+      <c r="F56" s="154"/>
+      <c r="G56" s="154"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -29712,11 +29845,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="168" t="s">
+      <c r="A107" s="169" t="s">
         <v>277</v>
       </c>
-      <c r="B107" s="153"/>
-      <c r="C107" s="153"/>
+      <c r="B107" s="154"/>
+      <c r="C107" s="154"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -29726,21 +29859,21 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="164" t="s">
+      <c r="A108" s="165" t="s">
         <v>278</v>
       </c>
-      <c r="B108" s="153"/>
-      <c r="C108" s="153"/>
+      <c r="B108" s="154"/>
+      <c r="C108" s="154"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="170">
+      <c r="E108" s="171">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="153"/>
-      <c r="G108" s="154"/>
+      <c r="F108" s="154"/>
+      <c r="G108" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D40B88-F5D5-49BB-98B1-43C5E4637B0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437AA31C-524B-4691-AE98-39E374D6DAFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="311">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -966,6 +966,15 @@
   </si>
   <si>
     <t>دارسينا عدد 1 الحبه 2</t>
+  </si>
+  <si>
+    <t>Inv-99</t>
+  </si>
+  <si>
+    <t>افوبيا عدد 9 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-100</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +1679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2081,6 +2090,9 @@
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="46" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -2140,14 +2152,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2491,45 +2503,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="A1" s="151" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="148"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="149"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>111.62500000000001</v>
+        <v>142.625</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="152"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
+      <c r="A3" s="153"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="149"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="151" t="s">
+      <c r="A4" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="148"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="149"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -5126,55 +5138,55 @@
       </c>
     </row>
     <row r="105" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="142" t="str">
+      <c r="A105" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(100,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46224</v>
       </c>
       <c r="B105" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(100,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-99</v>
       </c>
       <c r="C105" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(100,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D105" s="123" t="str">
+        <v>افوبيا عدد 9 الحبه 1</v>
+      </c>
+      <c r="D105" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(100,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E105" s="124" t="str">
+        <v>9</v>
+      </c>
+      <c r="E105" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(100,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F105" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F105" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>120.62500000000001</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="142" t="str">
+      <c r="A106" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(101,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46224</v>
       </c>
       <c r="B106" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(101,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-100</v>
       </c>
       <c r="C106" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(101,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D106" s="123" t="str">
+        <v>ربل عدد 11 الحبه 2</v>
+      </c>
+      <c r="D106" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(101,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E106" s="124" t="str">
+        <v>22</v>
+      </c>
+      <c r="E106" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(101,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F106" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F106" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>142.625</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7759,7 +7771,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>665.6</v>
+        <v>696.6</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7767,18 +7779,18 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>111.62500000000001</v>
+        <v>142.625</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="146" t="s">
+      <c r="A208" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="147"/>
-      <c r="C208" s="147"/>
-      <c r="D208" s="147"/>
-      <c r="E208" s="147"/>
-      <c r="F208" s="148"/>
+      <c r="B208" s="148"/>
+      <c r="C208" s="148"/>
+      <c r="D208" s="148"/>
+      <c r="E208" s="148"/>
+      <c r="F208" s="149"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10176,38 +10188,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="157" t="s">
+      <c r="E2" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -16275,18 +16287,30 @@
       </c>
     </row>
     <row r="120" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="139"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="37"/>
+      <c r="A120" s="139">
+        <v>46224</v>
+      </c>
+      <c r="B120" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" s="37" t="s">
+        <v>309</v>
+      </c>
       <c r="D120" s="38"/>
-      <c r="E120" s="39"/>
-      <c r="F120" s="136"/>
+      <c r="E120" s="39">
+        <v>9</v>
+      </c>
+      <c r="F120" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G120" s="40"/>
-      <c r="H120" s="41"/>
+      <c r="H120" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I120" s="42"/>
-      <c r="J120" s="43" t="str">
+      <c r="J120" s="43">
         <f>IF(AND(D120="",E120="",A120="",B120="",C120=""),"", IFERROR(IF(J119="",D2,J119),D2)+IF(E120="",0,E120)-IF(OR(G120="أبو اسحاق",G120="أبو آدم",G120="أبو اسحاق ",G120="أبو آدم "),0,IF(D120="",0,D120)))</f>
-        <v/>
+        <v>120.62500000000001</v>
       </c>
       <c r="K120" s="44"/>
       <c r="L120">
@@ -16305,9 +16329,9 @@
         <f>IF(AND(D119&gt;0,F119="أحد الشركاء"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$F$4:F119,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P120" t="str">
+      <c r="P120">
         <f>IF(OR($A120="",$F120="أحد الشركاء",AND($D120="",$E120="")),"",SUMPRODUCT(($A$4:$A120&lt;&gt;"")*($F$4:$F120&lt;&gt;"أحد الشركاء")*((($D$4:$D120&lt;&gt;"")+($E$4:$E120&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="Q120" t="str">
         <f>IF(OR($A120="",$F120&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A120,"&lt;&gt;",$F$4:F120,"أحد الشركاء"))</f>
@@ -16315,23 +16339,35 @@
       </c>
     </row>
     <row r="121" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="25"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="146">
+        <v>46224</v>
+      </c>
+      <c r="B121" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>188</v>
+      </c>
       <c r="D121" s="28"/>
-      <c r="E121" s="29"/>
-      <c r="F121" s="30"/>
+      <c r="E121" s="29">
+        <v>22</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G121" s="31"/>
-      <c r="H121" s="32"/>
+      <c r="H121" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I121" s="33"/>
-      <c r="J121" s="34" t="str">
+      <c r="J121" s="34">
         <f>IF(AND(D121="",E121="",A121="",B121="",C121=""),"", IFERROR(IF(J120="",D2,J120),D2)+IF(E121="",0,E121)-IF(OR(G121="أبو اسحاق",G121="أبو آدم",G121="أبو اسحاق ",G121="أبو آدم "),0,IF(D121="",0,D121)))</f>
-        <v/>
+        <v>142.625</v>
       </c>
       <c r="K121" s="35"/>
-      <c r="L121" t="str">
+      <c r="L121">
         <f>IF(E120&gt;0,COUNTIF($E$4:E120,"&gt;0"),"")</f>
-        <v/>
+        <v>84</v>
       </c>
       <c r="M121" t="str">
         <f>IF(AND(D120&gt;0,G120="المحفظة"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$G$4:G120,"المحفظة"),"")</f>
@@ -16345,9 +16381,9 @@
         <f>IF(AND(D120&gt;0,F120="أحد الشركاء"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$F$4:F120,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P121" t="str">
+      <c r="P121">
         <f>IF(OR($A121="",$F121="أحد الشركاء",AND($D121="",$E121="")),"",SUMPRODUCT(($A$4:$A121&lt;&gt;"")*($F$4:$F121&lt;&gt;"أحد الشركاء")*((($D$4:$D121&lt;&gt;"")+($E$4:$E121&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>101</v>
       </c>
       <c r="Q121" t="str">
         <f>IF(OR($A121="",$F121&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A121,"&lt;&gt;",$F$4:F121,"أحد الشركاء"))</f>
@@ -16369,9 +16405,9 @@
         <v/>
       </c>
       <c r="K122" s="44"/>
-      <c r="L122" t="str">
+      <c r="L122">
         <f>IF(E121&gt;0,COUNTIF($E$4:E121,"&gt;0"),"")</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="M122" t="str">
         <f>IF(AND(D121&gt;0,G121="المحفظة"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$G$4:G121,"المحفظة"),"")</f>
@@ -19635,14 +19671,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="160"/>
-      <c r="B204" s="154"/>
-      <c r="C204" s="155"/>
+      <c r="A204" s="161"/>
+      <c r="B204" s="155"/>
+      <c r="C204" s="156"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="153"/>
-      <c r="G204" s="154"/>
-      <c r="H204" s="155"/>
+      <c r="F204" s="154"/>
+      <c r="G204" s="155"/>
+      <c r="H204" s="156"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -19686,7 +19722,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>665.6</v>
+        <v>696.6</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -19777,11 +19813,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="162" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -19939,16 +19975,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="154"/>
+      <c r="B1" s="155"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="163" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="154"/>
+      <c r="B2" s="155"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -19967,10 +20003,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="163" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="154"/>
+      <c r="B5" s="155"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -20013,10 +20049,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="162" t="s">
+      <c r="A11" s="163" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="154"/>
+      <c r="B11" s="155"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -20081,47 +20117,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="164"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="165"/>
+      <c r="B2" s="155"/>
       <c r="C2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="164">
+      <c r="D2" s="165">
         <v>2026</v>
       </c>
-      <c r="E2" s="154"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="167" t="s">
+      <c r="G2" s="168" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="168" t="s">
+      <c r="A3" s="169" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="154"/>
-      <c r="C3" s="154"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -27063,11 +27099,11 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="165" t="s">
+      <c r="A155" s="166" t="s">
         <v>266</v>
       </c>
-      <c r="B155" s="154"/>
-      <c r="C155" s="154"/>
+      <c r="B155" s="155"/>
+      <c r="C155" s="155"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
         <v>724.8</v>
@@ -27076,12 +27112,12 @@
         <f>SUM(E5:E154)</f>
         <v>195.5</v>
       </c>
-      <c r="F155" s="166">
+      <c r="F155" s="167">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>3</v>
       </c>
-      <c r="G155" s="154"/>
-      <c r="H155" s="154"/>
+      <c r="G155" s="155"/>
+      <c r="H155" s="155"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
@@ -27164,45 +27200,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="154"/>
+      <c r="B2" s="155"/>
       <c r="C2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="164" t="s">
+      <c r="D2" s="165" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="154"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="168" t="s">
+      <c r="A3" s="169" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="154"/>
+      <c r="B3" s="155"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="168" t="s">
+      <c r="D3" s="169" t="s">
         <v>273</v>
       </c>
-      <c r="E3" s="154"/>
+      <c r="E3" s="155"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
@@ -27212,12 +27248,12 @@
       <c r="A4" s="170" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -28523,9 +28559,9 @@
       <c r="A55" s="170" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="154"/>
-      <c r="C55" s="154"/>
-      <c r="D55" s="154"/>
+      <c r="B55" s="155"/>
+      <c r="C55" s="155"/>
+      <c r="D55" s="155"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -28534,15 +28570,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="169" t="s">
+      <c r="A56" s="172" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="154"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="154"/>
-      <c r="E56" s="154"/>
-      <c r="F56" s="154"/>
-      <c r="G56" s="154"/>
+      <c r="B56" s="155"/>
+      <c r="C56" s="155"/>
+      <c r="D56" s="155"/>
+      <c r="E56" s="155"/>
+      <c r="F56" s="155"/>
+      <c r="G56" s="155"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -29845,11 +29881,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="169" t="s">
+      <c r="A107" s="172" t="s">
         <v>277</v>
       </c>
-      <c r="B107" s="154"/>
-      <c r="C107" s="154"/>
+      <c r="B107" s="155"/>
+      <c r="C107" s="155"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -29859,11 +29895,11 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="165" t="s">
+      <c r="A108" s="166" t="s">
         <v>278</v>
       </c>
-      <c r="B108" s="154"/>
-      <c r="C108" s="154"/>
+      <c r="B108" s="155"/>
+      <c r="C108" s="155"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
@@ -29872,22 +29908,22 @@
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="154"/>
-      <c r="G108" s="155"/>
+      <c r="F108" s="155"/>
+      <c r="G108" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437AA31C-524B-4691-AE98-39E374D6DAFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1E4BE2-436A-4FA4-BAC8-AB7FB4DC96DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="315">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -975,6 +975,18 @@
   </si>
   <si>
     <t>Inv-100</t>
+  </si>
+  <si>
+    <t>Inv-101</t>
+  </si>
+  <si>
+    <t>افوبيا عدد2 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-102</t>
+  </si>
+  <si>
+    <t>متنوع عدد2 الحبه 1</t>
   </si>
 </sst>
 </file>
@@ -2152,14 +2164,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2522,7 +2534,7 @@
       <c r="E2" s="149"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>142.625</v>
+        <v>146.625</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5190,55 +5202,55 @@
       </c>
     </row>
     <row r="107" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="142" t="str">
+      <c r="A107" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(102,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46225</v>
       </c>
       <c r="B107" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(102,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-101</v>
       </c>
       <c r="C107" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(102,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D107" s="123" t="str">
+        <v>افوبيا عدد2 الحبه 1</v>
+      </c>
+      <c r="D107" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(102,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E107" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E107" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(102,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F107" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F107" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>144.625</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="142" t="str">
+      <c r="A108" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(103,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46227</v>
       </c>
       <c r="B108" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(103,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-102</v>
       </c>
       <c r="C108" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(103,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D108" s="123" t="str">
+        <v>متنوع عدد2 الحبه 1</v>
+      </c>
+      <c r="D108" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(103,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E108" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E108" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(103,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F108" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F108" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>146.625</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7771,7 +7783,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>696.6</v>
+        <v>700.6</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7779,7 +7791,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>142.625</v>
+        <v>146.625</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -16093,7 +16105,7 @@
       </c>
       <c r="G116" s="40"/>
       <c r="H116" s="41" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I116" s="42"/>
       <c r="J116" s="43">
@@ -16147,7 +16159,7 @@
       </c>
       <c r="G117" s="31"/>
       <c r="H117" s="32" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I117" s="33"/>
       <c r="J117" s="34">
@@ -16391,18 +16403,30 @@
       </c>
     </row>
     <row r="122" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="139"/>
-      <c r="B122" s="36"/>
-      <c r="C122" s="37"/>
+      <c r="A122" s="139">
+        <v>46225</v>
+      </c>
+      <c r="B122" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>312</v>
+      </c>
       <c r="D122" s="38"/>
-      <c r="E122" s="39"/>
-      <c r="F122" s="136"/>
+      <c r="E122" s="39">
+        <v>2</v>
+      </c>
+      <c r="F122" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G122" s="40"/>
-      <c r="H122" s="41"/>
+      <c r="H122" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I122" s="42"/>
-      <c r="J122" s="43" t="str">
+      <c r="J122" s="43">
         <f>IF(AND(D122="",E122="",A122="",B122="",C122=""),"", IFERROR(IF(J121="",D2,J121),D2)+IF(E122="",0,E122)-IF(OR(G122="أبو اسحاق",G122="أبو آدم",G122="أبو اسحاق ",G122="أبو آدم "),0,IF(D122="",0,D122)))</f>
-        <v/>
+        <v>144.625</v>
       </c>
       <c r="K122" s="44"/>
       <c r="L122">
@@ -16421,9 +16445,9 @@
         <f>IF(AND(D121&gt;0,F121="أحد الشركاء"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$F$4:F121,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P122" t="str">
+      <c r="P122">
         <f>IF(OR($A122="",$F122="أحد الشركاء",AND($D122="",$E122="")),"",SUMPRODUCT(($A$4:$A122&lt;&gt;"")*($F$4:$F122&lt;&gt;"أحد الشركاء")*((($D$4:$D122&lt;&gt;"")+($E$4:$E122&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>102</v>
       </c>
       <c r="Q122" t="str">
         <f>IF(OR($A122="",$F122&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A122,"&lt;&gt;",$F$4:F122,"أحد الشركاء"))</f>
@@ -16431,23 +16455,35 @@
       </c>
     </row>
     <row r="123" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="25"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="25">
+        <v>46227</v>
+      </c>
+      <c r="B123" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="C123" s="27" t="s">
+        <v>314</v>
+      </c>
       <c r="D123" s="28"/>
-      <c r="E123" s="29"/>
-      <c r="F123" s="30"/>
+      <c r="E123" s="29">
+        <v>2</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G123" s="31"/>
-      <c r="H123" s="32"/>
+      <c r="H123" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I123" s="33"/>
-      <c r="J123" s="34" t="str">
+      <c r="J123" s="34">
         <f>IF(AND(D123="",E123="",A123="",B123="",C123=""),"", IFERROR(IF(J122="",D2,J122),D2)+IF(E123="",0,E123)-IF(OR(G123="أبو اسحاق",G123="أبو آدم",G123="أبو اسحاق ",G123="أبو آدم "),0,IF(D123="",0,D123)))</f>
-        <v/>
+        <v>146.625</v>
       </c>
       <c r="K123" s="35"/>
-      <c r="L123" t="str">
+      <c r="L123">
         <f>IF(E122&gt;0,COUNTIF($E$4:E122,"&gt;0"),"")</f>
-        <v/>
+        <v>86</v>
       </c>
       <c r="M123" t="str">
         <f>IF(AND(D122&gt;0,G122="المحفظة"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$G$4:G122,"المحفظة"),"")</f>
@@ -16461,9 +16497,9 @@
         <f>IF(AND(D122&gt;0,F122="أحد الشركاء"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$F$4:F122,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P123" t="str">
+      <c r="P123">
         <f>IF(OR($A123="",$F123="أحد الشركاء",AND($D123="",$E123="")),"",SUMPRODUCT(($A$4:$A123&lt;&gt;"")*($F$4:$F123&lt;&gt;"أحد الشركاء")*((($D$4:$D123&lt;&gt;"")+($E$4:$E123&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>103</v>
       </c>
       <c r="Q123" t="str">
         <f>IF(OR($A123="",$F123&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A123,"&lt;&gt;",$F$4:F123,"أحد الشركاء"))</f>
@@ -16485,9 +16521,9 @@
         <v/>
       </c>
       <c r="K124" s="44"/>
-      <c r="L124" t="str">
+      <c r="L124">
         <f>IF(E123&gt;0,COUNTIF($E$4:E123,"&gt;0"),"")</f>
-        <v/>
+        <v>87</v>
       </c>
       <c r="M124" t="str">
         <f>IF(AND(D123&gt;0,G123="المحفظة"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$G$4:G123,"المحفظة"),"")</f>
@@ -19722,11 +19758,11 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>696.6</v>
+        <v>700.6</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G205" s="137"/>
       <c r="H205" s="137"/>
@@ -27245,7 +27281,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="170" t="s">
+      <c r="A4" s="171" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="155"/>
@@ -28556,7 +28592,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="170" t="s">
+      <c r="A55" s="171" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="155"/>
@@ -28570,7 +28606,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="172" t="s">
+      <c r="A56" s="170" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="155"/>
@@ -29881,7 +29917,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="172" t="s">
+      <c r="A107" s="170" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="155"/>
@@ -29904,7 +29940,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="171">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -29913,17 +29949,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1E4BE2-436A-4FA4-BAC8-AB7FB4DC96DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2243DC22-8DE7-4837-8A10-CAC89C4B8604}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="318">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -987,6 +987,15 @@
   </si>
   <si>
     <t>متنوع عدد2 الحبه 1</t>
+  </si>
+  <si>
+    <t>كوكوبيد</t>
+  </si>
+  <si>
+    <t>Inv-103</t>
+  </si>
+  <si>
+    <t>متفرقات</t>
   </si>
 </sst>
 </file>
@@ -2534,7 +2543,7 @@
       <c r="E2" s="149"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>146.625</v>
+        <v>124.125</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5254,81 +5263,81 @@
       </c>
     </row>
     <row r="109" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="142" t="str">
+      <c r="A109" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(104,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B109" s="122" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B109" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(104,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C109" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(104,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D109" s="123" t="str">
+        <v>كوكوبيد</v>
+      </c>
+      <c r="D109" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(104,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E109" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E109" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(104,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F109" s="125" t="str">
+        <v>10</v>
+      </c>
+      <c r="F109" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>136.625</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="142" t="str">
+      <c r="A110" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(105,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B110" s="122" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B110" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(105,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C110" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(105,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D110" s="123" t="str">
+        <v>احواض عدد 1000 مقاس 14 سم</v>
+      </c>
+      <c r="D110" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(105,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E110" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E110" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(105,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F110" s="125" t="str">
+        <v>20</v>
+      </c>
+      <c r="F110" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>116.625</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="142" t="str">
+      <c r="A111" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(106,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46594</v>
       </c>
       <c r="B111" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(106,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-103</v>
       </c>
       <c r="C111" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(106,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D111" s="123" t="str">
+        <v>متفرقات</v>
+      </c>
+      <c r="D111" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(106,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E111" s="124" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="E111" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(106,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F111" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F111" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>124.125</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7783,15 +7792,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>700.6</v>
+        <v>708.1</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>553.97499999999991</v>
+        <v>583.97499999999991</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>146.625</v>
+        <v>124.125</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -16507,18 +16516,30 @@
       </c>
     </row>
     <row r="124" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="139"/>
+      <c r="A124" s="139">
+        <v>46229</v>
+      </c>
       <c r="B124" s="36"/>
-      <c r="C124" s="37"/>
-      <c r="D124" s="38"/>
+      <c r="C124" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="D124" s="38">
+        <v>10</v>
+      </c>
       <c r="E124" s="39"/>
-      <c r="F124" s="136"/>
-      <c r="G124" s="40"/>
-      <c r="H124" s="41"/>
+      <c r="F124" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G124" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I124" s="42"/>
-      <c r="J124" s="43" t="str">
+      <c r="J124" s="43">
         <f>IF(AND(D124="",E124="",A124="",B124="",C124=""),"", IFERROR(IF(J123="",D2,J123),D2)+IF(E124="",0,E124)-IF(OR(G124="أبو اسحاق",G124="أبو آدم",G124="أبو اسحاق ",G124="أبو آدم "),0,IF(D124="",0,D124)))</f>
-        <v/>
+        <v>136.625</v>
       </c>
       <c r="K124" s="44"/>
       <c r="L124">
@@ -16537,9 +16558,9 @@
         <f>IF(AND(D123&gt;0,F123="أحد الشركاء"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$F$4:F123,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P124" t="str">
+      <c r="P124">
         <f>IF(OR($A124="",$F124="أحد الشركاء",AND($D124="",$E124="")),"",SUMPRODUCT(($A$4:$A124&lt;&gt;"")*($F$4:$F124&lt;&gt;"أحد الشركاء")*((($D$4:$D124&lt;&gt;"")+($E$4:$E124&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>104</v>
       </c>
       <c r="Q124" t="str">
         <f>IF(OR($A124="",$F124&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A124,"&lt;&gt;",$F$4:F124,"أحد الشركاء"))</f>
@@ -16547,27 +16568,39 @@
       </c>
     </row>
     <row r="125" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="25"/>
+      <c r="A125" s="25">
+        <v>46229</v>
+      </c>
       <c r="B125" s="26"/>
-      <c r="C125" s="27"/>
-      <c r="D125" s="28"/>
+      <c r="C125" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="D125" s="28">
+        <v>20</v>
+      </c>
       <c r="E125" s="29"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="31"/>
-      <c r="H125" s="32"/>
+      <c r="F125" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I125" s="33"/>
-      <c r="J125" s="34" t="str">
+      <c r="J125" s="34">
         <f>IF(AND(D125="",E125="",A125="",B125="",C125=""),"", IFERROR(IF(J124="",D2,J124),D2)+IF(E125="",0,E125)-IF(OR(G125="أبو اسحاق",G125="أبو آدم",G125="أبو اسحاق ",G125="أبو آدم "),0,IF(D125="",0,D125)))</f>
-        <v/>
+        <v>116.625</v>
       </c>
       <c r="K125" s="35"/>
       <c r="L125" t="str">
         <f>IF(E124&gt;0,COUNTIF($E$4:E124,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M125" t="str">
+      <c r="M125">
         <f>IF(AND(D124&gt;0,G124="المحفظة"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$G$4:G124,"المحفظة"),"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="N125" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A125)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A125)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A125&lt;&gt;""),IFERROR(MAX($N$4:N124),0)+1,"")</f>
@@ -16577,9 +16610,9 @@
         <f>IF(AND(D124&gt;0,F124="أحد الشركاء"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$F$4:F124,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P125" t="str">
+      <c r="P125">
         <f>IF(OR($A125="",$F125="أحد الشركاء",AND($D125="",$E125="")),"",SUMPRODUCT(($A$4:$A125&lt;&gt;"")*($F$4:$F125&lt;&gt;"أحد الشركاء")*((($D$4:$D125&lt;&gt;"")+($E$4:$E125&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>105</v>
       </c>
       <c r="Q125" t="str">
         <f>IF(OR($A125="",$F125&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A125,"&lt;&gt;",$F$4:F125,"أحد الشركاء"))</f>
@@ -16587,27 +16620,39 @@
       </c>
     </row>
     <row r="126" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="139"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="37"/>
+      <c r="A126" s="139">
+        <v>46594</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>317</v>
+      </c>
       <c r="D126" s="38"/>
-      <c r="E126" s="39"/>
-      <c r="F126" s="136"/>
+      <c r="E126" s="39">
+        <v>7.5</v>
+      </c>
+      <c r="F126" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G126" s="40"/>
-      <c r="H126" s="41"/>
+      <c r="H126" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I126" s="42"/>
-      <c r="J126" s="43" t="str">
+      <c r="J126" s="43">
         <f>IF(AND(D126="",E126="",A126="",B126="",C126=""),"", IFERROR(IF(J125="",D2,J125),D2)+IF(E126="",0,E126)-IF(OR(G126="أبو اسحاق",G126="أبو آدم",G126="أبو اسحاق ",G126="أبو آدم "),0,IF(D126="",0,D126)))</f>
-        <v/>
+        <v>124.125</v>
       </c>
       <c r="K126" s="44"/>
       <c r="L126" t="str">
         <f>IF(E125&gt;0,COUNTIF($E$4:E125,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M126" t="str">
+      <c r="M126">
         <f>IF(AND(D125&gt;0,G125="المحفظة"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$G$4:G125,"المحفظة"),"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="N126" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A126)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A126)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A126&lt;&gt;""),IFERROR(MAX($N$4:N125),0)+1,"")</f>
@@ -16617,9 +16662,9 @@
         <f>IF(AND(D125&gt;0,F125="أحد الشركاء"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$F$4:F125,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P126" t="str">
+      <c r="P126">
         <f>IF(OR($A126="",$F126="أحد الشركاء",AND($D126="",$E126="")),"",SUMPRODUCT(($A$4:$A126&lt;&gt;"")*($F$4:$F126&lt;&gt;"أحد الشركاء")*((($D$4:$D126&lt;&gt;"")+($E$4:$E126&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>106</v>
       </c>
       <c r="Q126" t="str">
         <f>IF(OR($A126="",$F126&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A126,"&lt;&gt;",$F$4:F126,"أحد الشركاء"))</f>
@@ -16641,9 +16686,9 @@
         <v/>
       </c>
       <c r="K127" s="35"/>
-      <c r="L127" t="str">
+      <c r="L127">
         <f>IF(E126&gt;0,COUNTIF($E$4:E126,"&gt;0"),"")</f>
-        <v/>
+        <v>88</v>
       </c>
       <c r="M127" t="str">
         <f>IF(AND(D126&gt;0,G126="المحفظة"),COUNTIFS($D$4:D126,"&gt;"&amp;0,$G$4:G126,"المحفظة"),"")</f>
@@ -19754,11 +19799,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>1576.4749999999999</v>
+        <v>1606.4749999999999</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>700.6</v>
+        <v>708.1</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2243DC22-8DE7-4837-8A10-CAC89C4B8604}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6546A8B5-17A7-4C94-9746-715417BE2FDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="320">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -996,6 +996,12 @@
   </si>
   <si>
     <t>متفرقات</t>
+  </si>
+  <si>
+    <t>يوليو</t>
+  </si>
+  <si>
+    <t>تسوية رصيد فعلي - الكاش الفعلي 16.750</t>
   </si>
 </sst>
 </file>
@@ -2173,14 +2179,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2543,7 +2549,7 @@
       <c r="E2" s="149"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>124.125</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5341,29 +5347,29 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="142" t="str">
+      <c r="A112" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B112" s="122" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B112" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C112" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D112" s="123" t="str">
+        <v>تسوية رصيد فعلي - الكاش الفعلي 16.750</v>
+      </c>
+      <c r="D112" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E112" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E112" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F112" s="125" t="str">
+        <v>107.375</v>
+      </c>
+      <c r="F112" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>16.75</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7796,11 +7802,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>583.97499999999991</v>
+        <v>691.34999999999991</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>124.125</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13116,9 +13122,9 @@
         <f>IF(AND(D57&gt;0,G57="المحفظة"),COUNTIFS($D$4:D57,"&gt;"&amp;0,$G$4:G57,"المحفظة"),"")</f>
         <v>3</v>
       </c>
-      <c r="N58">
+      <c r="N58" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A58)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A58)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A58&lt;&gt;""),IFERROR(MAX($N$4:N57),0)+1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="O58" t="str">
         <f>IF(AND(D57&gt;0,F57="أحد الشركاء"),COUNTIFS($D$4:D57,"&gt;"&amp;0,$F$4:F57,"أحد الشركاء"),"")</f>
@@ -13168,9 +13174,9 @@
         <f>IF(AND(D58&gt;0,G58="المحفظة"),COUNTIFS($D$4:D58,"&gt;"&amp;0,$G$4:G58,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N59">
+      <c r="N59" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A59)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A59)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A59&lt;&gt;""),IFERROR(MAX($N$4:N58),0)+1,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="O59" t="str">
         <f>IF(AND(D58&gt;0,F58="أحد الشركاء"),COUNTIFS($D$4:D58,"&gt;"&amp;0,$F$4:F58,"أحد الشركاء"),"")</f>
@@ -13220,9 +13226,9 @@
         <f>IF(AND(D59&gt;0,G59="المحفظة"),COUNTIFS($D$4:D59,"&gt;"&amp;0,$G$4:G59,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N60">
+      <c r="N60" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A60)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A60)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A60&lt;&gt;""),IFERROR(MAX($N$4:N59),0)+1,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="O60" t="str">
         <f>IF(AND(D59&gt;0,F59="أحد الشركاء"),COUNTIFS($D$4:D59,"&gt;"&amp;0,$F$4:F59,"أحد الشركاء"),"")</f>
@@ -13272,9 +13278,9 @@
         <f>IF(AND(D60&gt;0,G60="المحفظة"),COUNTIFS($D$4:D60,"&gt;"&amp;0,$G$4:G60,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N61">
+      <c r="N61" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A61)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A61)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A61&lt;&gt;""),IFERROR(MAX($N$4:N60),0)+1,"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="O61" t="str">
         <f>IF(AND(D60&gt;0,F60="أحد الشركاء"),COUNTIFS($D$4:D60,"&gt;"&amp;0,$F$4:F60,"أحد الشركاء"),"")</f>
@@ -13324,9 +13330,9 @@
         <f>IF(AND(D61&gt;0,G61="المحفظة"),COUNTIFS($D$4:D61,"&gt;"&amp;0,$G$4:G61,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N62">
+      <c r="N62" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A62)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A62)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A62&lt;&gt;""),IFERROR(MAX($N$4:N61),0)+1,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="O62" t="str">
         <f>IF(AND(D61&gt;0,F61="أحد الشركاء"),COUNTIFS($D$4:D61,"&gt;"&amp;0,$F$4:F61,"أحد الشركاء"),"")</f>
@@ -13376,9 +13382,9 @@
         <f>IF(AND(D62&gt;0,G62="المحفظة"),COUNTIFS($D$4:D62,"&gt;"&amp;0,$G$4:G62,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N63">
+      <c r="N63" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A63)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A63)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A63&lt;&gt;""),IFERROR(MAX($N$4:N62),0)+1,"")</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="O63" t="str">
         <f>IF(AND(D62&gt;0,F62="أحد الشركاء"),COUNTIFS($D$4:D62,"&gt;"&amp;0,$F$4:F62,"أحد الشركاء"),"")</f>
@@ -13428,9 +13434,9 @@
         <f>IF(AND(D63&gt;0,G63="المحفظة"),COUNTIFS($D$4:D63,"&gt;"&amp;0,$G$4:G63,"المحفظة"),"")</f>
         <v>4</v>
       </c>
-      <c r="N64">
+      <c r="N64" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A64)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A64)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A64&lt;&gt;""),IFERROR(MAX($N$4:N63),0)+1,"")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="O64" t="str">
         <f>IF(AND(D63&gt;0,F63="أحد الشركاء"),COUNTIFS($D$4:D63,"&gt;"&amp;0,$F$4:F63,"أحد الشركاء"),"")</f>
@@ -13480,9 +13486,9 @@
         <f>IF(AND(D64&gt;0,G64="المحفظة"),COUNTIFS($D$4:D64,"&gt;"&amp;0,$G$4:G64,"المحفظة"),"")</f>
         <v>5</v>
       </c>
-      <c r="N65">
+      <c r="N65" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A65)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A65)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A65&lt;&gt;""),IFERROR(MAX($N$4:N64),0)+1,"")</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="O65" t="str">
         <f>IF(AND(D64&gt;0,F64="أحد الشركاء"),COUNTIFS($D$4:D64,"&gt;"&amp;0,$F$4:F64,"أحد الشركاء"),"")</f>
@@ -13532,9 +13538,9 @@
         <f>IF(AND(D65&gt;0,G65="المحفظة"),COUNTIFS($D$4:D65,"&gt;"&amp;0,$G$4:G65,"المحفظة"),"")</f>
         <v>6</v>
       </c>
-      <c r="N66">
+      <c r="N66" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A66)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A66)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A66&lt;&gt;""),IFERROR(MAX($N$4:N65),0)+1,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="O66" t="str">
         <f>IF(AND(D65&gt;0,F65="أحد الشركاء"),COUNTIFS($D$4:D65,"&gt;"&amp;0,$F$4:F65,"أحد الشركاء"),"")</f>
@@ -13584,9 +13590,9 @@
         <f>IF(AND(D66&gt;0,G66="المحفظة"),COUNTIFS($D$4:D66,"&gt;"&amp;0,$G$4:G66,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N67">
+      <c r="N67" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A67)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A67)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A67&lt;&gt;""),IFERROR(MAX($N$4:N66),0)+1,"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="O67" t="str">
         <f>IF(AND(D66&gt;0,F66="أحد الشركاء"),COUNTIFS($D$4:D66,"&gt;"&amp;0,$F$4:F66,"أحد الشركاء"),"")</f>
@@ -13636,9 +13642,9 @@
         <f>IF(AND(D67&gt;0,G67="المحفظة"),COUNTIFS($D$4:D67,"&gt;"&amp;0,$G$4:G67,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N68">
+      <c r="N68" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A68)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A68)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A68&lt;&gt;""),IFERROR(MAX($N$4:N67),0)+1,"")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="O68" t="str">
         <f>IF(AND(D67&gt;0,F67="أحد الشركاء"),COUNTIFS($D$4:D67,"&gt;"&amp;0,$F$4:F67,"أحد الشركاء"),"")</f>
@@ -13688,9 +13694,9 @@
         <f>IF(AND(D68&gt;0,G68="المحفظة"),COUNTIFS($D$4:D68,"&gt;"&amp;0,$G$4:G68,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N69">
+      <c r="N69" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A69)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A69)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A69&lt;&gt;""),IFERROR(MAX($N$4:N68),0)+1,"")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="O69" t="str">
         <f>IF(AND(D68&gt;0,F68="أحد الشركاء"),COUNTIFS($D$4:D68,"&gt;"&amp;0,$F$4:F68,"أحد الشركاء"),"")</f>
@@ -13739,9 +13745,9 @@
         <f>IF(AND(D69&gt;0,G69="المحفظة"),COUNTIFS($D$4:D69,"&gt;"&amp;0,$G$4:G69,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N70">
+      <c r="N70" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A70)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A70)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A70&lt;&gt;""),IFERROR(MAX($N$4:N69),0)+1,"")</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="O70" t="str">
         <f>IF(AND(D69&gt;0,F69="أحد الشركاء"),COUNTIFS($D$4:D69,"&gt;"&amp;0,$F$4:F69,"أحد الشركاء"),"")</f>
@@ -13790,9 +13796,9 @@
         <f>IF(AND(D70&gt;0,G70="المحفظة"),COUNTIFS($D$4:D70,"&gt;"&amp;0,$G$4:G70,"المحفظة"),"")</f>
         <v>7</v>
       </c>
-      <c r="N71">
+      <c r="N71" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A71)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A71)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A71&lt;&gt;""),IFERROR(MAX($N$4:N70),0)+1,"")</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="O71" t="str">
         <f>IF(AND(D70&gt;0,F70="أحد الشركاء"),COUNTIFS($D$4:D70,"&gt;"&amp;0,$F$4:F70,"أحد الشركاء"),"")</f>
@@ -13842,9 +13848,9 @@
         <f>IF(AND(D71&gt;0,G71="المحفظة"),COUNTIFS($D$4:D71,"&gt;"&amp;0,$G$4:G71,"المحفظة"),"")</f>
         <v>8</v>
       </c>
-      <c r="N72">
+      <c r="N72" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A72)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A72)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A72&lt;&gt;""),IFERROR(MAX($N$4:N71),0)+1,"")</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="O72" t="str">
         <f>IF(AND(D71&gt;0,F71="أحد الشركاء"),COUNTIFS($D$4:D71,"&gt;"&amp;0,$F$4:F71,"أحد الشركاء"),"")</f>
@@ -13894,9 +13900,9 @@
         <f>IF(AND(D72&gt;0,G72="المحفظة"),COUNTIFS($D$4:D72,"&gt;"&amp;0,$G$4:G72,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N73">
+      <c r="N73" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A73)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A73)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A73&lt;&gt;""),IFERROR(MAX($N$4:N72),0)+1,"")</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="O73" t="str">
         <f>IF(AND(D72&gt;0,F72="أحد الشركاء"),COUNTIFS($D$4:D72,"&gt;"&amp;0,$F$4:F72,"أحد الشركاء"),"")</f>
@@ -13946,9 +13952,9 @@
         <f>IF(AND(D73&gt;0,G73="المحفظة"),COUNTIFS($D$4:D73,"&gt;"&amp;0,$G$4:G73,"المحفظة"),"")</f>
         <v>9</v>
       </c>
-      <c r="N74">
+      <c r="N74" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A74)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A74)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A74&lt;&gt;""),IFERROR(MAX($N$4:N73),0)+1,"")</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="O74" t="str">
         <f>IF(AND(D73&gt;0,F73="أحد الشركاء"),COUNTIFS($D$4:D73,"&gt;"&amp;0,$F$4:F73,"أحد الشركاء"),"")</f>
@@ -13998,9 +14004,9 @@
         <f>IF(AND(D74&gt;0,G74="المحفظة"),COUNTIFS($D$4:D74,"&gt;"&amp;0,$G$4:G74,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N75">
+      <c r="N75" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A75)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A75)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A75&lt;&gt;""),IFERROR(MAX($N$4:N74),0)+1,"")</f>
-        <v>18</v>
+        <v/>
       </c>
       <c r="O75" t="str">
         <f>IF(AND(D74&gt;0,F74="أحد الشركاء"),COUNTIFS($D$4:D74,"&gt;"&amp;0,$F$4:F74,"أحد الشركاء"),"")</f>
@@ -14050,9 +14056,9 @@
         <f>IF(AND(D75&gt;0,G75="المحفظة"),COUNTIFS($D$4:D75,"&gt;"&amp;0,$G$4:G75,"المحفظة"),"")</f>
         <v>10</v>
       </c>
-      <c r="N76">
+      <c r="N76" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A76)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A76)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A76&lt;&gt;""),IFERROR(MAX($N$4:N75),0)+1,"")</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="O76" t="str">
         <f>IF(AND(D75&gt;0,F75="أحد الشركاء"),COUNTIFS($D$4:D75,"&gt;"&amp;0,$F$4:F75,"أحد الشركاء"),"")</f>
@@ -14102,9 +14108,9 @@
         <f>IF(AND(D76&gt;0,G76="المحفظة"),COUNTIFS($D$4:D76,"&gt;"&amp;0,$G$4:G76,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N77">
+      <c r="N77" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A77)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A77)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A77&lt;&gt;""),IFERROR(MAX($N$4:N76),0)+1,"")</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="O77" t="str">
         <f>IF(AND(D76&gt;0,F76="أحد الشركاء"),COUNTIFS($D$4:D76,"&gt;"&amp;0,$F$4:F76,"أحد الشركاء"),"")</f>
@@ -14154,9 +14160,9 @@
         <f>IF(AND(D77&gt;0,G77="المحفظة"),COUNTIFS($D$4:D77,"&gt;"&amp;0,$G$4:G77,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N78">
+      <c r="N78" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A78)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A78)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A78&lt;&gt;""),IFERROR(MAX($N$4:N77),0)+1,"")</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="O78" t="str">
         <f>IF(AND(D77&gt;0,F77="أحد الشركاء"),COUNTIFS($D$4:D77,"&gt;"&amp;0,$F$4:F77,"أحد الشركاء"),"")</f>
@@ -14206,9 +14212,9 @@
         <f>IF(AND(D78&gt;0,G78="المحفظة"),COUNTIFS($D$4:D78,"&gt;"&amp;0,$G$4:G78,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N79">
+      <c r="N79" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A79)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A79)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A79&lt;&gt;""),IFERROR(MAX($N$4:N78),0)+1,"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="O79">
         <f>IF(AND(D78&gt;0,F78="أحد الشركاء"),COUNTIFS($D$4:D78,"&gt;"&amp;0,$F$4:F78,"أحد الشركاء"),"")</f>
@@ -14258,9 +14264,9 @@
         <f>IF(AND(D79&gt;0,G79="المحفظة"),COUNTIFS($D$4:D79,"&gt;"&amp;0,$G$4:G79,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N80">
+      <c r="N80" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A80)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A80)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A80&lt;&gt;""),IFERROR(MAX($N$4:N79),0)+1,"")</f>
-        <v>23</v>
+        <v/>
       </c>
       <c r="O80" t="str">
         <f>IF(AND(D79&gt;0,F79="أحد الشركاء"),COUNTIFS($D$4:D79,"&gt;"&amp;0,$F$4:F79,"أحد الشركاء"),"")</f>
@@ -14310,9 +14316,9 @@
         <f>IF(AND(D80&gt;0,G80="المحفظة"),COUNTIFS($D$4:D80,"&gt;"&amp;0,$G$4:G80,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N81">
+      <c r="N81" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A81)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A81)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A81&lt;&gt;""),IFERROR(MAX($N$4:N80),0)+1,"")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="O81" t="str">
         <f>IF(AND(D80&gt;0,F80="أحد الشركاء"),COUNTIFS($D$4:D80,"&gt;"&amp;0,$F$4:F80,"أحد الشركاء"),"")</f>
@@ -14362,9 +14368,9 @@
         <f>IF(AND(D81&gt;0,G81="المحفظة"),COUNTIFS($D$4:D81,"&gt;"&amp;0,$G$4:G81,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N82">
+      <c r="N82" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A82)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A82)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A82&lt;&gt;""),IFERROR(MAX($N$4:N81),0)+1,"")</f>
-        <v>25</v>
+        <v/>
       </c>
       <c r="O82" t="str">
         <f>IF(AND(D81&gt;0,F81="أحد الشركاء"),COUNTIFS($D$4:D81,"&gt;"&amp;0,$F$4:F81,"أحد الشركاء"),"")</f>
@@ -14414,9 +14420,9 @@
         <f>IF(AND(D82&gt;0,G82="المحفظة"),COUNTIFS($D$4:D82,"&gt;"&amp;0,$G$4:G82,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N83">
+      <c r="N83" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A83)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A83)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A83&lt;&gt;""),IFERROR(MAX($N$4:N82),0)+1,"")</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="O83" t="str">
         <f>IF(AND(D82&gt;0,F82="أحد الشركاء"),COUNTIFS($D$4:D82,"&gt;"&amp;0,$F$4:F82,"أحد الشركاء"),"")</f>
@@ -14466,9 +14472,9 @@
         <f>IF(AND(D83&gt;0,G83="المحفظة"),COUNTIFS($D$4:D83,"&gt;"&amp;0,$G$4:G83,"المحفظة"),"")</f>
         <v>11</v>
       </c>
-      <c r="N84">
+      <c r="N84" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A84)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A84)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A84&lt;&gt;""),IFERROR(MAX($N$4:N83),0)+1,"")</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="O84" t="str">
         <f>IF(AND(D83&gt;0,F83="أحد الشركاء"),COUNTIFS($D$4:D83,"&gt;"&amp;0,$F$4:F83,"أحد الشركاء"),"")</f>
@@ -14518,9 +14524,9 @@
         <f>IF(AND(D84&gt;0,G84="المحفظة"),COUNTIFS($D$4:D84,"&gt;"&amp;0,$G$4:G84,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N85">
+      <c r="N85" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A85)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A85)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A85&lt;&gt;""),IFERROR(MAX($N$4:N84),0)+1,"")</f>
-        <v>28</v>
+        <v/>
       </c>
       <c r="O85" t="str">
         <f>IF(AND(D84&gt;0,F84="أحد الشركاء"),COUNTIFS($D$4:D84,"&gt;"&amp;0,$F$4:F84,"أحد الشركاء"),"")</f>
@@ -14570,9 +14576,9 @@
         <f>IF(AND(D85&gt;0,G85="المحفظة"),COUNTIFS($D$4:D85,"&gt;"&amp;0,$G$4:G85,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N86">
+      <c r="N86" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A86)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A86)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A86&lt;&gt;""),IFERROR(MAX($N$4:N85),0)+1,"")</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="O86" t="str">
         <f>IF(AND(D85&gt;0,F85="أحد الشركاء"),COUNTIFS($D$4:D85,"&gt;"&amp;0,$F$4:F85,"أحد الشركاء"),"")</f>
@@ -14622,9 +14628,9 @@
         <f>IF(AND(D86&gt;0,G86="المحفظة"),COUNTIFS($D$4:D86,"&gt;"&amp;0,$G$4:G86,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N87">
+      <c r="N87" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A87)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A87)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A87&lt;&gt;""),IFERROR(MAX($N$4:N86),0)+1,"")</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="O87" t="str">
         <f>IF(AND(D86&gt;0,F86="أحد الشركاء"),COUNTIFS($D$4:D86,"&gt;"&amp;0,$F$4:F86,"أحد الشركاء"),"")</f>
@@ -14674,9 +14680,9 @@
         <f>IF(AND(D87&gt;0,G87="المحفظة"),COUNTIFS($D$4:D87,"&gt;"&amp;0,$G$4:G87,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N88">
+      <c r="N88" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A88)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A88)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A88&lt;&gt;""),IFERROR(MAX($N$4:N87),0)+1,"")</f>
-        <v>31</v>
+        <v/>
       </c>
       <c r="O88" t="str">
         <f>IF(AND(D87&gt;0,F87="أحد الشركاء"),COUNTIFS($D$4:D87,"&gt;"&amp;0,$F$4:F87,"أحد الشركاء"),"")</f>
@@ -14726,9 +14732,9 @@
         <f>IF(AND(D88&gt;0,G88="المحفظة"),COUNTIFS($D$4:D88,"&gt;"&amp;0,$G$4:G88,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N89">
+      <c r="N89" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A89)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A89)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A89&lt;&gt;""),IFERROR(MAX($N$4:N88),0)+1,"")</f>
-        <v>32</v>
+        <v/>
       </c>
       <c r="O89" t="str">
         <f>IF(AND(D88&gt;0,F88="أحد الشركاء"),COUNTIFS($D$4:D88,"&gt;"&amp;0,$F$4:F88,"أحد الشركاء"),"")</f>
@@ -14778,9 +14784,9 @@
         <f>IF(AND(D89&gt;0,G89="المحفظة"),COUNTIFS($D$4:D89,"&gt;"&amp;0,$G$4:G89,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N90">
+      <c r="N90" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A90)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A90)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A90&lt;&gt;""),IFERROR(MAX($N$4:N89),0)+1,"")</f>
-        <v>33</v>
+        <v/>
       </c>
       <c r="O90" t="str">
         <f>IF(AND(D89&gt;0,F89="أحد الشركاء"),COUNTIFS($D$4:D89,"&gt;"&amp;0,$F$4:F89,"أحد الشركاء"),"")</f>
@@ -14830,9 +14836,9 @@
         <f>IF(AND(D90&gt;0,G90="المحفظة"),COUNTIFS($D$4:D90,"&gt;"&amp;0,$G$4:G90,"المحفظة"),"")</f>
         <v>12</v>
       </c>
-      <c r="N91">
+      <c r="N91" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A91)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A91)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A91&lt;&gt;""),IFERROR(MAX($N$4:N90),0)+1,"")</f>
-        <v>34</v>
+        <v/>
       </c>
       <c r="O91" t="str">
         <f>IF(AND(D90&gt;0,F90="أحد الشركاء"),COUNTIFS($D$4:D90,"&gt;"&amp;0,$F$4:F90,"أحد الشركاء"),"")</f>
@@ -14882,9 +14888,9 @@
         <f>IF(AND(D91&gt;0,G91="المحفظة"),COUNTIFS($D$4:D91,"&gt;"&amp;0,$G$4:G91,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N92">
+      <c r="N92" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A92)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A92)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A92&lt;&gt;""),IFERROR(MAX($N$4:N91),0)+1,"")</f>
-        <v>35</v>
+        <v/>
       </c>
       <c r="O92" t="str">
         <f>IF(AND(D91&gt;0,F91="أحد الشركاء"),COUNTIFS($D$4:D91,"&gt;"&amp;0,$F$4:F91,"أحد الشركاء"),"")</f>
@@ -14934,9 +14940,9 @@
         <f>IF(AND(D92&gt;0,G92="المحفظة"),COUNTIFS($D$4:D92,"&gt;"&amp;0,$G$4:G92,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N93">
+      <c r="N93" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A93)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A93)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A93&lt;&gt;""),IFERROR(MAX($N$4:N92),0)+1,"")</f>
-        <v>36</v>
+        <v/>
       </c>
       <c r="O93" t="str">
         <f>IF(AND(D92&gt;0,F92="أحد الشركاء"),COUNTIFS($D$4:D92,"&gt;"&amp;0,$F$4:F92,"أحد الشركاء"),"")</f>
@@ -14986,9 +14992,9 @@
         <f>IF(AND(D93&gt;0,G93="المحفظة"),COUNTIFS($D$4:D93,"&gt;"&amp;0,$G$4:G93,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N94">
+      <c r="N94" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A94)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A94)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A94&lt;&gt;""),IFERROR(MAX($N$4:N93),0)+1,"")</f>
-        <v>37</v>
+        <v/>
       </c>
       <c r="O94" t="str">
         <f>IF(AND(D93&gt;0,F93="أحد الشركاء"),COUNTIFS($D$4:D93,"&gt;"&amp;0,$F$4:F93,"أحد الشركاء"),"")</f>
@@ -15038,9 +15044,9 @@
         <f>IF(AND(D94&gt;0,G94="المحفظة"),COUNTIFS($D$4:D94,"&gt;"&amp;0,$G$4:G94,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N95">
+      <c r="N95" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A95)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A95)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A95&lt;&gt;""),IFERROR(MAX($N$4:N94),0)+1,"")</f>
-        <v>38</v>
+        <v/>
       </c>
       <c r="O95" t="str">
         <f>IF(AND(D94&gt;0,F94="أحد الشركاء"),COUNTIFS($D$4:D94,"&gt;"&amp;0,$F$4:F94,"أحد الشركاء"),"")</f>
@@ -15090,9 +15096,9 @@
         <f>IF(AND(D95&gt;0,G95="المحفظة"),COUNTIFS($D$4:D95,"&gt;"&amp;0,$G$4:G95,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N96">
+      <c r="N96" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A96)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A96)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A96&lt;&gt;""),IFERROR(MAX($N$4:N95),0)+1,"")</f>
-        <v>39</v>
+        <v/>
       </c>
       <c r="O96" t="str">
         <f>IF(AND(D95&gt;0,F95="أحد الشركاء"),COUNTIFS($D$4:D95,"&gt;"&amp;0,$F$4:F95,"أحد الشركاء"),"")</f>
@@ -15142,9 +15148,9 @@
         <f>IF(AND(D96&gt;0,G96="المحفظة"),COUNTIFS($D$4:D96,"&gt;"&amp;0,$G$4:G96,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N97">
+      <c r="N97" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A97)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A97)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A97&lt;&gt;""),IFERROR(MAX($N$4:N96),0)+1,"")</f>
-        <v>40</v>
+        <v/>
       </c>
       <c r="O97" t="str">
         <f>IF(AND(D96&gt;0,F96="أحد الشركاء"),COUNTIFS($D$4:D96,"&gt;"&amp;0,$F$4:F96,"أحد الشركاء"),"")</f>
@@ -15194,9 +15200,9 @@
         <f>IF(AND(D97&gt;0,G97="المحفظة"),COUNTIFS($D$4:D97,"&gt;"&amp;0,$G$4:G97,"المحفظة"),"")</f>
         <v>13</v>
       </c>
-      <c r="N98">
+      <c r="N98" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A98)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A98)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A98&lt;&gt;""),IFERROR(MAX($N$4:N97),0)+1,"")</f>
-        <v>41</v>
+        <v/>
       </c>
       <c r="O98" t="str">
         <f>IF(AND(D97&gt;0,F97="أحد الشركاء"),COUNTIFS($D$4:D97,"&gt;"&amp;0,$F$4:F97,"أحد الشركاء"),"")</f>
@@ -15246,9 +15252,9 @@
         <f>IF(AND(D98&gt;0,G98="المحفظة"),COUNTIFS($D$4:D98,"&gt;"&amp;0,$G$4:G98,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N99">
+      <c r="N99" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A99)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A99)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A99&lt;&gt;""),IFERROR(MAX($N$4:N98),0)+1,"")</f>
-        <v>42</v>
+        <v/>
       </c>
       <c r="O99">
         <f>IF(AND(D98&gt;0,F98="أحد الشركاء"),COUNTIFS($D$4:D98,"&gt;"&amp;0,$F$4:F98,"أحد الشركاء"),"")</f>
@@ -15298,9 +15304,9 @@
         <f>IF(AND(D99&gt;0,G99="المحفظة"),COUNTIFS($D$4:D99,"&gt;"&amp;0,$G$4:G99,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N100">
+      <c r="N100" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A100)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A100)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A100&lt;&gt;""),IFERROR(MAX($N$4:N99),0)+1,"")</f>
-        <v>43</v>
+        <v/>
       </c>
       <c r="O100">
         <f>IF(AND(D99&gt;0,F99="أحد الشركاء"),COUNTIFS($D$4:D99,"&gt;"&amp;0,$F$4:F99,"أحد الشركاء"),"")</f>
@@ -15350,9 +15356,9 @@
         <f>IF(AND(D100&gt;0,G100="المحفظة"),COUNTIFS($D$4:D100,"&gt;"&amp;0,$G$4:G100,"المحفظة"),"")</f>
         <v>14</v>
       </c>
-      <c r="N101" t="str">
+      <c r="N101">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A101)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A101)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A101&lt;&gt;""),IFERROR(MAX($N$4:N100),0)+1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O101" t="str">
         <f>IF(AND(D100&gt;0,F100="أحد الشركاء"),COUNTIFS($D$4:D100,"&gt;"&amp;0,$F$4:F100,"أحد الشركاء"),"")</f>
@@ -15402,9 +15408,9 @@
         <f>IF(AND(D101&gt;0,G101="المحفظة"),COUNTIFS($D$4:D101,"&gt;"&amp;0,$G$4:G101,"المحفظة"),"")</f>
         <v>15</v>
       </c>
-      <c r="N102" t="str">
+      <c r="N102">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A102)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A102)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A102&lt;&gt;""),IFERROR(MAX($N$4:N101),0)+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O102" t="str">
         <f>IF(AND(D101&gt;0,F101="أحد الشركاء"),COUNTIFS($D$4:D101,"&gt;"&amp;0,$F$4:F101,"أحد الشركاء"),"")</f>
@@ -15454,9 +15460,9 @@
         <f>IF(AND(D102&gt;0,G102="المحفظة"),COUNTIFS($D$4:D102,"&gt;"&amp;0,$G$4:G102,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N103" t="str">
+      <c r="N103">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A103)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A103)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A103&lt;&gt;""),IFERROR(MAX($N$4:N102),0)+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="O103" t="str">
         <f>IF(AND(D102&gt;0,F102="أحد الشركاء"),COUNTIFS($D$4:D102,"&gt;"&amp;0,$F$4:F102,"أحد الشركاء"),"")</f>
@@ -15506,9 +15512,9 @@
         <f>IF(AND(D103&gt;0,G103="المحفظة"),COUNTIFS($D$4:D103,"&gt;"&amp;0,$G$4:G103,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N104" t="str">
+      <c r="N104">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A104)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A104)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A104&lt;&gt;""),IFERROR(MAX($N$4:N103),0)+1,"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="O104" t="str">
         <f>IF(AND(D103&gt;0,F103="أحد الشركاء"),COUNTIFS($D$4:D103,"&gt;"&amp;0,$F$4:F103,"أحد الشركاء"),"")</f>
@@ -15558,9 +15564,9 @@
         <f>IF(AND(D104&gt;0,G104="المحفظة"),COUNTIFS($D$4:D104,"&gt;"&amp;0,$G$4:G104,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N105" t="str">
+      <c r="N105">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A105)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A105)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A105&lt;&gt;""),IFERROR(MAX($N$4:N104),0)+1,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O105" t="str">
         <f>IF(AND(D104&gt;0,F104="أحد الشركاء"),COUNTIFS($D$4:D104,"&gt;"&amp;0,$F$4:F104,"أحد الشركاء"),"")</f>
@@ -15610,9 +15616,9 @@
         <f>IF(AND(D105&gt;0,G105="المحفظة"),COUNTIFS($D$4:D105,"&gt;"&amp;0,$G$4:G105,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N106" t="str">
+      <c r="N106">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A106)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A106)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A106&lt;&gt;""),IFERROR(MAX($N$4:N105),0)+1,"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="O106" t="str">
         <f>IF(AND(D105&gt;0,F105="أحد الشركاء"),COUNTIFS($D$4:D105,"&gt;"&amp;0,$F$4:F105,"أحد الشركاء"),"")</f>
@@ -15662,9 +15668,9 @@
         <f>IF(AND(D106&gt;0,G106="المحفظة"),COUNTIFS($D$4:D106,"&gt;"&amp;0,$G$4:G106,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N107" t="str">
+      <c r="N107">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A107)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A107)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A107&lt;&gt;""),IFERROR(MAX($N$4:N106),0)+1,"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O107" t="str">
         <f>IF(AND(D106&gt;0,F106="أحد الشركاء"),COUNTIFS($D$4:D106,"&gt;"&amp;0,$F$4:F106,"أحد الشركاء"),"")</f>
@@ -15714,9 +15720,9 @@
         <f>IF(AND(D107&gt;0,G107="المحفظة"),COUNTIFS($D$4:D107,"&gt;"&amp;0,$G$4:G107,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N108" t="str">
+      <c r="N108">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A108)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A108)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A108&lt;&gt;""),IFERROR(MAX($N$4:N107),0)+1,"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="O108" t="str">
         <f>IF(AND(D107&gt;0,F107="أحد الشركاء"),COUNTIFS($D$4:D107,"&gt;"&amp;0,$F$4:F107,"أحد الشركاء"),"")</f>
@@ -15766,9 +15772,9 @@
         <f>IF(AND(D108&gt;0,G108="المحفظة"),COUNTIFS($D$4:D108,"&gt;"&amp;0,$G$4:G108,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N109" t="str">
+      <c r="N109">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A109)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A109)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A109&lt;&gt;""),IFERROR(MAX($N$4:N108),0)+1,"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="O109" t="str">
         <f>IF(AND(D108&gt;0,F108="أحد الشركاء"),COUNTIFS($D$4:D108,"&gt;"&amp;0,$F$4:F108,"أحد الشركاء"),"")</f>
@@ -15818,9 +15824,9 @@
         <f>IF(AND(D109&gt;0,G109="المحفظة"),COUNTIFS($D$4:D109,"&gt;"&amp;0,$G$4:G109,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N110" t="str">
+      <c r="N110">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A110)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A110)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A110&lt;&gt;""),IFERROR(MAX($N$4:N109),0)+1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O110" t="str">
         <f>IF(AND(D109&gt;0,F109="أحد الشركاء"),COUNTIFS($D$4:D109,"&gt;"&amp;0,$F$4:F109,"أحد الشركاء"),"")</f>
@@ -15870,9 +15876,9 @@
         <f>IF(AND(D110&gt;0,G110="المحفظة"),COUNTIFS($D$4:D110,"&gt;"&amp;0,$G$4:G110,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N111" t="str">
+      <c r="N111">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A111)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A111)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A111&lt;&gt;""),IFERROR(MAX($N$4:N110),0)+1,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="O111" t="str">
         <f>IF(AND(D110&gt;0,F110="أحد الشركاء"),COUNTIFS($D$4:D110,"&gt;"&amp;0,$F$4:F110,"أحد الشركاء"),"")</f>
@@ -15922,9 +15928,9 @@
         <f>IF(AND(D111&gt;0,G111="المحفظة"),COUNTIFS($D$4:D111,"&gt;"&amp;0,$G$4:G111,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N112" t="str">
+      <c r="N112">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A112)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A112)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A112&lt;&gt;""),IFERROR(MAX($N$4:N111),0)+1,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="O112" t="str">
         <f>IF(AND(D111&gt;0,F111="أحد الشركاء"),COUNTIFS($D$4:D111,"&gt;"&amp;0,$F$4:F111,"أحد الشركاء"),"")</f>
@@ -15974,9 +15980,9 @@
         <f>IF(AND(D112&gt;0,G112="المحفظة"),COUNTIFS($D$4:D112,"&gt;"&amp;0,$G$4:G112,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N113" t="str">
+      <c r="N113">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A113)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A113)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A113&lt;&gt;""),IFERROR(MAX($N$4:N112),0)+1,"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="O113" t="str">
         <f>IF(AND(D112&gt;0,F112="أحد الشركاء"),COUNTIFS($D$4:D112,"&gt;"&amp;0,$F$4:F112,"أحد الشركاء"),"")</f>
@@ -16026,9 +16032,9 @@
         <f>IF(AND(D113&gt;0,G113="المحفظة"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$G$4:G113,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N114" t="str">
+      <c r="N114">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A114)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A114)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A114&lt;&gt;""),IFERROR(MAX($N$4:N113),0)+1,"")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="O114" t="str">
         <f>IF(AND(D113&gt;0,F113="أحد الشركاء"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$F$4:F113,"أحد الشركاء"),"")</f>
@@ -16078,9 +16084,9 @@
         <f>IF(AND(D114&gt;0,G114="المحفظة"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$G$4:G114,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N115" t="str">
+      <c r="N115">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A115)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A115)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A115&lt;&gt;""),IFERROR(MAX($N$4:N114),0)+1,"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="O115" t="str">
         <f>IF(AND(D114&gt;0,F114="أحد الشركاء"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$F$4:F114,"أحد الشركاء"),"")</f>
@@ -16132,9 +16138,9 @@
         <f>IF(AND(D115&gt;0,G115="المحفظة"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$G$4:G115,"المحفظة"),"")</f>
         <v>16</v>
       </c>
-      <c r="N116" t="str">
+      <c r="N116">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A116)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A116)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A116&lt;&gt;""),IFERROR(MAX($N$4:N115),0)+1,"")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="O116" t="str">
         <f>IF(AND(D115&gt;0,F115="أحد الشركاء"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$F$4:F115,"أحد الشركاء"),"")</f>
@@ -16186,9 +16192,9 @@
         <f>IF(AND(D116&gt;0,G116="المحفظة"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$G$4:G116,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N117" t="str">
+      <c r="N117">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A117)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A117)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A117&lt;&gt;""),IFERROR(MAX($N$4:N116),0)+1,"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="O117" t="str">
         <f>IF(AND(D116&gt;0,F116="أحد الشركاء"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$F$4:F116,"أحد الشركاء"),"")</f>
@@ -16238,9 +16244,9 @@
         <f>IF(AND(D117&gt;0,G117="المحفظة"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$G$4:G117,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N118" t="str">
+      <c r="N118">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A118)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A118)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A118&lt;&gt;""),IFERROR(MAX($N$4:N117),0)+1,"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="O118" t="str">
         <f>IF(AND(D117&gt;0,F117="أحد الشركاء"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$F$4:F117,"أحد الشركاء"),"")</f>
@@ -16290,9 +16296,9 @@
         <f>IF(AND(D118&gt;0,G118="المحفظة"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$G$4:G118,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N119" t="str">
+      <c r="N119">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A119)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A119)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A119&lt;&gt;""),IFERROR(MAX($N$4:N118),0)+1,"")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="O119" t="str">
         <f>IF(AND(D118&gt;0,F118="أحد الشركاء"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$F$4:F118,"أحد الشركاء"),"")</f>
@@ -16342,9 +16348,9 @@
         <f>IF(AND(D119&gt;0,G119="المحفظة"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$G$4:G119,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N120" t="str">
+      <c r="N120">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A120)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A120)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A120&lt;&gt;""),IFERROR(MAX($N$4:N119),0)+1,"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="O120" t="str">
         <f>IF(AND(D119&gt;0,F119="أحد الشركاء"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$F$4:F119,"أحد الشركاء"),"")</f>
@@ -16394,9 +16400,9 @@
         <f>IF(AND(D120&gt;0,G120="المحفظة"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$G$4:G120,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N121" t="str">
+      <c r="N121">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A121)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A121)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A121&lt;&gt;""),IFERROR(MAX($N$4:N120),0)+1,"")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="O121" t="str">
         <f>IF(AND(D120&gt;0,F120="أحد الشركاء"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$F$4:F120,"أحد الشركاء"),"")</f>
@@ -16446,9 +16452,9 @@
         <f>IF(AND(D121&gt;0,G121="المحفظة"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$G$4:G121,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N122" t="str">
+      <c r="N122">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A122)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A122)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A122&lt;&gt;""),IFERROR(MAX($N$4:N121),0)+1,"")</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="O122" t="str">
         <f>IF(AND(D121&gt;0,F121="أحد الشركاء"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$F$4:F121,"أحد الشركاء"),"")</f>
@@ -16498,9 +16504,9 @@
         <f>IF(AND(D122&gt;0,G122="المحفظة"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$G$4:G122,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N123" t="str">
+      <c r="N123">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A123)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A123)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A123&lt;&gt;""),IFERROR(MAX($N$4:N122),0)+1,"")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="O123" t="str">
         <f>IF(AND(D122&gt;0,F122="أحد الشركاء"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$F$4:F122,"أحد الشركاء"),"")</f>
@@ -16550,9 +16556,9 @@
         <f>IF(AND(D123&gt;0,G123="المحفظة"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$G$4:G123,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N124" t="str">
+      <c r="N124">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A124)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A124)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A124&lt;&gt;""),IFERROR(MAX($N$4:N123),0)+1,"")</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="O124" t="str">
         <f>IF(AND(D123&gt;0,F123="أحد الشركاء"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$F$4:F123,"أحد الشركاء"),"")</f>
@@ -16602,9 +16608,9 @@
         <f>IF(AND(D124&gt;0,G124="المحفظة"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$G$4:G124,"المحفظة"),"")</f>
         <v>17</v>
       </c>
-      <c r="N125" t="str">
+      <c r="N125">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A125)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A125)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A125&lt;&gt;""),IFERROR(MAX($N$4:N124),0)+1,"")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="O125" t="str">
         <f>IF(AND(D124&gt;0,F124="أحد الشركاء"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$F$4:F124,"أحد الشركاء"),"")</f>
@@ -16654,9 +16660,9 @@
         <f>IF(AND(D125&gt;0,G125="المحفظة"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$G$4:G125,"المحفظة"),"")</f>
         <v>18</v>
       </c>
-      <c r="N126" t="str">
+      <c r="N126">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A126)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A126)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A126&lt;&gt;""),IFERROR(MAX($N$4:N125),0)+1,"")</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="O126" t="str">
         <f>IF(AND(D125&gt;0,F125="أحد الشركاء"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$F$4:F125,"أحد الشركاء"),"")</f>
@@ -16672,18 +16678,30 @@
       </c>
     </row>
     <row r="127" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="25"/>
+      <c r="A127" s="25">
+        <v>46229</v>
+      </c>
       <c r="B127" s="26"/>
-      <c r="C127" s="27"/>
-      <c r="D127" s="28"/>
+      <c r="C127" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="D127" s="28">
+        <v>107.375</v>
+      </c>
       <c r="E127" s="29"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="31"/>
-      <c r="H127" s="32"/>
+      <c r="F127" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G127" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I127" s="33"/>
-      <c r="J127" s="34" t="str">
+      <c r="J127" s="34">
         <f>IF(AND(D127="",E127="",A127="",B127="",C127=""),"", IFERROR(IF(J126="",D2,J126),D2)+IF(E127="",0,E127)-IF(OR(G127="أبو اسحاق",G127="أبو آدم",G127="أبو اسحاق ",G127="أبو آدم "),0,IF(D127="",0,D127)))</f>
-        <v/>
+        <v>16.75</v>
       </c>
       <c r="K127" s="35"/>
       <c r="L127">
@@ -16694,17 +16712,17 @@
         <f>IF(AND(D126&gt;0,G126="المحفظة"),COUNTIFS($D$4:D126,"&gt;"&amp;0,$G$4:G126,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N127" t="str">
+      <c r="N127">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A127)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A127)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A127&lt;&gt;""),IFERROR(MAX($N$4:N126),0)+1,"")</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="O127" t="str">
         <f>IF(AND(D126&gt;0,F126="أحد الشركاء"),COUNTIFS($D$4:D126,"&gt;"&amp;0,$F$4:F126,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P127" t="str">
+      <c r="P127">
         <f>IF(OR($A127="",$F127="أحد الشركاء",AND($D127="",$E127="")),"",SUMPRODUCT(($A$4:$A127&lt;&gt;"")*($F$4:$F127&lt;&gt;"أحد الشركاء")*((($D$4:$D127&lt;&gt;"")+($E$4:$E127&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="Q127" t="str">
         <f>IF(OR($A127="",$F127&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A127,"&lt;&gt;",$F$4:F127,"أحد الشركاء"))</f>
@@ -16730,9 +16748,9 @@
         <f>IF(E127&gt;0,COUNTIF($E$4:E127,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M128" t="str">
+      <c r="M128">
         <f>IF(AND(D127&gt;0,G127="المحفظة"),COUNTIFS($D$4:D127,"&gt;"&amp;0,$G$4:G127,"المحفظة"),"")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="N128" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A128)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A128)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A128&lt;&gt;""),IFERROR(MAX($N$4:N127),0)+1,"")</f>
@@ -19799,7 +19817,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>1606.4749999999999</v>
+        <v>1713.85</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -20216,7 +20234,7 @@
       <c r="A2" s="165"/>
       <c r="B2" s="155"/>
       <c r="C2" s="56" t="s">
-        <v>256</v>
+        <v>318</v>
       </c>
       <c r="D2" s="165">
         <v>2026</v>
@@ -20282,31 +20300,31 @@
     <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46175</v>
-      </c>
-      <c r="B5" s="59" t="str">
+        <v>46207</v>
+      </c>
+      <c r="B5" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-53</v>
+        <v>0</v>
       </c>
       <c r="C5" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 24 الحبه .750</v>
+        <v>احواض عدد 1000 مقاس 14 سم</v>
       </c>
       <c r="D5" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E5" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20318,7 +20336,7 @@
       </c>
       <c r="J5" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>364.85</v>
+        <v>5.0500000000000114</v>
       </c>
       <c r="K5" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20328,15 +20346,15 @@
     <row r="6" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46175</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-54</v>
+        <v>Inv-82</v>
       </c>
       <c r="C6" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا خضراء عدد 1 الحبه 2</v>
+        <v>دارسينا عدد 1 بقيمه 2.500</v>
       </c>
       <c r="D6" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20344,11 +20362,11 @@
       </c>
       <c r="E6" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F6" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G6" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20364,7 +20382,7 @@
       </c>
       <c r="J6" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>366.85</v>
+        <v>7.5500000000000114</v>
       </c>
       <c r="K6" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20374,15 +20392,15 @@
     <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46175</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-55</v>
+        <v>Inv-83</v>
       </c>
       <c r="C7" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبيا عدد 2 الحبه .750</v>
+        <v>ودليه عدد13 الحبه 1</v>
       </c>
       <c r="D7" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20390,7 +20408,7 @@
       </c>
       <c r="E7" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="F7" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20410,7 +20428,7 @@
       </c>
       <c r="J7" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>368.35</v>
+        <v>20.550000000000011</v>
       </c>
       <c r="K7" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20420,15 +20438,15 @@
     <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46175</v>
+        <v>46207</v>
       </c>
       <c r="B8" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-56</v>
+        <v>Inv-84</v>
       </c>
       <c r="C8" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا سوداء عدد 3 الحبه 1</v>
+        <v>معلقات عدد 4 الحبه 2</v>
       </c>
       <c r="D8" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20436,7 +20454,7 @@
       </c>
       <c r="E8" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20456,7 +20474,7 @@
       </c>
       <c r="J8" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>371.35</v>
+        <v>28.550000000000011</v>
       </c>
       <c r="K8" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20466,15 +20484,15 @@
     <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46177</v>
+        <v>46211</v>
       </c>
       <c r="B9" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>inv-57</v>
+        <v>Inv-85</v>
       </c>
       <c r="C9" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فوزير عدد1 قيمه 1</v>
+        <v>عطريات عدد8 الحبه 1</v>
       </c>
       <c r="D9" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20482,11 +20500,11 @@
       </c>
       <c r="E9" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F9" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G9" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20502,7 +20520,7 @@
       </c>
       <c r="J9" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>372.35</v>
+        <v>36.550000000000011</v>
       </c>
       <c r="K9" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20512,31 +20530,31 @@
     <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46177</v>
-      </c>
-      <c r="B10" s="61">
+        <v>46211</v>
+      </c>
+      <c r="B10" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-86</v>
       </c>
       <c r="C10" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>سماد</v>
+        <v>دارسينا سوداء عدد 12 الحبه 2</v>
       </c>
       <c r="D10" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G10" s="61" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G10" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H10" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20548,7 +20566,7 @@
       </c>
       <c r="J10" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>362.35</v>
+        <v>60.550000000000011</v>
       </c>
       <c r="K10" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20558,31 +20576,31 @@
     <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46177</v>
-      </c>
-      <c r="B11" s="59">
+        <v>46211</v>
+      </c>
+      <c r="B11" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-87</v>
       </c>
       <c r="C11" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تاير لعربة الرش</v>
+        <v>عطريات عدد 8 الحبه 1</v>
       </c>
       <c r="D11" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="E11" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G11" s="59" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G11" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H11" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20594,7 +20612,7 @@
       </c>
       <c r="J11" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>359.1</v>
+        <v>68.550000000000011</v>
       </c>
       <c r="K11" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20604,31 +20622,31 @@
     <row r="12" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46177</v>
-      </c>
-      <c r="B12" s="61">
+        <v>46212</v>
+      </c>
+      <c r="B12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-88</v>
       </c>
       <c r="C12" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>حفاره خلط السماد</v>
+        <v>دارسنا عدد1 الحبه 5</v>
       </c>
       <c r="D12" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E12" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G12" s="61" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G12" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20640,7 +20658,7 @@
       </c>
       <c r="J12" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>347.1</v>
+        <v>73.550000000000011</v>
       </c>
       <c r="K12" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20650,15 +20668,15 @@
     <row r="13" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46179</v>
+        <v>46212</v>
       </c>
       <c r="B13" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-58</v>
+        <v>Inv-89</v>
       </c>
       <c r="C13" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد3 بقيمه 1 للحبه</v>
+        <v>فل عدد1 الحبه .750</v>
       </c>
       <c r="D13" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20666,11 +20684,11 @@
       </c>
       <c r="E13" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G13" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20686,7 +20704,7 @@
       </c>
       <c r="J13" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>350.1</v>
+        <v>74.300000000000011</v>
       </c>
       <c r="K13" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20696,15 +20714,15 @@
     <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46179</v>
+        <v>46212</v>
       </c>
       <c r="B14" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-59</v>
+        <v>Inv-90</v>
       </c>
       <c r="C14" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه عدد 1 بقيمه 1</v>
+        <v>دارسينا عدد 1 الحبه 1.500</v>
       </c>
       <c r="D14" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20712,11 +20730,11 @@
       </c>
       <c r="E14" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G14" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20732,7 +20750,7 @@
       </c>
       <c r="J14" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>351.1</v>
+        <v>75.800000000000011</v>
       </c>
       <c r="K14" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20742,15 +20760,15 @@
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46179</v>
+        <v>46212</v>
       </c>
       <c r="B15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-60</v>
+        <v>Inv-91</v>
       </c>
       <c r="C15" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا حمراء عدد 1 بقيمه 3</v>
+        <v>افبوديا عدد الحبه 0.750</v>
       </c>
       <c r="D15" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20758,11 +20776,11 @@
       </c>
       <c r="E15" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="F15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20778,7 +20796,7 @@
       </c>
       <c r="J15" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>354.1</v>
+        <v>76.550000000000011</v>
       </c>
       <c r="K15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20788,15 +20806,15 @@
     <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46181</v>
+        <v>46212</v>
       </c>
       <c r="B16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-61</v>
+        <v>Inv-92</v>
       </c>
       <c r="C16" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 20 بقيمه 0.750</v>
+        <v>عطريات عدد 1 الفحبه 1</v>
       </c>
       <c r="D16" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20804,11 +20822,11 @@
       </c>
       <c r="E16" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G16" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20824,7 +20842,7 @@
       </c>
       <c r="J16" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>369.1</v>
+        <v>77.550000000000011</v>
       </c>
       <c r="K16" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20834,31 +20852,31 @@
     <row r="17" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46181</v>
-      </c>
-      <c r="B17" s="59">
+        <v>46217</v>
+      </c>
+      <c r="B17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-93</v>
       </c>
       <c r="C17" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>اسمنت اسود للمحميه الصغيره الجديده</v>
+        <v>متنوع عدد 2 الحبه 2.500</v>
       </c>
       <c r="D17" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E17" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G17" s="59" t="str">
+      <c r="G17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20870,7 +20888,7 @@
       </c>
       <c r="J17" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>366.3</v>
+        <v>82.550000000000011</v>
       </c>
       <c r="K17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20880,31 +20898,31 @@
     <row r="18" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46181</v>
-      </c>
-      <c r="B18" s="61">
+        <v>46217</v>
+      </c>
+      <c r="B18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-94</v>
       </c>
       <c r="C18" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>حديد اسود للمحميه الصغيره الجديده</v>
+        <v>متنوع عدد 12 الحبه 2</v>
       </c>
       <c r="D18" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="E18" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G18" s="61" t="str">
+      <c r="G18" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20916,7 +20934,7 @@
       </c>
       <c r="J18" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>319.55</v>
+        <v>106.55000000000001</v>
       </c>
       <c r="K18" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20926,31 +20944,31 @@
     <row r="19" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46182</v>
-      </c>
-      <c r="B19" s="59" t="str">
+        <v>46217</v>
+      </c>
+      <c r="B19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-62</v>
+        <v>0</v>
       </c>
       <c r="C19" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 30 الحبه 0.750</v>
+        <v>حبل تعليق</v>
       </c>
       <c r="D19" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="E19" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20962,7 +20980,7 @@
       </c>
       <c r="J19" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>342.05</v>
+        <v>104.62500000000001</v>
       </c>
       <c r="K19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20972,31 +20990,31 @@
     <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46184</v>
-      </c>
-      <c r="B20" s="61">
+        <v>46219</v>
+      </c>
+      <c r="B20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-95</v>
       </c>
       <c r="C20" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>براغي</v>
+        <v>ربل عدد 1 الحبه 2</v>
       </c>
       <c r="D20" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E20" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G20" s="61" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G20" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21008,25 +21026,25 @@
       </c>
       <c r="J20" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>338.55</v>
-      </c>
-      <c r="K20" s="61">
+        <v>106.62500000000001</v>
+      </c>
+      <c r="K20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>مهندس عامر</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46184</v>
+        <v>46219</v>
       </c>
       <c r="B21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-63</v>
+        <v>Inv-96</v>
       </c>
       <c r="C21" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 20 بقيمه 0.750</v>
+        <v xml:space="preserve">دارسينا عدد 1 الحبه 2 </v>
       </c>
       <c r="D21" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21034,11 +21052,11 @@
       </c>
       <c r="E21" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G21" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21054,41 +21072,41 @@
       </c>
       <c r="J21" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>338.55</v>
+        <v>108.62500000000001</v>
       </c>
       <c r="K21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ملغيه</v>
+        <v>مهندس عامر</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46185</v>
-      </c>
-      <c r="B22" s="61">
+        <v>46221</v>
+      </c>
+      <c r="B22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-97</v>
       </c>
       <c r="C22" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>رول لحيم</v>
+        <v>افوبيا عدد 1 الحبه 1</v>
       </c>
       <c r="D22" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G22" s="61" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G22" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21100,7 +21118,7 @@
       </c>
       <c r="J22" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>336.55</v>
+        <v>109.62500000000001</v>
       </c>
       <c r="K22" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21110,15 +21128,15 @@
     <row r="23" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46186</v>
+        <v>46221</v>
       </c>
       <c r="B23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-64</v>
+        <v>Inv-98</v>
       </c>
       <c r="C23" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلقات عدد 10 الحبه 1</v>
+        <v>دارسينا عدد 1 الحبه 2</v>
       </c>
       <c r="D23" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21126,11 +21144,11 @@
       </c>
       <c r="E23" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21146,7 +21164,7 @@
       </c>
       <c r="J23" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>346.55</v>
+        <v>111.62500000000001</v>
       </c>
       <c r="K23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21156,15 +21174,15 @@
     <row r="24" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46186</v>
+        <v>46224</v>
       </c>
       <c r="B24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-65</v>
+        <v>Inv-99</v>
       </c>
       <c r="C24" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودوليه عدد 5 الحبه 1</v>
+        <v>افوبيا عدد 9 الحبه 1</v>
       </c>
       <c r="D24" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21172,7 +21190,7 @@
       </c>
       <c r="E24" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21192,7 +21210,7 @@
       </c>
       <c r="J24" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>351.55</v>
+        <v>120.62500000000001</v>
       </c>
       <c r="K24" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21202,35 +21220,35 @@
     <row r="25" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46187</v>
-      </c>
-      <c r="B25" s="59">
+        <v>46224</v>
+      </c>
+      <c r="B25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-100</v>
       </c>
       <c r="C25" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عصايا عدد 2000 احواض معاقات عدد 250</v>
+        <v>ربل عدد 11 الحبه 2</v>
       </c>
       <c r="D25" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>107.5</v>
+        <v>0</v>
       </c>
       <c r="E25" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
-      </c>
-      <c r="G25" s="59" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
+        <v>0</v>
       </c>
       <c r="H25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
+        <v>تم الدفع</v>
       </c>
       <c r="I25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21238,7 +21256,7 @@
       </c>
       <c r="J25" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>351.55</v>
+        <v>142.625</v>
       </c>
       <c r="K25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21248,15 +21266,15 @@
     <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46189</v>
+        <v>46225</v>
       </c>
       <c r="B26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-66</v>
+        <v>Inv-101</v>
       </c>
       <c r="C26" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>شوكليرا عدد10 الحبه 1.500</v>
+        <v>افوبيا عدد2 الحبه 1</v>
       </c>
       <c r="D26" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21264,7 +21282,7 @@
       </c>
       <c r="E26" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21284,7 +21302,7 @@
       </c>
       <c r="J26" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>366.55</v>
+        <v>144.625</v>
       </c>
       <c r="K26" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21294,15 +21312,15 @@
     <row r="27" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46189</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-67</v>
+        <v>Inv-102</v>
       </c>
       <c r="C27" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فيكس عدد7 الحبه 1</v>
+        <v>متنوع عدد2 الحبه 1</v>
       </c>
       <c r="D27" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21310,7 +21328,7 @@
       </c>
       <c r="E27" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21330,7 +21348,7 @@
       </c>
       <c r="J27" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>373.55</v>
+        <v>146.625</v>
       </c>
       <c r="K27" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21340,31 +21358,31 @@
     <row r="28" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46189</v>
-      </c>
-      <c r="B28" s="61" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B28" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-68</v>
+        <v>0</v>
       </c>
       <c r="C28" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد 5 الحبه 2</v>
+        <v>كوكوبيد</v>
       </c>
       <c r="D28" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E28" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G28" s="61">
+        <v>نقداً</v>
+      </c>
+      <c r="G28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21376,7 +21394,7 @@
       </c>
       <c r="J28" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>383.55</v>
+        <v>136.625</v>
       </c>
       <c r="K28" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21386,31 +21404,31 @@
     <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46189</v>
-      </c>
-      <c r="B29" s="59" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-69</v>
+        <v>0</v>
       </c>
       <c r="C29" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 24 الحبه .750</v>
+        <v>احواض عدد 1000 مقاس 14 سم</v>
       </c>
       <c r="D29" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E29" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G29" s="59">
+        <v>نقداً</v>
+      </c>
+      <c r="G29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21422,7 +21440,7 @@
       </c>
       <c r="J29" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>401.55</v>
+        <v>116.625</v>
       </c>
       <c r="K29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21432,31 +21450,31 @@
     <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46188</v>
-      </c>
-      <c r="B30" s="61">
+        <v>46594</v>
+      </c>
+      <c r="B30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-103</v>
       </c>
       <c r="C30" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أقامه عبدول</v>
+        <v>متفرقات</v>
       </c>
       <c r="D30" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E30" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G30" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G30" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21468,7 +21486,7 @@
       </c>
       <c r="J30" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>376.55</v>
+        <v>124.125</v>
       </c>
       <c r="K30" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21478,31 +21496,31 @@
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46190</v>
-      </c>
-      <c r="B31" s="59" t="str">
+        <v>46229</v>
+      </c>
+      <c r="B31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-70</v>
+        <v>0</v>
       </c>
       <c r="C31" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبياعدد 1 الحبه .0.750</v>
+        <v>تسوية رصيد فعلي - الكاش الفعلي 16.750</v>
       </c>
       <c r="D31" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>107.375</v>
       </c>
       <c r="E31" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G31" s="59">
+        <v>نقداً</v>
+      </c>
+      <c r="G31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21514,7 +21532,7 @@
       </c>
       <c r="J31" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>377.3</v>
+        <v>16.75</v>
       </c>
       <c r="K31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21522,739 +21540,739 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25">
+      <c r="A32" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46190</v>
+        <v/>
       </c>
       <c r="B32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-71</v>
+        <v/>
       </c>
       <c r="C32" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 الحبه 1.500</v>
-      </c>
-      <c r="D32" s="28">
+        <v/>
+      </c>
+      <c r="D32" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="62">
+        <v/>
+      </c>
+      <c r="E32" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1.5</v>
+        <v/>
       </c>
       <c r="F32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G32" s="61">
+        <v/>
+      </c>
+      <c r="G32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I32" s="61">
+        <v/>
+      </c>
+      <c r="I32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="34">
+        <v/>
+      </c>
+      <c r="J32" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>378.8</v>
-      </c>
-      <c r="K32" s="61">
+        <v/>
+      </c>
+      <c r="K32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="139">
+      <c r="A33" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46191</v>
+        <v/>
       </c>
       <c r="B33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-72</v>
+        <v/>
       </c>
       <c r="C33" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 1 الحبه 0.750</v>
-      </c>
-      <c r="D33" s="38">
+        <v/>
+      </c>
+      <c r="D33" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="60">
+        <v/>
+      </c>
+      <c r="E33" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0.75</v>
+        <v/>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G33" s="59">
+        <v/>
+      </c>
+      <c r="G33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I33" s="59">
+        <v/>
+      </c>
+      <c r="I33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="43">
+        <v/>
+      </c>
+      <c r="J33" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>379.55</v>
-      </c>
-      <c r="K33" s="59">
+        <v/>
+      </c>
+      <c r="K33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
+      <c r="A34" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46191</v>
+        <v/>
       </c>
       <c r="B34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-73</v>
+        <v/>
       </c>
       <c r="C34" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه عدد 3 الحبه 1</v>
-      </c>
-      <c r="D34" s="28">
+        <v/>
+      </c>
+      <c r="D34" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="62">
+        <v/>
+      </c>
+      <c r="E34" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="F34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G34" s="61">
+        <v/>
+      </c>
+      <c r="G34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I34" s="61">
+        <v/>
+      </c>
+      <c r="I34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="34">
+        <v/>
+      </c>
+      <c r="J34" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>382.55</v>
-      </c>
-      <c r="K34" s="61">
+        <v/>
+      </c>
+      <c r="K34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63">
+      <c r="A35" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46199</v>
+        <v/>
       </c>
       <c r="B35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-74</v>
+        <v/>
       </c>
       <c r="C35" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد 11 الحبه 2</v>
-      </c>
-      <c r="D35" s="66">
+        <v/>
+      </c>
+      <c r="D35" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="67">
+        <v/>
+      </c>
+      <c r="E35" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="F35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G35" s="64">
+        <v/>
+      </c>
+      <c r="G35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I35" s="64">
+        <v/>
+      </c>
+      <c r="I35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="68">
+        <v/>
+      </c>
+      <c r="J35" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>404.55</v>
-      </c>
-      <c r="K35" s="64">
+        <v/>
+      </c>
+      <c r="K35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69">
+      <c r="A36" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46199</v>
+        <v/>
       </c>
       <c r="B36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-75</v>
+        <v/>
       </c>
       <c r="C36" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>شوفليرا عدد6 الحبه 1.500</v>
-      </c>
-      <c r="D36" s="72">
+        <v/>
+      </c>
+      <c r="D36" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="73">
+        <v/>
+      </c>
+      <c r="E36" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="F36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G36" s="70">
+        <v/>
+      </c>
+      <c r="G36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I36" s="70">
+        <v/>
+      </c>
+      <c r="I36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="74">
+        <v/>
+      </c>
+      <c r="J36" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>413.55</v>
-      </c>
-      <c r="K36" s="70">
+        <v/>
+      </c>
+      <c r="K36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="63">
+      <c r="A37" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46197</v>
-      </c>
-      <c r="B37" s="64">
+        <v/>
+      </c>
+      <c r="B37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C37" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>nbk 18-18-18</v>
-      </c>
-      <c r="D37" s="66">
+        <v/>
+      </c>
+      <c r="D37" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>12</v>
-      </c>
-      <c r="E37" s="67">
+        <v/>
+      </c>
+      <c r="E37" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I37" s="64">
+        <v/>
+      </c>
+      <c r="I37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="68">
+        <v/>
+      </c>
+      <c r="J37" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>401.55</v>
-      </c>
-      <c r="K37" s="64">
+        <v/>
+      </c>
+      <c r="K37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69">
+      <c r="A38" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46201</v>
+        <v/>
       </c>
       <c r="B38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-76</v>
+        <v/>
       </c>
       <c r="C38" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد 11 الحبه 0.750</v>
-      </c>
-      <c r="D38" s="72">
+        <v/>
+      </c>
+      <c r="D38" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="73">
+        <v/>
+      </c>
+      <c r="E38" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8.25</v>
+        <v/>
       </c>
       <c r="F38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G38" s="70">
+        <v/>
+      </c>
+      <c r="G38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I38" s="70">
+        <v/>
+      </c>
+      <c r="I38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="74">
+        <v/>
+      </c>
+      <c r="J38" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>409.8</v>
-      </c>
-      <c r="K38" s="70">
+        <v/>
+      </c>
+      <c r="K38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="63">
+      <c r="A39" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46202</v>
+        <v/>
       </c>
       <c r="B39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-77</v>
+        <v/>
       </c>
       <c r="C39" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عطره عدد 3 الحبه 0.750</v>
-      </c>
-      <c r="D39" s="66">
+        <v/>
+      </c>
+      <c r="D39" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="67">
+        <v/>
+      </c>
+      <c r="E39" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.25</v>
+        <v/>
       </c>
       <c r="F39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G39" s="64">
+        <v/>
+      </c>
+      <c r="G39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I39" s="64">
+        <v/>
+      </c>
+      <c r="I39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="68">
+        <v/>
+      </c>
+      <c r="J39" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>412.05</v>
-      </c>
-      <c r="K39" s="64">
+        <v/>
+      </c>
+      <c r="K39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="69">
+      <c r="A40" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46202</v>
+        <v/>
       </c>
       <c r="B40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-78</v>
+        <v/>
       </c>
       <c r="C40" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلقات عدد 3 الحبه 1</v>
-      </c>
-      <c r="D40" s="72">
+        <v/>
+      </c>
+      <c r="D40" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="73">
+        <v/>
+      </c>
+      <c r="E40" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="F40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G40" s="70">
+        <v/>
+      </c>
+      <c r="G40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I40" s="70">
+        <v/>
+      </c>
+      <c r="I40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="74">
+        <v/>
+      </c>
+      <c r="J40" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>415.05</v>
-      </c>
-      <c r="K40" s="70">
+        <v/>
+      </c>
+      <c r="K40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="63">
+      <c r="A41" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
+        <v/>
       </c>
       <c r="B41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-79</v>
+        <v/>
       </c>
       <c r="C41" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلقات عدد 4 الحبه 1</v>
-      </c>
-      <c r="D41" s="66">
+        <v/>
+      </c>
+      <c r="D41" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="67">
+        <v/>
+      </c>
+      <c r="E41" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="F41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G41" s="64">
+        <v/>
+      </c>
+      <c r="G41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I41" s="64">
+        <v/>
+      </c>
+      <c r="I41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="68">
+        <v/>
+      </c>
+      <c r="J41" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>419.05</v>
-      </c>
-      <c r="K41" s="64">
+        <v/>
+      </c>
+      <c r="K41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="69">
+      <c r="A42" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
+        <v/>
       </c>
       <c r="B42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-80</v>
+        <v/>
       </c>
       <c r="C42" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلقات عدد4 الحبه 1</v>
-      </c>
-      <c r="D42" s="72">
+        <v/>
+      </c>
+      <c r="D42" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="73">
+        <v/>
+      </c>
+      <c r="E42" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="F42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G42" s="70">
+        <v/>
+      </c>
+      <c r="G42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I42" s="70">
+        <v/>
+      </c>
+      <c r="I42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="74">
+        <v/>
+      </c>
+      <c r="J42" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>423.05</v>
-      </c>
-      <c r="K42" s="70">
+        <v/>
+      </c>
+      <c r="K42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="63">
+      <c r="A43" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
+        <v/>
       </c>
       <c r="B43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-81</v>
+        <v/>
       </c>
       <c r="C43" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبيا عدد 2 الحبه 1</v>
-      </c>
-      <c r="D43" s="66">
+        <v/>
+      </c>
+      <c r="D43" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="67">
+        <v/>
+      </c>
+      <c r="E43" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G43" s="64">
+        <v/>
+      </c>
+      <c r="G43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I43" s="64">
+        <v/>
+      </c>
+      <c r="I43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="68">
+        <v/>
+      </c>
+      <c r="J43" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>425.05</v>
-      </c>
-      <c r="K43" s="64">
+        <v/>
+      </c>
+      <c r="K43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="69">
+      <c r="A44" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
-      </c>
-      <c r="B44" s="70">
+        <v/>
+      </c>
+      <c r="B44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C44" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>رواتب عماله شهر يونيو 2026</v>
-      </c>
-      <c r="D44" s="72">
+        <v/>
+      </c>
+      <c r="D44" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>320</v>
-      </c>
-      <c r="E44" s="73">
+        <v/>
+      </c>
+      <c r="E44" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I44" s="70">
+        <v/>
+      </c>
+      <c r="I44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="74">
+        <v/>
+      </c>
+      <c r="J44" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>105.05000000000001</v>
-      </c>
-      <c r="K44" s="70">
+        <v/>
+      </c>
+      <c r="K44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="63">
+      <c r="A45" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
-      </c>
-      <c r="B45" s="64">
+        <v/>
+      </c>
+      <c r="B45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C45" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تكمله رواتب يونيو 2026 ابوادم</v>
-      </c>
-      <c r="D45" s="66">
+        <v/>
+      </c>
+      <c r="D45" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>50</v>
-      </c>
-      <c r="E45" s="67">
+        <v/>
+      </c>
+      <c r="E45" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v/>
       </c>
       <c r="G45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو آدم</v>
+        <v/>
       </c>
       <c r="H45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
-      </c>
-      <c r="I45" s="64">
+        <v/>
+      </c>
+      <c r="I45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="68">
+        <v/>
+      </c>
+      <c r="J45" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>105.05000000000001</v>
-      </c>
-      <c r="K45" s="64">
+        <v/>
+      </c>
+      <c r="K45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="69">
+      <c r="A46" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
-      </c>
-      <c r="B46" s="70">
+        <v/>
+      </c>
+      <c r="B46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C46" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تكمله رواتب يونيو 2026 ابواسحاق</v>
-      </c>
-      <c r="D46" s="72">
+        <v/>
+      </c>
+      <c r="D46" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>50</v>
-      </c>
-      <c r="E46" s="73">
+        <v/>
+      </c>
+      <c r="E46" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v/>
       </c>
       <c r="G46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
+        <v/>
       </c>
       <c r="H46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلق</v>
-      </c>
-      <c r="I46" s="70">
+        <v/>
+      </c>
+      <c r="I46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="74">
+        <v/>
+      </c>
+      <c r="J46" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>105.05000000000001</v>
-      </c>
-      <c r="K46" s="70">
+        <v/>
+      </c>
+      <c r="K46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="63">
+      <c r="A47" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46203</v>
-      </c>
-      <c r="B47" s="64">
+        <v/>
+      </c>
+      <c r="B47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C47" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>احواض عدد 1000 مقاس 25 سم</v>
-      </c>
-      <c r="D47" s="66">
+        <v/>
+      </c>
+      <c r="D47" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>80</v>
-      </c>
-      <c r="E47" s="67">
+        <v/>
+      </c>
+      <c r="E47" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I47" s="64">
+        <v/>
+      </c>
+      <c r="I47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="68">
+        <v/>
+      </c>
+      <c r="J47" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>25.050000000000011</v>
-      </c>
-      <c r="K47" s="64">
+        <v/>
+      </c>
+      <c r="K47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27187,22 +27205,22 @@
       <c r="C155" s="155"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>724.8</v>
+        <v>159.30000000000001</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>195.5</v>
+        <v>151</v>
       </c>
       <c r="F155" s="167">
         <f>COUNTIF(H5:H154,"معلق")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G155" s="155"/>
       <c r="H155" s="155"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-529.29999999999995</v>
+        <v>-8.3000000000000114</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27326,7 +27344,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="170" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="155"/>
@@ -28637,7 +28655,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="170" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="155"/>
@@ -28651,7 +28669,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="170" t="s">
+      <c r="A56" s="172" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="155"/>
@@ -29962,7 +29980,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="170" t="s">
+      <c r="A107" s="172" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="155"/>
@@ -29985,7 +30003,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="171">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -29994,17 +30012,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6546A8B5-17A7-4C94-9746-715417BE2FDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8383E9E7-8B68-492B-9C6C-1D1DB4A8655E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="324">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1001,7 +1001,19 @@
     <t>يوليو</t>
   </si>
   <si>
-    <t>تسوية رصيد فعلي - الكاش الفعلي 16.750</t>
+    <t>تسوية رصيد فعلي - المتوفر 107.305 (صافي الشهر 99.075 + فائض عام 16.750)</t>
+  </si>
+  <si>
+    <t>Inv-104</t>
+  </si>
+  <si>
+    <t>متنوع عدد 1 الحبه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-105</t>
+  </si>
+  <si>
+    <t>دارسينا عدد 1 الحبه 3</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2120,6 +2132,9 @@
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="46" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -2179,14 +2194,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2530,45 +2545,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="148"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="149"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>16.75</v>
+        <v>112.80500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="153"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149"/>
+      <c r="A3" s="154"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="150"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="148"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="149"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="150"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -5357,7 +5372,7 @@
       </c>
       <c r="C112" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>تسوية رصيد فعلي - الكاش الفعلي 16.750</v>
+        <v>تسوية رصيد فعلي - المتوفر 107.305 (صافي الشهر 99.075 + فائض عام 16.750)</v>
       </c>
       <c r="D112" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -5365,63 +5380,63 @@
       </c>
       <c r="E112" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(107,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>107.375</v>
+        <v>16.82</v>
       </c>
       <c r="F112" s="125">
         <f t="shared" si="3"/>
-        <v>16.75</v>
+        <v>107.30500000000001</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="142" t="str">
+      <c r="A113" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(108,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46231</v>
       </c>
       <c r="B113" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(108,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-104</v>
       </c>
       <c r="C113" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(108,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D113" s="123" t="str">
+        <v>متنوع عدد 1 الحبه 2.500</v>
+      </c>
+      <c r="D113" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(108,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E113" s="124" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E113" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(108,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F113" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F113" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>109.80500000000001</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="142" t="str">
+      <c r="A114" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(109,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46231</v>
       </c>
       <c r="B114" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(109,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-105</v>
       </c>
       <c r="C114" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(109,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D114" s="123" t="str">
+        <v>دارسينا عدد 1 الحبه 3</v>
+      </c>
+      <c r="D114" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(109,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E114" s="124" t="str">
+        <v>3</v>
+      </c>
+      <c r="E114" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(109,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F114" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F114" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>112.80500000000001</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7798,26 +7813,26 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>708.1</v>
+        <v>713.6</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>691.34999999999991</v>
+        <v>600.79499999999996</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>16.75</v>
+        <v>112.80500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="147" t="s">
+      <c r="A208" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="148"/>
-      <c r="C208" s="148"/>
-      <c r="D208" s="148"/>
-      <c r="E208" s="148"/>
-      <c r="F208" s="149"/>
+      <c r="B208" s="149"/>
+      <c r="C208" s="149"/>
+      <c r="D208" s="149"/>
+      <c r="E208" s="149"/>
+      <c r="F208" s="150"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10215,38 +10230,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="158" t="s">
+      <c r="E2" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -16686,7 +16701,7 @@
         <v>319</v>
       </c>
       <c r="D127" s="28">
-        <v>107.375</v>
+        <v>16.82</v>
       </c>
       <c r="E127" s="29"/>
       <c r="F127" s="30" t="s">
@@ -16701,7 +16716,7 @@
       <c r="I127" s="33"/>
       <c r="J127" s="34">
         <f>IF(AND(D127="",E127="",A127="",B127="",C127=""),"", IFERROR(IF(J126="",D2,J126),D2)+IF(E127="",0,E127)-IF(OR(G127="أبو اسحاق",G127="أبو آدم",G127="أبو اسحاق ",G127="أبو آدم "),0,IF(D127="",0,D127)))</f>
-        <v>16.75</v>
+        <v>107.30500000000001</v>
       </c>
       <c r="K127" s="35"/>
       <c r="L127">
@@ -16730,18 +16745,30 @@
       </c>
     </row>
     <row r="128" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="139"/>
-      <c r="B128" s="36"/>
-      <c r="C128" s="37"/>
+      <c r="A128" s="139">
+        <v>46231</v>
+      </c>
+      <c r="B128" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="C128" s="37" t="s">
+        <v>321</v>
+      </c>
       <c r="D128" s="38"/>
-      <c r="E128" s="39"/>
-      <c r="F128" s="136"/>
+      <c r="E128" s="39">
+        <v>2.5</v>
+      </c>
+      <c r="F128" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G128" s="40"/>
-      <c r="H128" s="41"/>
+      <c r="H128" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I128" s="42"/>
-      <c r="J128" s="43" t="str">
+      <c r="J128" s="43">
         <f>IF(AND(D128="",E128="",A128="",B128="",C128=""),"", IFERROR(IF(J127="",D2,J127),D2)+IF(E128="",0,E128)-IF(OR(G128="أبو اسحاق",G128="أبو آدم",G128="أبو اسحاق ",G128="أبو آدم "),0,IF(D128="",0,D128)))</f>
-        <v/>
+        <v>109.80500000000001</v>
       </c>
       <c r="K128" s="44"/>
       <c r="L128" t="str">
@@ -16752,17 +16779,17 @@
         <f>IF(AND(D127&gt;0,G127="المحفظة"),COUNTIFS($D$4:D127,"&gt;"&amp;0,$G$4:G127,"المحفظة"),"")</f>
         <v>19</v>
       </c>
-      <c r="N128" t="str">
+      <c r="N128">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A128)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A128)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A128&lt;&gt;""),IFERROR(MAX($N$4:N127),0)+1,"")</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="O128" t="str">
         <f>IF(AND(D127&gt;0,F127="أحد الشركاء"),COUNTIFS($D$4:D127,"&gt;"&amp;0,$F$4:F127,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P128" t="str">
+      <c r="P128">
         <f>IF(OR($A128="",$F128="أحد الشركاء",AND($D128="",$E128="")),"",SUMPRODUCT(($A$4:$A128&lt;&gt;"")*($F$4:$F128&lt;&gt;"أحد الشركاء")*((($D$4:$D128&lt;&gt;"")+($E$4:$E128&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>108</v>
       </c>
       <c r="Q128" t="str">
         <f>IF(OR($A128="",$F128&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A128,"&lt;&gt;",$F$4:F128,"أحد الشركاء"))</f>
@@ -16770,39 +16797,51 @@
       </c>
     </row>
     <row r="129" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="25"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="147">
+        <v>46231</v>
+      </c>
+      <c r="B129" s="36" t="s">
+        <v>322</v>
+      </c>
+      <c r="C129" s="27" t="s">
+        <v>323</v>
+      </c>
       <c r="D129" s="28"/>
-      <c r="E129" s="29"/>
-      <c r="F129" s="30"/>
+      <c r="E129" s="29">
+        <v>3</v>
+      </c>
+      <c r="F129" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G129" s="31"/>
-      <c r="H129" s="32"/>
+      <c r="H129" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I129" s="33"/>
-      <c r="J129" s="34" t="str">
+      <c r="J129" s="34">
         <f>IF(AND(D129="",E129="",A129="",B129="",C129=""),"", IFERROR(IF(J128="",D2,J128),D2)+IF(E129="",0,E129)-IF(OR(G129="أبو اسحاق",G129="أبو آدم",G129="أبو اسحاق ",G129="أبو آدم "),0,IF(D129="",0,D129)))</f>
-        <v/>
+        <v>112.80500000000001</v>
       </c>
       <c r="K129" s="35"/>
-      <c r="L129" t="str">
+      <c r="L129">
         <f>IF(E128&gt;0,COUNTIF($E$4:E128,"&gt;0"),"")</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="M129" t="str">
         <f>IF(AND(D128&gt;0,G128="المحفظة"),COUNTIFS($D$4:D128,"&gt;"&amp;0,$G$4:G128,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N129" t="str">
+      <c r="N129">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A129)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A129)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A129&lt;&gt;""),IFERROR(MAX($N$4:N128),0)+1,"")</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="O129" t="str">
         <f>IF(AND(D128&gt;0,F128="أحد الشركاء"),COUNTIFS($D$4:D128,"&gt;"&amp;0,$F$4:F128,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P129" t="str">
+      <c r="P129">
         <f>IF(OR($A129="",$F129="أحد الشركاء",AND($D129="",$E129="")),"",SUMPRODUCT(($A$4:$A129&lt;&gt;"")*($F$4:$F129&lt;&gt;"أحد الشركاء")*((($D$4:$D129&lt;&gt;"")+($E$4:$E129&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>109</v>
       </c>
       <c r="Q129" t="str">
         <f>IF(OR($A129="",$F129&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A129,"&lt;&gt;",$F$4:F129,"أحد الشركاء"))</f>
@@ -16824,9 +16863,9 @@
         <v/>
       </c>
       <c r="K130" s="44"/>
-      <c r="L130" t="str">
+      <c r="L130">
         <f>IF(E129&gt;0,COUNTIF($E$4:E129,"&gt;0"),"")</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="M130" t="str">
         <f>IF(AND(D129&gt;0,G129="المحفظة"),COUNTIFS($D$4:D129,"&gt;"&amp;0,$G$4:G129,"المحفظة"),"")</f>
@@ -19770,14 +19809,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="161"/>
-      <c r="B204" s="155"/>
-      <c r="C204" s="156"/>
+      <c r="A204" s="162"/>
+      <c r="B204" s="156"/>
+      <c r="C204" s="157"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="154"/>
-      <c r="G204" s="155"/>
-      <c r="H204" s="156"/>
+      <c r="F204" s="155"/>
+      <c r="G204" s="156"/>
+      <c r="H204" s="157"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -19817,11 +19856,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>1713.85</v>
+        <v>1623.2949999999998</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>708.1</v>
+        <v>713.6</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -19912,11 +19951,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -20074,16 +20113,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="165" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="156"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="164" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="155"/>
+      <c r="B2" s="156"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -20102,10 +20141,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="164" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="155"/>
+      <c r="B5" s="156"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -20148,10 +20187,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="163" t="s">
+      <c r="A11" s="164" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="155"/>
+      <c r="B11" s="156"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -20216,47 +20255,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="165"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="156"/>
       <c r="C2" s="56" t="s">
         <v>318</v>
       </c>
-      <c r="D2" s="165">
+      <c r="D2" s="166">
         <v>2026</v>
       </c>
-      <c r="E2" s="155"/>
+      <c r="E2" s="156"/>
       <c r="F2" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="168" t="s">
+      <c r="G2" s="169" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -21504,11 +21543,11 @@
       </c>
       <c r="C31" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تسوية رصيد فعلي - الكاش الفعلي 16.750</v>
+        <v>تسوية رصيد فعلي - المتوفر 107.305 (صافي الشهر 99.075 + فائض عام 16.750)</v>
       </c>
       <c r="D31" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>107.375</v>
+        <v>16.82</v>
       </c>
       <c r="E31" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21532,7 +21571,7 @@
       </c>
       <c r="J31" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>16.75</v>
+        <v>107.30500000000001</v>
       </c>
       <c r="K31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21540,95 +21579,95 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="str">
+      <c r="A32" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46231</v>
       </c>
       <c r="B32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-104</v>
       </c>
       <c r="C32" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="28" t="str">
+        <v>متنوع عدد 1 الحبه 2.500</v>
+      </c>
+      <c r="D32" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E32" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="F32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="61" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G32" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I32" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J32" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="61" t="str">
+        <v>109.80500000000001</v>
+      </c>
+      <c r="K32" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="139" t="str">
+      <c r="A33" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46231</v>
       </c>
       <c r="B33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-105</v>
       </c>
       <c r="C33" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="38" t="str">
+        <v>دارسينا عدد 1 الحبه 3</v>
+      </c>
+      <c r="D33" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="60" t="str">
+        <v>0</v>
+      </c>
+      <c r="E33" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="59" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J33" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="59" t="str">
+        <v>112.80500000000001</v>
+      </c>
+      <c r="K33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27198,29 +27237,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="166" t="s">
+      <c r="A155" s="167" t="s">
         <v>266</v>
       </c>
-      <c r="B155" s="155"/>
-      <c r="C155" s="155"/>
+      <c r="B155" s="156"/>
+      <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>159.30000000000001</v>
+        <v>68.745000000000005</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>151</v>
-      </c>
-      <c r="F155" s="167">
+        <v>156.5</v>
+      </c>
+      <c r="F155" s="168">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="155"/>
-      <c r="H155" s="155"/>
+      <c r="G155" s="156"/>
+      <c r="H155" s="156"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-8.3000000000000114</v>
+        <v>87.754999999999995</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27299,60 +27338,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="166" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="155"/>
+      <c r="B2" s="156"/>
       <c r="C2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="166" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="155"/>
+      <c r="E2" s="156"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="170" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="155"/>
+      <c r="B3" s="156"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="169" t="s">
+      <c r="D3" s="170" t="s">
         <v>273</v>
       </c>
-      <c r="E3" s="155"/>
+      <c r="E3" s="156"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="170" t="s">
+      <c r="A4" s="172" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -28655,12 +28694,12 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="170" t="s">
+      <c r="A55" s="172" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="155"/>
-      <c r="C55" s="155"/>
-      <c r="D55" s="155"/>
+      <c r="B55" s="156"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="156"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -28669,15 +28708,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="172" t="s">
+      <c r="A56" s="171" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="155"/>
-      <c r="C56" s="155"/>
-      <c r="D56" s="155"/>
-      <c r="E56" s="155"/>
-      <c r="F56" s="155"/>
-      <c r="G56" s="155"/>
+      <c r="B56" s="156"/>
+      <c r="C56" s="156"/>
+      <c r="D56" s="156"/>
+      <c r="E56" s="156"/>
+      <c r="F56" s="156"/>
+      <c r="G56" s="156"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -29980,11 +30019,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="172" t="s">
+      <c r="A107" s="171" t="s">
         <v>277</v>
       </c>
-      <c r="B107" s="155"/>
-      <c r="C107" s="155"/>
+      <c r="B107" s="156"/>
+      <c r="C107" s="156"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -29994,35 +30033,35 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="166" t="s">
+      <c r="A108" s="167" t="s">
         <v>278</v>
       </c>
-      <c r="B108" s="155"/>
-      <c r="C108" s="155"/>
+      <c r="B108" s="156"/>
+      <c r="C108" s="156"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="171">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="155"/>
-      <c r="G108" s="156"/>
+      <c r="F108" s="156"/>
+      <c r="G108" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8383E9E7-8B68-492B-9C6C-1D1DB4A8655E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA022ABB-4211-40ED-85CB-C50E6DBE50A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="326">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1014,6 +1014,12 @@
   </si>
   <si>
     <t>دارسينا عدد 1 الحبه 3</t>
+  </si>
+  <si>
+    <t>عدد 3 عماله + 10 ايام العامل البديل 40 دينار</t>
+  </si>
+  <si>
+    <t>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</t>
   </si>
 </sst>
 </file>
@@ -2194,14 +2200,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2564,7 +2570,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>112.80500000000001</v>
+        <v>13.805000000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5440,29 +5446,29 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="142" t="str">
+      <c r="A115" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(110,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B115" s="122" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B115" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(110,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C115" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(110,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D115" s="123" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار</v>
+      </c>
+      <c r="D115" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(110,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E115" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E115" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(110,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F115" s="125" t="str">
+        <v>99</v>
+      </c>
+      <c r="F115" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>13.805000000000007</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7817,11 +7823,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>600.79499999999996</v>
+        <v>699.79499999999996</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>112.80500000000001</v>
+        <v>13.805000000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8106,48 +8112,48 @@
       <c r="F220" s="132"/>
     </row>
     <row r="221" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="143" t="str">
+      <c r="A221" s="143">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(12,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B221" s="133" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B221" s="133">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(12,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C221" s="132" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(12,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D221" s="134" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
+      </c>
+      <c r="D221" s="134">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(12,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>205.5</v>
       </c>
       <c r="E221" s="135" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$G$4:$G$204,MATCH(12,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>أبو آدم</v>
       </c>
       <c r="F221" s="132"/>
     </row>
     <row r="222" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="143" t="str">
+      <c r="A222" s="143">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(13,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B222" s="133" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B222" s="133">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(13,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C222" s="132" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(13,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D222" s="134" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
+      </c>
+      <c r="D222" s="134">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(13,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>205.5</v>
       </c>
       <c r="E222" s="135" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$G$4:$G$204,MATCH(13,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="F222" s="132"/>
     </row>
@@ -10160,7 +10166,7 @@
       </c>
       <c r="D310" s="128">
         <f>SUM(D210:D309)</f>
-        <v>1022.5</v>
+        <v>1433.5</v>
       </c>
       <c r="E310" s="129"/>
       <c r="F310" s="130"/>
@@ -10173,7 +10179,7 @@
       </c>
       <c r="D311" s="128">
         <f>SUMIF(E210:E309,"أبو اسحاق",D210:D309)</f>
-        <v>562.5</v>
+        <v>768</v>
       </c>
       <c r="E311" s="129"/>
       <c r="F311" s="130"/>
@@ -10186,7 +10192,7 @@
       </c>
       <c r="D312" s="128">
         <f>SUMIF(E210:E309,"أبو آدم",D210:D309)</f>
-        <v>460</v>
+        <v>665.5</v>
       </c>
       <c r="E312" s="129"/>
       <c r="F312" s="130"/>
@@ -16849,18 +16855,30 @@
       </c>
     </row>
     <row r="130" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="139"/>
+      <c r="A130" s="139">
+        <v>46232</v>
+      </c>
       <c r="B130" s="36"/>
-      <c r="C130" s="37"/>
-      <c r="D130" s="38"/>
+      <c r="C130" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="D130" s="38">
+        <v>99</v>
+      </c>
       <c r="E130" s="39"/>
-      <c r="F130" s="136"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="41"/>
+      <c r="F130" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G130" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I130" s="42"/>
-      <c r="J130" s="43" t="str">
+      <c r="J130" s="43">
         <f>IF(AND(D130="",E130="",A130="",B130="",C130=""),"", IFERROR(IF(J129="",D2,J129),D2)+IF(E130="",0,E130)-IF(OR(G130="أبو اسحاق",G130="أبو آدم",G130="أبو اسحاق ",G130="أبو آدم "),0,IF(D130="",0,D130)))</f>
-        <v/>
+        <v>13.805000000000007</v>
       </c>
       <c r="K130" s="44"/>
       <c r="L130">
@@ -16871,49 +16889,61 @@
         <f>IF(AND(D129&gt;0,G129="المحفظة"),COUNTIFS($D$4:D129,"&gt;"&amp;0,$G$4:G129,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N130" t="str">
+      <c r="N130">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A130)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A130)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A130&lt;&gt;""),IFERROR(MAX($N$4:N129),0)+1,"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="O130" t="str">
         <f>IF(AND(D129&gt;0,F129="أحد الشركاء"),COUNTIFS($D$4:D129,"&gt;"&amp;0,$F$4:F129,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P130" t="str">
+      <c r="P130">
         <f>IF(OR($A130="",$F130="أحد الشركاء",AND($D130="",$E130="")),"",SUMPRODUCT(($A$4:$A130&lt;&gt;"")*($F$4:$F130&lt;&gt;"أحد الشركاء")*((($D$4:$D130&lt;&gt;"")+($E$4:$E130&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="Q130" t="str">
         <f>IF(OR($A130="",$F130&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A130,"&lt;&gt;",$F$4:F130,"أحد الشركاء"))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="25"/>
+    <row r="131" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="25">
+        <v>46232</v>
+      </c>
       <c r="B131" s="26"/>
-      <c r="C131" s="27"/>
-      <c r="D131" s="28"/>
+      <c r="C131" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="D131" s="28">
+        <v>205.5</v>
+      </c>
       <c r="E131" s="29"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="31"/>
-      <c r="H131" s="32"/>
+      <c r="F131" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G131" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H131" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I131" s="33"/>
-      <c r="J131" s="34" t="str">
+      <c r="J131" s="34">
         <f>IF(AND(D131="",E131="",A131="",B131="",C131=""),"", IFERROR(IF(J130="",D2,J130),D2)+IF(E131="",0,E131)-IF(OR(G131="أبو اسحاق",G131="أبو آدم",G131="أبو اسحاق ",G131="أبو آدم "),0,IF(D131="",0,D131)))</f>
-        <v/>
+        <v>13.805000000000007</v>
       </c>
       <c r="K131" s="35"/>
       <c r="L131" t="str">
         <f>IF(E130&gt;0,COUNTIF($E$4:E130,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M131" t="str">
+      <c r="M131">
         <f>IF(AND(D130&gt;0,G130="المحفظة"),COUNTIFS($D$4:D130,"&gt;"&amp;0,$G$4:G130,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N131" t="str">
+        <v>20</v>
+      </c>
+      <c r="N131">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A131)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A131)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A131&lt;&gt;""),IFERROR(MAX($N$4:N130),0)+1,"")</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="O131" t="str">
         <f>IF(AND(D130&gt;0,F130="أحد الشركاء"),COUNTIFS($D$4:D130,"&gt;"&amp;0,$F$4:F130,"أحد الشركاء"),"")</f>
@@ -16923,24 +16953,36 @@
         <f>IF(OR($A131="",$F131="أحد الشركاء",AND($D131="",$E131="")),"",SUMPRODUCT(($A$4:$A131&lt;&gt;"")*($F$4:$F131&lt;&gt;"أحد الشركاء")*((($D$4:$D131&lt;&gt;"")+($E$4:$E131&lt;&gt;""))&gt;0)))</f>
         <v/>
       </c>
-      <c r="Q131" t="str">
+      <c r="Q131">
         <f>IF(OR($A131="",$F131&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A131,"&lt;&gt;",$F$4:F131,"أحد الشركاء"))</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="139"/>
+      <c r="A132" s="139">
+        <v>46232</v>
+      </c>
       <c r="B132" s="36"/>
-      <c r="C132" s="37"/>
-      <c r="D132" s="38"/>
+      <c r="C132" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="D132" s="38">
+        <v>205.5</v>
+      </c>
       <c r="E132" s="39"/>
-      <c r="F132" s="136"/>
-      <c r="G132" s="40"/>
-      <c r="H132" s="41"/>
+      <c r="F132" s="136" t="s">
+        <v>48</v>
+      </c>
+      <c r="G132" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H132" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I132" s="42"/>
-      <c r="J132" s="43" t="str">
+      <c r="J132" s="43">
         <f>IF(AND(D132="",E132="",A132="",B132="",C132=""),"", IFERROR(IF(J131="",D2,J131),D2)+IF(E132="",0,E132)-IF(OR(G132="أبو اسحاق",G132="أبو آدم",G132="أبو اسحاق ",G132="أبو آدم "),0,IF(D132="",0,D132)))</f>
-        <v/>
+        <v>13.805000000000007</v>
       </c>
       <c r="K132" s="44"/>
       <c r="L132" t="str">
@@ -16951,21 +16993,21 @@
         <f>IF(AND(D131&gt;0,G131="المحفظة"),COUNTIFS($D$4:D131,"&gt;"&amp;0,$G$4:G131,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N132" t="str">
+      <c r="N132">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A132)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A132)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A132&lt;&gt;""),IFERROR(MAX($N$4:N131),0)+1,"")</f>
-        <v/>
-      </c>
-      <c r="O132" t="str">
+        <v>32</v>
+      </c>
+      <c r="O132">
         <f>IF(AND(D131&gt;0,F131="أحد الشركاء"),COUNTIFS($D$4:D131,"&gt;"&amp;0,$F$4:F131,"أحد الشركاء"),"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="P132" t="str">
         <f>IF(OR($A132="",$F132="أحد الشركاء",AND($D132="",$E132="")),"",SUMPRODUCT(($A$4:$A132&lt;&gt;"")*($F$4:$F132&lt;&gt;"أحد الشركاء")*((($D$4:$D132&lt;&gt;"")+($E$4:$E132&lt;&gt;""))&gt;0)))</f>
         <v/>
       </c>
-      <c r="Q132" t="str">
+      <c r="Q132">
         <f>IF(OR($A132="",$F132&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A132,"&lt;&gt;",$F$4:F132,"أحد الشركاء"))</f>
-        <v/>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16995,9 +17037,9 @@
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A133)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A133)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A133&lt;&gt;""),IFERROR(MAX($N$4:N132),0)+1,"")</f>
         <v/>
       </c>
-      <c r="O133" t="str">
+      <c r="O133">
         <f>IF(AND(D132&gt;0,F132="أحد الشركاء"),COUNTIFS($D$4:D132,"&gt;"&amp;0,$F$4:F132,"أحد الشركاء"),"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="P133" t="str">
         <f>IF(OR($A133="",$F133="أحد الشركاء",AND($D133="",$E133="")),"",SUMPRODUCT(($A$4:$A133&lt;&gt;"")*($F$4:$F133&lt;&gt;"أحد الشركاء")*((($D$4:$D133&lt;&gt;"")+($E$4:$E133&lt;&gt;""))&gt;0)))</f>
@@ -19856,7 +19898,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>1623.2949999999998</v>
+        <v>2133.2950000000001</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -21671,141 +21713,141 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="str">
+      <c r="A34" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="61" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C34" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="28" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار</v>
+      </c>
+      <c r="D34" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="62" t="str">
+        <v>99</v>
+      </c>
+      <c r="E34" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J34" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="61" t="str">
+        <v>13.805000000000007</v>
+      </c>
+      <c r="K34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="str">
+      <c r="A35" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="64" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C35" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="66" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
+      </c>
+      <c r="D35" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="67" t="str">
+        <v>205.5</v>
+      </c>
+      <c r="E35" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو آدم</v>
       </c>
       <c r="H35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J35" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="64" t="str">
+        <v>13.805000000000007</v>
+      </c>
+      <c r="K35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="str">
+      <c r="A36" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="70" t="str">
+        <v>46232</v>
+      </c>
+      <c r="B36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C36" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="72" t="str">
+        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
+      </c>
+      <c r="D36" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="73" t="str">
+        <v>205.5</v>
+      </c>
+      <c r="E36" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="H36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J36" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="70" t="str">
+        <v>13.805000000000007</v>
+      </c>
+      <c r="K36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27244,7 +27286,7 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>68.745000000000005</v>
+        <v>578.745</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27259,7 +27301,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>87.754999999999995</v>
+        <v>-422.245</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27383,7 +27425,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="156"/>
@@ -28694,7 +28736,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="156"/>
@@ -28708,7 +28750,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="156"/>
@@ -30019,7 +30061,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="156"/>
@@ -30042,7 +30084,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30051,17 +30093,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA022ABB-4211-40ED-85CB-C50E6DBE50A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58B742C-F62C-4033-A572-D1823A0D6EA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="327">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1020,6 +1020,9 @@
   </si>
   <si>
     <t>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</t>
+  </si>
+  <si>
+    <t>تعديل رصيد</t>
   </si>
 </sst>
 </file>
@@ -2200,14 +2203,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2570,7 +2573,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>13.805000000000007</v>
+        <v>22.395000000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5472,29 +5475,29 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="142" t="str">
+      <c r="A116" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(111,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B116" s="122" t="str">
+        <v>46234</v>
+      </c>
+      <c r="B116" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(111,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C116" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(111,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D116" s="123" t="str">
+        <v>تعديل رصيد</v>
+      </c>
+      <c r="D116" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(111,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E116" s="124" t="str">
+        <v>8.59</v>
+      </c>
+      <c r="E116" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(111,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F116" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F116" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>22.395000000000007</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7819,7 +7822,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>713.6</v>
+        <v>722.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7827,7 +7830,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>13.805000000000007</v>
+        <v>22.395000000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17011,18 +17014,28 @@
       </c>
     </row>
     <row r="133" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="25"/>
+      <c r="A133" s="25">
+        <v>46234</v>
+      </c>
       <c r="B133" s="26"/>
-      <c r="C133" s="27"/>
+      <c r="C133" s="27" t="s">
+        <v>326</v>
+      </c>
       <c r="D133" s="28"/>
-      <c r="E133" s="29"/>
-      <c r="F133" s="30"/>
+      <c r="E133" s="29">
+        <v>8.59</v>
+      </c>
+      <c r="F133" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G133" s="31"/>
-      <c r="H133" s="32"/>
+      <c r="H133" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I133" s="33"/>
-      <c r="J133" s="34" t="str">
+      <c r="J133" s="34">
         <f>IF(AND(D133="",E133="",A133="",B133="",C133=""),"", IFERROR(IF(J132="",D2,J132),D2)+IF(E133="",0,E133)-IF(OR(G133="أبو اسحاق",G133="أبو آدم",G133="أبو اسحاق ",G133="أبو آدم "),0,IF(D133="",0,D133)))</f>
-        <v/>
+        <v>22.395000000000007</v>
       </c>
       <c r="K133" s="35"/>
       <c r="L133" t="str">
@@ -17033,17 +17046,17 @@
         <f>IF(AND(D132&gt;0,G132="المحفظة"),COUNTIFS($D$4:D132,"&gt;"&amp;0,$G$4:G132,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N133" t="str">
+      <c r="N133">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A133)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A133)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A133&lt;&gt;""),IFERROR(MAX($N$4:N132),0)+1,"")</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="O133">
         <f>IF(AND(D132&gt;0,F132="أحد الشركاء"),COUNTIFS($D$4:D132,"&gt;"&amp;0,$F$4:F132,"أحد الشركاء"),"")</f>
         <v>13</v>
       </c>
-      <c r="P133" t="str">
+      <c r="P133">
         <f>IF(OR($A133="",$F133="أحد الشركاء",AND($D133="",$E133="")),"",SUMPRODUCT(($A$4:$A133&lt;&gt;"")*($F$4:$F133&lt;&gt;"أحد الشركاء")*((($D$4:$D133&lt;&gt;"")+($E$4:$E133&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>111</v>
       </c>
       <c r="Q133" t="str">
         <f>IF(OR($A133="",$F133&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A133,"&lt;&gt;",$F$4:F133,"أحد الشركاء"))</f>
@@ -17065,9 +17078,9 @@
         <v/>
       </c>
       <c r="K134" s="44"/>
-      <c r="L134" t="str">
+      <c r="L134">
         <f>IF(E133&gt;0,COUNTIF($E$4:E133,"&gt;0"),"")</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="M134" t="str">
         <f>IF(AND(D133&gt;0,G133="المحفظة"),COUNTIFS($D$4:D133,"&gt;"&amp;0,$G$4:G133,"المحفظة"),"")</f>
@@ -19902,7 +19915,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>713.6</v>
+        <v>722.19</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -21851,49 +21864,40 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="63" t="str">
-        <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="64" t="str">
+      <c r="A37" s="63"/>
+      <c r="B37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="65" t="str">
-        <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="66" t="str">
+        <v>0</v>
+      </c>
+      <c r="C37" s="65"/>
+      <c r="D37" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="67" t="str">
-        <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E37"/>
       <c r="F37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="64" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J37" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="64" t="str">
+        <v>22.395000000000007</v>
+      </c>
+      <c r="K37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27425,7 +27429,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="156"/>
@@ -28736,7 +28740,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="156"/>
@@ -28750,7 +28754,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="156"/>
@@ -30061,7 +30065,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="156"/>
@@ -30084,7 +30088,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30093,17 +30097,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58B742C-F62C-4033-A572-D1823A0D6EA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F50CFF-D325-498F-9C10-EEAB08F96AB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="328">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>تعديل رصيد</t>
+  </si>
+  <si>
+    <t>Inv-106</t>
   </si>
 </sst>
 </file>
@@ -2203,14 +2206,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2573,7 +2576,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>22.395000000000007</v>
+        <v>44.39500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5501,29 +5504,29 @@
       </c>
     </row>
     <row r="117" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="142" t="str">
+      <c r="A117" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(112,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46235</v>
       </c>
       <c r="B117" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(112,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-106</v>
       </c>
       <c r="C117" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(112,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D117" s="123" t="str">
+        <v>ربل عدد 11 الحبه 2</v>
+      </c>
+      <c r="D117" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(112,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E117" s="124" t="str">
+        <v>22</v>
+      </c>
+      <c r="E117" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(112,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F117" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F117" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>44.39500000000001</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7822,7 +7825,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>722.19</v>
+        <v>744.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7830,7 +7833,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>22.395000000000007</v>
+        <v>44.39500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17064,18 +17067,30 @@
       </c>
     </row>
     <row r="134" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="139"/>
-      <c r="B134" s="36"/>
-      <c r="C134" s="37"/>
+      <c r="A134" s="139">
+        <v>46235</v>
+      </c>
+      <c r="B134" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="C134" s="37" t="s">
+        <v>188</v>
+      </c>
       <c r="D134" s="38"/>
-      <c r="E134" s="39"/>
-      <c r="F134" s="136"/>
+      <c r="E134" s="39">
+        <v>22</v>
+      </c>
+      <c r="F134" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G134" s="40"/>
-      <c r="H134" s="41"/>
+      <c r="H134" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I134" s="42"/>
-      <c r="J134" s="43" t="str">
+      <c r="J134" s="43">
         <f>IF(AND(D134="",E134="",A134="",B134="",C134=""),"", IFERROR(IF(J133="",D2,J133),D2)+IF(E134="",0,E134)-IF(OR(G134="أبو اسحاق",G134="أبو آدم",G134="أبو اسحاق ",G134="أبو آدم "),0,IF(D134="",0,D134)))</f>
-        <v/>
+        <v>44.39500000000001</v>
       </c>
       <c r="K134" s="44"/>
       <c r="L134">
@@ -17094,9 +17109,9 @@
         <f>IF(AND(D133&gt;0,F133="أحد الشركاء"),COUNTIFS($D$4:D133,"&gt;"&amp;0,$F$4:F133,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P134" t="str">
+      <c r="P134">
         <f>IF(OR($A134="",$F134="أحد الشركاء",AND($D134="",$E134="")),"",SUMPRODUCT(($A$4:$A134&lt;&gt;"")*($F$4:$F134&lt;&gt;"أحد الشركاء")*((($D$4:$D134&lt;&gt;"")+($E$4:$E134&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>112</v>
       </c>
       <c r="Q134" t="str">
         <f>IF(OR($A134="",$F134&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A134,"&lt;&gt;",$F$4:F134,"أحد الشركاء"))</f>
@@ -17118,9 +17133,9 @@
         <v/>
       </c>
       <c r="K135" s="35"/>
-      <c r="L135" t="str">
+      <c r="L135">
         <f>IF(E134&gt;0,COUNTIF($E$4:E134,"&gt;0"),"")</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="M135" t="str">
         <f>IF(AND(D134&gt;0,G134="المحفظة"),COUNTIFS($D$4:D134,"&gt;"&amp;0,$G$4:G134,"المحفظة"),"")</f>
@@ -19915,7 +19930,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>722.19</v>
+        <v>744.19</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -27429,7 +27444,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="156"/>
@@ -28740,7 +28755,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="156"/>
@@ -28754,7 +28769,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="156"/>
@@ -30065,7 +30080,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="156"/>
@@ -30088,7 +30103,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30097,17 +30112,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F50CFF-D325-498F-9C10-EEAB08F96AB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DEA931-C3CD-4526-A92C-C5D6BCC7F725}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="333">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1026,6 +1026,21 @@
   </si>
   <si>
     <t>Inv-106</t>
+  </si>
+  <si>
+    <t>Inv-107</t>
+  </si>
+  <si>
+    <t>متنوع عدد 1 بقيمه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-108</t>
+  </si>
+  <si>
+    <t>فل عدد 1 بقيمه .750</t>
+  </si>
+  <si>
+    <t>بتموس عدد 2 الواحده 12</t>
   </si>
 </sst>
 </file>
@@ -2206,14 +2221,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2576,7 +2591,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>44.39500000000001</v>
+        <v>23.64500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5530,81 +5545,81 @@
       </c>
     </row>
     <row r="118" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="142" t="str">
+      <c r="A118" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(113,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46235</v>
       </c>
       <c r="B118" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(113,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-107</v>
       </c>
       <c r="C118" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(113,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D118" s="123" t="str">
+        <v>متنوع عدد 1 بقيمه 2.500</v>
+      </c>
+      <c r="D118" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(113,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E118" s="124" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E118" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(113,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F118" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F118" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>46.89500000000001</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="142" t="str">
+      <c r="A119" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(114,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46235</v>
       </c>
       <c r="B119" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(114,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-108</v>
       </c>
       <c r="C119" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(114,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D119" s="123" t="str">
+        <v>فل عدد 1 بقيمه .750</v>
+      </c>
+      <c r="D119" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(114,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E119" s="124" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="E119" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(114,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F119" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F119" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>47.64500000000001</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="142" t="str">
+      <c r="A120" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(115,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B120" s="122" t="str">
+        <v>46235</v>
+      </c>
+      <c r="B120" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(115,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C120" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(115,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D120" s="123" t="str">
+        <v>بتموس عدد 2 الواحده 12</v>
+      </c>
+      <c r="D120" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(115,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E120" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E120" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(115,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F120" s="125" t="str">
+        <v>24</v>
+      </c>
+      <c r="F120" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>23.64500000000001</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7825,15 +7840,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>744.19</v>
+        <v>747.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>699.79499999999996</v>
+        <v>723.79499999999996</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>44.39500000000001</v>
+        <v>23.64500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17119,18 +17134,30 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="25"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="25">
+        <v>46235</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="C135" s="27" t="s">
+        <v>329</v>
+      </c>
       <c r="D135" s="28"/>
-      <c r="E135" s="29"/>
-      <c r="F135" s="30"/>
+      <c r="E135" s="29">
+        <v>2.5</v>
+      </c>
+      <c r="F135" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G135" s="31"/>
-      <c r="H135" s="32"/>
+      <c r="H135" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I135" s="33"/>
-      <c r="J135" s="34" t="str">
+      <c r="J135" s="34">
         <f>IF(AND(D135="",E135="",A135="",B135="",C135=""),"", IFERROR(IF(J134="",D2,J134),D2)+IF(E135="",0,E135)-IF(OR(G135="أبو اسحاق",G135="أبو آدم",G135="أبو اسحاق ",G135="أبو آدم "),0,IF(D135="",0,D135)))</f>
-        <v/>
+        <v>46.89500000000001</v>
       </c>
       <c r="K135" s="35"/>
       <c r="L135">
@@ -17149,9 +17176,9 @@
         <f>IF(AND(D134&gt;0,F134="أحد الشركاء"),COUNTIFS($D$4:D134,"&gt;"&amp;0,$F$4:F134,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P135" t="str">
+      <c r="P135">
         <f>IF(OR($A135="",$F135="أحد الشركاء",AND($D135="",$E135="")),"",SUMPRODUCT(($A$4:$A135&lt;&gt;"")*($F$4:$F135&lt;&gt;"أحد الشركاء")*((($D$4:$D135&lt;&gt;"")+($E$4:$E135&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>113</v>
       </c>
       <c r="Q135" t="str">
         <f>IF(OR($A135="",$F135&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A135,"&lt;&gt;",$F$4:F135,"أحد الشركاء"))</f>
@@ -17159,23 +17186,35 @@
       </c>
     </row>
     <row r="136" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="139"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="37"/>
+      <c r="A136" s="139">
+        <v>46235</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="C136" s="37" t="s">
+        <v>331</v>
+      </c>
       <c r="D136" s="38"/>
-      <c r="E136" s="39"/>
-      <c r="F136" s="136"/>
+      <c r="E136" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="F136" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G136" s="40"/>
-      <c r="H136" s="41"/>
+      <c r="H136" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I136" s="42"/>
-      <c r="J136" s="43" t="str">
+      <c r="J136" s="43">
         <f>IF(AND(D136="",E136="",A136="",B136="",C136=""),"", IFERROR(IF(J135="",D2,J135),D2)+IF(E136="",0,E136)-IF(OR(G136="أبو اسحاق",G136="أبو آدم",G136="أبو اسحاق ",G136="أبو آدم "),0,IF(D136="",0,D136)))</f>
-        <v/>
+        <v>47.64500000000001</v>
       </c>
       <c r="K136" s="44"/>
-      <c r="L136" t="str">
+      <c r="L136">
         <f>IF(E135&gt;0,COUNTIF($E$4:E135,"&gt;0"),"")</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="M136" t="str">
         <f>IF(AND(D135&gt;0,G135="المحفظة"),COUNTIFS($D$4:D135,"&gt;"&amp;0,$G$4:G135,"المحفظة"),"")</f>
@@ -17189,9 +17228,9 @@
         <f>IF(AND(D135&gt;0,F135="أحد الشركاء"),COUNTIFS($D$4:D135,"&gt;"&amp;0,$F$4:F135,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P136" t="str">
+      <c r="P136">
         <f>IF(OR($A136="",$F136="أحد الشركاء",AND($D136="",$E136="")),"",SUMPRODUCT(($A$4:$A136&lt;&gt;"")*($F$4:$F136&lt;&gt;"أحد الشركاء")*((($D$4:$D136&lt;&gt;"")+($E$4:$E136&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="Q136" t="str">
         <f>IF(OR($A136="",$F136&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A136,"&lt;&gt;",$F$4:F136,"أحد الشركاء"))</f>
@@ -17199,23 +17238,35 @@
       </c>
     </row>
     <row r="137" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="25"/>
+      <c r="A137" s="25">
+        <v>46235</v>
+      </c>
       <c r="B137" s="26"/>
-      <c r="C137" s="27"/>
-      <c r="D137" s="28"/>
+      <c r="C137" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="D137" s="28">
+        <v>24</v>
+      </c>
       <c r="E137" s="29"/>
-      <c r="F137" s="30"/>
-      <c r="G137" s="31"/>
-      <c r="H137" s="32"/>
+      <c r="F137" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G137" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I137" s="33"/>
-      <c r="J137" s="34" t="str">
+      <c r="J137" s="34">
         <f>IF(AND(D137="",E137="",A137="",B137="",C137=""),"", IFERROR(IF(J136="",D2,J136),D2)+IF(E137="",0,E137)-IF(OR(G137="أبو اسحاق",G137="أبو آدم",G137="أبو اسحاق ",G137="أبو آدم "),0,IF(D137="",0,D137)))</f>
-        <v/>
+        <v>23.64500000000001</v>
       </c>
       <c r="K137" s="35"/>
-      <c r="L137" t="str">
+      <c r="L137">
         <f>IF(E136&gt;0,COUNTIF($E$4:E136,"&gt;0"),"")</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="M137" t="str">
         <f>IF(AND(D136&gt;0,G136="المحفظة"),COUNTIFS($D$4:D136,"&gt;"&amp;0,$G$4:G136,"المحفظة"),"")</f>
@@ -17229,9 +17280,9 @@
         <f>IF(AND(D136&gt;0,F136="أحد الشركاء"),COUNTIFS($D$4:D136,"&gt;"&amp;0,$F$4:F136,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P137" t="str">
+      <c r="P137">
         <f>IF(OR($A137="",$F137="أحد الشركاء",AND($D137="",$E137="")),"",SUMPRODUCT(($A$4:$A137&lt;&gt;"")*($F$4:$F137&lt;&gt;"أحد الشركاء")*((($D$4:$D137&lt;&gt;"")+($E$4:$E137&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>115</v>
       </c>
       <c r="Q137" t="str">
         <f>IF(OR($A137="",$F137&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A137,"&lt;&gt;",$F$4:F137,"أحد الشركاء"))</f>
@@ -17257,9 +17308,9 @@
         <f>IF(E137&gt;0,COUNTIF($E$4:E137,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M138" t="str">
+      <c r="M138">
         <f>IF(AND(D137&gt;0,G137="المحفظة"),COUNTIFS($D$4:D137,"&gt;"&amp;0,$G$4:G137,"المحفظة"),"")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="N138" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A138)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A138)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A138&lt;&gt;""),IFERROR(MAX($N$4:N137),0)+1,"")</f>
@@ -19926,11 +19977,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2133.2950000000001</v>
+        <v>2157.2950000000001</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>744.19</v>
+        <v>747.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -27444,7 +27495,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>274</v>
       </c>
       <c r="B4" s="156"/>
@@ -28755,7 +28806,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>267</v>
       </c>
       <c r="B55" s="156"/>
@@ -28769,7 +28820,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B56" s="156"/>
@@ -30080,7 +30131,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>277</v>
       </c>
       <c r="B107" s="156"/>
@@ -30103,7 +30154,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30112,17 +30163,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DEA931-C3CD-4526-A92C-C5D6BCC7F725}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFF9F62-6098-449D-AAF1-A7985781E56C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="343">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -812,9 +812,6 @@
     <t>الرصيد في الخلية C3 يتحدث فورياً مع أي تغيير في كشف الحساب</t>
   </si>
   <si>
-    <t>يونيو</t>
-  </si>
-  <si>
     <t>الكل</t>
   </si>
   <si>
@@ -998,9 +995,6 @@
     <t>متفرقات</t>
   </si>
   <si>
-    <t>يوليو</t>
-  </si>
-  <si>
     <t>تسوية رصيد فعلي - المتوفر 107.305 (صافي الشهر 99.075 + فائض عام 16.750)</t>
   </si>
   <si>
@@ -1041,6 +1035,42 @@
   </si>
   <si>
     <t>بتموس عدد 2 الواحده 12</t>
+  </si>
+  <si>
+    <t>Inv-109</t>
+  </si>
+  <si>
+    <t>متنوع عدد 1 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-110</t>
+  </si>
+  <si>
+    <t>متنوع عدد10 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-111</t>
+  </si>
+  <si>
+    <t>متنوع 6 عدد 1</t>
+  </si>
+  <si>
+    <t>Inv-112</t>
+  </si>
+  <si>
+    <t>ربل عدد 15 الحبه2</t>
+  </si>
+  <si>
+    <t>السعر الأصلي 30 تم خصم 1 ليكون 29</t>
+  </si>
+  <si>
+    <t>كيميكل للمعالج</t>
+  </si>
+  <si>
+    <t>ترمستات الثلاجه الكبيره</t>
+  </si>
+  <si>
+    <t>أغسطس</t>
   </si>
 </sst>
 </file>
@@ -2591,7 +2621,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>23.64500000000001</v>
+        <v>34.89500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5623,159 +5653,159 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="142" t="str">
+      <c r="A121" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(116,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46239</v>
       </c>
       <c r="B121" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(116,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-109</v>
       </c>
       <c r="C121" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(116,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D121" s="123" t="str">
+        <v>متنوع عدد 1 الحبه 1</v>
+      </c>
+      <c r="D121" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(116,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E121" s="124" t="str">
+        <v>1</v>
+      </c>
+      <c r="E121" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(116,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F121" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F121" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>24.64500000000001</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="142" t="str">
+      <c r="A122" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(117,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46240</v>
       </c>
       <c r="B122" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(117,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-110</v>
       </c>
       <c r="C122" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(117,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D122" s="123" t="str">
+        <v>متنوع عدد10 الحبه 1</v>
+      </c>
+      <c r="D122" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(117,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E122" s="124" t="str">
+        <v>10</v>
+      </c>
+      <c r="E122" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(117,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F122" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F122" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>34.64500000000001</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="142" t="str">
+      <c r="A123" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(118,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46240</v>
       </c>
       <c r="B123" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(118,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-111</v>
       </c>
       <c r="C123" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(118,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D123" s="123" t="str">
+        <v>متنوع 6 عدد 1</v>
+      </c>
+      <c r="D123" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(118,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E123" s="124" t="str">
+        <v>6</v>
+      </c>
+      <c r="E123" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(118,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F123" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F123" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>40.64500000000001</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="142" t="str">
+      <c r="A124" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(119,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46240</v>
       </c>
       <c r="B124" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(119,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-112</v>
       </c>
       <c r="C124" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(119,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D124" s="123" t="str">
+        <v>ربل عدد 15 الحبه2</v>
+      </c>
+      <c r="D124" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(119,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E124" s="124" t="str">
+        <v>29</v>
+      </c>
+      <c r="E124" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(119,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F124" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F124" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>69.64500000000001</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="142" t="str">
+      <c r="A125" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(120,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B125" s="122" t="str">
+        <v>46240</v>
+      </c>
+      <c r="B125" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(120,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C125" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(120,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D125" s="123" t="str">
+        <v>كيميكل للمعالج</v>
+      </c>
+      <c r="D125" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(120,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E125" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E125" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(120,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F125" s="125" t="str">
+        <v>29</v>
+      </c>
+      <c r="F125" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>40.64500000000001</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="142" t="str">
+      <c r="A126" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(121,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B126" s="122" t="str">
+        <v>46240</v>
+      </c>
+      <c r="B126" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(121,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C126" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(121,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D126" s="123" t="str">
+        <v>ترمستات الثلاجه الكبيره</v>
+      </c>
+      <c r="D126" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(121,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E126" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E126" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(121,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F126" s="125" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="F126" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>34.89500000000001</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7840,15 +7870,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>747.44</v>
+        <v>793.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>723.79499999999996</v>
+        <v>758.54499999999996</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>23.64500000000001</v>
+        <v>34.89500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -15398,9 +15428,9 @@
         <f>IF(AND(D100&gt;0,G100="المحفظة"),COUNTIFS($D$4:D100,"&gt;"&amp;0,$G$4:G100,"المحفظة"),"")</f>
         <v>14</v>
       </c>
-      <c r="N101">
+      <c r="N101" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A101)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A101)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A101&lt;&gt;""),IFERROR(MAX($N$4:N100),0)+1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="O101" t="str">
         <f>IF(AND(D100&gt;0,F100="أحد الشركاء"),COUNTIFS($D$4:D100,"&gt;"&amp;0,$F$4:F100,"أحد الشركاء"),"")</f>
@@ -15450,9 +15480,9 @@
         <f>IF(AND(D101&gt;0,G101="المحفظة"),COUNTIFS($D$4:D101,"&gt;"&amp;0,$G$4:G101,"المحفظة"),"")</f>
         <v>15</v>
       </c>
-      <c r="N102">
+      <c r="N102" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A102)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A102)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A102&lt;&gt;""),IFERROR(MAX($N$4:N101),0)+1,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="O102" t="str">
         <f>IF(AND(D101&gt;0,F101="أحد الشركاء"),COUNTIFS($D$4:D101,"&gt;"&amp;0,$F$4:F101,"أحد الشركاء"),"")</f>
@@ -15502,9 +15532,9 @@
         <f>IF(AND(D102&gt;0,G102="المحفظة"),COUNTIFS($D$4:D102,"&gt;"&amp;0,$G$4:G102,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N103">
+      <c r="N103" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A103)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A103)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A103&lt;&gt;""),IFERROR(MAX($N$4:N102),0)+1,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="O103" t="str">
         <f>IF(AND(D102&gt;0,F102="أحد الشركاء"),COUNTIFS($D$4:D102,"&gt;"&amp;0,$F$4:F102,"أحد الشركاء"),"")</f>
@@ -15554,9 +15584,9 @@
         <f>IF(AND(D103&gt;0,G103="المحفظة"),COUNTIFS($D$4:D103,"&gt;"&amp;0,$G$4:G103,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N104">
+      <c r="N104" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A104)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A104)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A104&lt;&gt;""),IFERROR(MAX($N$4:N103),0)+1,"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="O104" t="str">
         <f>IF(AND(D103&gt;0,F103="أحد الشركاء"),COUNTIFS($D$4:D103,"&gt;"&amp;0,$F$4:F103,"أحد الشركاء"),"")</f>
@@ -15576,10 +15606,10 @@
         <v>46211</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D105" s="28"/>
       <c r="E105" s="29">
@@ -15606,9 +15636,9 @@
         <f>IF(AND(D104&gt;0,G104="المحفظة"),COUNTIFS($D$4:D104,"&gt;"&amp;0,$G$4:G104,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N105">
+      <c r="N105" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A105)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A105)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A105&lt;&gt;""),IFERROR(MAX($N$4:N104),0)+1,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="O105" t="str">
         <f>IF(AND(D104&gt;0,F104="أحد الشركاء"),COUNTIFS($D$4:D104,"&gt;"&amp;0,$F$4:F104,"أحد الشركاء"),"")</f>
@@ -15628,10 +15658,10 @@
         <v>46211</v>
       </c>
       <c r="B106" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="C106" s="37" t="s">
         <v>280</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>281</v>
       </c>
       <c r="D106" s="38"/>
       <c r="E106" s="39">
@@ -15658,9 +15688,9 @@
         <f>IF(AND(D105&gt;0,G105="المحفظة"),COUNTIFS($D$4:D105,"&gt;"&amp;0,$G$4:G105,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N106">
+      <c r="N106" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A106)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A106)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A106&lt;&gt;""),IFERROR(MAX($N$4:N105),0)+1,"")</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="O106" t="str">
         <f>IF(AND(D105&gt;0,F105="أحد الشركاء"),COUNTIFS($D$4:D105,"&gt;"&amp;0,$F$4:F105,"أحد الشركاء"),"")</f>
@@ -15680,10 +15710,10 @@
         <v>46211</v>
       </c>
       <c r="B107" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="C107" s="27" t="s">
         <v>282</v>
-      </c>
-      <c r="C107" s="27" t="s">
-        <v>283</v>
       </c>
       <c r="D107" s="28"/>
       <c r="E107" s="29">
@@ -15710,9 +15740,9 @@
         <f>IF(AND(D106&gt;0,G106="المحفظة"),COUNTIFS($D$4:D106,"&gt;"&amp;0,$G$4:G106,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N107">
+      <c r="N107" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A107)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A107)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A107&lt;&gt;""),IFERROR(MAX($N$4:N106),0)+1,"")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="O107" t="str">
         <f>IF(AND(D106&gt;0,F106="أحد الشركاء"),COUNTIFS($D$4:D106,"&gt;"&amp;0,$F$4:F106,"أحد الشركاء"),"")</f>
@@ -15732,10 +15762,10 @@
         <v>46212</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="39">
@@ -15762,9 +15792,9 @@
         <f>IF(AND(D107&gt;0,G107="المحفظة"),COUNTIFS($D$4:D107,"&gt;"&amp;0,$G$4:G107,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N108">
+      <c r="N108" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A108)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A108)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A108&lt;&gt;""),IFERROR(MAX($N$4:N107),0)+1,"")</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="O108" t="str">
         <f>IF(AND(D107&gt;0,F107="أحد الشركاء"),COUNTIFS($D$4:D107,"&gt;"&amp;0,$F$4:F107,"أحد الشركاء"),"")</f>
@@ -15784,10 +15814,10 @@
         <v>46212</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D109" s="28"/>
       <c r="E109" s="29">
@@ -15814,9 +15844,9 @@
         <f>IF(AND(D108&gt;0,G108="المحفظة"),COUNTIFS($D$4:D108,"&gt;"&amp;0,$G$4:G108,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N109">
+      <c r="N109" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A109)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A109)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A109&lt;&gt;""),IFERROR(MAX($N$4:N108),0)+1,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="O109" t="str">
         <f>IF(AND(D108&gt;0,F108="أحد الشركاء"),COUNTIFS($D$4:D108,"&gt;"&amp;0,$F$4:F108,"أحد الشركاء"),"")</f>
@@ -15836,7 +15866,7 @@
         <v>46212</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C110" s="37" t="s">
         <v>182</v>
@@ -15866,9 +15896,9 @@
         <f>IF(AND(D109&gt;0,G109="المحفظة"),COUNTIFS($D$4:D109,"&gt;"&amp;0,$G$4:G109,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N110">
+      <c r="N110" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A110)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A110)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A110&lt;&gt;""),IFERROR(MAX($N$4:N109),0)+1,"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="O110" t="str">
         <f>IF(AND(D109&gt;0,F109="أحد الشركاء"),COUNTIFS($D$4:D109,"&gt;"&amp;0,$F$4:F109,"أحد الشركاء"),"")</f>
@@ -15888,10 +15918,10 @@
         <v>46212</v>
       </c>
       <c r="B111" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="C111" s="27" t="s">
         <v>289</v>
-      </c>
-      <c r="C111" s="27" t="s">
-        <v>290</v>
       </c>
       <c r="D111" s="28"/>
       <c r="E111" s="29">
@@ -15918,9 +15948,9 @@
         <f>IF(AND(D110&gt;0,G110="المحفظة"),COUNTIFS($D$4:D110,"&gt;"&amp;0,$G$4:G110,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N111">
+      <c r="N111" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A111)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A111)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A111&lt;&gt;""),IFERROR(MAX($N$4:N110),0)+1,"")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="O111" t="str">
         <f>IF(AND(D110&gt;0,F110="أحد الشركاء"),COUNTIFS($D$4:D110,"&gt;"&amp;0,$F$4:F110,"أحد الشركاء"),"")</f>
@@ -15940,10 +15970,10 @@
         <v>46212</v>
       </c>
       <c r="B112" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="C112" s="37" t="s">
         <v>291</v>
-      </c>
-      <c r="C112" s="37" t="s">
-        <v>292</v>
       </c>
       <c r="D112" s="38"/>
       <c r="E112" s="39">
@@ -15970,9 +16000,9 @@
         <f>IF(AND(D111&gt;0,G111="المحفظة"),COUNTIFS($D$4:D111,"&gt;"&amp;0,$G$4:G111,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N112">
+      <c r="N112" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A112)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A112)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A112&lt;&gt;""),IFERROR(MAX($N$4:N111),0)+1,"")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="O112" t="str">
         <f>IF(AND(D111&gt;0,F111="أحد الشركاء"),COUNTIFS($D$4:D111,"&gt;"&amp;0,$F$4:F111,"أحد الشركاء"),"")</f>
@@ -15992,10 +16022,10 @@
         <v>46217</v>
       </c>
       <c r="B113" s="36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D113" s="28"/>
       <c r="E113" s="29">
@@ -16022,9 +16052,9 @@
         <f>IF(AND(D112&gt;0,G112="المحفظة"),COUNTIFS($D$4:D112,"&gt;"&amp;0,$G$4:G112,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N113">
+      <c r="N113" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A113)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A113)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A113&lt;&gt;""),IFERROR(MAX($N$4:N112),0)+1,"")</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="O113" t="str">
         <f>IF(AND(D112&gt;0,F112="أحد الشركاء"),COUNTIFS($D$4:D112,"&gt;"&amp;0,$F$4:F112,"أحد الشركاء"),"")</f>
@@ -16044,10 +16074,10 @@
         <v>46217</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D114" s="38"/>
       <c r="E114" s="39">
@@ -16074,9 +16104,9 @@
         <f>IF(AND(D113&gt;0,G113="المحفظة"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$G$4:G113,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N114">
+      <c r="N114" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A114)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A114)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A114&lt;&gt;""),IFERROR(MAX($N$4:N113),0)+1,"")</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="O114" t="str">
         <f>IF(AND(D113&gt;0,F113="أحد الشركاء"),COUNTIFS($D$4:D113,"&gt;"&amp;0,$F$4:F113,"أحد الشركاء"),"")</f>
@@ -16097,7 +16127,7 @@
       </c>
       <c r="B115" s="26"/>
       <c r="C115" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D115" s="28">
         <v>1.925</v>
@@ -16126,9 +16156,9 @@
         <f>IF(AND(D114&gt;0,G114="المحفظة"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$G$4:G114,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N115">
+      <c r="N115" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A115)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A115)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A115&lt;&gt;""),IFERROR(MAX($N$4:N114),0)+1,"")</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="O115" t="str">
         <f>IF(AND(D114&gt;0,F114="أحد الشركاء"),COUNTIFS($D$4:D114,"&gt;"&amp;0,$F$4:F114,"أحد الشركاء"),"")</f>
@@ -16148,10 +16178,10 @@
         <v>46219</v>
       </c>
       <c r="B116" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="C116" s="37" t="s">
         <v>299</v>
-      </c>
-      <c r="C116" s="37" t="s">
-        <v>300</v>
       </c>
       <c r="D116" s="38"/>
       <c r="E116" s="39">
@@ -16170,7 +16200,7 @@
         <v>106.62500000000001</v>
       </c>
       <c r="K116" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L116" t="str">
         <f>IF(E115&gt;0,COUNTIF($E$4:E115,"&gt;0"),"")</f>
@@ -16180,9 +16210,9 @@
         <f>IF(AND(D115&gt;0,G115="المحفظة"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$G$4:G115,"المحفظة"),"")</f>
         <v>16</v>
       </c>
-      <c r="N116">
+      <c r="N116" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A116)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A116)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A116&lt;&gt;""),IFERROR(MAX($N$4:N115),0)+1,"")</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="O116" t="str">
         <f>IF(AND(D115&gt;0,F115="أحد الشركاء"),COUNTIFS($D$4:D115,"&gt;"&amp;0,$F$4:F115,"أحد الشركاء"),"")</f>
@@ -16202,10 +16232,10 @@
         <v>46219</v>
       </c>
       <c r="B117" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="C117" s="27" t="s">
         <v>302</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>303</v>
       </c>
       <c r="D117" s="28"/>
       <c r="E117" s="29">
@@ -16224,7 +16254,7 @@
         <v>108.62500000000001</v>
       </c>
       <c r="K117" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L117">
         <f>IF(E116&gt;0,COUNTIF($E$4:E116,"&gt;0"),"")</f>
@@ -16234,9 +16264,9 @@
         <f>IF(AND(D116&gt;0,G116="المحفظة"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$G$4:G116,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N117">
+      <c r="N117" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A117)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A117)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A117&lt;&gt;""),IFERROR(MAX($N$4:N116),0)+1,"")</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="O117" t="str">
         <f>IF(AND(D116&gt;0,F116="أحد الشركاء"),COUNTIFS($D$4:D116,"&gt;"&amp;0,$F$4:F116,"أحد الشركاء"),"")</f>
@@ -16256,10 +16286,10 @@
         <v>46221</v>
       </c>
       <c r="B118" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D118" s="38"/>
       <c r="E118" s="39">
@@ -16286,9 +16316,9 @@
         <f>IF(AND(D117&gt;0,G117="المحفظة"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$G$4:G117,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N118">
+      <c r="N118" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A118)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A118)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A118&lt;&gt;""),IFERROR(MAX($N$4:N117),0)+1,"")</f>
-        <v>18</v>
+        <v/>
       </c>
       <c r="O118" t="str">
         <f>IF(AND(D117&gt;0,F117="أحد الشركاء"),COUNTIFS($D$4:D117,"&gt;"&amp;0,$F$4:F117,"أحد الشركاء"),"")</f>
@@ -16308,10 +16338,10 @@
         <v>46221</v>
       </c>
       <c r="B119" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="C119" s="27" t="s">
         <v>306</v>
-      </c>
-      <c r="C119" s="27" t="s">
-        <v>307</v>
       </c>
       <c r="D119" s="28"/>
       <c r="E119" s="29">
@@ -16338,9 +16368,9 @@
         <f>IF(AND(D118&gt;0,G118="المحفظة"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$G$4:G118,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N119">
+      <c r="N119" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A119)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A119)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A119&lt;&gt;""),IFERROR(MAX($N$4:N118),0)+1,"")</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="O119" t="str">
         <f>IF(AND(D118&gt;0,F118="أحد الشركاء"),COUNTIFS($D$4:D118,"&gt;"&amp;0,$F$4:F118,"أحد الشركاء"),"")</f>
@@ -16360,10 +16390,10 @@
         <v>46224</v>
       </c>
       <c r="B120" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="C120" s="37" t="s">
         <v>308</v>
-      </c>
-      <c r="C120" s="37" t="s">
-        <v>309</v>
       </c>
       <c r="D120" s="38"/>
       <c r="E120" s="39">
@@ -16390,9 +16420,9 @@
         <f>IF(AND(D119&gt;0,G119="المحفظة"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$G$4:G119,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N120">
+      <c r="N120" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A120)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A120)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A120&lt;&gt;""),IFERROR(MAX($N$4:N119),0)+1,"")</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="O120" t="str">
         <f>IF(AND(D119&gt;0,F119="أحد الشركاء"),COUNTIFS($D$4:D119,"&gt;"&amp;0,$F$4:F119,"أحد الشركاء"),"")</f>
@@ -16412,7 +16442,7 @@
         <v>46224</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C121" s="27" t="s">
         <v>188</v>
@@ -16442,9 +16472,9 @@
         <f>IF(AND(D120&gt;0,G120="المحفظة"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$G$4:G120,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N121">
+      <c r="N121" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A121)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A121)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A121&lt;&gt;""),IFERROR(MAX($N$4:N120),0)+1,"")</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="O121" t="str">
         <f>IF(AND(D120&gt;0,F120="أحد الشركاء"),COUNTIFS($D$4:D120,"&gt;"&amp;0,$F$4:F120,"أحد الشركاء"),"")</f>
@@ -16464,10 +16494,10 @@
         <v>46225</v>
       </c>
       <c r="B122" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="C122" s="37" t="s">
         <v>311</v>
-      </c>
-      <c r="C122" s="37" t="s">
-        <v>312</v>
       </c>
       <c r="D122" s="38"/>
       <c r="E122" s="39">
@@ -16494,9 +16524,9 @@
         <f>IF(AND(D121&gt;0,G121="المحفظة"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$G$4:G121,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N122">
+      <c r="N122" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A122)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A122)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A122&lt;&gt;""),IFERROR(MAX($N$4:N121),0)+1,"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="O122" t="str">
         <f>IF(AND(D121&gt;0,F121="أحد الشركاء"),COUNTIFS($D$4:D121,"&gt;"&amp;0,$F$4:F121,"أحد الشركاء"),"")</f>
@@ -16516,10 +16546,10 @@
         <v>46227</v>
       </c>
       <c r="B123" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C123" s="27" t="s">
         <v>313</v>
-      </c>
-      <c r="C123" s="27" t="s">
-        <v>314</v>
       </c>
       <c r="D123" s="28"/>
       <c r="E123" s="29">
@@ -16546,9 +16576,9 @@
         <f>IF(AND(D122&gt;0,G122="المحفظة"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$G$4:G122,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N123">
+      <c r="N123" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A123)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A123)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A123&lt;&gt;""),IFERROR(MAX($N$4:N122),0)+1,"")</f>
-        <v>23</v>
+        <v/>
       </c>
       <c r="O123" t="str">
         <f>IF(AND(D122&gt;0,F122="أحد الشركاء"),COUNTIFS($D$4:D122,"&gt;"&amp;0,$F$4:F122,"أحد الشركاء"),"")</f>
@@ -16569,7 +16599,7 @@
       </c>
       <c r="B124" s="36"/>
       <c r="C124" s="37" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D124" s="38">
         <v>10</v>
@@ -16598,9 +16628,9 @@
         <f>IF(AND(D123&gt;0,G123="المحفظة"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$G$4:G123,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N124">
+      <c r="N124" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A124)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A124)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A124&lt;&gt;""),IFERROR(MAX($N$4:N123),0)+1,"")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="O124" t="str">
         <f>IF(AND(D123&gt;0,F123="أحد الشركاء"),COUNTIFS($D$4:D123,"&gt;"&amp;0,$F$4:F123,"أحد الشركاء"),"")</f>
@@ -16650,9 +16680,9 @@
         <f>IF(AND(D124&gt;0,G124="المحفظة"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$G$4:G124,"المحفظة"),"")</f>
         <v>17</v>
       </c>
-      <c r="N125">
+      <c r="N125" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A125)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A125)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A125&lt;&gt;""),IFERROR(MAX($N$4:N124),0)+1,"")</f>
-        <v>25</v>
+        <v/>
       </c>
       <c r="O125" t="str">
         <f>IF(AND(D124&gt;0,F124="أحد الشركاء"),COUNTIFS($D$4:D124,"&gt;"&amp;0,$F$4:F124,"أحد الشركاء"),"")</f>
@@ -16672,10 +16702,10 @@
         <v>46594</v>
       </c>
       <c r="B126" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="C126" s="37" t="s">
         <v>316</v>
-      </c>
-      <c r="C126" s="37" t="s">
-        <v>317</v>
       </c>
       <c r="D126" s="38"/>
       <c r="E126" s="39">
@@ -16702,9 +16732,9 @@
         <f>IF(AND(D125&gt;0,G125="المحفظة"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$G$4:G125,"المحفظة"),"")</f>
         <v>18</v>
       </c>
-      <c r="N126">
+      <c r="N126" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A126)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A126)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A126&lt;&gt;""),IFERROR(MAX($N$4:N125),0)+1,"")</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="O126" t="str">
         <f>IF(AND(D125&gt;0,F125="أحد الشركاء"),COUNTIFS($D$4:D125,"&gt;"&amp;0,$F$4:F125,"أحد الشركاء"),"")</f>
@@ -16725,7 +16755,7 @@
       </c>
       <c r="B127" s="26"/>
       <c r="C127" s="27" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D127" s="28">
         <v>16.82</v>
@@ -16754,9 +16784,9 @@
         <f>IF(AND(D126&gt;0,G126="المحفظة"),COUNTIFS($D$4:D126,"&gt;"&amp;0,$G$4:G126,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N127">
+      <c r="N127" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A127)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A127)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A127&lt;&gt;""),IFERROR(MAX($N$4:N126),0)+1,"")</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="O127" t="str">
         <f>IF(AND(D126&gt;0,F126="أحد الشركاء"),COUNTIFS($D$4:D126,"&gt;"&amp;0,$F$4:F126,"أحد الشركاء"),"")</f>
@@ -16776,10 +16806,10 @@
         <v>46231</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C128" s="37" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D128" s="38"/>
       <c r="E128" s="39">
@@ -16806,9 +16836,9 @@
         <f>IF(AND(D127&gt;0,G127="المحفظة"),COUNTIFS($D$4:D127,"&gt;"&amp;0,$G$4:G127,"المحفظة"),"")</f>
         <v>19</v>
       </c>
-      <c r="N128">
+      <c r="N128" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A128)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A128)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A128&lt;&gt;""),IFERROR(MAX($N$4:N127),0)+1,"")</f>
-        <v>28</v>
+        <v/>
       </c>
       <c r="O128" t="str">
         <f>IF(AND(D127&gt;0,F127="أحد الشركاء"),COUNTIFS($D$4:D127,"&gt;"&amp;0,$F$4:F127,"أحد الشركاء"),"")</f>
@@ -16828,10 +16858,10 @@
         <v>46231</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C129" s="27" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D129" s="28"/>
       <c r="E129" s="29">
@@ -16858,9 +16888,9 @@
         <f>IF(AND(D128&gt;0,G128="المحفظة"),COUNTIFS($D$4:D128,"&gt;"&amp;0,$G$4:G128,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N129">
+      <c r="N129" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A129)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A129)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A129&lt;&gt;""),IFERROR(MAX($N$4:N128),0)+1,"")</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="O129" t="str">
         <f>IF(AND(D128&gt;0,F128="أحد الشركاء"),COUNTIFS($D$4:D128,"&gt;"&amp;0,$F$4:F128,"أحد الشركاء"),"")</f>
@@ -16881,7 +16911,7 @@
       </c>
       <c r="B130" s="36"/>
       <c r="C130" s="37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D130" s="38">
         <v>99</v>
@@ -16910,9 +16940,9 @@
         <f>IF(AND(D129&gt;0,G129="المحفظة"),COUNTIFS($D$4:D129,"&gt;"&amp;0,$G$4:G129,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N130">
+      <c r="N130" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A130)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A130)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A130&lt;&gt;""),IFERROR(MAX($N$4:N129),0)+1,"")</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="O130" t="str">
         <f>IF(AND(D129&gt;0,F129="أحد الشركاء"),COUNTIFS($D$4:D129,"&gt;"&amp;0,$F$4:F129,"أحد الشركاء"),"")</f>
@@ -16933,7 +16963,7 @@
       </c>
       <c r="B131" s="26"/>
       <c r="C131" s="27" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D131" s="28">
         <v>205.5</v>
@@ -16962,9 +16992,9 @@
         <f>IF(AND(D130&gt;0,G130="المحفظة"),COUNTIFS($D$4:D130,"&gt;"&amp;0,$G$4:G130,"المحفظة"),"")</f>
         <v>20</v>
       </c>
-      <c r="N131">
+      <c r="N131" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A131)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A131)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A131&lt;&gt;""),IFERROR(MAX($N$4:N130),0)+1,"")</f>
-        <v>31</v>
+        <v/>
       </c>
       <c r="O131" t="str">
         <f>IF(AND(D130&gt;0,F130="أحد الشركاء"),COUNTIFS($D$4:D130,"&gt;"&amp;0,$F$4:F130,"أحد الشركاء"),"")</f>
@@ -16985,7 +17015,7 @@
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="37" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D132" s="38">
         <v>205.5</v>
@@ -17014,9 +17044,9 @@
         <f>IF(AND(D131&gt;0,G131="المحفظة"),COUNTIFS($D$4:D131,"&gt;"&amp;0,$G$4:G131,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N132">
+      <c r="N132" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A132)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A132)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A132&lt;&gt;""),IFERROR(MAX($N$4:N131),0)+1,"")</f>
-        <v>32</v>
+        <v/>
       </c>
       <c r="O132">
         <f>IF(AND(D131&gt;0,F131="أحد الشركاء"),COUNTIFS($D$4:D131,"&gt;"&amp;0,$F$4:F131,"أحد الشركاء"),"")</f>
@@ -17037,7 +17067,7 @@
       </c>
       <c r="B133" s="26"/>
       <c r="C133" s="27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D133" s="28"/>
       <c r="E133" s="29">
@@ -17064,9 +17094,9 @@
         <f>IF(AND(D132&gt;0,G132="المحفظة"),COUNTIFS($D$4:D132,"&gt;"&amp;0,$G$4:G132,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N133">
+      <c r="N133" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A133)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A133)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A133&lt;&gt;""),IFERROR(MAX($N$4:N132),0)+1,"")</f>
-        <v>33</v>
+        <v/>
       </c>
       <c r="O133">
         <f>IF(AND(D132&gt;0,F132="أحد الشركاء"),COUNTIFS($D$4:D132,"&gt;"&amp;0,$F$4:F132,"أحد الشركاء"),"")</f>
@@ -17086,7 +17116,7 @@
         <v>46235</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C134" s="37" t="s">
         <v>188</v>
@@ -17116,9 +17146,9 @@
         <f>IF(AND(D133&gt;0,G133="المحفظة"),COUNTIFS($D$4:D133,"&gt;"&amp;0,$G$4:G133,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N134" t="str">
+      <c r="N134">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A134)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A134)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A134&lt;&gt;""),IFERROR(MAX($N$4:N133),0)+1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O134" t="str">
         <f>IF(AND(D133&gt;0,F133="أحد الشركاء"),COUNTIFS($D$4:D133,"&gt;"&amp;0,$F$4:F133,"أحد الشركاء"),"")</f>
@@ -17138,10 +17168,10 @@
         <v>46235</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D135" s="28"/>
       <c r="E135" s="29">
@@ -17168,9 +17198,9 @@
         <f>IF(AND(D134&gt;0,G134="المحفظة"),COUNTIFS($D$4:D134,"&gt;"&amp;0,$G$4:G134,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N135" t="str">
+      <c r="N135">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A135)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A135)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A135&lt;&gt;""),IFERROR(MAX($N$4:N134),0)+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O135" t="str">
         <f>IF(AND(D134&gt;0,F134="أحد الشركاء"),COUNTIFS($D$4:D134,"&gt;"&amp;0,$F$4:F134,"أحد الشركاء"),"")</f>
@@ -17190,10 +17220,10 @@
         <v>46235</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C136" s="37" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D136" s="38"/>
       <c r="E136" s="39">
@@ -17220,9 +17250,9 @@
         <f>IF(AND(D135&gt;0,G135="المحفظة"),COUNTIFS($D$4:D135,"&gt;"&amp;0,$G$4:G135,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N136" t="str">
+      <c r="N136">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A136)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A136)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A136&lt;&gt;""),IFERROR(MAX($N$4:N135),0)+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="O136" t="str">
         <f>IF(AND(D135&gt;0,F135="أحد الشركاء"),COUNTIFS($D$4:D135,"&gt;"&amp;0,$F$4:F135,"أحد الشركاء"),"")</f>
@@ -17243,7 +17273,7 @@
       </c>
       <c r="B137" s="26"/>
       <c r="C137" s="27" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D137" s="28">
         <v>24</v>
@@ -17272,9 +17302,9 @@
         <f>IF(AND(D136&gt;0,G136="المحفظة"),COUNTIFS($D$4:D136,"&gt;"&amp;0,$G$4:G136,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N137" t="str">
+      <c r="N137">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A137)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A137)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A137&lt;&gt;""),IFERROR(MAX($N$4:N136),0)+1,"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="O137" t="str">
         <f>IF(AND(D136&gt;0,F136="أحد الشركاء"),COUNTIFS($D$4:D136,"&gt;"&amp;0,$F$4:F136,"أحد الشركاء"),"")</f>
@@ -17290,18 +17320,30 @@
       </c>
     </row>
     <row r="138" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="139"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="37"/>
+      <c r="A138" s="139">
+        <v>46239</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="C138" s="37" t="s">
+        <v>332</v>
+      </c>
       <c r="D138" s="38"/>
-      <c r="E138" s="39"/>
-      <c r="F138" s="136"/>
+      <c r="E138" s="39">
+        <v>1</v>
+      </c>
+      <c r="F138" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G138" s="40"/>
-      <c r="H138" s="41"/>
+      <c r="H138" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I138" s="42"/>
-      <c r="J138" s="43" t="str">
+      <c r="J138" s="43">
         <f>IF(AND(D138="",E138="",A138="",B138="",C138=""),"", IFERROR(IF(J137="",D2,J137),D2)+IF(E138="",0,E138)-IF(OR(G138="أبو اسحاق",G138="أبو آدم",G138="أبو اسحاق ",G138="أبو آدم "),0,IF(D138="",0,D138)))</f>
-        <v/>
+        <v>24.64500000000001</v>
       </c>
       <c r="K138" s="44"/>
       <c r="L138" t="str">
@@ -17312,17 +17354,17 @@
         <f>IF(AND(D137&gt;0,G137="المحفظة"),COUNTIFS($D$4:D137,"&gt;"&amp;0,$G$4:G137,"المحفظة"),"")</f>
         <v>21</v>
       </c>
-      <c r="N138" t="str">
+      <c r="N138">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A138)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A138)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A138&lt;&gt;""),IFERROR(MAX($N$4:N137),0)+1,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O138" t="str">
         <f>IF(AND(D137&gt;0,F137="أحد الشركاء"),COUNTIFS($D$4:D137,"&gt;"&amp;0,$F$4:F137,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P138" t="str">
+      <c r="P138">
         <f>IF(OR($A138="",$F138="أحد الشركاء",AND($D138="",$E138="")),"",SUMPRODUCT(($A$4:$A138&lt;&gt;"")*($F$4:$F138&lt;&gt;"أحد الشركاء")*((($D$4:$D138&lt;&gt;"")+($E$4:$E138&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>116</v>
       </c>
       <c r="Q138" t="str">
         <f>IF(OR($A138="",$F138&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A138,"&lt;&gt;",$F$4:F138,"أحد الشركاء"))</f>
@@ -17330,39 +17372,51 @@
       </c>
     </row>
     <row r="139" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="25"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="25">
+        <v>46240</v>
+      </c>
+      <c r="B139" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C139" s="27" t="s">
+        <v>334</v>
+      </c>
       <c r="D139" s="28"/>
-      <c r="E139" s="29"/>
-      <c r="F139" s="30"/>
+      <c r="E139" s="29">
+        <v>10</v>
+      </c>
+      <c r="F139" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G139" s="31"/>
-      <c r="H139" s="32"/>
+      <c r="H139" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I139" s="33"/>
-      <c r="J139" s="34" t="str">
+      <c r="J139" s="34">
         <f>IF(AND(D139="",E139="",A139="",B139="",C139=""),"", IFERROR(IF(J138="",D2,J138),D2)+IF(E139="",0,E139)-IF(OR(G139="أبو اسحاق",G139="أبو آدم",G139="أبو اسحاق ",G139="أبو آدم "),0,IF(D139="",0,D139)))</f>
-        <v/>
+        <v>34.64500000000001</v>
       </c>
       <c r="K139" s="35"/>
-      <c r="L139" t="str">
+      <c r="L139">
         <f>IF(E138&gt;0,COUNTIF($E$4:E138,"&gt;0"),"")</f>
-        <v/>
+        <v>95</v>
       </c>
       <c r="M139" t="str">
         <f>IF(AND(D138&gt;0,G138="المحفظة"),COUNTIFS($D$4:D138,"&gt;"&amp;0,$G$4:G138,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N139" t="str">
+      <c r="N139">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A139)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A139)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A139&lt;&gt;""),IFERROR(MAX($N$4:N138),0)+1,"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="O139" t="str">
         <f>IF(AND(D138&gt;0,F138="أحد الشركاء"),COUNTIFS($D$4:D138,"&gt;"&amp;0,$F$4:F138,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P139" t="str">
+      <c r="P139">
         <f>IF(OR($A139="",$F139="أحد الشركاء",AND($D139="",$E139="")),"",SUMPRODUCT(($A$4:$A139&lt;&gt;"")*($F$4:$F139&lt;&gt;"أحد الشركاء")*((($D$4:$D139&lt;&gt;"")+($E$4:$E139&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>117</v>
       </c>
       <c r="Q139" t="str">
         <f>IF(OR($A139="",$F139&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A139,"&lt;&gt;",$F$4:F139,"أحد الشركاء"))</f>
@@ -17370,39 +17424,51 @@
       </c>
     </row>
     <row r="140" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="139"/>
-      <c r="B140" s="36"/>
-      <c r="C140" s="37"/>
+      <c r="A140" s="139">
+        <v>46240</v>
+      </c>
+      <c r="B140" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C140" s="37" t="s">
+        <v>336</v>
+      </c>
       <c r="D140" s="38"/>
-      <c r="E140" s="39"/>
-      <c r="F140" s="136"/>
+      <c r="E140" s="39">
+        <v>6</v>
+      </c>
+      <c r="F140" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G140" s="40"/>
-      <c r="H140" s="41"/>
+      <c r="H140" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I140" s="42"/>
-      <c r="J140" s="43" t="str">
+      <c r="J140" s="43">
         <f>IF(AND(D140="",E140="",A140="",B140="",C140=""),"", IFERROR(IF(J139="",D2,J139),D2)+IF(E140="",0,E140)-IF(OR(G140="أبو اسحاق",G140="أبو آدم",G140="أبو اسحاق ",G140="أبو آدم "),0,IF(D140="",0,D140)))</f>
-        <v/>
+        <v>40.64500000000001</v>
       </c>
       <c r="K140" s="44"/>
-      <c r="L140" t="str">
+      <c r="L140">
         <f>IF(E139&gt;0,COUNTIF($E$4:E139,"&gt;0"),"")</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="M140" t="str">
         <f>IF(AND(D139&gt;0,G139="المحفظة"),COUNTIFS($D$4:D139,"&gt;"&amp;0,$G$4:G139,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N140" t="str">
+      <c r="N140">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A140)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A140)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A140&lt;&gt;""),IFERROR(MAX($N$4:N139),0)+1,"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O140" t="str">
         <f>IF(AND(D139&gt;0,F139="أحد الشركاء"),COUNTIFS($D$4:D139,"&gt;"&amp;0,$F$4:F139,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P140" t="str">
+      <c r="P140">
         <f>IF(OR($A140="",$F140="أحد الشركاء",AND($D140="",$E140="")),"",SUMPRODUCT(($A$4:$A140&lt;&gt;"")*($F$4:$F140&lt;&gt;"أحد الشركاء")*((($D$4:$D140&lt;&gt;"")+($E$4:$E140&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="Q140" t="str">
         <f>IF(OR($A140="",$F140&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A140,"&lt;&gt;",$F$4:F140,"أحد الشركاء"))</f>
@@ -17410,39 +17476,53 @@
       </c>
     </row>
     <row r="141" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="25"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="25">
+        <v>46240</v>
+      </c>
+      <c r="B141" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="C141" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D141" s="28"/>
-      <c r="E141" s="29"/>
-      <c r="F141" s="30"/>
+      <c r="E141" s="29">
+        <v>29</v>
+      </c>
+      <c r="F141" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="G141" s="31"/>
-      <c r="H141" s="32"/>
+      <c r="H141" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I141" s="33"/>
-      <c r="J141" s="34" t="str">
+      <c r="J141" s="34">
         <f>IF(AND(D141="",E141="",A141="",B141="",C141=""),"", IFERROR(IF(J140="",D2,J140),D2)+IF(E141="",0,E141)-IF(OR(G141="أبو اسحاق",G141="أبو آدم",G141="أبو اسحاق ",G141="أبو آدم "),0,IF(D141="",0,D141)))</f>
-        <v/>
-      </c>
-      <c r="K141" s="35"/>
-      <c r="L141" t="str">
+        <v>69.64500000000001</v>
+      </c>
+      <c r="K141" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="L141">
         <f>IF(E140&gt;0,COUNTIF($E$4:E140,"&gt;0"),"")</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="M141" t="str">
         <f>IF(AND(D140&gt;0,G140="المحفظة"),COUNTIFS($D$4:D140,"&gt;"&amp;0,$G$4:G140,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N141" t="str">
+      <c r="N141">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A141)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A141)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A141&lt;&gt;""),IFERROR(MAX($N$4:N140),0)+1,"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="O141" t="str">
         <f>IF(AND(D140&gt;0,F140="أحد الشركاء"),COUNTIFS($D$4:D140,"&gt;"&amp;0,$F$4:F140,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P141" t="str">
+      <c r="P141">
         <f>IF(OR($A141="",$F141="أحد الشركاء",AND($D141="",$E141="")),"",SUMPRODUCT(($A$4:$A141&lt;&gt;"")*($F$4:$F141&lt;&gt;"أحد الشركاء")*((($D$4:$D141&lt;&gt;"")+($E$4:$E141&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>119</v>
       </c>
       <c r="Q141" t="str">
         <f>IF(OR($A141="",$F141&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A141,"&lt;&gt;",$F$4:F141,"أحد الشركاء"))</f>
@@ -17450,39 +17530,51 @@
       </c>
     </row>
     <row r="142" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="139"/>
+      <c r="A142" s="139">
+        <v>46240</v>
+      </c>
       <c r="B142" s="36"/>
-      <c r="C142" s="37"/>
-      <c r="D142" s="38"/>
+      <c r="C142" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="D142" s="38">
+        <v>29</v>
+      </c>
       <c r="E142" s="39"/>
-      <c r="F142" s="136"/>
-      <c r="G142" s="40"/>
-      <c r="H142" s="41"/>
+      <c r="F142" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G142" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I142" s="42"/>
-      <c r="J142" s="43" t="str">
+      <c r="J142" s="43">
         <f>IF(AND(D142="",E142="",A142="",B142="",C142=""),"", IFERROR(IF(J141="",D2,J141),D2)+IF(E142="",0,E142)-IF(OR(G142="أبو اسحاق",G142="أبو آدم",G142="أبو اسحاق ",G142="أبو آدم "),0,IF(D142="",0,D142)))</f>
-        <v/>
+        <v>40.64500000000001</v>
       </c>
       <c r="K142" s="44"/>
-      <c r="L142" t="str">
+      <c r="L142">
         <f>IF(E141&gt;0,COUNTIF($E$4:E141,"&gt;0"),"")</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="M142" t="str">
         <f>IF(AND(D141&gt;0,G141="المحفظة"),COUNTIFS($D$4:D141,"&gt;"&amp;0,$G$4:G141,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N142" t="str">
+      <c r="N142">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A142)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A142)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A142&lt;&gt;""),IFERROR(MAX($N$4:N141),0)+1,"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="O142" t="str">
         <f>IF(AND(D141&gt;0,F141="أحد الشركاء"),COUNTIFS($D$4:D141,"&gt;"&amp;0,$F$4:F141,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P142" t="str">
+      <c r="P142">
         <f>IF(OR($A142="",$F142="أحد الشركاء",AND($D142="",$E142="")),"",SUMPRODUCT(($A$4:$A142&lt;&gt;"")*($F$4:$F142&lt;&gt;"أحد الشركاء")*((($D$4:$D142&lt;&gt;"")+($E$4:$E142&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="Q142" t="str">
         <f>IF(OR($A142="",$F142&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A142,"&lt;&gt;",$F$4:F142,"أحد الشركاء"))</f>
@@ -17490,39 +17582,51 @@
       </c>
     </row>
     <row r="143" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="25"/>
+      <c r="A143" s="25">
+        <v>46240</v>
+      </c>
       <c r="B143" s="26"/>
-      <c r="C143" s="27"/>
-      <c r="D143" s="28"/>
+      <c r="C143" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="D143" s="28">
+        <v>5.75</v>
+      </c>
       <c r="E143" s="29"/>
-      <c r="F143" s="30"/>
-      <c r="G143" s="31"/>
-      <c r="H143" s="32"/>
+      <c r="F143" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G143" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H143" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I143" s="33"/>
-      <c r="J143" s="34" t="str">
+      <c r="J143" s="34">
         <f>IF(AND(D143="",E143="",A143="",B143="",C143=""),"", IFERROR(IF(J142="",D2,J142),D2)+IF(E143="",0,E143)-IF(OR(G143="أبو اسحاق",G143="أبو آدم",G143="أبو اسحاق ",G143="أبو آدم "),0,IF(D143="",0,D143)))</f>
-        <v/>
+        <v>34.89500000000001</v>
       </c>
       <c r="K143" s="35"/>
       <c r="L143" t="str">
         <f>IF(E142&gt;0,COUNTIF($E$4:E142,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M143" t="str">
+      <c r="M143">
         <f>IF(AND(D142&gt;0,G142="المحفظة"),COUNTIFS($D$4:D142,"&gt;"&amp;0,$G$4:G142,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N143" t="str">
+        <v>22</v>
+      </c>
+      <c r="N143">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A143)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A143)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A143&lt;&gt;""),IFERROR(MAX($N$4:N142),0)+1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O143" t="str">
         <f>IF(AND(D142&gt;0,F142="أحد الشركاء"),COUNTIFS($D$4:D142,"&gt;"&amp;0,$F$4:F142,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P143" t="str">
+      <c r="P143">
         <f>IF(OR($A143="",$F143="أحد الشركاء",AND($D143="",$E143="")),"",SUMPRODUCT(($A$4:$A143&lt;&gt;"")*($F$4:$F143&lt;&gt;"أحد الشركاء")*((($D$4:$D143&lt;&gt;"")+($E$4:$E143&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>121</v>
       </c>
       <c r="Q143" t="str">
         <f>IF(OR($A143="",$F143&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A143,"&lt;&gt;",$F$4:F143,"أحد الشركاء"))</f>
@@ -17548,9 +17652,9 @@
         <f>IF(E143&gt;0,COUNTIF($E$4:E143,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M144" t="str">
+      <c r="M144">
         <f>IF(AND(D143&gt;0,G143="المحفظة"),COUNTIFS($D$4:D143,"&gt;"&amp;0,$G$4:G143,"المحفظة"),"")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="N144" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A144)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A144)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A144&lt;&gt;""),IFERROR(MAX($N$4:N143),0)+1,"")</f>
@@ -19977,11 +20081,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2157.2950000000001</v>
+        <v>2192.0450000000001</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>747.44</v>
+        <v>793.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -20394,17 +20498,17 @@
       <c r="A2" s="166"/>
       <c r="B2" s="156"/>
       <c r="C2" s="56" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="D2" s="166">
         <v>2026</v>
       </c>
       <c r="E2" s="156"/>
       <c r="F2" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="169" t="s">
         <v>257</v>
-      </c>
-      <c r="G2" s="169" t="s">
-        <v>258</v>
       </c>
       <c r="H2" s="160"/>
       <c r="I2" s="160"/>
@@ -20413,7 +20517,7 @@
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="170" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="156"/>
       <c r="C3" s="156"/>
@@ -20433,25 +20537,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="58" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="F4" s="58" t="s">
         <v>261</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="G4" s="58" t="s">
         <v>262</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="H4" s="58" t="s">
         <v>263</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>264</v>
       </c>
       <c r="I4" s="58" t="s">
         <v>221</v>
       </c>
       <c r="J4" s="58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K4" s="58" t="s">
         <v>223</v>
@@ -20460,31 +20564,31 @@
     <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46207</v>
-      </c>
-      <c r="B5" s="59">
+        <v>46235</v>
+      </c>
+      <c r="B5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-106</v>
       </c>
       <c r="C5" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>احواض عدد 1000 مقاس 14 سم</v>
+        <v>ربل عدد 11 الحبه 2</v>
       </c>
       <c r="D5" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G5" s="59" t="str">
+      <c r="G5" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v>0</v>
       </c>
       <c r="H5" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20496,7 +20600,7 @@
       </c>
       <c r="J5" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5.0500000000000114</v>
+        <v>44.39500000000001</v>
       </c>
       <c r="K5" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(1,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20506,15 +20610,15 @@
     <row r="6" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46206</v>
+        <v>46235</v>
       </c>
       <c r="B6" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-82</v>
+        <v>Inv-107</v>
       </c>
       <c r="C6" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 بقيمه 2.500</v>
+        <v>متنوع عدد 1 بقيمه 2.500</v>
       </c>
       <c r="D6" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20542,7 +20646,7 @@
       </c>
       <c r="J6" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7.5500000000000114</v>
+        <v>46.89500000000001</v>
       </c>
       <c r="K6" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(2,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20552,15 +20656,15 @@
     <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46207</v>
+        <v>46235</v>
       </c>
       <c r="B7" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-83</v>
+        <v>Inv-108</v>
       </c>
       <c r="C7" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ودليه عدد13 الحبه 1</v>
+        <v>فل عدد 1 بقيمه .750</v>
       </c>
       <c r="D7" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20568,11 +20672,11 @@
       </c>
       <c r="E7" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>13</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v>أون لاين</v>
       </c>
       <c r="G7" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20588,7 +20692,7 @@
       </c>
       <c r="J7" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>20.550000000000011</v>
+        <v>47.64500000000001</v>
       </c>
       <c r="K7" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(3,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20598,31 +20702,31 @@
     <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46207</v>
-      </c>
-      <c r="B8" s="61" t="str">
+        <v>46235</v>
+      </c>
+      <c r="B8" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-84</v>
+        <v>0</v>
       </c>
       <c r="C8" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>معلقات عدد 4 الحبه 2</v>
+        <v>بتموس عدد 2 الواحده 12</v>
       </c>
       <c r="D8" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E8" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F8" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>نقداً</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H8" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20634,7 +20738,7 @@
       </c>
       <c r="J8" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>28.550000000000011</v>
+        <v>23.64500000000001</v>
       </c>
       <c r="K8" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(4,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20644,15 +20748,15 @@
     <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46211</v>
+        <v>46239</v>
       </c>
       <c r="B9" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-85</v>
+        <v>Inv-109</v>
       </c>
       <c r="C9" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عطريات عدد8 الحبه 1</v>
+        <v>متنوع عدد 1 الحبه 1</v>
       </c>
       <c r="D9" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20660,7 +20764,7 @@
       </c>
       <c r="E9" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F9" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20680,7 +20784,7 @@
       </c>
       <c r="J9" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>36.550000000000011</v>
+        <v>24.64500000000001</v>
       </c>
       <c r="K9" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(5,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20690,15 +20794,15 @@
     <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46211</v>
+        <v>46240</v>
       </c>
       <c r="B10" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-86</v>
+        <v>Inv-110</v>
       </c>
       <c r="C10" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا سوداء عدد 12 الحبه 2</v>
+        <v>متنوع عدد10 الحبه 1</v>
       </c>
       <c r="D10" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20706,7 +20810,7 @@
       </c>
       <c r="E10" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F10" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20726,7 +20830,7 @@
       </c>
       <c r="J10" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>60.550000000000011</v>
+        <v>34.64500000000001</v>
       </c>
       <c r="K10" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(6,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20736,15 +20840,15 @@
     <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46211</v>
+        <v>46240</v>
       </c>
       <c r="B11" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-87</v>
+        <v>Inv-111</v>
       </c>
       <c r="C11" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عطريات عدد 8 الحبه 1</v>
+        <v>متنوع 6 عدد 1</v>
       </c>
       <c r="D11" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20752,7 +20856,7 @@
       </c>
       <c r="E11" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20772,7 +20876,7 @@
       </c>
       <c r="J11" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>68.550000000000011</v>
+        <v>40.64500000000001</v>
       </c>
       <c r="K11" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(7,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20782,15 +20886,15 @@
     <row r="12" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="B12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-88</v>
+        <v>Inv-112</v>
       </c>
       <c r="C12" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسنا عدد1 الحبه 5</v>
+        <v>ربل عدد 15 الحبه2</v>
       </c>
       <c r="D12" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20798,7 +20902,7 @@
       </c>
       <c r="E12" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20818,41 +20922,41 @@
       </c>
       <c r="J12" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>73.550000000000011</v>
-      </c>
-      <c r="K12" s="61">
+        <v>69.64500000000001</v>
+      </c>
+      <c r="K12" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(8,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>السعر الأصلي 30 تم خصم 1 ليكون 29</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46212</v>
-      </c>
-      <c r="B13" s="59" t="str">
+        <v>46240</v>
+      </c>
+      <c r="B13" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-89</v>
+        <v>0</v>
       </c>
       <c r="C13" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>فل عدد1 الحبه .750</v>
+        <v>كيميكل للمعالج</v>
       </c>
       <c r="D13" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E13" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F13" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G13" s="59">
+        <v>نقداً</v>
+      </c>
+      <c r="G13" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H13" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20864,7 +20968,7 @@
       </c>
       <c r="J13" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>74.300000000000011</v>
+        <v>40.64500000000001</v>
       </c>
       <c r="K13" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(9,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20874,31 +20978,31 @@
     <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46212</v>
-      </c>
-      <c r="B14" s="61" t="str">
+        <v>46240</v>
+      </c>
+      <c r="B14" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-90</v>
+        <v>0</v>
       </c>
       <c r="C14" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 الحبه 1.500</v>
+        <v>ترمستات الثلاجه الكبيره</v>
       </c>
       <c r="D14" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="E14" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G14" s="61">
+        <v>نقداً</v>
+      </c>
+      <c r="G14" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>المحفظة</v>
       </c>
       <c r="H14" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20910,7 +21014,7 @@
       </c>
       <c r="J14" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>75.800000000000011</v>
+        <v>34.89500000000001</v>
       </c>
       <c r="K14" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(10,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -20918,1052 +21022,1052 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="139">
+      <c r="A15" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46212</v>
+        <v/>
       </c>
       <c r="B15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-91</v>
+        <v/>
       </c>
       <c r="C15" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افبوديا عدد الحبه 0.750</v>
-      </c>
-      <c r="D15" s="38">
+        <v/>
+      </c>
+      <c r="D15" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="60">
+        <v/>
+      </c>
+      <c r="E15" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0.75</v>
+        <v/>
       </c>
       <c r="F15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G15" s="59">
+        <v/>
+      </c>
+      <c r="G15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I15" s="59">
+        <v/>
+      </c>
+      <c r="I15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="43">
+        <v/>
+      </c>
+      <c r="J15" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>76.550000000000011</v>
-      </c>
-      <c r="K15" s="59">
+        <v/>
+      </c>
+      <c r="K15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25">
+      <c r="A16" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46212</v>
+        <v/>
       </c>
       <c r="B16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-92</v>
+        <v/>
       </c>
       <c r="C16" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عطريات عدد 1 الفحبه 1</v>
-      </c>
-      <c r="D16" s="28">
+        <v/>
+      </c>
+      <c r="D16" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="62">
+        <v/>
+      </c>
+      <c r="E16" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G16" s="61">
+        <v/>
+      </c>
+      <c r="G16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I16" s="61">
+        <v/>
+      </c>
+      <c r="I16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="34">
+        <v/>
+      </c>
+      <c r="J16" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>77.550000000000011</v>
-      </c>
-      <c r="K16" s="61">
+        <v/>
+      </c>
+      <c r="K16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="139">
+      <c r="A17" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46217</v>
+        <v/>
       </c>
       <c r="B17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-93</v>
+        <v/>
       </c>
       <c r="C17" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>متنوع عدد 2 الحبه 2.500</v>
-      </c>
-      <c r="D17" s="38">
+        <v/>
+      </c>
+      <c r="D17" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="60">
+        <v/>
+      </c>
+      <c r="E17" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G17" s="59">
+        <v/>
+      </c>
+      <c r="G17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I17" s="59">
+        <v/>
+      </c>
+      <c r="I17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="43">
+        <v/>
+      </c>
+      <c r="J17" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>82.550000000000011</v>
-      </c>
-      <c r="K17" s="59">
+        <v/>
+      </c>
+      <c r="K17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+      <c r="A18" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46217</v>
+        <v/>
       </c>
       <c r="B18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-94</v>
+        <v/>
       </c>
       <c r="C18" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>متنوع عدد 12 الحبه 2</v>
-      </c>
-      <c r="D18" s="28">
+        <v/>
+      </c>
+      <c r="D18" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="62">
+        <v/>
+      </c>
+      <c r="E18" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="F18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G18" s="61">
+        <v/>
+      </c>
+      <c r="G18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I18" s="61">
+        <v/>
+      </c>
+      <c r="I18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="34">
+        <v/>
+      </c>
+      <c r="J18" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>106.55000000000001</v>
-      </c>
-      <c r="K18" s="61">
+        <v/>
+      </c>
+      <c r="K18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="139">
+      <c r="A19" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46217</v>
-      </c>
-      <c r="B19" s="59">
+        <v/>
+      </c>
+      <c r="B19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C19" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>حبل تعليق</v>
-      </c>
-      <c r="D19" s="38">
+        <v/>
+      </c>
+      <c r="D19" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1.925</v>
-      </c>
-      <c r="E19" s="60">
+        <v/>
+      </c>
+      <c r="E19" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I19" s="59">
+        <v/>
+      </c>
+      <c r="I19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="43">
+        <v/>
+      </c>
+      <c r="J19" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>104.62500000000001</v>
-      </c>
-      <c r="K19" s="59">
+        <v/>
+      </c>
+      <c r="K19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25">
+      <c r="A20" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46219</v>
+        <v/>
       </c>
       <c r="B20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-95</v>
+        <v/>
       </c>
       <c r="C20" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد 1 الحبه 2</v>
-      </c>
-      <c r="D20" s="28">
+        <v/>
+      </c>
+      <c r="D20" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="62">
+        <v/>
+      </c>
+      <c r="E20" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G20" s="61">
+        <v/>
+      </c>
+      <c r="G20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I20" s="61">
+        <v/>
+      </c>
+      <c r="I20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="34">
+        <v/>
+      </c>
+      <c r="J20" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>106.62500000000001</v>
+        <v/>
       </c>
       <c r="K20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>مهندس عامر</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="139">
+      <c r="A21" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46219</v>
+        <v/>
       </c>
       <c r="B21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-96</v>
+        <v/>
       </c>
       <c r="C21" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v xml:space="preserve">دارسينا عدد 1 الحبه 2 </v>
-      </c>
-      <c r="D21" s="38">
+        <v/>
+      </c>
+      <c r="D21" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="60">
+        <v/>
+      </c>
+      <c r="E21" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G21" s="59">
+        <v/>
+      </c>
+      <c r="G21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I21" s="59">
+        <v/>
+      </c>
+      <c r="I21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="43">
+        <v/>
+      </c>
+      <c r="J21" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>108.62500000000001</v>
+        <v/>
       </c>
       <c r="K21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>مهندس عامر</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25">
+      <c r="A22" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46221</v>
+        <v/>
       </c>
       <c r="B22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-97</v>
+        <v/>
       </c>
       <c r="C22" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبيا عدد 1 الحبه 1</v>
-      </c>
-      <c r="D22" s="28">
+        <v/>
+      </c>
+      <c r="D22" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="62">
+        <v/>
+      </c>
+      <c r="E22" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G22" s="61">
+        <v/>
+      </c>
+      <c r="G22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I22" s="61">
+        <v/>
+      </c>
+      <c r="I22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="34">
+        <v/>
+      </c>
+      <c r="J22" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>109.62500000000001</v>
-      </c>
-      <c r="K22" s="61">
+        <v/>
+      </c>
+      <c r="K22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="139">
+      <c r="A23" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46221</v>
+        <v/>
       </c>
       <c r="B23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-98</v>
+        <v/>
       </c>
       <c r="C23" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 الحبه 2</v>
-      </c>
-      <c r="D23" s="38">
+        <v/>
+      </c>
+      <c r="D23" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="60">
+        <v/>
+      </c>
+      <c r="E23" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G23" s="59">
+        <v/>
+      </c>
+      <c r="G23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I23" s="59">
+        <v/>
+      </c>
+      <c r="I23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="43">
+        <v/>
+      </c>
+      <c r="J23" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>111.62500000000001</v>
-      </c>
-      <c r="K23" s="59">
+        <v/>
+      </c>
+      <c r="K23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25">
+      <c r="A24" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46224</v>
+        <v/>
       </c>
       <c r="B24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-99</v>
+        <v/>
       </c>
       <c r="C24" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبيا عدد 9 الحبه 1</v>
-      </c>
-      <c r="D24" s="28">
+        <v/>
+      </c>
+      <c r="D24" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="62">
+        <v/>
+      </c>
+      <c r="E24" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="F24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G24" s="61">
+        <v/>
+      </c>
+      <c r="G24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I24" s="61">
+        <v/>
+      </c>
+      <c r="I24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="34">
+        <v/>
+      </c>
+      <c r="J24" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>120.62500000000001</v>
-      </c>
-      <c r="K24" s="61">
+        <v/>
+      </c>
+      <c r="K24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="139">
+      <c r="A25" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46224</v>
+        <v/>
       </c>
       <c r="B25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-100</v>
+        <v/>
       </c>
       <c r="C25" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>ربل عدد 11 الحبه 2</v>
-      </c>
-      <c r="D25" s="38">
+        <v/>
+      </c>
+      <c r="D25" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="60">
+        <v/>
+      </c>
+      <c r="E25" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G25" s="59">
+        <v/>
+      </c>
+      <c r="G25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I25" s="59">
+        <v/>
+      </c>
+      <c r="I25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="43">
+        <v/>
+      </c>
+      <c r="J25" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>142.625</v>
-      </c>
-      <c r="K25" s="59">
+        <v/>
+      </c>
+      <c r="K25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25">
+      <c r="A26" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46225</v>
+        <v/>
       </c>
       <c r="B26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-101</v>
+        <v/>
       </c>
       <c r="C26" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>افوبيا عدد2 الحبه 1</v>
-      </c>
-      <c r="D26" s="28">
+        <v/>
+      </c>
+      <c r="D26" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="62">
+        <v/>
+      </c>
+      <c r="E26" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G26" s="61">
+        <v/>
+      </c>
+      <c r="G26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I26" s="61">
+        <v/>
+      </c>
+      <c r="I26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="34">
+        <v/>
+      </c>
+      <c r="J26" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>144.625</v>
-      </c>
-      <c r="K26" s="61">
+        <v/>
+      </c>
+      <c r="K26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="139">
+      <c r="A27" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46227</v>
+        <v/>
       </c>
       <c r="B27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-102</v>
+        <v/>
       </c>
       <c r="C27" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>متنوع عدد2 الحبه 1</v>
-      </c>
-      <c r="D27" s="38">
+        <v/>
+      </c>
+      <c r="D27" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="60">
+        <v/>
+      </c>
+      <c r="E27" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G27" s="59">
+        <v/>
+      </c>
+      <c r="G27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I27" s="59">
+        <v/>
+      </c>
+      <c r="I27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="43">
+        <v/>
+      </c>
+      <c r="J27" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>146.625</v>
-      </c>
-      <c r="K27" s="59">
+        <v/>
+      </c>
+      <c r="K27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+      <c r="A28" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46229</v>
-      </c>
-      <c r="B28" s="61">
+        <v/>
+      </c>
+      <c r="B28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C28" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>كوكوبيد</v>
-      </c>
-      <c r="D28" s="28">
+        <v/>
+      </c>
+      <c r="D28" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>10</v>
-      </c>
-      <c r="E28" s="62">
+        <v/>
+      </c>
+      <c r="E28" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I28" s="61">
+        <v/>
+      </c>
+      <c r="I28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="34">
+        <v/>
+      </c>
+      <c r="J28" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>136.625</v>
-      </c>
-      <c r="K28" s="61">
+        <v/>
+      </c>
+      <c r="K28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="139">
+      <c r="A29" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46229</v>
-      </c>
-      <c r="B29" s="59">
+        <v/>
+      </c>
+      <c r="B29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C29" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>احواض عدد 1000 مقاس 14 سم</v>
-      </c>
-      <c r="D29" s="38">
+        <v/>
+      </c>
+      <c r="D29" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>20</v>
-      </c>
-      <c r="E29" s="60">
+        <v/>
+      </c>
+      <c r="E29" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I29" s="59">
+        <v/>
+      </c>
+      <c r="I29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="43">
+        <v/>
+      </c>
+      <c r="J29" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>116.625</v>
-      </c>
-      <c r="K29" s="59">
+        <v/>
+      </c>
+      <c r="K29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25">
+      <c r="A30" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46594</v>
+        <v/>
       </c>
       <c r="B30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-103</v>
+        <v/>
       </c>
       <c r="C30" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>متفرقات</v>
-      </c>
-      <c r="D30" s="28">
+        <v/>
+      </c>
+      <c r="D30" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="62">
+        <v/>
+      </c>
+      <c r="E30" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>7.5</v>
+        <v/>
       </c>
       <c r="F30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G30" s="61">
+        <v/>
+      </c>
+      <c r="G30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I30" s="61">
+        <v/>
+      </c>
+      <c r="I30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="34">
+        <v/>
+      </c>
+      <c r="J30" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>124.125</v>
-      </c>
-      <c r="K30" s="61">
+        <v/>
+      </c>
+      <c r="K30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="139">
+      <c r="A31" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46229</v>
-      </c>
-      <c r="B31" s="59">
+        <v/>
+      </c>
+      <c r="B31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C31" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تسوية رصيد فعلي - المتوفر 107.305 (صافي الشهر 99.075 + فائض عام 16.750)</v>
-      </c>
-      <c r="D31" s="38">
+        <v/>
+      </c>
+      <c r="D31" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>16.82</v>
-      </c>
-      <c r="E31" s="60">
+        <v/>
+      </c>
+      <c r="E31" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I31" s="59">
+        <v/>
+      </c>
+      <c r="I31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="43">
+        <v/>
+      </c>
+      <c r="J31" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>107.30500000000001</v>
-      </c>
-      <c r="K31" s="59">
+        <v/>
+      </c>
+      <c r="K31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25">
+      <c r="A32" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46231</v>
+        <v/>
       </c>
       <c r="B32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-104</v>
+        <v/>
       </c>
       <c r="C32" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>متنوع عدد 1 الحبه 2.500</v>
-      </c>
-      <c r="D32" s="28">
+        <v/>
+      </c>
+      <c r="D32" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="62">
+        <v/>
+      </c>
+      <c r="E32" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>2.5</v>
+        <v/>
       </c>
       <c r="F32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G32" s="61">
+        <v/>
+      </c>
+      <c r="G32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I32" s="61">
+        <v/>
+      </c>
+      <c r="I32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="34">
+        <v/>
+      </c>
+      <c r="J32" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>109.80500000000001</v>
-      </c>
-      <c r="K32" s="61">
+        <v/>
+      </c>
+      <c r="K32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="139">
+      <c r="A33" s="139" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46231</v>
+        <v/>
       </c>
       <c r="B33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-105</v>
+        <v/>
       </c>
       <c r="C33" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>دارسينا عدد 1 الحبه 3</v>
-      </c>
-      <c r="D33" s="38">
+        <v/>
+      </c>
+      <c r="D33" s="38" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="60">
+        <v/>
+      </c>
+      <c r="E33" s="60" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أون لاين</v>
-      </c>
-      <c r="G33" s="59">
+        <v/>
+      </c>
+      <c r="G33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I33" s="59">
+        <v/>
+      </c>
+      <c r="I33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="43">
+        <v/>
+      </c>
+      <c r="J33" s="43" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>112.80500000000001</v>
-      </c>
-      <c r="K33" s="59">
+        <v/>
+      </c>
+      <c r="K33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
+      <c r="A34" s="25" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46232</v>
-      </c>
-      <c r="B34" s="61">
+        <v/>
+      </c>
+      <c r="B34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C34" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار</v>
-      </c>
-      <c r="D34" s="28">
+        <v/>
+      </c>
+      <c r="D34" s="28" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>99</v>
-      </c>
-      <c r="E34" s="62">
+        <v/>
+      </c>
+      <c r="E34" s="62" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
+        <v/>
       </c>
       <c r="G34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>المحفظة</v>
+        <v/>
       </c>
       <c r="H34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I34" s="61">
+        <v/>
+      </c>
+      <c r="I34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="34">
+        <v/>
+      </c>
+      <c r="J34" s="34" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>13.805000000000007</v>
-      </c>
-      <c r="K34" s="61">
+        <v/>
+      </c>
+      <c r="K34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63">
+      <c r="A35" s="63" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46232</v>
-      </c>
-      <c r="B35" s="64">
+        <v/>
+      </c>
+      <c r="B35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C35" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
-      </c>
-      <c r="D35" s="66">
+        <v/>
+      </c>
+      <c r="D35" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>205.5</v>
-      </c>
-      <c r="E35" s="67">
+        <v/>
+      </c>
+      <c r="E35" s="67" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v/>
       </c>
       <c r="G35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو آدم</v>
+        <v/>
       </c>
       <c r="H35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I35" s="64">
+        <v/>
+      </c>
+      <c r="I35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="68">
+        <v/>
+      </c>
+      <c r="J35" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>13.805000000000007</v>
-      </c>
-      <c r="K35" s="64">
+        <v/>
+      </c>
+      <c r="K35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69">
+      <c r="A36" s="69" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>46232</v>
-      </c>
-      <c r="B36" s="70">
+        <v/>
+      </c>
+      <c r="B36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C36" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>عدد 3 عماله + 10 ايام العامل البديل 40 دينار +50 كهرباء (تم دفه 99 من المحفظه)</v>
-      </c>
-      <c r="D36" s="72">
+        <v/>
+      </c>
+      <c r="D36" s="72" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>205.5</v>
-      </c>
-      <c r="E36" s="73">
+        <v/>
+      </c>
+      <c r="E36" s="73" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أحد الشركاء</v>
+        <v/>
       </c>
       <c r="G36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>أبو اسحاق</v>
+        <v/>
       </c>
       <c r="H36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I36" s="70">
+        <v/>
+      </c>
+      <c r="I36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="74">
+        <v/>
+      </c>
+      <c r="J36" s="74" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>13.805000000000007</v>
-      </c>
-      <c r="K36" s="70">
+        <v/>
+      </c>
+      <c r="K36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="63"/>
-      <c r="B37" s="64">
+      <c r="B37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C37" s="65"/>
-      <c r="D37" s="66">
+      <c r="D37" s="66" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E37"/>
       <c r="F37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>نقداً</v>
-      </c>
-      <c r="G37" s="64">
+        <v/>
+      </c>
+      <c r="G37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>تم الدفع</v>
-      </c>
-      <c r="I37" s="64">
+        <v/>
+      </c>
+      <c r="I37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="68">
+        <v/>
+      </c>
+      <c r="J37" s="68" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>22.395000000000007</v>
-      </c>
-      <c r="K37" s="64">
+        <v/>
+      </c>
+      <c r="K37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27350,17 +27454,17 @@
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="167" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B155" s="156"/>
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>578.745</v>
+        <v>58.75</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>156.5</v>
+        <v>71.25</v>
       </c>
       <c r="F155" s="168">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27371,7 +27475,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-422.245</v>
+        <v>12.5</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27383,7 +27487,7 @@
         <v>216</v>
       </c>
       <c r="E156" s="48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F156" s="49" t="s">
         <v>218</v>
@@ -27392,7 +27496,7 @@
       <c r="H156" s="77"/>
       <c r="I156" s="77"/>
       <c r="J156" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K156" s="77"/>
     </row>
@@ -27451,7 +27555,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="161" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B1" s="156"/>
       <c r="C1" s="156"/>
@@ -27462,14 +27566,14 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="166" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="156"/>
       <c r="C2" s="56" t="s">
-        <v>256</v>
+        <v>342</v>
       </c>
       <c r="D2" s="166" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E2" s="156"/>
       <c r="F2" s="56">
@@ -27478,7 +27582,7 @@
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B3" s="156"/>
       <c r="C3" s="57">
@@ -27486,7 +27590,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="170" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E3" s="156"/>
       <c r="F3" s="78">
@@ -27496,7 +27600,7 @@
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="172" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B4" s="156"/>
       <c r="C4" s="156"/>
@@ -27519,7 +27623,7 @@
         <v/>
       </c>
       <c r="D5" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E5" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(1,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27545,7 +27649,7 @@
         <v/>
       </c>
       <c r="D6" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E6" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(2,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27571,7 +27675,7 @@
         <v/>
       </c>
       <c r="D7" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E7" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(3,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27597,7 +27701,7 @@
         <v/>
       </c>
       <c r="D8" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E8" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(4,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27623,7 +27727,7 @@
         <v/>
       </c>
       <c r="D9" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E9" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(5,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27649,7 +27753,7 @@
         <v/>
       </c>
       <c r="D10" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E10" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(6,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27675,7 +27779,7 @@
         <v/>
       </c>
       <c r="D11" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E11" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(7,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27701,7 +27805,7 @@
         <v/>
       </c>
       <c r="D12" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E12" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(8,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27727,7 +27831,7 @@
         <v/>
       </c>
       <c r="D13" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E13" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(9,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27753,7 +27857,7 @@
         <v/>
       </c>
       <c r="D14" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E14" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(10,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27779,7 +27883,7 @@
         <v/>
       </c>
       <c r="D15" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E15" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(11,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27805,7 +27909,7 @@
         <v/>
       </c>
       <c r="D16" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E16" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(12,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27831,7 +27935,7 @@
         <v/>
       </c>
       <c r="D17" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E17" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(13,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27857,7 +27961,7 @@
         <v/>
       </c>
       <c r="D18" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E18" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(14,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27883,7 +27987,7 @@
         <v/>
       </c>
       <c r="D19" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E19" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(15,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27909,7 +28013,7 @@
         <v/>
       </c>
       <c r="D20" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E20" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(16,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27935,7 +28039,7 @@
         <v/>
       </c>
       <c r="D21" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E21" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(17,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27961,7 +28065,7 @@
         <v/>
       </c>
       <c r="D22" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E22" s="10" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(18,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -27987,7 +28091,7 @@
         <v/>
       </c>
       <c r="D23" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E23" s="5" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(19,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28013,7 +28117,7 @@
         <v/>
       </c>
       <c r="D24" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E24" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(20,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28039,7 +28143,7 @@
         <v/>
       </c>
       <c r="D25" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E25" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(21,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28065,7 +28169,7 @@
         <v/>
       </c>
       <c r="D26" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E26" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(22,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28091,7 +28195,7 @@
         <v/>
       </c>
       <c r="D27" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E27" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(23,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28117,7 +28221,7 @@
         <v/>
       </c>
       <c r="D28" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E28" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(24,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28143,7 +28247,7 @@
         <v/>
       </c>
       <c r="D29" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E29" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(25,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28169,7 +28273,7 @@
         <v/>
       </c>
       <c r="D30" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E30" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(26,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28195,7 +28299,7 @@
         <v/>
       </c>
       <c r="D31" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E31" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(27,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28221,7 +28325,7 @@
         <v/>
       </c>
       <c r="D32" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E32" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(28,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28247,7 +28351,7 @@
         <v/>
       </c>
       <c r="D33" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E33" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(29,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28273,7 +28377,7 @@
         <v/>
       </c>
       <c r="D34" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E34" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(30,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28299,7 +28403,7 @@
         <v/>
       </c>
       <c r="D35" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E35" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(31,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28325,7 +28429,7 @@
         <v/>
       </c>
       <c r="D36" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E36" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(32,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28351,7 +28455,7 @@
         <v/>
       </c>
       <c r="D37" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E37" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(33,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28377,7 +28481,7 @@
         <v/>
       </c>
       <c r="D38" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E38" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(34,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28403,7 +28507,7 @@
         <v/>
       </c>
       <c r="D39" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E39" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(35,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28429,7 +28533,7 @@
         <v/>
       </c>
       <c r="D40" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E40" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(36,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28455,7 +28559,7 @@
         <v/>
       </c>
       <c r="D41" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E41" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(37,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28481,7 +28585,7 @@
         <v/>
       </c>
       <c r="D42" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E42" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(38,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28507,7 +28611,7 @@
         <v/>
       </c>
       <c r="D43" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E43" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(39,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28533,7 +28637,7 @@
         <v/>
       </c>
       <c r="D44" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E44" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(40,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28559,7 +28663,7 @@
         <v/>
       </c>
       <c r="D45" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E45" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(41,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28585,7 +28689,7 @@
         <v/>
       </c>
       <c r="D46" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E46" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(42,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28611,7 +28715,7 @@
         <v/>
       </c>
       <c r="D47" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E47" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(43,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28637,7 +28741,7 @@
         <v/>
       </c>
       <c r="D48" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E48" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(44,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28663,7 +28767,7 @@
         <v/>
       </c>
       <c r="D49" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E49" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(45,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28689,7 +28793,7 @@
         <v/>
       </c>
       <c r="D50" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E50" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(46,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28715,7 +28819,7 @@
         <v/>
       </c>
       <c r="D51" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E51" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(47,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28741,7 +28845,7 @@
         <v/>
       </c>
       <c r="D52" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E52" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(48,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28767,7 +28871,7 @@
         <v/>
       </c>
       <c r="D53" s="91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E53" s="92" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(49,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28793,7 +28897,7 @@
         <v/>
       </c>
       <c r="D54" s="86" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E54" s="87" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,المحفظة!$H$5:$H$104,0),0)=0,"",INDEX(المحفظة!$E$5:$E$104,IFERROR(MATCH(50,المحفظة!$H$5:$H$104,0),0))),"")</f>
@@ -28807,7 +28911,7 @@
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="172" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B55" s="156"/>
       <c r="C55" s="156"/>
@@ -28821,7 +28925,7 @@
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="171" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B56" s="156"/>
       <c r="C56" s="156"/>
@@ -28848,7 +28952,7 @@
         <v/>
       </c>
       <c r="E57" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F57" s="13" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(1,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(1,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -28874,7 +28978,7 @@
         <v/>
       </c>
       <c r="E58" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F58" s="18" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(2,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(2,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -28900,7 +29004,7 @@
         <v/>
       </c>
       <c r="E59" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F59" s="13" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(3,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(3,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -28926,7 +29030,7 @@
         <v/>
       </c>
       <c r="E60" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F60" s="18" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(4,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(4,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -28952,7 +29056,7 @@
         <v/>
       </c>
       <c r="E61" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F61" s="13" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(5,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(5,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -28978,7 +29082,7 @@
         <v/>
       </c>
       <c r="E62" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F62" s="18" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(6,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(6,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29004,7 +29108,7 @@
         <v/>
       </c>
       <c r="E63" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F63" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(7,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(7,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29030,7 +29134,7 @@
         <v/>
       </c>
       <c r="E64" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F64" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(8,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(8,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29056,7 +29160,7 @@
         <v/>
       </c>
       <c r="E65" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F65" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(9,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29082,7 +29186,7 @@
         <v/>
       </c>
       <c r="E66" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F66" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(10,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29108,7 +29212,7 @@
         <v/>
       </c>
       <c r="E67" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F67" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(11,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29134,7 +29238,7 @@
         <v/>
       </c>
       <c r="E68" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F68" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(12,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29160,7 +29264,7 @@
         <v/>
       </c>
       <c r="E69" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F69" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(13,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29186,7 +29290,7 @@
         <v/>
       </c>
       <c r="E70" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F70" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(14,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29212,7 +29316,7 @@
         <v/>
       </c>
       <c r="E71" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F71" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(15,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29238,7 +29342,7 @@
         <v/>
       </c>
       <c r="E72" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F72" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(16,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29264,7 +29368,7 @@
         <v/>
       </c>
       <c r="E73" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F73" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(17,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29290,7 +29394,7 @@
         <v/>
       </c>
       <c r="E74" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F74" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(18,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29316,7 +29420,7 @@
         <v/>
       </c>
       <c r="E75" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F75" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(19,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29342,7 +29446,7 @@
         <v/>
       </c>
       <c r="E76" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F76" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(20,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29368,7 +29472,7 @@
         <v/>
       </c>
       <c r="E77" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F77" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(21,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29394,7 +29498,7 @@
         <v/>
       </c>
       <c r="E78" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F78" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(22,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29420,7 +29524,7 @@
         <v/>
       </c>
       <c r="E79" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F79" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(23,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29446,7 +29550,7 @@
         <v/>
       </c>
       <c r="E80" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F80" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(24,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29472,7 +29576,7 @@
         <v/>
       </c>
       <c r="E81" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F81" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(25,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29498,7 +29602,7 @@
         <v/>
       </c>
       <c r="E82" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F82" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(26,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29524,7 +29628,7 @@
         <v/>
       </c>
       <c r="E83" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F83" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(27,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29550,7 +29654,7 @@
         <v/>
       </c>
       <c r="E84" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F84" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(28,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29576,7 +29680,7 @@
         <v/>
       </c>
       <c r="E85" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F85" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(29,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29602,7 +29706,7 @@
         <v/>
       </c>
       <c r="E86" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F86" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(30,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29628,7 +29732,7 @@
         <v/>
       </c>
       <c r="E87" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F87" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(31,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29654,7 +29758,7 @@
         <v/>
       </c>
       <c r="E88" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(32,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29680,7 +29784,7 @@
         <v/>
       </c>
       <c r="E89" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F89" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(33,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29706,7 +29810,7 @@
         <v/>
       </c>
       <c r="E90" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F90" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(34,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29732,7 +29836,7 @@
         <v/>
       </c>
       <c r="E91" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F91" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(35,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29758,7 +29862,7 @@
         <v/>
       </c>
       <c r="E92" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F92" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(36,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29784,7 +29888,7 @@
         <v/>
       </c>
       <c r="E93" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F93" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(37,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29810,7 +29914,7 @@
         <v/>
       </c>
       <c r="E94" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F94" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(38,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29836,7 +29940,7 @@
         <v/>
       </c>
       <c r="E95" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F95" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(39,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29862,7 +29966,7 @@
         <v/>
       </c>
       <c r="E96" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F96" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(40,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29888,7 +29992,7 @@
         <v/>
       </c>
       <c r="E97" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F97" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(41,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29914,7 +30018,7 @@
         <v/>
       </c>
       <c r="E98" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F98" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(42,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29940,7 +30044,7 @@
         <v/>
       </c>
       <c r="E99" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F99" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(43,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29966,7 +30070,7 @@
         <v/>
       </c>
       <c r="E100" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F100" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(44,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -29992,7 +30096,7 @@
         <v/>
       </c>
       <c r="E101" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F101" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(45,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(45,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30018,7 +30122,7 @@
         <v/>
       </c>
       <c r="E102" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F102" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(46,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(46,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30044,7 +30148,7 @@
         <v/>
       </c>
       <c r="E103" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F103" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(47,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(47,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30070,7 +30174,7 @@
         <v/>
       </c>
       <c r="E104" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F104" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(48,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(48,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30096,7 +30200,7 @@
         <v/>
       </c>
       <c r="E105" s="101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F105" s="98" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(49,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(49,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30122,7 +30226,7 @@
         <v/>
       </c>
       <c r="E106" s="106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F106" s="103" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(50,المحفظة!$H$107:$H$206,0),0)=0,"",INDEX(المحفظة!$F$107:$F$206,IFERROR(MATCH(50,المحفظة!$H$107:$H$206,0),0))),"")</f>
@@ -30132,7 +30236,7 @@
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="171" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B107" s="156"/>
       <c r="C107" s="156"/>
@@ -30146,7 +30250,7 @@
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="167" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B108" s="156"/>
       <c r="C108" s="156"/>

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFF9F62-6098-449D-AAF1-A7985781E56C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886EAFAB-9B2A-4AEC-9CB2-E17E93EC92F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المحفظة" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="346">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1071,6 +1071,15 @@
   </si>
   <si>
     <t>أغسطس</t>
+  </si>
+  <si>
+    <t>Inv-113</t>
+  </si>
+  <si>
+    <t>ربل  عدد 40 الحبه 2.250</t>
+  </si>
+  <si>
+    <t>متنوع 8 الحبه 1</t>
   </si>
 </sst>
 </file>
@@ -2251,14 +2260,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2621,7 +2630,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>34.89500000000001</v>
+        <v>132.89500000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5809,55 +5818,55 @@
       </c>
     </row>
     <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="142" t="str">
+      <c r="A127" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(122,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46244</v>
       </c>
       <c r="B127" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(122,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-113</v>
       </c>
       <c r="C127" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(122,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D127" s="123" t="str">
+        <v>ربل  عدد 40 الحبه 2.250</v>
+      </c>
+      <c r="D127" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(122,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E127" s="124" t="str">
+        <v>90</v>
+      </c>
+      <c r="E127" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(122,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F127" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F127" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>124.89500000000001</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="142" t="str">
+      <c r="A128" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46244</v>
       </c>
       <c r="B128" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-113</v>
       </c>
       <c r="C128" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D128" s="123" t="str">
+        <v>متنوع 8 الحبه 1</v>
+      </c>
+      <c r="D128" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E128" s="124" t="str">
+        <v>8</v>
+      </c>
+      <c r="E128" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F128" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F128" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>132.89500000000001</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7870,7 +7879,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>793.44</v>
+        <v>891.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7878,7 +7887,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>34.89500000000001</v>
+        <v>132.89500000000001</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17634,18 +17643,30 @@
       </c>
     </row>
     <row r="144" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="139"/>
-      <c r="B144" s="36"/>
-      <c r="C144" s="37"/>
+      <c r="A144" s="139">
+        <v>46244</v>
+      </c>
+      <c r="B144" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="C144" s="37" t="s">
+        <v>344</v>
+      </c>
       <c r="D144" s="38"/>
-      <c r="E144" s="39"/>
-      <c r="F144" s="136"/>
+      <c r="E144" s="39">
+        <v>90</v>
+      </c>
+      <c r="F144" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G144" s="40"/>
-      <c r="H144" s="41"/>
+      <c r="H144" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I144" s="42"/>
-      <c r="J144" s="43" t="str">
+      <c r="J144" s="43">
         <f>IF(AND(D144="",E144="",A144="",B144="",C144=""),"", IFERROR(IF(J143="",D2,J143),D2)+IF(E144="",0,E144)-IF(OR(G144="أبو اسحاق",G144="أبو آدم",G144="أبو اسحاق ",G144="أبو آدم "),0,IF(D144="",0,D144)))</f>
-        <v/>
+        <v>124.89500000000001</v>
       </c>
       <c r="K144" s="44"/>
       <c r="L144" t="str">
@@ -17656,17 +17677,17 @@
         <f>IF(AND(D143&gt;0,G143="المحفظة"),COUNTIFS($D$4:D143,"&gt;"&amp;0,$G$4:G143,"المحفظة"),"")</f>
         <v>23</v>
       </c>
-      <c r="N144" t="str">
+      <c r="N144">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A144)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A144)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A144&lt;&gt;""),IFERROR(MAX($N$4:N143),0)+1,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="O144" t="str">
         <f>IF(AND(D143&gt;0,F143="أحد الشركاء"),COUNTIFS($D$4:D143,"&gt;"&amp;0,$F$4:F143,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P144" t="str">
+      <c r="P144">
         <f>IF(OR($A144="",$F144="أحد الشركاء",AND($D144="",$E144="")),"",SUMPRODUCT(($A$4:$A144&lt;&gt;"")*($F$4:$F144&lt;&gt;"أحد الشركاء")*((($D$4:$D144&lt;&gt;"")+($E$4:$E144&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>122</v>
       </c>
       <c r="Q144" t="str">
         <f>IF(OR($A144="",$F144&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A144,"&lt;&gt;",$F$4:F144,"أحد الشركاء"))</f>
@@ -17674,39 +17695,51 @@
       </c>
     </row>
     <row r="145" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="25"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="25">
+        <v>46244</v>
+      </c>
+      <c r="B145" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="C145" s="27" t="s">
+        <v>345</v>
+      </c>
       <c r="D145" s="28"/>
-      <c r="E145" s="29"/>
-      <c r="F145" s="30"/>
+      <c r="E145" s="29">
+        <v>8</v>
+      </c>
+      <c r="F145" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G145" s="31"/>
-      <c r="H145" s="32"/>
+      <c r="H145" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I145" s="33"/>
-      <c r="J145" s="34" t="str">
+      <c r="J145" s="34">
         <f>IF(AND(D145="",E145="",A145="",B145="",C145=""),"", IFERROR(IF(J144="",D2,J144),D2)+IF(E145="",0,E145)-IF(OR(G145="أبو اسحاق",G145="أبو آدم",G145="أبو اسحاق ",G145="أبو آدم "),0,IF(D145="",0,D145)))</f>
-        <v/>
+        <v>132.89500000000001</v>
       </c>
       <c r="K145" s="35"/>
-      <c r="L145" t="str">
+      <c r="L145">
         <f>IF(E144&gt;0,COUNTIF($E$4:E144,"&gt;0"),"")</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="M145" t="str">
         <f>IF(AND(D144&gt;0,G144="المحفظة"),COUNTIFS($D$4:D144,"&gt;"&amp;0,$G$4:G144,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N145" t="str">
+      <c r="N145">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A145)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A145)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A145&lt;&gt;""),IFERROR(MAX($N$4:N144),0)+1,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="O145" t="str">
         <f>IF(AND(D144&gt;0,F144="أحد الشركاء"),COUNTIFS($D$4:D144,"&gt;"&amp;0,$F$4:F144,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P145" t="str">
+      <c r="P145">
         <f>IF(OR($A145="",$F145="أحد الشركاء",AND($D145="",$E145="")),"",SUMPRODUCT(($A$4:$A145&lt;&gt;"")*($F$4:$F145&lt;&gt;"أحد الشركاء")*((($D$4:$D145&lt;&gt;"")+($E$4:$E145&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>123</v>
       </c>
       <c r="Q145" t="str">
         <f>IF(OR($A145="",$F145&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A145,"&lt;&gt;",$F$4:F145,"أحد الشركاء"))</f>
@@ -17728,9 +17761,9 @@
         <v/>
       </c>
       <c r="K146" s="44"/>
-      <c r="L146" t="str">
+      <c r="L146">
         <f>IF(E145&gt;0,COUNTIF($E$4:E145,"&gt;0"),"")</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="M146" t="str">
         <f>IF(AND(D145&gt;0,G145="المحفظة"),COUNTIFS($D$4:D145,"&gt;"&amp;0,$G$4:G145,"المحفظة"),"")</f>
@@ -20085,7 +20118,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>793.44</v>
+        <v>891.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -21022,95 +21055,95 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="139" t="str">
+      <c r="A15" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46244</v>
       </c>
       <c r="B15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-113</v>
       </c>
       <c r="C15" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="38" t="str">
+        <v>ربل  عدد 40 الحبه 2.250</v>
+      </c>
+      <c r="D15" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="60" t="str">
+        <v>0</v>
+      </c>
+      <c r="E15" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="59" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H15" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J15" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="59" t="str">
+        <v>124.89500000000001</v>
+      </c>
+      <c r="K15" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(11,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="str">
+      <c r="A16" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46244</v>
       </c>
       <c r="B16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-113</v>
       </c>
       <c r="C16" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="28" t="str">
+        <v>متنوع 8 الحبه 1</v>
+      </c>
+      <c r="D16" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G16" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I16" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J16" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="61" t="str">
+        <v>132.89500000000001</v>
+      </c>
+      <c r="K16" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27464,7 +27497,7 @@
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>71.25</v>
+        <v>169.25</v>
       </c>
       <c r="F155" s="168">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27475,7 +27508,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>12.5</v>
+        <v>110.5</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27599,7 +27632,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -28910,7 +28943,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -28924,7 +28957,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30235,7 +30268,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30258,7 +30291,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30267,17 +30300,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886EAFAB-9B2A-4AEC-9CB2-E17E93EC92F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7C73A-0A51-47A8-832E-41888C254B56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="348">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1080,6 +1080,12 @@
   </si>
   <si>
     <t>متنوع 8 الحبه 1</t>
+  </si>
+  <si>
+    <t>احواض معلقه + كوكوبيت</t>
+  </si>
+  <si>
+    <t>15-15-15 خرماشه</t>
   </si>
 </sst>
 </file>
@@ -2260,14 +2266,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2630,7 +2636,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>132.89500000000001</v>
+        <v>70.220000000000013</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5870,55 +5876,55 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="142" t="str">
+      <c r="A129" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(124,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B129" s="122" t="str">
+        <v>46245</v>
+      </c>
+      <c r="B129" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(124,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C129" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(124,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D129" s="123" t="str">
+        <v>احواض معلقه + كوكوبيت</v>
+      </c>
+      <c r="D129" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(124,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E129" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E129" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(124,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F129" s="125" t="str">
+        <v>55</v>
+      </c>
+      <c r="F129" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>77.89500000000001</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="142" t="str">
+      <c r="A130" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(125,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B130" s="122" t="str">
+        <v>46245</v>
+      </c>
+      <c r="B130" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(125,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C130" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(125,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D130" s="123" t="str">
+        <v>15-15-15 خرماشه</v>
+      </c>
+      <c r="D130" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(125,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E130" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E130" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(125,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F130" s="125" t="str">
+        <v>7.6749999999999998</v>
+      </c>
+      <c r="F130" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>70.220000000000013</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7883,11 +7889,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>758.54499999999996</v>
+        <v>821.21999999999991</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>132.89500000000001</v>
+        <v>70.220000000000013</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17747,18 +17753,30 @@
       </c>
     </row>
     <row r="146" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="139"/>
+      <c r="A146" s="139">
+        <v>46245</v>
+      </c>
       <c r="B146" s="36"/>
-      <c r="C146" s="37"/>
-      <c r="D146" s="38"/>
+      <c r="C146" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="D146" s="38">
+        <v>55</v>
+      </c>
       <c r="E146" s="39"/>
-      <c r="F146" s="136"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="41"/>
+      <c r="F146" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G146" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H146" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I146" s="42"/>
-      <c r="J146" s="43" t="str">
+      <c r="J146" s="43">
         <f>IF(AND(D146="",E146="",A146="",B146="",C146=""),"", IFERROR(IF(J145="",D2,J145),D2)+IF(E146="",0,E146)-IF(OR(G146="أبو اسحاق",G146="أبو آدم",G146="أبو اسحاق ",G146="أبو آدم "),0,IF(D146="",0,D146)))</f>
-        <v/>
+        <v>77.89500000000001</v>
       </c>
       <c r="K146" s="44"/>
       <c r="L146">
@@ -17769,17 +17787,17 @@
         <f>IF(AND(D145&gt;0,G145="المحفظة"),COUNTIFS($D$4:D145,"&gt;"&amp;0,$G$4:G145,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N146" t="str">
+      <c r="N146">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A146)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A146)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A146&lt;&gt;""),IFERROR(MAX($N$4:N145),0)+1,"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="O146" t="str">
         <f>IF(AND(D145&gt;0,F145="أحد الشركاء"),COUNTIFS($D$4:D145,"&gt;"&amp;0,$F$4:F145,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P146" t="str">
+      <c r="P146">
         <f>IF(OR($A146="",$F146="أحد الشركاء",AND($D146="",$E146="")),"",SUMPRODUCT(($A$4:$A146&lt;&gt;"")*($F$4:$F146&lt;&gt;"أحد الشركاء")*((($D$4:$D146&lt;&gt;"")+($E$4:$E146&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>124</v>
       </c>
       <c r="Q146" t="str">
         <f>IF(OR($A146="",$F146&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A146,"&lt;&gt;",$F$4:F146,"أحد الشركاء"))</f>
@@ -17787,39 +17805,51 @@
       </c>
     </row>
     <row r="147" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="25"/>
+      <c r="A147" s="25">
+        <v>46245</v>
+      </c>
       <c r="B147" s="26"/>
-      <c r="C147" s="27"/>
-      <c r="D147" s="28"/>
+      <c r="C147" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="D147" s="28">
+        <v>7.6749999999999998</v>
+      </c>
       <c r="E147" s="29"/>
-      <c r="F147" s="30"/>
-      <c r="G147" s="31"/>
-      <c r="H147" s="32"/>
+      <c r="F147" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G147" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H147" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I147" s="33"/>
-      <c r="J147" s="34" t="str">
+      <c r="J147" s="34">
         <f>IF(AND(D147="",E147="",A147="",B147="",C147=""),"", IFERROR(IF(J146="",D2,J146),D2)+IF(E147="",0,E147)-IF(OR(G147="أبو اسحاق",G147="أبو آدم",G147="أبو اسحاق ",G147="أبو آدم "),0,IF(D147="",0,D147)))</f>
-        <v/>
+        <v>70.220000000000013</v>
       </c>
       <c r="K147" s="35"/>
       <c r="L147" t="str">
         <f>IF(E146&gt;0,COUNTIF($E$4:E146,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M147" t="str">
+      <c r="M147">
         <f>IF(AND(D146&gt;0,G146="المحفظة"),COUNTIFS($D$4:D146,"&gt;"&amp;0,$G$4:G146,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N147" t="str">
+        <v>24</v>
+      </c>
+      <c r="N147">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A147)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A147)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A147&lt;&gt;""),IFERROR(MAX($N$4:N146),0)+1,"")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="O147" t="str">
         <f>IF(AND(D146&gt;0,F146="أحد الشركاء"),COUNTIFS($D$4:D146,"&gt;"&amp;0,$F$4:F146,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P147" t="str">
+      <c r="P147">
         <f>IF(OR($A147="",$F147="أحد الشركاء",AND($D147="",$E147="")),"",SUMPRODUCT(($A$4:$A147&lt;&gt;"")*($F$4:$F147&lt;&gt;"أحد الشركاء")*((($D$4:$D147&lt;&gt;"")+($E$4:$E147&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>125</v>
       </c>
       <c r="Q147" t="str">
         <f>IF(OR($A147="",$F147&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A147,"&lt;&gt;",$F$4:F147,"أحد الشركاء"))</f>
@@ -17845,9 +17875,9 @@
         <f>IF(E147&gt;0,COUNTIF($E$4:E147,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M148" t="str">
+      <c r="M148">
         <f>IF(AND(D147&gt;0,G147="المحفظة"),COUNTIFS($D$4:D147,"&gt;"&amp;0,$G$4:G147,"المحفظة"),"")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="N148" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A148)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A148)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A148&lt;&gt;""),IFERROR(MAX($N$4:N147),0)+1,"")</f>
@@ -20114,7 +20144,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2192.0450000000001</v>
+        <v>2254.7200000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -21147,95 +21177,95 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="139" t="str">
+      <c r="A17" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="59" t="str">
+        <v>46245</v>
+      </c>
+      <c r="B17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C17" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="38" t="str">
+        <v>احواض معلقه + كوكوبيت</v>
+      </c>
+      <c r="D17" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="60" t="str">
+        <v>55</v>
+      </c>
+      <c r="E17" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H17" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J17" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="59" t="str">
+        <v>77.89500000000001</v>
+      </c>
+      <c r="K17" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(13,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="str">
+      <c r="A18" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="61" t="str">
+        <v>46245</v>
+      </c>
+      <c r="B18" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C18" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="28" t="str">
+        <v>15-15-15 خرماشه</v>
+      </c>
+      <c r="D18" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="62" t="str">
+        <v>7.6749999999999998</v>
+      </c>
+      <c r="E18" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H18" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I18" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="61" t="str">
+        <v>70.220000000000013</v>
+      </c>
+      <c r="K18" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(14,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27493,7 +27523,7 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>58.75</v>
+        <v>121.425</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27508,7 +27538,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>110.5</v>
+        <v>47.825000000000003</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27632,7 +27662,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -28943,7 +28973,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -28957,7 +28987,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30268,7 +30298,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30291,7 +30321,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30300,17 +30330,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7C73A-0A51-47A8-832E-41888C254B56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCBA7AE-0E4E-4AAF-9872-9949B87A1775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="351">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1086,6 +1086,15 @@
   </si>
   <si>
     <t>15-15-15 خرماشه</t>
+  </si>
+  <si>
+    <t>هرمون تدير</t>
+  </si>
+  <si>
+    <t>احواض مقاس 14 عدد 1000</t>
+  </si>
+  <si>
+    <t>وصلات</t>
   </si>
 </sst>
 </file>
@@ -2266,14 +2275,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2636,7 +2645,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>70.220000000000013</v>
+        <v>45.320000000000014</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5928,81 +5937,81 @@
       </c>
     </row>
     <row r="131" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="142" t="str">
+      <c r="A131" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(126,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B131" s="122" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B131" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(126,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C131" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(126,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D131" s="123" t="str">
+        <v>هرمون تدير</v>
+      </c>
+      <c r="D131" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(126,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E131" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E131" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(126,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F131" s="125" t="str">
+        <v>4</v>
+      </c>
+      <c r="F131" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>66.220000000000013</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="142" t="str">
+      <c r="A132" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(127,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B132" s="122" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B132" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(127,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C132" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(127,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D132" s="123" t="str">
+        <v>احواض مقاس 14 عدد 1000</v>
+      </c>
+      <c r="D132" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(127,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E132" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E132" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(127,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F132" s="125" t="str">
+        <v>20</v>
+      </c>
+      <c r="F132" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>46.220000000000013</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="142" t="str">
+      <c r="A133" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(128,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B133" s="122" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B133" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(128,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C133" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(128,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D133" s="123" t="str">
+        <v>وصلات</v>
+      </c>
+      <c r="D133" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(128,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E133" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E133" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(128,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F133" s="125" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="F133" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>45.320000000000014</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7889,11 +7898,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>821.21999999999991</v>
+        <v>846.11999999999989</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>70.220000000000013</v>
+        <v>45.320000000000014</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -17857,18 +17866,30 @@
       </c>
     </row>
     <row r="148" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="139"/>
+      <c r="A148" s="139">
+        <v>46247</v>
+      </c>
       <c r="B148" s="36"/>
-      <c r="C148" s="37"/>
-      <c r="D148" s="38"/>
+      <c r="C148" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D148" s="38">
+        <v>4</v>
+      </c>
       <c r="E148" s="39"/>
-      <c r="F148" s="136"/>
-      <c r="G148" s="40"/>
-      <c r="H148" s="41"/>
+      <c r="F148" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G148" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I148" s="42"/>
-      <c r="J148" s="43" t="str">
+      <c r="J148" s="43">
         <f>IF(AND(D148="",E148="",A148="",B148="",C148=""),"", IFERROR(IF(J147="",D2,J147),D2)+IF(E148="",0,E148)-IF(OR(G148="أبو اسحاق",G148="أبو آدم",G148="أبو اسحاق ",G148="أبو آدم "),0,IF(D148="",0,D148)))</f>
-        <v/>
+        <v>66.220000000000013</v>
       </c>
       <c r="K148" s="44"/>
       <c r="L148" t="str">
@@ -17879,17 +17900,17 @@
         <f>IF(AND(D147&gt;0,G147="المحفظة"),COUNTIFS($D$4:D147,"&gt;"&amp;0,$G$4:G147,"المحفظة"),"")</f>
         <v>25</v>
       </c>
-      <c r="N148" t="str">
+      <c r="N148">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A148)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A148)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A148&lt;&gt;""),IFERROR(MAX($N$4:N147),0)+1,"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="O148" t="str">
         <f>IF(AND(D147&gt;0,F147="أحد الشركاء"),COUNTIFS($D$4:D147,"&gt;"&amp;0,$F$4:F147,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P148" t="str">
+      <c r="P148">
         <f>IF(OR($A148="",$F148="أحد الشركاء",AND($D148="",$E148="")),"",SUMPRODUCT(($A$4:$A148&lt;&gt;"")*($F$4:$F148&lt;&gt;"أحد الشركاء")*((($D$4:$D148&lt;&gt;"")+($E$4:$E148&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="Q148" t="str">
         <f>IF(OR($A148="",$F148&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A148,"&lt;&gt;",$F$4:F148,"أحد الشركاء"))</f>
@@ -17897,39 +17918,51 @@
       </c>
     </row>
     <row r="149" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="25"/>
+      <c r="A149" s="25">
+        <v>46247</v>
+      </c>
       <c r="B149" s="26"/>
-      <c r="C149" s="27"/>
-      <c r="D149" s="28"/>
+      <c r="C149" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="D149" s="28">
+        <v>20</v>
+      </c>
       <c r="E149" s="29"/>
-      <c r="F149" s="30"/>
-      <c r="G149" s="31"/>
-      <c r="H149" s="32"/>
+      <c r="F149" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G149" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H149" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I149" s="33"/>
-      <c r="J149" s="34" t="str">
+      <c r="J149" s="34">
         <f>IF(AND(D149="",E149="",A149="",B149="",C149=""),"", IFERROR(IF(J148="",D2,J148),D2)+IF(E149="",0,E149)-IF(OR(G149="أبو اسحاق",G149="أبو آدم",G149="أبو اسحاق ",G149="أبو آدم "),0,IF(D149="",0,D149)))</f>
-        <v/>
+        <v>46.220000000000013</v>
       </c>
       <c r="K149" s="35"/>
       <c r="L149" t="str">
         <f>IF(E148&gt;0,COUNTIF($E$4:E148,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M149" t="str">
+      <c r="M149">
         <f>IF(AND(D148&gt;0,G148="المحفظة"),COUNTIFS($D$4:D148,"&gt;"&amp;0,$G$4:G148,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N149" t="str">
+        <v>26</v>
+      </c>
+      <c r="N149">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A149)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A149)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A149&lt;&gt;""),IFERROR(MAX($N$4:N148),0)+1,"")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="O149" t="str">
         <f>IF(AND(D148&gt;0,F148="أحد الشركاء"),COUNTIFS($D$4:D148,"&gt;"&amp;0,$F$4:F148,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P149" t="str">
+      <c r="P149">
         <f>IF(OR($A149="",$F149="أحد الشركاء",AND($D149="",$E149="")),"",SUMPRODUCT(($A$4:$A149&lt;&gt;"")*($F$4:$F149&lt;&gt;"أحد الشركاء")*((($D$4:$D149&lt;&gt;"")+($E$4:$E149&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>127</v>
       </c>
       <c r="Q149" t="str">
         <f>IF(OR($A149="",$F149&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A149,"&lt;&gt;",$F$4:F149,"أحد الشركاء"))</f>
@@ -17937,39 +17970,51 @@
       </c>
     </row>
     <row r="150" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="139"/>
+      <c r="A150" s="139">
+        <v>46247</v>
+      </c>
       <c r="B150" s="36"/>
-      <c r="C150" s="37"/>
-      <c r="D150" s="38"/>
+      <c r="C150" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="D150" s="38">
+        <v>0.9</v>
+      </c>
       <c r="E150" s="39"/>
-      <c r="F150" s="136"/>
-      <c r="G150" s="40"/>
-      <c r="H150" s="41"/>
+      <c r="F150" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G150" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H150" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I150" s="42"/>
-      <c r="J150" s="43" t="str">
+      <c r="J150" s="43">
         <f>IF(AND(D150="",E150="",A150="",B150="",C150=""),"", IFERROR(IF(J149="",D2,J149),D2)+IF(E150="",0,E150)-IF(OR(G150="أبو اسحاق",G150="أبو آدم",G150="أبو اسحاق ",G150="أبو آدم "),0,IF(D150="",0,D150)))</f>
-        <v/>
+        <v>45.320000000000014</v>
       </c>
       <c r="K150" s="44"/>
       <c r="L150" t="str">
         <f>IF(E149&gt;0,COUNTIF($E$4:E149,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M150" t="str">
+      <c r="M150">
         <f>IF(AND(D149&gt;0,G149="المحفظة"),COUNTIFS($D$4:D149,"&gt;"&amp;0,$G$4:G149,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N150" t="str">
+        <v>27</v>
+      </c>
+      <c r="N150">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A150)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A150)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A150&lt;&gt;""),IFERROR(MAX($N$4:N149),0)+1,"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="O150" t="str">
         <f>IF(AND(D149&gt;0,F149="أحد الشركاء"),COUNTIFS($D$4:D149,"&gt;"&amp;0,$F$4:F149,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P150" t="str">
+      <c r="P150">
         <f>IF(OR($A150="",$F150="أحد الشركاء",AND($D150="",$E150="")),"",SUMPRODUCT(($A$4:$A150&lt;&gt;"")*($F$4:$F150&lt;&gt;"أحد الشركاء")*((($D$4:$D150&lt;&gt;"")+($E$4:$E150&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>128</v>
       </c>
       <c r="Q150" t="str">
         <f>IF(OR($A150="",$F150&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A150,"&lt;&gt;",$F$4:F150,"أحد الشركاء"))</f>
@@ -17995,9 +18040,9 @@
         <f>IF(E150&gt;0,COUNTIF($E$4:E150,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M151" t="str">
+      <c r="M151">
         <f>IF(AND(D150&gt;0,G150="المحفظة"),COUNTIFS($D$4:D150,"&gt;"&amp;0,$G$4:G150,"المحفظة"),"")</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="N151" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A151)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A151)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A151&lt;&gt;""),IFERROR(MAX($N$4:N150),0)+1,"")</f>
@@ -20144,7 +20189,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2254.7200000000003</v>
+        <v>2279.6200000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -21269,141 +21314,141 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="139" t="str">
+      <c r="A19" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="59" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C19" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="38" t="str">
+        <v>هرمون تدير</v>
+      </c>
+      <c r="D19" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="60" t="str">
+        <v>4</v>
+      </c>
+      <c r="E19" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H19" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J19" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="59" t="str">
+        <v>66.220000000000013</v>
+      </c>
+      <c r="K19" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(15,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="str">
+      <c r="A20" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="61" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B20" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C20" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="28" t="str">
+        <v>احواض مقاس 14 عدد 1000</v>
+      </c>
+      <c r="D20" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="62" t="str">
+        <v>20</v>
+      </c>
+      <c r="E20" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H20" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I20" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J20" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="61" t="str">
+        <v>46.220000000000013</v>
+      </c>
+      <c r="K20" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(16,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="139" t="str">
+      <c r="A21" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="59" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B21" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C21" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="38" t="str">
+        <v>وصلات</v>
+      </c>
+      <c r="D21" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="60" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="E21" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H21" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I21" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J21" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="59" t="str">
+        <v>45.320000000000014</v>
+      </c>
+      <c r="K21" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(17,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27523,7 +27568,7 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>121.425</v>
+        <v>146.32500000000002</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27538,7 +27583,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>47.825000000000003</v>
+        <v>22.924999999999983</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27662,7 +27707,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -28973,7 +29018,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -28987,7 +29032,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30298,7 +30343,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30321,7 +30366,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30330,17 +30375,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCBA7AE-0E4E-4AAF-9872-9949B87A1775}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A66C87-6400-4796-AFE9-FC31C2879DB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="352">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1095,6 +1095,9 @@
   </si>
   <si>
     <t>وصلات</t>
+  </si>
+  <si>
+    <t>وصلات وحنفيه</t>
   </si>
 </sst>
 </file>
@@ -2275,14 +2278,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2645,7 +2648,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>45.320000000000014</v>
+        <v>43.320000000000014</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6015,29 +6018,29 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="142" t="str">
+      <c r="A134" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(129,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B134" s="122" t="str">
+        <v>46249</v>
+      </c>
+      <c r="B134" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(129,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C134" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(129,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D134" s="123" t="str">
+        <v>وصلات وحنفيه</v>
+      </c>
+      <c r="D134" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(129,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E134" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E134" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(129,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F134" s="125" t="str">
+        <v>2</v>
+      </c>
+      <c r="F134" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>43.320000000000014</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7898,11 +7901,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>846.11999999999989</v>
+        <v>848.11999999999989</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>45.320000000000014</v>
+        <v>43.320000000000014</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -18022,18 +18025,30 @@
       </c>
     </row>
     <row r="151" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="25"/>
+      <c r="A151" s="25">
+        <v>46249</v>
+      </c>
       <c r="B151" s="26"/>
-      <c r="C151" s="27"/>
-      <c r="D151" s="28"/>
+      <c r="C151" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="D151" s="28">
+        <v>2</v>
+      </c>
       <c r="E151" s="29"/>
-      <c r="F151" s="30"/>
-      <c r="G151" s="31"/>
-      <c r="H151" s="32"/>
+      <c r="F151" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G151" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I151" s="33"/>
-      <c r="J151" s="34" t="str">
+      <c r="J151" s="34">
         <f>IF(AND(D151="",E151="",A151="",B151="",C151=""),"", IFERROR(IF(J150="",D2,J150),D2)+IF(E151="",0,E151)-IF(OR(G151="أبو اسحاق",G151="أبو آدم",G151="أبو اسحاق ",G151="أبو آدم "),0,IF(D151="",0,D151)))</f>
-        <v/>
+        <v>43.320000000000014</v>
       </c>
       <c r="K151" s="35"/>
       <c r="L151" t="str">
@@ -18044,17 +18059,17 @@
         <f>IF(AND(D150&gt;0,G150="المحفظة"),COUNTIFS($D$4:D150,"&gt;"&amp;0,$G$4:G150,"المحفظة"),"")</f>
         <v>28</v>
       </c>
-      <c r="N151" t="str">
+      <c r="N151">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A151)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A151)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A151&lt;&gt;""),IFERROR(MAX($N$4:N150),0)+1,"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="O151" t="str">
         <f>IF(AND(D150&gt;0,F150="أحد الشركاء"),COUNTIFS($D$4:D150,"&gt;"&amp;0,$F$4:F150,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P151" t="str">
+      <c r="P151">
         <f>IF(OR($A151="",$F151="أحد الشركاء",AND($D151="",$E151="")),"",SUMPRODUCT(($A$4:$A151&lt;&gt;"")*($F$4:$F151&lt;&gt;"أحد الشركاء")*((($D$4:$D151&lt;&gt;"")+($E$4:$E151&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>129</v>
       </c>
       <c r="Q151" t="str">
         <f>IF(OR($A151="",$F151&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A151,"&lt;&gt;",$F$4:F151,"أحد الشركاء"))</f>
@@ -18080,9 +18095,9 @@
         <f>IF(E151&gt;0,COUNTIF($E$4:E151,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M152" t="str">
+      <c r="M152">
         <f>IF(AND(D151&gt;0,G151="المحفظة"),COUNTIFS($D$4:D151,"&gt;"&amp;0,$G$4:G151,"المحفظة"),"")</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="N152" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A152)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A152)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A152&lt;&gt;""),IFERROR(MAX($N$4:N151),0)+1,"")</f>
@@ -20189,7 +20204,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2279.6200000000003</v>
+        <v>2281.6200000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -21452,49 +21467,49 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="str">
+      <c r="A22" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B22" s="61" t="str">
+        <v>46249</v>
+      </c>
+      <c r="B22" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C22" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="28" t="str">
+        <v>وصلات وحنفيه</v>
+      </c>
+      <c r="D22" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="62" t="str">
+        <v>2</v>
+      </c>
+      <c r="E22" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H22" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I22" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J22" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="61" t="str">
+        <v>43.320000000000014</v>
+      </c>
+      <c r="K22" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(18,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27568,7 +27583,7 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>146.32500000000002</v>
+        <v>148.32500000000002</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27583,7 +27598,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>22.924999999999983</v>
+        <v>20.924999999999983</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27707,7 +27722,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -29018,7 +29033,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -29032,7 +29047,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30343,7 +30358,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30366,7 +30381,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30375,17 +30390,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A66C87-6400-4796-AFE9-FC31C2879DB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E937CBB9-DF87-4FA5-B82C-BA0A90DC62F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="353">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1098,6 +1098,9 @@
   </si>
   <si>
     <t>وصلات وحنفيه</t>
+  </si>
+  <si>
+    <t>فل عدد 14 الحبه .750</t>
   </si>
 </sst>
 </file>
@@ -2278,14 +2281,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2648,7 +2651,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>43.320000000000014</v>
+        <v>56.320000000000014</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6044,55 +6047,55 @@
       </c>
     </row>
     <row r="135" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="142" t="str">
+      <c r="A135" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B135" s="122" t="str">
+        <v>46252</v>
+      </c>
+      <c r="B135" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C135" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D135" s="123" t="str">
+        <v>فل عدد 14 الحبه .750</v>
+      </c>
+      <c r="D135" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E135" s="124" t="str">
+        <v>10.5</v>
+      </c>
+      <c r="E135" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F135" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F135" s="125">
         <f t="shared" ref="F135:F166" si="4">IF($A135="","",IF($F134="",0,$F134)+IF($D135="",0,$D135)-IF($E135="",0,$E135))</f>
-        <v/>
+        <v>53.820000000000014</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="142" t="str">
+      <c r="A136" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B136" s="122" t="str">
+        <v>46252</v>
+      </c>
+      <c r="B136" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C136" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D136" s="123" t="str">
+        <v>متنوع عدد 1 الحبه 2.500</v>
+      </c>
+      <c r="D136" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E136" s="124" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E136" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F136" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F136" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>56.320000000000014</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7897,7 +7900,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>891.44</v>
+        <v>904.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7905,7 +7908,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>43.320000000000014</v>
+        <v>56.320000000000014</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -18077,18 +18080,28 @@
       </c>
     </row>
     <row r="152" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="139"/>
+      <c r="A152" s="139">
+        <v>46252</v>
+      </c>
       <c r="B152" s="36"/>
-      <c r="C152" s="37"/>
+      <c r="C152" s="37" t="s">
+        <v>352</v>
+      </c>
       <c r="D152" s="38"/>
-      <c r="E152" s="39"/>
-      <c r="F152" s="136"/>
+      <c r="E152" s="39">
+        <v>10.5</v>
+      </c>
+      <c r="F152" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G152" s="40"/>
-      <c r="H152" s="41"/>
+      <c r="H152" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I152" s="42"/>
-      <c r="J152" s="43" t="str">
+      <c r="J152" s="43">
         <f>IF(AND(D152="",E152="",A152="",B152="",C152=""),"", IFERROR(IF(J151="",D2,J151),D2)+IF(E152="",0,E152)-IF(OR(G152="أبو اسحاق",G152="أبو آدم",G152="أبو اسحاق ",G152="أبو آدم "),0,IF(D152="",0,D152)))</f>
-        <v/>
+        <v>53.820000000000014</v>
       </c>
       <c r="K152" s="44"/>
       <c r="L152" t="str">
@@ -18099,17 +18112,17 @@
         <f>IF(AND(D151&gt;0,G151="المحفظة"),COUNTIFS($D$4:D151,"&gt;"&amp;0,$G$4:G151,"المحفظة"),"")</f>
         <v>29</v>
       </c>
-      <c r="N152" t="str">
+      <c r="N152">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A152)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A152)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A152&lt;&gt;""),IFERROR(MAX($N$4:N151),0)+1,"")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="O152" t="str">
         <f>IF(AND(D151&gt;0,F151="أحد الشركاء"),COUNTIFS($D$4:D151,"&gt;"&amp;0,$F$4:F151,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P152" t="str">
+      <c r="P152">
         <f>IF(OR($A152="",$F152="أحد الشركاء",AND($D152="",$E152="")),"",SUMPRODUCT(($A$4:$A152&lt;&gt;"")*($F$4:$F152&lt;&gt;"أحد الشركاء")*((($D$4:$D152&lt;&gt;"")+($E$4:$E152&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="Q152" t="str">
         <f>IF(OR($A152="",$F152&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A152,"&lt;&gt;",$F$4:F152,"أحد الشركاء"))</f>
@@ -18117,39 +18130,49 @@
       </c>
     </row>
     <row r="153" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="25"/>
+      <c r="A153" s="25">
+        <v>46252</v>
+      </c>
       <c r="B153" s="26"/>
-      <c r="C153" s="27"/>
+      <c r="C153" s="27" t="s">
+        <v>319</v>
+      </c>
       <c r="D153" s="28"/>
-      <c r="E153" s="29"/>
-      <c r="F153" s="30"/>
+      <c r="E153" s="29">
+        <v>2.5</v>
+      </c>
+      <c r="F153" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G153" s="31"/>
-      <c r="H153" s="32"/>
+      <c r="H153" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I153" s="33"/>
-      <c r="J153" s="34" t="str">
+      <c r="J153" s="34">
         <f>IF(AND(D153="",E153="",A153="",B153="",C153=""),"", IFERROR(IF(J152="",D2,J152),D2)+IF(E153="",0,E153)-IF(OR(G153="أبو اسحاق",G153="أبو آدم",G153="أبو اسحاق ",G153="أبو آدم "),0,IF(D153="",0,D153)))</f>
-        <v/>
+        <v>56.320000000000014</v>
       </c>
       <c r="K153" s="35"/>
-      <c r="L153" t="str">
+      <c r="L153">
         <f>IF(E152&gt;0,COUNTIF($E$4:E152,"&gt;0"),"")</f>
-        <v/>
+        <v>101</v>
       </c>
       <c r="M153" t="str">
         <f>IF(AND(D152&gt;0,G152="المحفظة"),COUNTIFS($D$4:D152,"&gt;"&amp;0,$G$4:G152,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N153" t="str">
+      <c r="N153">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A153)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A153)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A153&lt;&gt;""),IFERROR(MAX($N$4:N152),0)+1,"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="O153" t="str">
         <f>IF(AND(D152&gt;0,F152="أحد الشركاء"),COUNTIFS($D$4:D152,"&gt;"&amp;0,$F$4:F152,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P153" t="str">
+      <c r="P153">
         <f>IF(OR($A153="",$F153="أحد الشركاء",AND($D153="",$E153="")),"",SUMPRODUCT(($A$4:$A153&lt;&gt;"")*($F$4:$F153&lt;&gt;"أحد الشركاء")*((($D$4:$D153&lt;&gt;"")+($E$4:$E153&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>131</v>
       </c>
       <c r="Q153" t="str">
         <f>IF(OR($A153="",$F153&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A153,"&lt;&gt;",$F$4:F153,"أحد الشركاء"))</f>
@@ -18171,9 +18194,9 @@
         <v/>
       </c>
       <c r="K154" s="44"/>
-      <c r="L154" t="str">
+      <c r="L154">
         <f>IF(E153&gt;0,COUNTIF($E$4:E153,"&gt;0"),"")</f>
-        <v/>
+        <v>102</v>
       </c>
       <c r="M154" t="str">
         <f>IF(AND(D153&gt;0,G153="المحفظة"),COUNTIFS($D$4:D153,"&gt;"&amp;0,$G$4:G153,"المحفظة"),"")</f>
@@ -20208,7 +20231,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>891.44</v>
+        <v>904.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -21513,95 +21536,95 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="139" t="str">
+      <c r="A23" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="59" t="str">
+        <v>46252</v>
+      </c>
+      <c r="B23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C23" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="38" t="str">
+        <v>فل عدد 14 الحبه .750</v>
+      </c>
+      <c r="D23" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="60" t="str">
+        <v>0</v>
+      </c>
+      <c r="E23" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>10.5</v>
       </c>
       <c r="F23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="59" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J23" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="59" t="str">
+        <v>53.820000000000014</v>
+      </c>
+      <c r="K23" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="str">
+      <c r="A24" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B24" s="61" t="str">
+        <v>46252</v>
+      </c>
+      <c r="B24" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C24" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="28" t="str">
+        <v>متنوع عدد 1 الحبه 2.500</v>
+      </c>
+      <c r="D24" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E24" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="F24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G24" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I24" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J24" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="61" t="str">
+        <v>56.320000000000014</v>
+      </c>
+      <c r="K24" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27587,7 +27610,7 @@
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>169.25</v>
+        <v>182.25</v>
       </c>
       <c r="F155" s="168">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27598,7 +27621,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>20.924999999999983</v>
+        <v>33.924999999999983</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27722,7 +27745,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -29033,7 +29056,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -29047,7 +29070,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30358,7 +30381,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30381,7 +30404,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30390,17 +30413,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E937CBB9-DF87-4FA5-B82C-BA0A90DC62F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20623621-8C39-4E2F-A56F-F1C3E4E06DB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="356">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1101,6 +1101,15 @@
   </si>
   <si>
     <t>فل عدد 14 الحبه .750</t>
+  </si>
+  <si>
+    <t>Inv-114</t>
+  </si>
+  <si>
+    <t>Inv-115</t>
+  </si>
+  <si>
+    <t>Inv-116</t>
   </si>
 </sst>
 </file>
@@ -2281,14 +2290,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5871,7 +5880,7 @@
       </c>
       <c r="B128" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>Inv-113</v>
+        <v>Inv-114</v>
       </c>
       <c r="C128" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(123,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -6051,9 +6060,9 @@
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
         <v>46252</v>
       </c>
-      <c r="B135" s="122">
+      <c r="B135" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>0</v>
+        <v>Inv-115</v>
       </c>
       <c r="C135" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(130,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -6077,9 +6086,9 @@
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
         <v>46252</v>
       </c>
-      <c r="B136" s="122">
+      <c r="B136" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>0</v>
+        <v>Inv-116</v>
       </c>
       <c r="C136" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(131,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -17720,7 +17729,7 @@
         <v>46244</v>
       </c>
       <c r="B145" s="36" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C145" s="27" t="s">
         <v>345</v>
@@ -18083,7 +18092,9 @@
       <c r="A152" s="139">
         <v>46252</v>
       </c>
-      <c r="B152" s="36"/>
+      <c r="B152" s="36" t="s">
+        <v>354</v>
+      </c>
       <c r="C152" s="37" t="s">
         <v>352</v>
       </c>
@@ -18133,7 +18144,9 @@
       <c r="A153" s="25">
         <v>46252</v>
       </c>
-      <c r="B153" s="26"/>
+      <c r="B153" s="36" t="s">
+        <v>355</v>
+      </c>
       <c r="C153" s="27" t="s">
         <v>319</v>
       </c>
@@ -21220,7 +21233,7 @@
       </c>
       <c r="B16" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>Inv-113</v>
+        <v>Inv-114</v>
       </c>
       <c r="C16" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(12,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21540,9 +21553,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="B23" s="59">
+      <c r="B23" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-115</v>
       </c>
       <c r="C23" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(19,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -21586,9 +21599,9 @@
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
         <v>46252</v>
       </c>
-      <c r="B24" s="61">
+      <c r="B24" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v>0</v>
+        <v>Inv-116</v>
       </c>
       <c r="C24" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(20,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
@@ -27745,7 +27758,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -29056,7 +29069,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -29070,7 +29083,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30381,7 +30394,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30404,7 +30417,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30413,17 +30426,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20623621-8C39-4E2F-A56F-F1C3E4E06DB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577CF6A6-9C9D-460F-B0BF-8BC693A1504F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="366">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1110,6 +1110,36 @@
   </si>
   <si>
     <t>Inv-116</t>
+  </si>
+  <si>
+    <t>Inv-117</t>
+  </si>
+  <si>
+    <t>ربل عدد 10 الحبه 2.250</t>
+  </si>
+  <si>
+    <t>Inv-118</t>
+  </si>
+  <si>
+    <t>متنوع عدد 4 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-119</t>
+  </si>
+  <si>
+    <t>دارسينا عدد 2 الحبه 3</t>
+  </si>
+  <si>
+    <t>Inv-120</t>
+  </si>
+  <si>
+    <t>فل عدد 2 الحبه .750</t>
+  </si>
+  <si>
+    <t>احواض عدد 3500 مقاس 25 سم</t>
+  </si>
+  <si>
+    <t>حديد كحميه 2</t>
   </si>
 </sst>
 </file>
@@ -2290,14 +2320,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2660,7 +2690,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>56.320000000000014</v>
+        <v>90.320000000000022</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6108,107 +6138,107 @@
       </c>
     </row>
     <row r="137" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="142" t="str">
+      <c r="A137" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(132,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B137" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(132,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-117</v>
       </c>
       <c r="C137" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(132,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D137" s="123" t="str">
+        <v>ربل عدد 10 الحبه 2.250</v>
+      </c>
+      <c r="D137" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(132,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E137" s="124" t="str">
+        <v>22.5</v>
+      </c>
+      <c r="E137" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(132,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F137" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F137" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>78.820000000000022</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="142" t="str">
+      <c r="A138" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(133,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B138" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(133,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-118</v>
       </c>
       <c r="C138" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(133,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D138" s="123" t="str">
+        <v>متنوع عدد 4 الحبه 1</v>
+      </c>
+      <c r="D138" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(133,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E138" s="124" t="str">
+        <v>4</v>
+      </c>
+      <c r="E138" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(133,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F138" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F138" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>82.820000000000022</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="142" t="str">
+      <c r="A139" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(134,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B139" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(134,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-119</v>
       </c>
       <c r="C139" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(134,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D139" s="123" t="str">
+        <v>دارسينا عدد 2 الحبه 3</v>
+      </c>
+      <c r="D139" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(134,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E139" s="124" t="str">
+        <v>6</v>
+      </c>
+      <c r="E139" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(134,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F139" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F139" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>88.820000000000022</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="142" t="str">
+      <c r="A140" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(135,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B140" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(135,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-120</v>
       </c>
       <c r="C140" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(135,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D140" s="123" t="str">
+        <v>فل عدد 2 الحبه .750</v>
+      </c>
+      <c r="D140" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(135,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E140" s="124" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E140" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(135,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F140" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F140" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>90.320000000000022</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7909,7 +7939,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>904.44</v>
+        <v>938.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7917,7 +7947,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>56.320000000000014</v>
+        <v>90.320000000000022</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8248,48 +8278,48 @@
       <c r="F222" s="132"/>
     </row>
     <row r="223" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="143" t="str">
+      <c r="A223" s="143">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(14,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B223" s="133" t="str">
+        <v>46235</v>
+      </c>
+      <c r="B223" s="133">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(14,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C223" s="132" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(14,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D223" s="134" t="str">
+        <v>احواض عدد 3500 مقاس 25 سم</v>
+      </c>
+      <c r="D223" s="134">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(14,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="E223" s="135" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$G$4:$G$204,MATCH(14,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>أبو آدم</v>
       </c>
       <c r="F223" s="132"/>
     </row>
     <row r="224" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="143" t="str">
+      <c r="A224" s="143">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(15,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B224" s="133" t="str">
+        <v>46238</v>
+      </c>
+      <c r="B224" s="133">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(15,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C224" s="132" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(15,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D224" s="134" t="str">
+        <v>حديد كحميه 2</v>
+      </c>
+      <c r="D224" s="134">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(15,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>68</v>
       </c>
       <c r="E224" s="135" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$G$4:$G$204,MATCH(15,'كشف الحساب'!$Q$4:$Q$204,0)),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="F224" s="132"/>
     </row>
@@ -10256,7 +10286,7 @@
       </c>
       <c r="D310" s="128">
         <f>SUM(D210:D309)</f>
-        <v>1433.5</v>
+        <v>1781.5</v>
       </c>
       <c r="E310" s="129"/>
       <c r="F310" s="130"/>
@@ -10269,7 +10299,7 @@
       </c>
       <c r="D311" s="128">
         <f>SUMIF(E210:E309,"أبو اسحاق",D210:D309)</f>
-        <v>768</v>
+        <v>836</v>
       </c>
       <c r="E311" s="129"/>
       <c r="F311" s="130"/>
@@ -10282,7 +10312,7 @@
       </c>
       <c r="D312" s="128">
         <f>SUMIF(E210:E309,"أبو آدم",D210:D309)</f>
-        <v>665.5</v>
+        <v>945.5</v>
       </c>
       <c r="E312" s="129"/>
       <c r="F312" s="130"/>
@@ -18193,18 +18223,30 @@
       </c>
     </row>
     <row r="154" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="139"/>
-      <c r="B154" s="36"/>
-      <c r="C154" s="37"/>
+      <c r="A154" s="139">
+        <v>46258</v>
+      </c>
+      <c r="B154" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="C154" s="37" t="s">
+        <v>357</v>
+      </c>
       <c r="D154" s="38"/>
-      <c r="E154" s="39"/>
-      <c r="F154" s="136"/>
+      <c r="E154" s="39">
+        <v>22.5</v>
+      </c>
+      <c r="F154" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G154" s="40"/>
-      <c r="H154" s="41"/>
+      <c r="H154" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I154" s="42"/>
-      <c r="J154" s="43" t="str">
+      <c r="J154" s="43">
         <f>IF(AND(D154="",E154="",A154="",B154="",C154=""),"", IFERROR(IF(J153="",D2,J153),D2)+IF(E154="",0,E154)-IF(OR(G154="أبو اسحاق",G154="أبو آدم",G154="أبو اسحاق ",G154="أبو آدم "),0,IF(D154="",0,D154)))</f>
-        <v/>
+        <v>78.820000000000022</v>
       </c>
       <c r="K154" s="44"/>
       <c r="L154">
@@ -18215,17 +18257,17 @@
         <f>IF(AND(D153&gt;0,G153="المحفظة"),COUNTIFS($D$4:D153,"&gt;"&amp;0,$G$4:G153,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N154" t="str">
+      <c r="N154">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A154)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A154)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A154&lt;&gt;""),IFERROR(MAX($N$4:N153),0)+1,"")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="O154" t="str">
         <f>IF(AND(D153&gt;0,F153="أحد الشركاء"),COUNTIFS($D$4:D153,"&gt;"&amp;0,$F$4:F153,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P154" t="str">
+      <c r="P154">
         <f>IF(OR($A154="",$F154="أحد الشركاء",AND($D154="",$E154="")),"",SUMPRODUCT(($A$4:$A154&lt;&gt;"")*($F$4:$F154&lt;&gt;"أحد الشركاء")*((($D$4:$D154&lt;&gt;"")+($E$4:$E154&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>132</v>
       </c>
       <c r="Q154" t="str">
         <f>IF(OR($A154="",$F154&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A154,"&lt;&gt;",$F$4:F154,"أحد الشركاء"))</f>
@@ -18233,39 +18275,51 @@
       </c>
     </row>
     <row r="155" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="25"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="25">
+        <v>46258</v>
+      </c>
+      <c r="B155" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="C155" s="27" t="s">
+        <v>359</v>
+      </c>
       <c r="D155" s="28"/>
-      <c r="E155" s="29"/>
-      <c r="F155" s="30"/>
+      <c r="E155" s="29">
+        <v>4</v>
+      </c>
+      <c r="F155" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G155" s="31"/>
-      <c r="H155" s="32"/>
+      <c r="H155" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I155" s="33"/>
-      <c r="J155" s="34" t="str">
+      <c r="J155" s="34">
         <f>IF(AND(D155="",E155="",A155="",B155="",C155=""),"", IFERROR(IF(J154="",D2,J154),D2)+IF(E155="",0,E155)-IF(OR(G155="أبو اسحاق",G155="أبو آدم",G155="أبو اسحاق ",G155="أبو آدم "),0,IF(D155="",0,D155)))</f>
-        <v/>
+        <v>82.820000000000022</v>
       </c>
       <c r="K155" s="35"/>
-      <c r="L155" t="str">
+      <c r="L155">
         <f>IF(E154&gt;0,COUNTIF($E$4:E154,"&gt;0"),"")</f>
-        <v/>
+        <v>103</v>
       </c>
       <c r="M155" t="str">
         <f>IF(AND(D154&gt;0,G154="المحفظة"),COUNTIFS($D$4:D154,"&gt;"&amp;0,$G$4:G154,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N155" t="str">
+      <c r="N155">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A155)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A155)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A155&lt;&gt;""),IFERROR(MAX($N$4:N154),0)+1,"")</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="O155" t="str">
         <f>IF(AND(D154&gt;0,F154="أحد الشركاء"),COUNTIFS($D$4:D154,"&gt;"&amp;0,$F$4:F154,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P155" t="str">
+      <c r="P155">
         <f>IF(OR($A155="",$F155="أحد الشركاء",AND($D155="",$E155="")),"",SUMPRODUCT(($A$4:$A155&lt;&gt;"")*($F$4:$F155&lt;&gt;"أحد الشركاء")*((($D$4:$D155&lt;&gt;"")+($E$4:$E155&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>133</v>
       </c>
       <c r="Q155" t="str">
         <f>IF(OR($A155="",$F155&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A155,"&lt;&gt;",$F$4:F155,"أحد الشركاء"))</f>
@@ -18273,39 +18327,51 @@
       </c>
     </row>
     <row r="156" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="139"/>
-      <c r="B156" s="36"/>
-      <c r="C156" s="37"/>
+      <c r="A156" s="139">
+        <v>46258</v>
+      </c>
+      <c r="B156" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="C156" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="D156" s="38"/>
-      <c r="E156" s="39"/>
-      <c r="F156" s="136"/>
+      <c r="E156" s="39">
+        <v>6</v>
+      </c>
+      <c r="F156" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G156" s="40"/>
-      <c r="H156" s="41"/>
+      <c r="H156" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I156" s="42"/>
-      <c r="J156" s="43" t="str">
+      <c r="J156" s="43">
         <f>IF(AND(D156="",E156="",A156="",B156="",C156=""),"", IFERROR(IF(J155="",D2,J155),D2)+IF(E156="",0,E156)-IF(OR(G156="أبو اسحاق",G156="أبو آدم",G156="أبو اسحاق ",G156="أبو آدم "),0,IF(D156="",0,D156)))</f>
-        <v/>
+        <v>88.820000000000022</v>
       </c>
       <c r="K156" s="44"/>
-      <c r="L156" t="str">
+      <c r="L156">
         <f>IF(E155&gt;0,COUNTIF($E$4:E155,"&gt;0"),"")</f>
-        <v/>
+        <v>104</v>
       </c>
       <c r="M156" t="str">
         <f>IF(AND(D155&gt;0,G155="المحفظة"),COUNTIFS($D$4:D155,"&gt;"&amp;0,$G$4:G155,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N156" t="str">
+      <c r="N156">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A156)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A156)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A156&lt;&gt;""),IFERROR(MAX($N$4:N155),0)+1,"")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="O156" t="str">
         <f>IF(AND(D155&gt;0,F155="أحد الشركاء"),COUNTIFS($D$4:D155,"&gt;"&amp;0,$F$4:F155,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P156" t="str">
+      <c r="P156">
         <f>IF(OR($A156="",$F156="أحد الشركاء",AND($D156="",$E156="")),"",SUMPRODUCT(($A$4:$A156&lt;&gt;"")*($F$4:$F156&lt;&gt;"أحد الشركاء")*((($D$4:$D156&lt;&gt;"")+($E$4:$E156&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>134</v>
       </c>
       <c r="Q156" t="str">
         <f>IF(OR($A156="",$F156&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A156,"&lt;&gt;",$F$4:F156,"أحد الشركاء"))</f>
@@ -18313,39 +18379,51 @@
       </c>
     </row>
     <row r="157" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="25"/>
-      <c r="B157" s="26"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="25">
+        <v>46258</v>
+      </c>
+      <c r="B157" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="C157" s="27" t="s">
+        <v>363</v>
+      </c>
       <c r="D157" s="28"/>
-      <c r="E157" s="29"/>
-      <c r="F157" s="30"/>
+      <c r="E157" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="F157" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G157" s="31"/>
-      <c r="H157" s="32"/>
+      <c r="H157" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I157" s="33"/>
-      <c r="J157" s="34" t="str">
+      <c r="J157" s="34">
         <f>IF(AND(D157="",E157="",A157="",B157="",C157=""),"", IFERROR(IF(J156="",D2,J156),D2)+IF(E157="",0,E157)-IF(OR(G157="أبو اسحاق",G157="أبو آدم",G157="أبو اسحاق ",G157="أبو آدم "),0,IF(D157="",0,D157)))</f>
-        <v/>
+        <v>90.320000000000022</v>
       </c>
       <c r="K157" s="35"/>
-      <c r="L157" t="str">
+      <c r="L157">
         <f>IF(E156&gt;0,COUNTIF($E$4:E156,"&gt;0"),"")</f>
-        <v/>
+        <v>105</v>
       </c>
       <c r="M157" t="str">
         <f>IF(AND(D156&gt;0,G156="المحفظة"),COUNTIFS($D$4:D156,"&gt;"&amp;0,$G$4:G156,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N157" t="str">
+      <c r="N157">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A157)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A157)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A157&lt;&gt;""),IFERROR(MAX($N$4:N156),0)+1,"")</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="O157" t="str">
         <f>IF(AND(D156&gt;0,F156="أحد الشركاء"),COUNTIFS($D$4:D156,"&gt;"&amp;0,$F$4:F156,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P157" t="str">
+      <c r="P157">
         <f>IF(OR($A157="",$F157="أحد الشركاء",AND($D157="",$E157="")),"",SUMPRODUCT(($A$4:$A157&lt;&gt;"")*($F$4:$F157&lt;&gt;"أحد الشركاء")*((($D$4:$D157&lt;&gt;"")+($E$4:$E157&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="Q157" t="str">
         <f>IF(OR($A157="",$F157&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A157,"&lt;&gt;",$F$4:F157,"أحد الشركاء"))</f>
@@ -18353,31 +18431,43 @@
       </c>
     </row>
     <row r="158" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="139"/>
+      <c r="A158" s="139">
+        <v>46235</v>
+      </c>
       <c r="B158" s="36"/>
-      <c r="C158" s="37"/>
-      <c r="D158" s="38"/>
+      <c r="C158" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="D158" s="38">
+        <v>280</v>
+      </c>
       <c r="E158" s="39"/>
-      <c r="F158" s="136"/>
-      <c r="G158" s="40"/>
-      <c r="H158" s="41"/>
+      <c r="F158" s="136" t="s">
+        <v>48</v>
+      </c>
+      <c r="G158" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H158" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I158" s="42"/>
-      <c r="J158" s="43" t="str">
+      <c r="J158" s="43">
         <f>IF(AND(D158="",E158="",A158="",B158="",C158=""),"", IFERROR(IF(J157="",D2,J157),D2)+IF(E158="",0,E158)-IF(OR(G158="أبو اسحاق",G158="أبو آدم",G158="أبو اسحاق ",G158="أبو آدم "),0,IF(D158="",0,D158)))</f>
-        <v/>
+        <v>90.320000000000022</v>
       </c>
       <c r="K158" s="44"/>
-      <c r="L158" t="str">
+      <c r="L158">
         <f>IF(E157&gt;0,COUNTIF($E$4:E157,"&gt;0"),"")</f>
-        <v/>
+        <v>106</v>
       </c>
       <c r="M158" t="str">
         <f>IF(AND(D157&gt;0,G157="المحفظة"),COUNTIFS($D$4:D157,"&gt;"&amp;0,$G$4:G157,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N158" t="str">
+      <c r="N158">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A158)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A158)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A158&lt;&gt;""),IFERROR(MAX($N$4:N157),0)+1,"")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="O158" t="str">
         <f>IF(AND(D157&gt;0,F157="أحد الشركاء"),COUNTIFS($D$4:D157,"&gt;"&amp;0,$F$4:F157,"أحد الشركاء"),"")</f>
@@ -18387,24 +18477,36 @@
         <f>IF(OR($A158="",$F158="أحد الشركاء",AND($D158="",$E158="")),"",SUMPRODUCT(($A$4:$A158&lt;&gt;"")*($F$4:$F158&lt;&gt;"أحد الشركاء")*((($D$4:$D158&lt;&gt;"")+($E$4:$E158&lt;&gt;""))&gt;0)))</f>
         <v/>
       </c>
-      <c r="Q158" t="str">
+      <c r="Q158">
         <f>IF(OR($A158="",$F158&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A158,"&lt;&gt;",$F$4:F158,"أحد الشركاء"))</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="25"/>
+      <c r="A159" s="25">
+        <v>46238</v>
+      </c>
       <c r="B159" s="26"/>
-      <c r="C159" s="27"/>
-      <c r="D159" s="28"/>
+      <c r="C159" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="D159" s="28">
+        <v>68</v>
+      </c>
       <c r="E159" s="29"/>
-      <c r="F159" s="30"/>
-      <c r="G159" s="31"/>
-      <c r="H159" s="32"/>
+      <c r="F159" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G159" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="H159" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I159" s="33"/>
-      <c r="J159" s="34" t="str">
+      <c r="J159" s="34">
         <f>IF(AND(D159="",E159="",A159="",B159="",C159=""),"", IFERROR(IF(J158="",D2,J158),D2)+IF(E159="",0,E159)-IF(OR(G159="أبو اسحاق",G159="أبو آدم",G159="أبو اسحاق ",G159="أبو آدم "),0,IF(D159="",0,D159)))</f>
-        <v/>
+        <v>90.320000000000022</v>
       </c>
       <c r="K159" s="35"/>
       <c r="L159" t="str">
@@ -18415,21 +18517,21 @@
         <f>IF(AND(D158&gt;0,G158="المحفظة"),COUNTIFS($D$4:D158,"&gt;"&amp;0,$G$4:G158,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N159" t="str">
+      <c r="N159">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A159)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A159)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A159&lt;&gt;""),IFERROR(MAX($N$4:N158),0)+1,"")</f>
-        <v/>
-      </c>
-      <c r="O159" t="str">
+        <v>26</v>
+      </c>
+      <c r="O159">
         <f>IF(AND(D158&gt;0,F158="أحد الشركاء"),COUNTIFS($D$4:D158,"&gt;"&amp;0,$F$4:F158,"أحد الشركاء"),"")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="P159" t="str">
         <f>IF(OR($A159="",$F159="أحد الشركاء",AND($D159="",$E159="")),"",SUMPRODUCT(($A$4:$A159&lt;&gt;"")*($F$4:$F159&lt;&gt;"أحد الشركاء")*((($D$4:$D159&lt;&gt;"")+($E$4:$E159&lt;&gt;""))&gt;0)))</f>
         <v/>
       </c>
-      <c r="Q159" t="str">
+      <c r="Q159">
         <f>IF(OR($A159="",$F159&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A159,"&lt;&gt;",$F$4:F159,"أحد الشركاء"))</f>
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18459,9 +18561,9 @@
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A160)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A160)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A160&lt;&gt;""),IFERROR(MAX($N$4:N159),0)+1,"")</f>
         <v/>
       </c>
-      <c r="O160" t="str">
+      <c r="O160">
         <f>IF(AND(D159&gt;0,F159="أحد الشركاء"),COUNTIFS($D$4:D159,"&gt;"&amp;0,$F$4:F159,"أحد الشركاء"),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="P160" t="str">
         <f>IF(OR($A160="",$F160="أحد الشركاء",AND($D160="",$E160="")),"",SUMPRODUCT(($A$4:$A160&lt;&gt;"")*($F$4:$F160&lt;&gt;"أحد الشركاء")*((($D$4:$D160&lt;&gt;"")+($E$4:$E160&lt;&gt;""))&gt;0)))</f>
@@ -20240,11 +20342,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2281.6200000000003</v>
+        <v>2629.6200000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>904.44</v>
+        <v>938.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -21641,279 +21743,279 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="139" t="str">
+      <c r="A25" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-117</v>
       </c>
       <c r="C25" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="38" t="str">
+        <v>ربل عدد 10 الحبه 2.250</v>
+      </c>
+      <c r="D25" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="60" t="str">
+        <v>0</v>
+      </c>
+      <c r="E25" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>22.5</v>
       </c>
       <c r="F25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="59" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H25" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J25" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="59" t="str">
+        <v>78.820000000000022</v>
+      </c>
+      <c r="K25" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(21,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="str">
+      <c r="A26" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-118</v>
       </c>
       <c r="C26" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="28" t="str">
+        <v>متنوع عدد 4 الحبه 1</v>
+      </c>
+      <c r="D26" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E26" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G26" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H26" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I26" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J26" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="61" t="str">
+        <v>82.820000000000022</v>
+      </c>
+      <c r="K26" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(22,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="139" t="str">
+      <c r="A27" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-119</v>
       </c>
       <c r="C27" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="38" t="str">
+        <v>دارسينا عدد 2 الحبه 3</v>
+      </c>
+      <c r="D27" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="60" t="str">
+        <v>0</v>
+      </c>
+      <c r="E27" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="F27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="59" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G27" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H27" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I27" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J27" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="59" t="str">
+        <v>88.820000000000022</v>
+      </c>
+      <c r="K27" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(23,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="str">
+      <c r="A28" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="B28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-120</v>
       </c>
       <c r="C28" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="28" t="str">
+        <v>فل عدد 2 الحبه .750</v>
+      </c>
+      <c r="D28" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E28" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="F28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G28" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H28" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I28" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J28" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="61" t="str">
+        <v>90.320000000000022</v>
+      </c>
+      <c r="K28" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(24,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="139" t="str">
+      <c r="A29" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B29" s="59" t="str">
+        <v>46235</v>
+      </c>
+      <c r="B29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C29" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="38" t="str">
+        <v>احواض عدد 3500 مقاس 25 سم</v>
+      </c>
+      <c r="D29" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="60" t="str">
+        <v>280</v>
+      </c>
+      <c r="E29" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو آدم</v>
       </c>
       <c r="H29" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J29" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="59" t="str">
+        <v>90.320000000000022</v>
+      </c>
+      <c r="K29" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(25,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="str">
+      <c r="A30" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B30" s="61" t="str">
+        <v>46238</v>
+      </c>
+      <c r="B30" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C30" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="28" t="str">
+        <v>حديد كحميه 2</v>
+      </c>
+      <c r="D30" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="62" t="str">
+        <v>68</v>
+      </c>
+      <c r="E30" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أحد الشركاء</v>
       </c>
       <c r="G30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>أبو اسحاق</v>
       </c>
       <c r="H30" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I30" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J30" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="61" t="str">
+        <v>90.320000000000022</v>
+      </c>
+      <c r="K30" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(26,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27619,11 +27721,11 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>148.32500000000002</v>
+        <v>496.32500000000005</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>182.25</v>
+        <v>216.25</v>
       </c>
       <c r="F155" s="168">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27634,7 +27736,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>33.924999999999983</v>
+        <v>-280.07500000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27758,7 +27860,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="171" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -29069,7 +29171,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="171" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -29083,7 +29185,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="173" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30394,7 +30496,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="173" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30417,7 +30519,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="172">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30426,17 +30528,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577CF6A6-9C9D-460F-B0BF-8BC693A1504F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB15F3-66D3-4AD6-B898-D478B882C63F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="367">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1140,6 +1140,9 @@
   </si>
   <si>
     <t>حديد كحميه 2</t>
+  </si>
+  <si>
+    <t>اسمده</t>
   </si>
 </sst>
 </file>
@@ -2320,14 +2323,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2690,7 +2693,7 @@
       <c r="E2" s="150"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>90.320000000000022</v>
+        <v>86.195000000000022</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6242,29 +6245,29 @@
       </c>
     </row>
     <row r="141" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="142" t="str">
+      <c r="A141" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(136,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B141" s="122" t="str">
+        <v>46258</v>
+      </c>
+      <c r="B141" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(136,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C141" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(136,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D141" s="123" t="str">
+        <v>اسمده</v>
+      </c>
+      <c r="D141" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(136,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E141" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E141" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(136,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F141" s="125" t="str">
+        <v>4.125</v>
+      </c>
+      <c r="F141" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>86.195000000000022</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7943,11 +7946,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>848.11999999999989</v>
+        <v>852.24499999999989</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>90.320000000000022</v>
+        <v>86.195000000000022</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -18535,18 +18538,30 @@
       </c>
     </row>
     <row r="160" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="139"/>
+      <c r="A160" s="139">
+        <v>46258</v>
+      </c>
       <c r="B160" s="36"/>
-      <c r="C160" s="37"/>
-      <c r="D160" s="38"/>
+      <c r="C160" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="D160" s="38">
+        <v>4.125</v>
+      </c>
       <c r="E160" s="39"/>
-      <c r="F160" s="136"/>
-      <c r="G160" s="40"/>
-      <c r="H160" s="41"/>
+      <c r="F160" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G160" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H160" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I160" s="42"/>
-      <c r="J160" s="43" t="str">
+      <c r="J160" s="43">
         <f>IF(AND(D160="",E160="",A160="",B160="",C160=""),"", IFERROR(IF(J159="",D2,J159),D2)+IF(E160="",0,E160)-IF(OR(G160="أبو اسحاق",G160="أبو آدم",G160="أبو اسحاق ",G160="أبو آدم "),0,IF(D160="",0,D160)))</f>
-        <v/>
+        <v>86.195000000000022</v>
       </c>
       <c r="K160" s="44"/>
       <c r="L160" t="str">
@@ -18557,17 +18572,17 @@
         <f>IF(AND(D159&gt;0,G159="المحفظة"),COUNTIFS($D$4:D159,"&gt;"&amp;0,$G$4:G159,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N160" t="str">
+      <c r="N160">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A160)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A160)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A160&lt;&gt;""),IFERROR(MAX($N$4:N159),0)+1,"")</f>
-        <v/>
+        <v>27</v>
       </c>
       <c r="O160">
         <f>IF(AND(D159&gt;0,F159="أحد الشركاء"),COUNTIFS($D$4:D159,"&gt;"&amp;0,$F$4:F159,"أحد الشركاء"),"")</f>
         <v>15</v>
       </c>
-      <c r="P160" t="str">
+      <c r="P160">
         <f>IF(OR($A160="",$F160="أحد الشركاء",AND($D160="",$E160="")),"",SUMPRODUCT(($A$4:$A160&lt;&gt;"")*($F$4:$F160&lt;&gt;"أحد الشركاء")*((($D$4:$D160&lt;&gt;"")+($E$4:$E160&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>136</v>
       </c>
       <c r="Q160" t="str">
         <f>IF(OR($A160="",$F160&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A160,"&lt;&gt;",$F$4:F160,"أحد الشركاء"))</f>
@@ -18593,9 +18608,9 @@
         <f>IF(E160&gt;0,COUNTIF($E$4:E160,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M161" t="str">
+      <c r="M161">
         <f>IF(AND(D160&gt;0,G160="المحفظة"),COUNTIFS($D$4:D160,"&gt;"&amp;0,$G$4:G160,"المحفظة"),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="N161" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A161)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A161)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A161&lt;&gt;""),IFERROR(MAX($N$4:N160),0)+1,"")</f>
@@ -20342,7 +20357,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2629.6200000000003</v>
+        <v>2633.7450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -22019,49 +22034,49 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="139" t="str">
+      <c r="A31" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B31" s="59" t="str">
+        <v>46258</v>
+      </c>
+      <c r="B31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C31" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="38" t="str">
+        <v>اسمده</v>
+      </c>
+      <c r="D31" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="60" t="str">
+        <v>4.125</v>
+      </c>
+      <c r="E31" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H31" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="59" t="str">
+        <v>86.195000000000022</v>
+      </c>
+      <c r="K31" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(27,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27721,7 +27736,7 @@
       <c r="C155" s="156"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>496.32500000000005</v>
+        <v>500.45000000000005</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27736,7 +27751,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-280.07500000000005</v>
+        <v>-284.20000000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27860,7 +27875,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="156"/>
@@ -29171,7 +29186,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="171" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="156"/>
@@ -29185,7 +29200,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="171" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="156"/>
@@ -30496,7 +30511,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173" t="s">
+      <c r="A107" s="171" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="156"/>
@@ -30519,7 +30534,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="172">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30528,17 +30543,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB15F3-66D3-4AD6-B898-D478B882C63F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFDEF08-2133-4097-96B2-89964BA3E0FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="378">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1143,6 +1143,39 @@
   </si>
   <si>
     <t>اسمده</t>
+  </si>
+  <si>
+    <t>Inv-121</t>
+  </si>
+  <si>
+    <t>شركه التهاني</t>
+  </si>
+  <si>
+    <t>تم عمل خصم من ابوادم 3.750</t>
+  </si>
+  <si>
+    <t>, حوض معلق عدد500 (الوحده.170(,بتموس عدد 10 الحبه 15</t>
+  </si>
+  <si>
+    <t>تاير توكتوك</t>
+  </si>
+  <si>
+    <t>Inv-122</t>
+  </si>
+  <si>
+    <t>Inv-123</t>
+  </si>
+  <si>
+    <t>ربل عدد 4 الحبه 2.250</t>
+  </si>
+  <si>
+    <t>Inv-124</t>
+  </si>
+  <si>
+    <t>متنوع عدد 10 الحبه 1</t>
+  </si>
+  <si>
+    <t>هوز اصفر 3/4 طول 50 متر</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2251,6 +2284,9 @@
     </xf>
     <xf numFmtId="168" fontId="41" fillId="48" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2674,45 +2710,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="150"/>
+      <c r="A1" s="153" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="150"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>86.195000000000022</v>
+        <v>117.69500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="154"/>
-      <c r="B3" s="149"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="150"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="151"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="150"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="151"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -6271,185 +6307,185 @@
       </c>
     </row>
     <row r="142" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="142" t="str">
+      <c r="A142" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(137,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46260</v>
       </c>
       <c r="B142" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(137,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-121</v>
       </c>
       <c r="C142" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(137,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D142" s="123" t="str">
+        <v>شركه التهاني</v>
+      </c>
+      <c r="D142" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(137,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E142" s="124" t="str">
+        <v>260</v>
+      </c>
+      <c r="E142" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(137,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F142" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F142" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>346.19500000000005</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="142" t="str">
+      <c r="A143" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(138,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B143" s="122" t="str">
+        <v>46260</v>
+      </c>
+      <c r="B143" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(138,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C143" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(138,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D143" s="123" t="str">
+        <v>, حوض معلق عدد500 (الوحده.170(,بتموس عدد 10 الحبه 15</v>
+      </c>
+      <c r="D143" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(138,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E143" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E143" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(138,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F143" s="125" t="str">
+        <v>243</v>
+      </c>
+      <c r="F143" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>103.19500000000005</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="142" t="str">
+      <c r="A144" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(139,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B144" s="122" t="str">
+        <v>46251</v>
+      </c>
+      <c r="B144" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(139,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C144" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(139,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D144" s="123" t="str">
+        <v>تاير توكتوك</v>
+      </c>
+      <c r="D144" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(139,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E144" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E144" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(139,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F144" s="125" t="str">
+        <v>3</v>
+      </c>
+      <c r="F144" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>100.19500000000005</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="142" t="str">
+      <c r="A145" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(140,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46229</v>
       </c>
       <c r="B145" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(140,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-122</v>
       </c>
       <c r="C145" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(140,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D145" s="123" t="str">
+        <v>متنوع عدد10 الحبه 1</v>
+      </c>
+      <c r="D145" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(140,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E145" s="124" t="str">
+        <v>10</v>
+      </c>
+      <c r="E145" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(140,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F145" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F145" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>110.19500000000005</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="142" t="str">
+      <c r="A146" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(141,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46229</v>
       </c>
       <c r="B146" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(141,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-123</v>
       </c>
       <c r="C146" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(141,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D146" s="123" t="str">
+        <v>ربل عدد 4 الحبه 2.250</v>
+      </c>
+      <c r="D146" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(141,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E146" s="124" t="str">
+        <v>9</v>
+      </c>
+      <c r="E146" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(141,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F146" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F146" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>119.19500000000005</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="142" t="str">
+      <c r="A147" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(142,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46229</v>
       </c>
       <c r="B147" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(142,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-124</v>
       </c>
       <c r="C147" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(142,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D147" s="123" t="str">
+        <v>متنوع عدد 10 الحبه 1</v>
+      </c>
+      <c r="D147" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(142,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E147" s="124" t="str">
+        <v>10</v>
+      </c>
+      <c r="E147" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(142,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F147" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F147" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>129.19500000000005</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="142" t="str">
+      <c r="A148" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(143,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B148" s="122" t="str">
+        <v>46251</v>
+      </c>
+      <c r="B148" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(143,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C148" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(143,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D148" s="123" t="str">
+        <v>هوز اصفر 3/4 طول 50 متر</v>
+      </c>
+      <c r="D148" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(143,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E148" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E148" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(143,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F148" s="125" t="str">
+        <v>11.5</v>
+      </c>
+      <c r="F148" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>117.69500000000005</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7942,26 +7978,26 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>938.44</v>
+        <v>1227.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>852.24499999999989</v>
+        <v>1109.7449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>86.195000000000022</v>
+        <v>117.69500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="148" t="s">
+      <c r="A208" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="149"/>
-      <c r="C208" s="149"/>
-      <c r="D208" s="149"/>
-      <c r="E208" s="149"/>
-      <c r="F208" s="150"/>
+      <c r="B208" s="150"/>
+      <c r="C208" s="150"/>
+      <c r="D208" s="150"/>
+      <c r="E208" s="150"/>
+      <c r="F208" s="151"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10359,38 +10395,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="159" t="s">
+      <c r="E2" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -18590,20 +18626,34 @@
       </c>
     </row>
     <row r="161" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="25"/>
-      <c r="B161" s="26"/>
-      <c r="C161" s="27"/>
+      <c r="A161" s="25">
+        <v>46260</v>
+      </c>
+      <c r="B161" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C161" s="27" t="s">
+        <v>368</v>
+      </c>
       <c r="D161" s="28"/>
-      <c r="E161" s="29"/>
-      <c r="F161" s="30"/>
+      <c r="E161" s="29">
+        <v>260</v>
+      </c>
+      <c r="F161" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G161" s="31"/>
-      <c r="H161" s="32"/>
+      <c r="H161" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I161" s="33"/>
-      <c r="J161" s="34" t="str">
+      <c r="J161" s="34">
         <f>IF(AND(D161="",E161="",A161="",B161="",C161=""),"", IFERROR(IF(J160="",D2,J160),D2)+IF(E161="",0,E161)-IF(OR(G161="أبو اسحاق",G161="أبو آدم",G161="أبو اسحاق ",G161="أبو آدم "),0,IF(D161="",0,D161)))</f>
-        <v/>
-      </c>
-      <c r="K161" s="35"/>
+        <v>346.19500000000005</v>
+      </c>
+      <c r="K161" s="35" t="s">
+        <v>369</v>
+      </c>
       <c r="L161" t="str">
         <f>IF(E160&gt;0,COUNTIF($E$4:E160,"&gt;0"),"")</f>
         <v/>
@@ -18612,57 +18662,69 @@
         <f>IF(AND(D160&gt;0,G160="المحفظة"),COUNTIFS($D$4:D160,"&gt;"&amp;0,$G$4:G160,"المحفظة"),"")</f>
         <v>30</v>
       </c>
-      <c r="N161" t="str">
+      <c r="N161">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A161)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A161)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A161&lt;&gt;""),IFERROR(MAX($N$4:N160),0)+1,"")</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="O161" t="str">
         <f>IF(AND(D160&gt;0,F160="أحد الشركاء"),COUNTIFS($D$4:D160,"&gt;"&amp;0,$F$4:F160,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P161" t="str">
+      <c r="P161">
         <f>IF(OR($A161="",$F161="أحد الشركاء",AND($D161="",$E161="")),"",SUMPRODUCT(($A$4:$A161&lt;&gt;"")*($F$4:$F161&lt;&gt;"أحد الشركاء")*((($D$4:$D161&lt;&gt;"")+($E$4:$E161&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="Q161" t="str">
         <f>IF(OR($A161="",$F161&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A161,"&lt;&gt;",$F$4:F161,"أحد الشركاء"))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="139"/>
+    <row r="162" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="139">
+        <v>46260</v>
+      </c>
       <c r="B162" s="36"/>
-      <c r="C162" s="37"/>
-      <c r="D162" s="38"/>
+      <c r="C162" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="D162" s="38">
+        <v>243</v>
+      </c>
       <c r="E162" s="39"/>
-      <c r="F162" s="136"/>
-      <c r="G162" s="40"/>
-      <c r="H162" s="41"/>
+      <c r="F162" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G162" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H162" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I162" s="42"/>
-      <c r="J162" s="43" t="str">
+      <c r="J162" s="43">
         <f>IF(AND(D162="",E162="",A162="",B162="",C162=""),"", IFERROR(IF(J161="",D2,J161),D2)+IF(E162="",0,E162)-IF(OR(G162="أبو اسحاق",G162="أبو آدم",G162="أبو اسحاق ",G162="أبو آدم "),0,IF(D162="",0,D162)))</f>
-        <v/>
+        <v>103.19500000000005</v>
       </c>
       <c r="K162" s="44"/>
-      <c r="L162" t="str">
+      <c r="L162">
         <f>IF(E161&gt;0,COUNTIF($E$4:E161,"&gt;0"),"")</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="M162" t="str">
         <f>IF(AND(D161&gt;0,G161="المحفظة"),COUNTIFS($D$4:D161,"&gt;"&amp;0,$G$4:G161,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N162" t="str">
+      <c r="N162">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A162)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A162)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A162&lt;&gt;""),IFERROR(MAX($N$4:N161),0)+1,"")</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="O162" t="str">
         <f>IF(AND(D161&gt;0,F161="أحد الشركاء"),COUNTIFS($D$4:D161,"&gt;"&amp;0,$F$4:F161,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P162" t="str">
+      <c r="P162">
         <f>IF(OR($A162="",$F162="أحد الشركاء",AND($D162="",$E162="")),"",SUMPRODUCT(($A$4:$A162&lt;&gt;"")*($F$4:$F162&lt;&gt;"أحد الشركاء")*((($D$4:$D162&lt;&gt;"")+($E$4:$E162&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>138</v>
       </c>
       <c r="Q162" t="str">
         <f>IF(OR($A162="",$F162&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A162,"&lt;&gt;",$F$4:F162,"أحد الشركاء"))</f>
@@ -18670,39 +18732,51 @@
       </c>
     </row>
     <row r="163" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="25"/>
+      <c r="A163" s="25">
+        <v>46251</v>
+      </c>
       <c r="B163" s="26"/>
-      <c r="C163" s="27"/>
-      <c r="D163" s="28"/>
+      <c r="C163" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="D163" s="28">
+        <v>3</v>
+      </c>
       <c r="E163" s="29"/>
-      <c r="F163" s="30"/>
-      <c r="G163" s="31"/>
-      <c r="H163" s="32"/>
+      <c r="F163" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G163" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H163" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I163" s="33"/>
-      <c r="J163" s="34" t="str">
+      <c r="J163" s="34">
         <f>IF(AND(D163="",E163="",A163="",B163="",C163=""),"", IFERROR(IF(J162="",D2,J162),D2)+IF(E163="",0,E163)-IF(OR(G163="أبو اسحاق",G163="أبو آدم",G163="أبو اسحاق ",G163="أبو آدم "),0,IF(D163="",0,D163)))</f>
-        <v/>
+        <v>100.19500000000005</v>
       </c>
       <c r="K163" s="35"/>
       <c r="L163" t="str">
         <f>IF(E162&gt;0,COUNTIF($E$4:E162,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M163" t="str">
+      <c r="M163">
         <f>IF(AND(D162&gt;0,G162="المحفظة"),COUNTIFS($D$4:D162,"&gt;"&amp;0,$G$4:G162,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N163" t="str">
+        <v>31</v>
+      </c>
+      <c r="N163">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A163)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A163)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A163&lt;&gt;""),IFERROR(MAX($N$4:N162),0)+1,"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="O163" t="str">
         <f>IF(AND(D162&gt;0,F162="أحد الشركاء"),COUNTIFS($D$4:D162,"&gt;"&amp;0,$F$4:F162,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P163" t="str">
+      <c r="P163">
         <f>IF(OR($A163="",$F163="أحد الشركاء",AND($D163="",$E163="")),"",SUMPRODUCT(($A$4:$A163&lt;&gt;"")*($F$4:$F163&lt;&gt;"أحد الشركاء")*((($D$4:$D163&lt;&gt;"")+($E$4:$E163&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>139</v>
       </c>
       <c r="Q163" t="str">
         <f>IF(OR($A163="",$F163&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A163,"&lt;&gt;",$F$4:F163,"أحد الشركاء"))</f>
@@ -18710,27 +18784,39 @@
       </c>
     </row>
     <row r="164" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="139"/>
-      <c r="B164" s="36"/>
-      <c r="C164" s="37"/>
+      <c r="A164" s="139">
+        <v>46229</v>
+      </c>
+      <c r="B164" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="C164" s="37" t="s">
+        <v>334</v>
+      </c>
       <c r="D164" s="38"/>
-      <c r="E164" s="39"/>
-      <c r="F164" s="136"/>
+      <c r="E164" s="39">
+        <v>10</v>
+      </c>
+      <c r="F164" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G164" s="40"/>
-      <c r="H164" s="41"/>
+      <c r="H164" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I164" s="42"/>
-      <c r="J164" s="43" t="str">
+      <c r="J164" s="43">
         <f>IF(AND(D164="",E164="",A164="",B164="",C164=""),"", IFERROR(IF(J163="",D2,J163),D2)+IF(E164="",0,E164)-IF(OR(G164="أبو اسحاق",G164="أبو آدم",G164="أبو اسحاق ",G164="أبو آدم "),0,IF(D164="",0,D164)))</f>
-        <v/>
+        <v>110.19500000000005</v>
       </c>
       <c r="K164" s="44"/>
       <c r="L164" t="str">
         <f>IF(E163&gt;0,COUNTIF($E$4:E163,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M164" t="str">
+      <c r="M164">
         <f>IF(AND(D163&gt;0,G163="المحفظة"),COUNTIFS($D$4:D163,"&gt;"&amp;0,$G$4:G163,"المحفظة"),"")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="N164" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A164)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A164)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A164&lt;&gt;""),IFERROR(MAX($N$4:N163),0)+1,"")</f>
@@ -18740,9 +18826,9 @@
         <f>IF(AND(D163&gt;0,F163="أحد الشركاء"),COUNTIFS($D$4:D163,"&gt;"&amp;0,$F$4:F163,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P164" t="str">
+      <c r="P164">
         <f>IF(OR($A164="",$F164="أحد الشركاء",AND($D164="",$E164="")),"",SUMPRODUCT(($A$4:$A164&lt;&gt;"")*($F$4:$F164&lt;&gt;"أحد الشركاء")*((($D$4:$D164&lt;&gt;"")+($E$4:$E164&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>140</v>
       </c>
       <c r="Q164" t="str">
         <f>IF(OR($A164="",$F164&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A164,"&lt;&gt;",$F$4:F164,"أحد الشركاء"))</f>
@@ -18750,23 +18836,35 @@
       </c>
     </row>
     <row r="165" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="25"/>
-      <c r="B165" s="26"/>
-      <c r="C165" s="27"/>
+      <c r="A165" s="148">
+        <v>46229</v>
+      </c>
+      <c r="B165" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="C165" s="27" t="s">
+        <v>374</v>
+      </c>
       <c r="D165" s="28"/>
-      <c r="E165" s="29"/>
-      <c r="F165" s="30"/>
+      <c r="E165" s="29">
+        <v>9</v>
+      </c>
+      <c r="F165" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G165" s="31"/>
-      <c r="H165" s="32"/>
+      <c r="H165" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I165" s="33"/>
-      <c r="J165" s="34" t="str">
+      <c r="J165" s="34">
         <f>IF(AND(D165="",E165="",A165="",B165="",C165=""),"", IFERROR(IF(J164="",D2,J164),D2)+IF(E165="",0,E165)-IF(OR(G165="أبو اسحاق",G165="أبو آدم",G165="أبو اسحاق ",G165="أبو آدم "),0,IF(D165="",0,D165)))</f>
-        <v/>
+        <v>119.19500000000005</v>
       </c>
       <c r="K165" s="35"/>
-      <c r="L165" t="str">
+      <c r="L165">
         <f>IF(E164&gt;0,COUNTIF($E$4:E164,"&gt;0"),"")</f>
-        <v/>
+        <v>108</v>
       </c>
       <c r="M165" t="str">
         <f>IF(AND(D164&gt;0,G164="المحفظة"),COUNTIFS($D$4:D164,"&gt;"&amp;0,$G$4:G164,"المحفظة"),"")</f>
@@ -18780,9 +18878,9 @@
         <f>IF(AND(D164&gt;0,F164="أحد الشركاء"),COUNTIFS($D$4:D164,"&gt;"&amp;0,$F$4:F164,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P165" t="str">
+      <c r="P165">
         <f>IF(OR($A165="",$F165="أحد الشركاء",AND($D165="",$E165="")),"",SUMPRODUCT(($A$4:$A165&lt;&gt;"")*($F$4:$F165&lt;&gt;"أحد الشركاء")*((($D$4:$D165&lt;&gt;"")+($E$4:$E165&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>141</v>
       </c>
       <c r="Q165" t="str">
         <f>IF(OR($A165="",$F165&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A165,"&lt;&gt;",$F$4:F165,"أحد الشركاء"))</f>
@@ -18790,23 +18888,35 @@
       </c>
     </row>
     <row r="166" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="139"/>
-      <c r="B166" s="36"/>
-      <c r="C166" s="37"/>
+      <c r="A166" s="148">
+        <v>46229</v>
+      </c>
+      <c r="B166" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="C166" s="37" t="s">
+        <v>376</v>
+      </c>
       <c r="D166" s="38"/>
-      <c r="E166" s="39"/>
-      <c r="F166" s="136"/>
+      <c r="E166" s="39">
+        <v>10</v>
+      </c>
+      <c r="F166" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G166" s="40"/>
-      <c r="H166" s="41"/>
+      <c r="H166" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I166" s="42"/>
-      <c r="J166" s="43" t="str">
+      <c r="J166" s="43">
         <f>IF(AND(D166="",E166="",A166="",B166="",C166=""),"", IFERROR(IF(J165="",D2,J165),D2)+IF(E166="",0,E166)-IF(OR(G166="أبو اسحاق",G166="أبو آدم",G166="أبو اسحاق ",G166="أبو آدم "),0,IF(D166="",0,D166)))</f>
-        <v/>
+        <v>129.19500000000005</v>
       </c>
       <c r="K166" s="44"/>
-      <c r="L166" t="str">
+      <c r="L166">
         <f>IF(E165&gt;0,COUNTIF($E$4:E165,"&gt;0"),"")</f>
-        <v/>
+        <v>109</v>
       </c>
       <c r="M166" t="str">
         <f>IF(AND(D165&gt;0,G165="المحفظة"),COUNTIFS($D$4:D165,"&gt;"&amp;0,$G$4:G165,"المحفظة"),"")</f>
@@ -18820,9 +18930,9 @@
         <f>IF(AND(D165&gt;0,F165="أحد الشركاء"),COUNTIFS($D$4:D165,"&gt;"&amp;0,$F$4:F165,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P166" t="str">
+      <c r="P166">
         <f>IF(OR($A166="",$F166="أحد الشركاء",AND($D166="",$E166="")),"",SUMPRODUCT(($A$4:$A166&lt;&gt;"")*($F$4:$F166&lt;&gt;"أحد الشركاء")*((($D$4:$D166&lt;&gt;"")+($E$4:$E166&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>142</v>
       </c>
       <c r="Q166" t="str">
         <f>IF(OR($A166="",$F166&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A166,"&lt;&gt;",$F$4:F166,"أحد الشركاء"))</f>
@@ -18830,39 +18940,51 @@
       </c>
     </row>
     <row r="167" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="25"/>
+      <c r="A167" s="25">
+        <v>46251</v>
+      </c>
       <c r="B167" s="26"/>
-      <c r="C167" s="27"/>
-      <c r="D167" s="28"/>
+      <c r="C167" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="D167" s="28">
+        <v>11.5</v>
+      </c>
       <c r="E167" s="29"/>
-      <c r="F167" s="30"/>
-      <c r="G167" s="31"/>
-      <c r="H167" s="32"/>
+      <c r="F167" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G167" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H167" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I167" s="33"/>
-      <c r="J167" s="34" t="str">
+      <c r="J167" s="34">
         <f>IF(AND(D167="",E167="",A167="",B167="",C167=""),"", IFERROR(IF(J166="",D2,J166),D2)+IF(E167="",0,E167)-IF(OR(G167="أبو اسحاق",G167="أبو آدم",G167="أبو اسحاق ",G167="أبو آدم "),0,IF(D167="",0,D167)))</f>
-        <v/>
+        <v>117.69500000000005</v>
       </c>
       <c r="K167" s="35"/>
-      <c r="L167" t="str">
+      <c r="L167">
         <f>IF(E166&gt;0,COUNTIF($E$4:E166,"&gt;0"),"")</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="M167" t="str">
         <f>IF(AND(D166&gt;0,G166="المحفظة"),COUNTIFS($D$4:D166,"&gt;"&amp;0,$G$4:G166,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N167" t="str">
+      <c r="N167">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A167)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A167)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A167&lt;&gt;""),IFERROR(MAX($N$4:N166),0)+1,"")</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="O167" t="str">
         <f>IF(AND(D166&gt;0,F166="أحد الشركاء"),COUNTIFS($D$4:D166,"&gt;"&amp;0,$F$4:F166,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P167" t="str">
+      <c r="P167">
         <f>IF(OR($A167="",$F167="أحد الشركاء",AND($D167="",$E167="")),"",SUMPRODUCT(($A$4:$A167&lt;&gt;"")*($F$4:$F167&lt;&gt;"أحد الشركاء")*((($D$4:$D167&lt;&gt;"")+($E$4:$E167&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>143</v>
       </c>
       <c r="Q167" t="str">
         <f>IF(OR($A167="",$F167&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A167,"&lt;&gt;",$F$4:F167,"أحد الشركاء"))</f>
@@ -18888,9 +19010,9 @@
         <f>IF(E167&gt;0,COUNTIF($E$4:E167,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M168" t="str">
+      <c r="M168">
         <f>IF(AND(D167&gt;0,G167="المحفظة"),COUNTIFS($D$4:D167,"&gt;"&amp;0,$G$4:G167,"المحفظة"),"")</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="N168" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A168)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A168)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A168&lt;&gt;""),IFERROR(MAX($N$4:N167),0)+1,"")</f>
@@ -20310,14 +20432,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="162"/>
-      <c r="B204" s="156"/>
-      <c r="C204" s="157"/>
+      <c r="A204" s="163"/>
+      <c r="B204" s="157"/>
+      <c r="C204" s="158"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="155"/>
-      <c r="G204" s="156"/>
-      <c r="H204" s="157"/>
+      <c r="F204" s="156"/>
+      <c r="G204" s="157"/>
+      <c r="H204" s="158"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -20357,11 +20479,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2633.7450000000003</v>
+        <v>2891.2450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>938.44</v>
+        <v>1227.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -20452,11 +20574,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -20614,16 +20736,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="166" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="156"/>
+      <c r="B1" s="157"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="156"/>
+      <c r="B2" s="157"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -20642,10 +20764,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="165" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="156"/>
+      <c r="B5" s="157"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -20688,10 +20810,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="164" t="s">
+      <c r="A11" s="165" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="156"/>
+      <c r="B11" s="157"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -20756,47 +20878,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="166"/>
-      <c r="B2" s="156"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="157"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="166">
+      <c r="D2" s="167">
         <v>2026</v>
       </c>
-      <c r="E2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="169" t="s">
+      <c r="G2" s="170" t="s">
         <v>257</v>
       </c>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="171" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -22080,187 +22202,187 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="str">
+      <c r="A32" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46260</v>
       </c>
       <c r="B32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-121</v>
       </c>
       <c r="C32" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="28" t="str">
+        <v>شركه التهاني</v>
+      </c>
+      <c r="D32" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="62" t="str">
+        <v>0</v>
+      </c>
+      <c r="E32" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>260</v>
       </c>
       <c r="F32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="61" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G32" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I32" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J32" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>346.19500000000005</v>
       </c>
       <c r="K32" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(28,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>تم عمل خصم من ابوادم 3.750</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="139" t="str">
+      <c r="A33" s="139">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="59" t="str">
+        <v>46260</v>
+      </c>
+      <c r="B33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C33" s="37" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="38" t="str">
+        <v>, حوض معلق عدد500 (الوحده.170(,بتموس عدد 10 الحبه 15</v>
+      </c>
+      <c r="D33" s="38">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="60" t="str">
+        <v>243</v>
+      </c>
+      <c r="E33" s="60">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H33" s="59" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="59" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="43" t="str">
+        <v>0</v>
+      </c>
+      <c r="J33" s="43">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="59" t="str">
+        <v>103.19500000000005</v>
+      </c>
+      <c r="K33" s="59">
         <f>IFERROR(IF(IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(29,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="str">
+      <c r="A34" s="25">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="61" t="str">
+        <v>46251</v>
+      </c>
+      <c r="B34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C34" s="27" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="28" t="str">
+        <v>تاير توكتوك</v>
+      </c>
+      <c r="D34" s="28">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="62" t="str">
+        <v>3</v>
+      </c>
+      <c r="E34" s="62">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H34" s="61" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="61" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="J34" s="34">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="61" t="str">
+        <v>100.19500000000005</v>
+      </c>
+      <c r="K34" s="61">
         <f>IFERROR(IF(IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(30,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="str">
+      <c r="A35" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="64" t="str">
+        <v>46251</v>
+      </c>
+      <c r="B35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C35" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="66" t="str">
+        <v>هوز اصفر 3/4 طول 50 متر</v>
+      </c>
+      <c r="D35" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="67" t="str">
+        <v>11.5</v>
+      </c>
+      <c r="E35" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H35" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J35" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="64" t="str">
+        <v>117.69500000000005</v>
+      </c>
+      <c r="K35" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(31,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27729,29 +27851,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="167" t="s">
+      <c r="A155" s="168" t="s">
         <v>265</v>
       </c>
-      <c r="B155" s="156"/>
-      <c r="C155" s="156"/>
+      <c r="B155" s="157"/>
+      <c r="C155" s="157"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>500.45000000000005</v>
+        <v>757.95</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>216.25</v>
-      </c>
-      <c r="F155" s="168">
+        <v>476.25</v>
+      </c>
+      <c r="F155" s="169">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="156"/>
-      <c r="H155" s="156"/>
+      <c r="G155" s="157"/>
+      <c r="H155" s="157"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-284.20000000000005</v>
+        <v>-281.70000000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27830,60 +27952,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="162" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="167" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="156"/>
+      <c r="B2" s="157"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="166" t="s">
+      <c r="D2" s="167" t="s">
         <v>270</v>
       </c>
-      <c r="E2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="171" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="156"/>
+      <c r="B3" s="157"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="170" t="s">
+      <c r="D3" s="171" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="156"/>
+      <c r="E3" s="157"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="173" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
+      <c r="B4" s="157"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -29186,12 +29308,12 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="173" t="s">
         <v>266</v>
       </c>
-      <c r="B55" s="156"/>
-      <c r="C55" s="156"/>
-      <c r="D55" s="156"/>
+      <c r="B55" s="157"/>
+      <c r="C55" s="157"/>
+      <c r="D55" s="157"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -29200,15 +29322,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="172" t="s">
         <v>275</v>
       </c>
-      <c r="B56" s="156"/>
-      <c r="C56" s="156"/>
-      <c r="D56" s="156"/>
-      <c r="E56" s="156"/>
-      <c r="F56" s="156"/>
-      <c r="G56" s="156"/>
+      <c r="B56" s="157"/>
+      <c r="C56" s="157"/>
+      <c r="D56" s="157"/>
+      <c r="E56" s="157"/>
+      <c r="F56" s="157"/>
+      <c r="G56" s="157"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -30511,11 +30633,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="171" t="s">
+      <c r="A107" s="172" t="s">
         <v>276</v>
       </c>
-      <c r="B107" s="156"/>
-      <c r="C107" s="156"/>
+      <c r="B107" s="157"/>
+      <c r="C107" s="157"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -30525,21 +30647,21 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="167" t="s">
+      <c r="A108" s="168" t="s">
         <v>277</v>
       </c>
-      <c r="B108" s="156"/>
-      <c r="C108" s="156"/>
+      <c r="B108" s="157"/>
+      <c r="C108" s="157"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="174">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="156"/>
-      <c r="G108" s="157"/>
+      <c r="F108" s="157"/>
+      <c r="G108" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFDEF08-2133-4097-96B2-89964BA3E0FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B90A9A1-5051-448E-9B31-CB433FC149E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="380">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1176,6 +1176,12 @@
   </si>
   <si>
     <t>هوز اصفر 3/4 طول 50 متر</t>
+  </si>
+  <si>
+    <t>Inv-125</t>
+  </si>
+  <si>
+    <t>متنوع - تم الدفع 26/8</t>
   </si>
 </sst>
 </file>
@@ -2359,14 +2365,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2729,7 +2735,7 @@
       <c r="E2" s="151"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>117.69500000000005</v>
+        <v>176.69500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6489,29 +6495,29 @@
       </c>
     </row>
     <row r="149" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="142" t="str">
+      <c r="A149" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(144,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="B149" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(144,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-125</v>
       </c>
       <c r="C149" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(144,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D149" s="123" t="str">
+        <v>متنوع - تم الدفع 26/8</v>
+      </c>
+      <c r="D149" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(144,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E149" s="124" t="str">
+        <v>59</v>
+      </c>
+      <c r="E149" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(144,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F149" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F149" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>176.69500000000005</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7978,7 +7984,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>1227.44</v>
+        <v>1286.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -7986,7 +7992,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>117.69500000000005</v>
+        <v>176.69500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -18992,18 +18998,30 @@
       </c>
     </row>
     <row r="168" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="139"/>
-      <c r="B168" s="36"/>
-      <c r="C168" s="37"/>
+      <c r="A168" s="139">
+        <v>46254</v>
+      </c>
+      <c r="B168" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="C168" s="37" t="s">
+        <v>379</v>
+      </c>
       <c r="D168" s="38"/>
-      <c r="E168" s="39"/>
-      <c r="F168" s="136"/>
+      <c r="E168" s="39">
+        <v>59</v>
+      </c>
+      <c r="F168" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G168" s="40"/>
-      <c r="H168" s="41"/>
+      <c r="H168" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I168" s="42"/>
-      <c r="J168" s="43" t="str">
+      <c r="J168" s="43">
         <f>IF(AND(D168="",E168="",A168="",B168="",C168=""),"", IFERROR(IF(J167="",D2,J167),D2)+IF(E168="",0,E168)-IF(OR(G168="أبو اسحاق",G168="أبو آدم",G168="أبو اسحاق ",G168="أبو آدم "),0,IF(D168="",0,D168)))</f>
-        <v/>
+        <v>176.69500000000005</v>
       </c>
       <c r="K168" s="44"/>
       <c r="L168" t="str">
@@ -19014,17 +19032,17 @@
         <f>IF(AND(D167&gt;0,G167="المحفظة"),COUNTIFS($D$4:D167,"&gt;"&amp;0,$G$4:G167,"المحفظة"),"")</f>
         <v>33</v>
       </c>
-      <c r="N168" t="str">
+      <c r="N168">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A168)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A168)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A168&lt;&gt;""),IFERROR(MAX($N$4:N167),0)+1,"")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="O168" t="str">
         <f>IF(AND(D167&gt;0,F167="أحد الشركاء"),COUNTIFS($D$4:D167,"&gt;"&amp;0,$F$4:F167,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P168" t="str">
+      <c r="P168">
         <f>IF(OR($A168="",$F168="أحد الشركاء",AND($D168="",$E168="")),"",SUMPRODUCT(($A$4:$A168&lt;&gt;"")*($F$4:$F168&lt;&gt;"أحد الشركاء")*((($D$4:$D168&lt;&gt;"")+($E$4:$E168&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>144</v>
       </c>
       <c r="Q168" t="str">
         <f>IF(OR($A168="",$F168&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A168,"&lt;&gt;",$F$4:F168,"أحد الشركاء"))</f>
@@ -19046,9 +19064,9 @@
         <v/>
       </c>
       <c r="K169" s="35"/>
-      <c r="L169" t="str">
+      <c r="L169">
         <f>IF(E168&gt;0,COUNTIF($E$4:E168,"&gt;0"),"")</f>
-        <v/>
+        <v>111</v>
       </c>
       <c r="M169" t="str">
         <f>IF(AND(D168&gt;0,G168="المحفظة"),COUNTIFS($D$4:D168,"&gt;"&amp;0,$G$4:G168,"المحفظة"),"")</f>
@@ -20483,7 +20501,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>1227.44</v>
+        <v>1286.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -22386,49 +22404,49 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="str">
+      <c r="A36" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="B36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-125</v>
       </c>
       <c r="C36" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="72" t="str">
+        <v>متنوع - تم الدفع 26/8</v>
+      </c>
+      <c r="D36" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="73" t="str">
+        <v>0</v>
+      </c>
+      <c r="E36" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="F36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="70" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H36" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J36" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="70" t="str">
+        <v>176.69500000000005</v>
+      </c>
+      <c r="K36" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(32,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27862,7 +27880,7 @@
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>476.25</v>
+        <v>535.25</v>
       </c>
       <c r="F155" s="169">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27873,7 +27891,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-281.70000000000005</v>
+        <v>-222.70000000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -27997,7 +28015,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="157"/>
@@ -29308,7 +29326,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="173" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="157"/>
@@ -29322,7 +29340,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="172" t="s">
+      <c r="A56" s="174" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="157"/>
@@ -30633,7 +30651,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="172" t="s">
+      <c r="A107" s="174" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="157"/>
@@ -30656,7 +30674,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="174">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30665,17 +30683,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B90A9A1-5051-448E-9B31-CB433FC149E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4006824-5BC7-4D00-9008-1135611F1B5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="384">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1182,6 +1182,18 @@
   </si>
   <si>
     <t>متنوع - تم الدفع 26/8</t>
+  </si>
+  <si>
+    <t>Inv-126</t>
+  </si>
+  <si>
+    <t>فاتوره لزهور التهاني</t>
+  </si>
+  <si>
+    <t>صبار عدد 15 الحبه 1</t>
+  </si>
+  <si>
+    <t>زيتون عدد 2 الحبه 12</t>
   </si>
 </sst>
 </file>
@@ -2365,14 +2377,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2735,7 +2747,7 @@
       <c r="E2" s="151"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>176.69500000000005</v>
+        <v>537.69500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6521,81 +6533,81 @@
       </c>
     </row>
     <row r="150" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="142" t="str">
+      <c r="A150" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(145,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46263</v>
       </c>
       <c r="B150" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(145,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-126</v>
       </c>
       <c r="C150" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(145,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D150" s="123" t="str">
+        <v>فاتوره لزهور التهاني</v>
+      </c>
+      <c r="D150" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(145,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E150" s="124" t="str">
+        <v>400</v>
+      </c>
+      <c r="E150" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(145,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F150" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F150" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>576.69500000000005</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="142" t="str">
+      <c r="A151" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(146,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B151" s="122" t="str">
+        <v>46263</v>
+      </c>
+      <c r="B151" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(146,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C151" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(146,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D151" s="123" t="str">
+        <v>صبار عدد 15 الحبه 1</v>
+      </c>
+      <c r="D151" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(146,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E151" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E151" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(146,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F151" s="125" t="str">
+        <v>15</v>
+      </c>
+      <c r="F151" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>561.69500000000005</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="142" t="str">
+      <c r="A152" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(147,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B152" s="122" t="str">
+        <v>46263</v>
+      </c>
+      <c r="B152" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(147,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C152" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(147,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D152" s="123" t="str">
+        <v>زيتون عدد 2 الحبه 12</v>
+      </c>
+      <c r="D152" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(147,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E152" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E152" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(147,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F152" s="125" t="str">
+        <v>24</v>
+      </c>
+      <c r="F152" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>537.69500000000005</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7984,15 +7996,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>1286.44</v>
+        <v>1686.44</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1109.7449999999999</v>
+        <v>1148.7449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>176.69500000000005</v>
+        <v>537.69500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19050,18 +19062,30 @@
       </c>
     </row>
     <row r="169" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="25"/>
-      <c r="B169" s="26"/>
-      <c r="C169" s="27"/>
+      <c r="A169" s="25">
+        <v>46263</v>
+      </c>
+      <c r="B169" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="C169" s="27" t="s">
+        <v>381</v>
+      </c>
       <c r="D169" s="28"/>
-      <c r="E169" s="29"/>
-      <c r="F169" s="30"/>
+      <c r="E169" s="29">
+        <v>400</v>
+      </c>
+      <c r="F169" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G169" s="31"/>
-      <c r="H169" s="32"/>
+      <c r="H169" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I169" s="33"/>
-      <c r="J169" s="34" t="str">
+      <c r="J169" s="34">
         <f>IF(AND(D169="",E169="",A169="",B169="",C169=""),"", IFERROR(IF(J168="",D2,J168),D2)+IF(E169="",0,E169)-IF(OR(G169="أبو اسحاق",G169="أبو آدم",G169="أبو اسحاق ",G169="أبو آدم "),0,IF(D169="",0,D169)))</f>
-        <v/>
+        <v>576.69500000000005</v>
       </c>
       <c r="K169" s="35"/>
       <c r="L169">
@@ -19072,17 +19096,17 @@
         <f>IF(AND(D168&gt;0,G168="المحفظة"),COUNTIFS($D$4:D168,"&gt;"&amp;0,$G$4:G168,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N169" t="str">
+      <c r="N169">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A169)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A169)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A169&lt;&gt;""),IFERROR(MAX($N$4:N168),0)+1,"")</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="O169" t="str">
         <f>IF(AND(D168&gt;0,F168="أحد الشركاء"),COUNTIFS($D$4:D168,"&gt;"&amp;0,$F$4:F168,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P169" t="str">
+      <c r="P169">
         <f>IF(OR($A169="",$F169="أحد الشركاء",AND($D169="",$E169="")),"",SUMPRODUCT(($A$4:$A169&lt;&gt;"")*($F$4:$F169&lt;&gt;"أحد الشركاء")*((($D$4:$D169&lt;&gt;"")+($E$4:$E169&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>145</v>
       </c>
       <c r="Q169" t="str">
         <f>IF(OR($A169="",$F169&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A169,"&lt;&gt;",$F$4:F169,"أحد الشركاء"))</f>
@@ -19090,39 +19114,51 @@
       </c>
     </row>
     <row r="170" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="139"/>
+      <c r="A170" s="139">
+        <v>46263</v>
+      </c>
       <c r="B170" s="36"/>
-      <c r="C170" s="37"/>
-      <c r="D170" s="38"/>
+      <c r="C170" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="D170" s="38">
+        <v>15</v>
+      </c>
       <c r="E170" s="39"/>
-      <c r="F170" s="136"/>
-      <c r="G170" s="40"/>
-      <c r="H170" s="41"/>
+      <c r="F170" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G170" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H170" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I170" s="42"/>
-      <c r="J170" s="43" t="str">
+      <c r="J170" s="43">
         <f>IF(AND(D170="",E170="",A170="",B170="",C170=""),"", IFERROR(IF(J169="",D2,J169),D2)+IF(E170="",0,E170)-IF(OR(G170="أبو اسحاق",G170="أبو آدم",G170="أبو اسحاق ",G170="أبو آدم "),0,IF(D170="",0,D170)))</f>
-        <v/>
+        <v>561.69500000000005</v>
       </c>
       <c r="K170" s="44"/>
-      <c r="L170" t="str">
+      <c r="L170">
         <f>IF(E169&gt;0,COUNTIF($E$4:E169,"&gt;0"),"")</f>
-        <v/>
+        <v>112</v>
       </c>
       <c r="M170" t="str">
         <f>IF(AND(D169&gt;0,G169="المحفظة"),COUNTIFS($D$4:D169,"&gt;"&amp;0,$G$4:G169,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N170" t="str">
+      <c r="N170">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A170)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A170)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A170&lt;&gt;""),IFERROR(MAX($N$4:N169),0)+1,"")</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="O170" t="str">
         <f>IF(AND(D169&gt;0,F169="أحد الشركاء"),COUNTIFS($D$4:D169,"&gt;"&amp;0,$F$4:F169,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P170" t="str">
+      <c r="P170">
         <f>IF(OR($A170="",$F170="أحد الشركاء",AND($D170="",$E170="")),"",SUMPRODUCT(($A$4:$A170&lt;&gt;"")*($F$4:$F170&lt;&gt;"أحد الشركاء")*((($D$4:$D170&lt;&gt;"")+($E$4:$E170&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>146</v>
       </c>
       <c r="Q170" t="str">
         <f>IF(OR($A170="",$F170&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A170,"&lt;&gt;",$F$4:F170,"أحد الشركاء"))</f>
@@ -19130,39 +19166,51 @@
       </c>
     </row>
     <row r="171" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="25"/>
+      <c r="A171" s="25">
+        <v>46263</v>
+      </c>
       <c r="B171" s="26"/>
-      <c r="C171" s="27"/>
-      <c r="D171" s="28"/>
+      <c r="C171" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D171" s="28">
+        <v>24</v>
+      </c>
       <c r="E171" s="29"/>
-      <c r="F171" s="30"/>
-      <c r="G171" s="31"/>
-      <c r="H171" s="32"/>
+      <c r="F171" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G171" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H171" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I171" s="33"/>
-      <c r="J171" s="34" t="str">
+      <c r="J171" s="34">
         <f>IF(AND(D171="",E171="",A171="",B171="",C171=""),"", IFERROR(IF(J170="",D2,J170),D2)+IF(E171="",0,E171)-IF(OR(G171="أبو اسحاق",G171="أبو آدم",G171="أبو اسحاق ",G171="أبو آدم "),0,IF(D171="",0,D171)))</f>
-        <v/>
+        <v>537.69500000000005</v>
       </c>
       <c r="K171" s="35"/>
       <c r="L171" t="str">
         <f>IF(E170&gt;0,COUNTIF($E$4:E170,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M171" t="str">
+      <c r="M171">
         <f>IF(AND(D170&gt;0,G170="المحفظة"),COUNTIFS($D$4:D170,"&gt;"&amp;0,$G$4:G170,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N171" t="str">
+        <v>34</v>
+      </c>
+      <c r="N171">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A171)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A171)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A171&lt;&gt;""),IFERROR(MAX($N$4:N170),0)+1,"")</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="O171" t="str">
         <f>IF(AND(D170&gt;0,F170="أحد الشركاء"),COUNTIFS($D$4:D170,"&gt;"&amp;0,$F$4:F170,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P171" t="str">
+      <c r="P171">
         <f>IF(OR($A171="",$F171="أحد الشركاء",AND($D171="",$E171="")),"",SUMPRODUCT(($A$4:$A171&lt;&gt;"")*($F$4:$F171&lt;&gt;"أحد الشركاء")*((($D$4:$D171&lt;&gt;"")+($E$4:$E171&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>147</v>
       </c>
       <c r="Q171" t="str">
         <f>IF(OR($A171="",$F171&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A171,"&lt;&gt;",$F$4:F171,"أحد الشركاء"))</f>
@@ -19188,9 +19236,9 @@
         <f>IF(E171&gt;0,COUNTIF($E$4:E171,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M172" t="str">
+      <c r="M172">
         <f>IF(AND(D171&gt;0,G171="المحفظة"),COUNTIFS($D$4:D171,"&gt;"&amp;0,$G$4:G171,"المحفظة"),"")</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="N172" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A172)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A172)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A172&lt;&gt;""),IFERROR(MAX($N$4:N171),0)+1,"")</f>
@@ -20497,11 +20545,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2891.2450000000003</v>
+        <v>2930.2450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>1286.44</v>
+        <v>1686.44</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -22453,129 +22501,129 @@
       <c r="A37" s="63"/>
       <c r="B37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-126</v>
       </c>
       <c r="C37" s="65"/>
-      <c r="D37" s="66" t="str">
+      <c r="D37" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="64" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H37" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J37" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="64" t="str">
+        <v>576.69500000000005</v>
+      </c>
+      <c r="K37" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(33,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69" t="str">
+      <c r="A38" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B38" s="70" t="str">
+        <v>46263</v>
+      </c>
+      <c r="B38" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C38" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="72" t="str">
+        <v>صبار عدد 15 الحبه 1</v>
+      </c>
+      <c r="D38" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="73" t="str">
+        <v>15</v>
+      </c>
+      <c r="E38" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H38" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I38" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J38" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="70" t="str">
+        <v>561.69500000000005</v>
+      </c>
+      <c r="K38" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(34,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="str">
+      <c r="A39" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B39" s="64" t="str">
+        <v>46263</v>
+      </c>
+      <c r="B39" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C39" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="66" t="str">
+        <v>زيتون عدد 2 الحبه 12</v>
+      </c>
+      <c r="D39" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="E39" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H39" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I39" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J39" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="64" t="str">
+        <v>537.69500000000005</v>
+      </c>
+      <c r="K39" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(35,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27876,7 +27924,7 @@
       <c r="C155" s="157"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>757.95</v>
+        <v>796.95</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -27891,7 +27939,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-222.70000000000005</v>
+        <v>-261.70000000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -28015,7 +28063,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="173" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="157"/>
@@ -29326,7 +29374,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="173" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="157"/>
@@ -29340,7 +29388,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="174" t="s">
+      <c r="A56" s="172" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="157"/>
@@ -30651,7 +30699,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="174" t="s">
+      <c r="A107" s="172" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="157"/>
@@ -30674,7 +30722,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="174">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30683,17 +30731,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4006824-5BC7-4D00-9008-1135611F1B5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0715973-E87E-493D-8EF3-121E5EA68FEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="394">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1194,6 +1194,36 @@
   </si>
   <si>
     <t>زيتون عدد 2 الحبه 12</t>
+  </si>
+  <si>
+    <t>Inv-127</t>
+  </si>
+  <si>
+    <t>اناناس عدد 4 الواحده 4</t>
+  </si>
+  <si>
+    <t>Inv-128</t>
+  </si>
+  <si>
+    <t>ربل عدد 6 الحبه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-129</t>
+  </si>
+  <si>
+    <t>متنوع عدد 17 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-130</t>
+  </si>
+  <si>
+    <t>صبار عدد 13 الحبه 0.750</t>
+  </si>
+  <si>
+    <t>Inv-131</t>
+  </si>
+  <si>
+    <t>تين عدد5 الحبه 1.500</t>
   </si>
 </sst>
 </file>
@@ -2377,14 +2407,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2747,7 +2777,7 @@
       <c r="E2" s="151"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>537.69500000000005</v>
+        <v>602.94500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6611,133 +6641,133 @@
       </c>
     </row>
     <row r="153" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="142" t="str">
+      <c r="A153" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(148,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B153" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(148,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-127</v>
       </c>
       <c r="C153" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(148,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D153" s="123" t="str">
+        <v>اناناس عدد 4 الواحده 4</v>
+      </c>
+      <c r="D153" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(148,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E153" s="124" t="str">
+        <v>16</v>
+      </c>
+      <c r="E153" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(148,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F153" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F153" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>553.69500000000005</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="142" t="str">
+      <c r="A154" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(149,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B154" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(149,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-128</v>
       </c>
       <c r="C154" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(149,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D154" s="123" t="str">
+        <v>ربل عدد 6 الحبه 2.500</v>
+      </c>
+      <c r="D154" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(149,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E154" s="124" t="str">
+        <v>15</v>
+      </c>
+      <c r="E154" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(149,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F154" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F154" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>568.69500000000005</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="142" t="str">
+      <c r="A155" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(150,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B155" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(150,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-129</v>
       </c>
       <c r="C155" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(150,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D155" s="123" t="str">
+        <v>متنوع عدد 17 الحبه 1</v>
+      </c>
+      <c r="D155" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(150,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E155" s="124" t="str">
+        <v>17</v>
+      </c>
+      <c r="E155" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(150,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F155" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F155" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>585.69500000000005</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="142" t="str">
+      <c r="A156" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(151,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B156" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(151,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-130</v>
       </c>
       <c r="C156" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(151,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D156" s="123" t="str">
+        <v>صبار عدد 13 الحبه 0.750</v>
+      </c>
+      <c r="D156" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(151,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E156" s="124" t="str">
+        <v>9.75</v>
+      </c>
+      <c r="E156" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(151,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F156" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F156" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>595.44500000000005</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="142" t="str">
+      <c r="A157" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(152,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B157" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(152,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-131</v>
       </c>
       <c r="C157" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(152,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D157" s="123" t="str">
+        <v>تين عدد5 الحبه 1.500</v>
+      </c>
+      <c r="D157" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(152,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E157" s="124" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="E157" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(152,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F157" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F157" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>602.94500000000005</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7996,7 +8026,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>1686.44</v>
+        <v>1751.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8004,7 +8034,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>537.69500000000005</v>
+        <v>602.94500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19218,18 +19248,30 @@
       </c>
     </row>
     <row r="172" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="139"/>
-      <c r="B172" s="36"/>
-      <c r="C172" s="37"/>
+      <c r="A172" s="139">
+        <v>46264</v>
+      </c>
+      <c r="B172" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="C172" s="37" t="s">
+        <v>385</v>
+      </c>
       <c r="D172" s="38"/>
-      <c r="E172" s="39"/>
-      <c r="F172" s="136"/>
+      <c r="E172" s="39">
+        <v>16</v>
+      </c>
+      <c r="F172" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G172" s="40"/>
-      <c r="H172" s="41"/>
+      <c r="H172" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I172" s="42"/>
-      <c r="J172" s="43" t="str">
+      <c r="J172" s="43">
         <f>IF(AND(D172="",E172="",A172="",B172="",C172=""),"", IFERROR(IF(J171="",D2,J171),D2)+IF(E172="",0,E172)-IF(OR(G172="أبو اسحاق",G172="أبو آدم",G172="أبو اسحاق ",G172="أبو آدم "),0,IF(D172="",0,D172)))</f>
-        <v/>
+        <v>553.69500000000005</v>
       </c>
       <c r="K172" s="44"/>
       <c r="L172" t="str">
@@ -19240,17 +19282,17 @@
         <f>IF(AND(D171&gt;0,G171="المحفظة"),COUNTIFS($D$4:D171,"&gt;"&amp;0,$G$4:G171,"المحفظة"),"")</f>
         <v>35</v>
       </c>
-      <c r="N172" t="str">
+      <c r="N172">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A172)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A172)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A172&lt;&gt;""),IFERROR(MAX($N$4:N171),0)+1,"")</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="O172" t="str">
         <f>IF(AND(D171&gt;0,F171="أحد الشركاء"),COUNTIFS($D$4:D171,"&gt;"&amp;0,$F$4:F171,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P172" t="str">
+      <c r="P172">
         <f>IF(OR($A172="",$F172="أحد الشركاء",AND($D172="",$E172="")),"",SUMPRODUCT(($A$4:$A172&lt;&gt;"")*($F$4:$F172&lt;&gt;"أحد الشركاء")*((($D$4:$D172&lt;&gt;"")+($E$4:$E172&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>148</v>
       </c>
       <c r="Q172" t="str">
         <f>IF(OR($A172="",$F172&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A172,"&lt;&gt;",$F$4:F172,"أحد الشركاء"))</f>
@@ -19258,39 +19300,51 @@
       </c>
     </row>
     <row r="173" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="25"/>
-      <c r="B173" s="26"/>
-      <c r="C173" s="27"/>
+      <c r="A173" s="25">
+        <v>46264</v>
+      </c>
+      <c r="B173" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="C173" s="27" t="s">
+        <v>387</v>
+      </c>
       <c r="D173" s="28"/>
-      <c r="E173" s="29"/>
-      <c r="F173" s="30"/>
+      <c r="E173" s="29">
+        <v>15</v>
+      </c>
+      <c r="F173" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G173" s="31"/>
-      <c r="H173" s="32"/>
+      <c r="H173" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I173" s="33"/>
-      <c r="J173" s="34" t="str">
+      <c r="J173" s="34">
         <f>IF(AND(D173="",E173="",A173="",B173="",C173=""),"", IFERROR(IF(J172="",D2,J172),D2)+IF(E173="",0,E173)-IF(OR(G173="أبو اسحاق",G173="أبو آدم",G173="أبو اسحاق ",G173="أبو آدم "),0,IF(D173="",0,D173)))</f>
-        <v/>
+        <v>568.69500000000005</v>
       </c>
       <c r="K173" s="35"/>
-      <c r="L173" t="str">
+      <c r="L173">
         <f>IF(E172&gt;0,COUNTIF($E$4:E172,"&gt;0"),"")</f>
-        <v/>
+        <v>113</v>
       </c>
       <c r="M173" t="str">
         <f>IF(AND(D172&gt;0,G172="المحفظة"),COUNTIFS($D$4:D172,"&gt;"&amp;0,$G$4:G172,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N173" t="str">
+      <c r="N173">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A173)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A173)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A173&lt;&gt;""),IFERROR(MAX($N$4:N172),0)+1,"")</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="O173" t="str">
         <f>IF(AND(D172&gt;0,F172="أحد الشركاء"),COUNTIFS($D$4:D172,"&gt;"&amp;0,$F$4:F172,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P173" t="str">
+      <c r="P173">
         <f>IF(OR($A173="",$F173="أحد الشركاء",AND($D173="",$E173="")),"",SUMPRODUCT(($A$4:$A173&lt;&gt;"")*($F$4:$F173&lt;&gt;"أحد الشركاء")*((($D$4:$D173&lt;&gt;"")+($E$4:$E173&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="Q173" t="str">
         <f>IF(OR($A173="",$F173&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A173,"&lt;&gt;",$F$4:F173,"أحد الشركاء"))</f>
@@ -19298,39 +19352,51 @@
       </c>
     </row>
     <row r="174" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="139"/>
-      <c r="B174" s="36"/>
-      <c r="C174" s="37"/>
+      <c r="A174" s="139">
+        <v>46264</v>
+      </c>
+      <c r="B174" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="C174" s="37" t="s">
+        <v>389</v>
+      </c>
       <c r="D174" s="38"/>
-      <c r="E174" s="39"/>
-      <c r="F174" s="136"/>
+      <c r="E174" s="39">
+        <v>17</v>
+      </c>
+      <c r="F174" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G174" s="40"/>
-      <c r="H174" s="41"/>
+      <c r="H174" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I174" s="42"/>
-      <c r="J174" s="43" t="str">
+      <c r="J174" s="43">
         <f>IF(AND(D174="",E174="",A174="",B174="",C174=""),"", IFERROR(IF(J173="",D2,J173),D2)+IF(E174="",0,E174)-IF(OR(G174="أبو اسحاق",G174="أبو آدم",G174="أبو اسحاق ",G174="أبو آدم "),0,IF(D174="",0,D174)))</f>
-        <v/>
+        <v>585.69500000000005</v>
       </c>
       <c r="K174" s="44"/>
-      <c r="L174" t="str">
+      <c r="L174">
         <f>IF(E173&gt;0,COUNTIF($E$4:E173,"&gt;0"),"")</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="M174" t="str">
         <f>IF(AND(D173&gt;0,G173="المحفظة"),COUNTIFS($D$4:D173,"&gt;"&amp;0,$G$4:G173,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N174" t="str">
+      <c r="N174">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A174)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A174)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A174&lt;&gt;""),IFERROR(MAX($N$4:N173),0)+1,"")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="O174" t="str">
         <f>IF(AND(D173&gt;0,F173="أحد الشركاء"),COUNTIFS($D$4:D173,"&gt;"&amp;0,$F$4:F173,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P174" t="str">
+      <c r="P174">
         <f>IF(OR($A174="",$F174="أحد الشركاء",AND($D174="",$E174="")),"",SUMPRODUCT(($A$4:$A174&lt;&gt;"")*($F$4:$F174&lt;&gt;"أحد الشركاء")*((($D$4:$D174&lt;&gt;"")+($E$4:$E174&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="Q174" t="str">
         <f>IF(OR($A174="",$F174&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A174,"&lt;&gt;",$F$4:F174,"أحد الشركاء"))</f>
@@ -19338,39 +19404,51 @@
       </c>
     </row>
     <row r="175" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="25"/>
-      <c r="B175" s="26"/>
-      <c r="C175" s="27"/>
+      <c r="A175" s="25">
+        <v>46264</v>
+      </c>
+      <c r="B175" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="C175" s="27" t="s">
+        <v>391</v>
+      </c>
       <c r="D175" s="28"/>
-      <c r="E175" s="29"/>
-      <c r="F175" s="30"/>
+      <c r="E175" s="29">
+        <v>9.75</v>
+      </c>
+      <c r="F175" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G175" s="31"/>
-      <c r="H175" s="32"/>
+      <c r="H175" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I175" s="33"/>
-      <c r="J175" s="34" t="str">
+      <c r="J175" s="34">
         <f>IF(AND(D175="",E175="",A175="",B175="",C175=""),"", IFERROR(IF(J174="",D2,J174),D2)+IF(E175="",0,E175)-IF(OR(G175="أبو اسحاق",G175="أبو آدم",G175="أبو اسحاق ",G175="أبو آدم "),0,IF(D175="",0,D175)))</f>
-        <v/>
+        <v>595.44500000000005</v>
       </c>
       <c r="K175" s="35"/>
-      <c r="L175" t="str">
+      <c r="L175">
         <f>IF(E174&gt;0,COUNTIF($E$4:E174,"&gt;0"),"")</f>
-        <v/>
+        <v>115</v>
       </c>
       <c r="M175" t="str">
         <f>IF(AND(D174&gt;0,G174="المحفظة"),COUNTIFS($D$4:D174,"&gt;"&amp;0,$G$4:G174,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N175" t="str">
+      <c r="N175">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A175)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A175)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A175&lt;&gt;""),IFERROR(MAX($N$4:N174),0)+1,"")</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="O175" t="str">
         <f>IF(AND(D174&gt;0,F174="أحد الشركاء"),COUNTIFS($D$4:D174,"&gt;"&amp;0,$F$4:F174,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P175" t="str">
+      <c r="P175">
         <f>IF(OR($A175="",$F175="أحد الشركاء",AND($D175="",$E175="")),"",SUMPRODUCT(($A$4:$A175&lt;&gt;"")*($F$4:$F175&lt;&gt;"أحد الشركاء")*((($D$4:$D175&lt;&gt;"")+($E$4:$E175&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="Q175" t="str">
         <f>IF(OR($A175="",$F175&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A175,"&lt;&gt;",$F$4:F175,"أحد الشركاء"))</f>
@@ -19378,39 +19456,51 @@
       </c>
     </row>
     <row r="176" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="139"/>
-      <c r="B176" s="36"/>
-      <c r="C176" s="37"/>
+      <c r="A176" s="139">
+        <v>46264</v>
+      </c>
+      <c r="B176" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="C176" s="37" t="s">
+        <v>393</v>
+      </c>
       <c r="D176" s="38"/>
-      <c r="E176" s="39"/>
-      <c r="F176" s="136"/>
+      <c r="E176" s="39">
+        <v>7.5</v>
+      </c>
+      <c r="F176" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G176" s="40"/>
-      <c r="H176" s="41"/>
+      <c r="H176" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I176" s="42"/>
-      <c r="J176" s="43" t="str">
+      <c r="J176" s="43">
         <f>IF(AND(D176="",E176="",A176="",B176="",C176=""),"", IFERROR(IF(J175="",D2,J175),D2)+IF(E176="",0,E176)-IF(OR(G176="أبو اسحاق",G176="أبو آدم",G176="أبو اسحاق ",G176="أبو آدم "),0,IF(D176="",0,D176)))</f>
-        <v/>
+        <v>602.94500000000005</v>
       </c>
       <c r="K176" s="44"/>
-      <c r="L176" t="str">
+      <c r="L176">
         <f>IF(E175&gt;0,COUNTIF($E$4:E175,"&gt;0"),"")</f>
-        <v/>
+        <v>116</v>
       </c>
       <c r="M176" t="str">
         <f>IF(AND(D175&gt;0,G175="المحفظة"),COUNTIFS($D$4:D175,"&gt;"&amp;0,$G$4:G175,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N176" t="str">
+      <c r="N176">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A176)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A176)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A176&lt;&gt;""),IFERROR(MAX($N$4:N175),0)+1,"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="O176" t="str">
         <f>IF(AND(D175&gt;0,F175="أحد الشركاء"),COUNTIFS($D$4:D175,"&gt;"&amp;0,$F$4:F175,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P176" t="str">
+      <c r="P176">
         <f>IF(OR($A176="",$F176="أحد الشركاء",AND($D176="",$E176="")),"",SUMPRODUCT(($A$4:$A176&lt;&gt;"")*($F$4:$F176&lt;&gt;"أحد الشركاء")*((($D$4:$D176&lt;&gt;"")+($E$4:$E176&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>152</v>
       </c>
       <c r="Q176" t="str">
         <f>IF(OR($A176="",$F176&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A176,"&lt;&gt;",$F$4:F176,"أحد الشركاء"))</f>
@@ -19432,9 +19522,9 @@
         <v/>
       </c>
       <c r="K177" s="35"/>
-      <c r="L177" t="str">
+      <c r="L177">
         <f>IF(E176&gt;0,COUNTIF($E$4:E176,"&gt;0"),"")</f>
-        <v/>
+        <v>117</v>
       </c>
       <c r="M177" t="str">
         <f>IF(AND(D176&gt;0,G176="المحفظة"),COUNTIFS($D$4:D176,"&gt;"&amp;0,$G$4:G176,"المحفظة"),"")</f>
@@ -20549,7 +20639,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>1686.44</v>
+        <v>1751.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -22627,233 +22717,233 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="69" t="str">
+      <c r="A40" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-127</v>
       </c>
       <c r="C40" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="72" t="str">
+        <v>اناناس عدد 4 الواحده 4</v>
+      </c>
+      <c r="D40" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="73" t="str">
+        <v>0</v>
+      </c>
+      <c r="E40" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="70" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G40" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I40" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J40" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="70" t="str">
+        <v>553.69500000000005</v>
+      </c>
+      <c r="K40" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(36,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="63" t="str">
+      <c r="A41" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-128</v>
       </c>
       <c r="C41" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="66" t="str">
+        <v>ربل عدد 6 الحبه 2.500</v>
+      </c>
+      <c r="D41" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="E41" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="64" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G41" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I41" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J41" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="64" t="str">
+        <v>568.69500000000005</v>
+      </c>
+      <c r="K41" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(37,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="69" t="str">
+      <c r="A42" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-129</v>
       </c>
       <c r="C42" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="72" t="str">
+        <v>متنوع عدد 17 الحبه 1</v>
+      </c>
+      <c r="D42" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="73" t="str">
+        <v>0</v>
+      </c>
+      <c r="E42" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="70" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G42" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I42" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J42" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="70" t="str">
+        <v>585.69500000000005</v>
+      </c>
+      <c r="K42" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(38,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="63" t="str">
+      <c r="A43" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-130</v>
       </c>
       <c r="C43" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="66" t="str">
+        <v>صبار عدد 13 الحبه 0.750</v>
+      </c>
+      <c r="D43" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="E43" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>9.75</v>
       </c>
       <c r="F43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="64" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G43" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I43" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J43" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="64" t="str">
+        <v>595.44500000000005</v>
+      </c>
+      <c r="K43" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(39,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="69" t="str">
+      <c r="A44" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46264</v>
       </c>
       <c r="B44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-131</v>
       </c>
       <c r="C44" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="72" t="str">
+        <v>تين عدد5 الحبه 1.500</v>
+      </c>
+      <c r="D44" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="73" t="str">
+        <v>0</v>
+      </c>
+      <c r="E44" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>7.5</v>
       </c>
       <c r="F44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="70" t="str">
+        <v>نقداً</v>
+      </c>
+      <c r="G44" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H44" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I44" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J44" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="70" t="str">
+        <v>602.94500000000005</v>
+      </c>
+      <c r="K44" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(40,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27928,7 +28018,7 @@
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>535.25</v>
+        <v>600.5</v>
       </c>
       <c r="F155" s="169">
         <f>COUNTIF(H5:H154,"معلق")</f>
@@ -27939,7 +28029,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-261.70000000000005</v>
+        <v>-196.45000000000005</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -28063,7 +28153,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="172" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="157"/>
@@ -29374,7 +29464,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="173" t="s">
+      <c r="A55" s="172" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="157"/>
@@ -29388,7 +29478,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="172" t="s">
+      <c r="A56" s="174" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="157"/>
@@ -30699,7 +30789,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="172" t="s">
+      <c r="A107" s="174" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="157"/>
@@ -30722,7 +30812,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="174">
+      <c r="E108" s="173">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30731,17 +30821,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0715973-E87E-493D-8EF3-121E5EA68FEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723839B-100D-48F4-A76B-65DB5F53D8CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="396">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1224,6 +1224,12 @@
   </si>
   <si>
     <t>تين عدد5 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>أقامه نزمول 3 سنوات</t>
+  </si>
+  <si>
+    <t>رواتب + كهرباء وماء</t>
   </si>
 </sst>
 </file>
@@ -2407,14 +2413,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2777,7 +2783,7 @@
       <c r="E2" s="151"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>602.94500000000005</v>
+        <v>97.94500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6771,55 +6777,55 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="142" t="str">
+      <c r="A158" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(153,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B158" s="122" t="str">
+        <v>46264</v>
+      </c>
+      <c r="B158" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(153,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C158" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(153,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D158" s="123" t="str">
+        <v>أقامه نزمول 3 سنوات</v>
+      </c>
+      <c r="D158" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(153,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E158" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E158" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(153,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F158" s="125" t="str">
+        <v>35</v>
+      </c>
+      <c r="F158" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>567.94500000000005</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="142" t="str">
+      <c r="A159" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(154,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B159" s="122" t="str">
+        <v>46265</v>
+      </c>
+      <c r="B159" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(154,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C159" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(154,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D159" s="123" t="str">
+        <v>رواتب + كهرباء وماء</v>
+      </c>
+      <c r="D159" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(154,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E159" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E159" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(154,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F159" s="125" t="str">
+        <v>470</v>
+      </c>
+      <c r="F159" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>97.94500000000005</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8030,11 +8036,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1148.7449999999999</v>
+        <v>1653.7449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>602.94500000000005</v>
+        <v>97.94500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19508,18 +19514,30 @@
       </c>
     </row>
     <row r="177" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="25"/>
+      <c r="A177" s="25">
+        <v>46264</v>
+      </c>
       <c r="B177" s="26"/>
-      <c r="C177" s="27"/>
-      <c r="D177" s="28"/>
+      <c r="C177" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="D177" s="28">
+        <v>35</v>
+      </c>
       <c r="E177" s="29"/>
-      <c r="F177" s="30"/>
-      <c r="G177" s="31"/>
-      <c r="H177" s="32"/>
+      <c r="F177" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G177" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H177" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I177" s="33"/>
-      <c r="J177" s="34" t="str">
+      <c r="J177" s="34">
         <f>IF(AND(D177="",E177="",A177="",B177="",C177=""),"", IFERROR(IF(J176="",D2,J176),D2)+IF(E177="",0,E177)-IF(OR(G177="أبو اسحاق",G177="أبو آدم",G177="أبو اسحاق ",G177="أبو آدم "),0,IF(D177="",0,D177)))</f>
-        <v/>
+        <v>567.94500000000005</v>
       </c>
       <c r="K177" s="35"/>
       <c r="L177">
@@ -19530,17 +19548,17 @@
         <f>IF(AND(D176&gt;0,G176="المحفظة"),COUNTIFS($D$4:D176,"&gt;"&amp;0,$G$4:G176,"المحفظة"),"")</f>
         <v/>
       </c>
-      <c r="N177" t="str">
+      <c r="N177">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A177)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A177)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A177&lt;&gt;""),IFERROR(MAX($N$4:N176),0)+1,"")</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="O177" t="str">
         <f>IF(AND(D176&gt;0,F176="أحد الشركاء"),COUNTIFS($D$4:D176,"&gt;"&amp;0,$F$4:F176,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P177" t="str">
+      <c r="P177">
         <f>IF(OR($A177="",$F177="أحد الشركاء",AND($D177="",$E177="")),"",SUMPRODUCT(($A$4:$A177&lt;&gt;"")*($F$4:$F177&lt;&gt;"أحد الشركاء")*((($D$4:$D177&lt;&gt;"")+($E$4:$E177&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="Q177" t="str">
         <f>IF(OR($A177="",$F177&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A177,"&lt;&gt;",$F$4:F177,"أحد الشركاء"))</f>
@@ -19548,39 +19566,51 @@
       </c>
     </row>
     <row r="178" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="139"/>
+      <c r="A178" s="139">
+        <v>46265</v>
+      </c>
       <c r="B178" s="36"/>
-      <c r="C178" s="37"/>
-      <c r="D178" s="38"/>
+      <c r="C178" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="D178" s="38">
+        <v>470</v>
+      </c>
       <c r="E178" s="39"/>
-      <c r="F178" s="136"/>
-      <c r="G178" s="40"/>
-      <c r="H178" s="41"/>
+      <c r="F178" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G178" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H178" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I178" s="42"/>
-      <c r="J178" s="43" t="str">
+      <c r="J178" s="43">
         <f>IF(AND(D178="",E178="",A178="",B178="",C178=""),"", IFERROR(IF(J177="",D2,J177),D2)+IF(E178="",0,E178)-IF(OR(G178="أبو اسحاق",G178="أبو آدم",G178="أبو اسحاق ",G178="أبو آدم "),0,IF(D178="",0,D178)))</f>
-        <v/>
+        <v>97.94500000000005</v>
       </c>
       <c r="K178" s="44"/>
       <c r="L178" t="str">
         <f>IF(E177&gt;0,COUNTIF($E$4:E177,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M178" t="str">
+      <c r="M178">
         <f>IF(AND(D177&gt;0,G177="المحفظة"),COUNTIFS($D$4:D177,"&gt;"&amp;0,$G$4:G177,"المحفظة"),"")</f>
-        <v/>
-      </c>
-      <c r="N178" t="str">
+        <v>36</v>
+      </c>
+      <c r="N178">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A178)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A178)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A178&lt;&gt;""),IFERROR(MAX($N$4:N177),0)+1,"")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="O178" t="str">
         <f>IF(AND(D177&gt;0,F177="أحد الشركاء"),COUNTIFS($D$4:D177,"&gt;"&amp;0,$F$4:F177,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P178" t="str">
+      <c r="P178">
         <f>IF(OR($A178="",$F178="أحد الشركاء",AND($D178="",$E178="")),"",SUMPRODUCT(($A$4:$A178&lt;&gt;"")*($F$4:$F178&lt;&gt;"أحد الشركاء")*((($D$4:$D178&lt;&gt;"")+($E$4:$E178&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>154</v>
       </c>
       <c r="Q178" t="str">
         <f>IF(OR($A178="",$F178&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A178,"&lt;&gt;",$F$4:F178,"أحد الشركاء"))</f>
@@ -19606,9 +19636,9 @@
         <f>IF(E178&gt;0,COUNTIF($E$4:E178,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M179" t="str">
+      <c r="M179">
         <f>IF(AND(D178&gt;0,G178="المحفظة"),COUNTIFS($D$4:D178,"&gt;"&amp;0,$G$4:G178,"المحفظة"),"")</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="N179" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A179)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A179)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A179&lt;&gt;""),IFERROR(MAX($N$4:N178),0)+1,"")</f>
@@ -20635,7 +20665,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>2930.2450000000003</v>
+        <v>3435.2450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -22947,95 +22977,95 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="63" t="str">
+      <c r="A45" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B45" s="64" t="str">
+        <v>46264</v>
+      </c>
+      <c r="B45" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C45" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="66" t="str">
+        <v>أقامه نزمول 3 سنوات</v>
+      </c>
+      <c r="D45" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="67" t="str">
+        <v>35</v>
+      </c>
+      <c r="E45" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H45" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I45" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J45" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="64" t="str">
+        <v>567.94500000000005</v>
+      </c>
+      <c r="K45" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(41,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="69" t="str">
+      <c r="A46" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B46" s="70" t="str">
+        <v>46265</v>
+      </c>
+      <c r="B46" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C46" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="72" t="str">
+        <v>رواتب + كهرباء وماء</v>
+      </c>
+      <c r="D46" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="73" t="str">
+        <v>470</v>
+      </c>
+      <c r="E46" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>نقداً</v>
       </c>
       <c r="G46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H46" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I46" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J46" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="70" t="str">
+        <v>97.94500000000005</v>
+      </c>
+      <c r="K46" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(42,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28014,7 +28044,7 @@
       <c r="C155" s="157"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>796.95</v>
+        <v>1301.95</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
@@ -28029,7 +28059,7 @@
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-196.45000000000005</v>
+        <v>-701.45</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -28153,7 +28183,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="173" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="157"/>
@@ -29464,7 +29494,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="173" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="157"/>
@@ -29478,7 +29508,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="174" t="s">
+      <c r="A56" s="172" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="157"/>
@@ -30789,7 +30819,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="174" t="s">
+      <c r="A107" s="172" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="157"/>
@@ -30812,7 +30842,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="173">
+      <c r="E108" s="174">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30821,17 +30851,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723839B-100D-48F4-A76B-65DB5F53D8CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DB5B8E-9109-4CE9-9AE1-A405403A964F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="397">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1230,6 +1230,9 @@
   </si>
   <si>
     <t>رواتب + كهرباء وماء</t>
+  </si>
+  <si>
+    <t>نصف قيمه فلتر المالج</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2354,6 +2357,9 @@
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="46" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -2413,14 +2419,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2764,45 +2770,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="A1" s="154" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="151"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="152"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>97.94500000000005</v>
+        <v>35.44500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="155"/>
-      <c r="B3" s="150"/>
-      <c r="C3" s="150"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="151"/>
+      <c r="A3" s="156"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="152"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="154" t="s">
+      <c r="A4" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="150"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="151"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="152"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -6829,29 +6835,29 @@
       </c>
     </row>
     <row r="160" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="142" t="str">
+      <c r="A160" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(155,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B160" s="122" t="str">
+        <v>46265</v>
+      </c>
+      <c r="B160" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(155,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C160" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(155,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D160" s="123" t="str">
+        <v>نصف قيمه فلتر المالج</v>
+      </c>
+      <c r="D160" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(155,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E160" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E160" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(155,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F160" s="125" t="str">
+        <v>62.5</v>
+      </c>
+      <c r="F160" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>35.44500000000005</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8036,22 +8042,22 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1653.7449999999999</v>
+        <v>1716.2449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>97.94500000000005</v>
+        <v>35.44500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="149" t="s">
+      <c r="A208" s="150" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="150"/>
-      <c r="C208" s="150"/>
-      <c r="D208" s="150"/>
-      <c r="E208" s="150"/>
-      <c r="F208" s="151"/>
+      <c r="B208" s="151"/>
+      <c r="C208" s="151"/>
+      <c r="D208" s="151"/>
+      <c r="E208" s="151"/>
+      <c r="F208" s="152"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10449,38 +10455,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="160" t="s">
+      <c r="E2" s="161" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -19618,18 +19624,28 @@
       </c>
     </row>
     <row r="179" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="25"/>
+      <c r="A179" s="149">
+        <v>46265</v>
+      </c>
       <c r="B179" s="26"/>
-      <c r="C179" s="27"/>
-      <c r="D179" s="28"/>
+      <c r="C179" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="D179" s="28">
+        <v>62.5</v>
+      </c>
       <c r="E179" s="29"/>
       <c r="F179" s="30"/>
-      <c r="G179" s="31"/>
-      <c r="H179" s="32"/>
+      <c r="G179" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H179" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I179" s="33"/>
-      <c r="J179" s="34" t="str">
+      <c r="J179" s="34">
         <f>IF(AND(D179="",E179="",A179="",B179="",C179=""),"", IFERROR(IF(J178="",D2,J178),D2)+IF(E179="",0,E179)-IF(OR(G179="أبو اسحاق",G179="أبو آدم",G179="أبو اسحاق ",G179="أبو آدم "),0,IF(D179="",0,D179)))</f>
-        <v/>
+        <v>35.44500000000005</v>
       </c>
       <c r="K179" s="35"/>
       <c r="L179" t="str">
@@ -19640,17 +19656,17 @@
         <f>IF(AND(D178&gt;0,G178="المحفظة"),COUNTIFS($D$4:D178,"&gt;"&amp;0,$G$4:G178,"المحفظة"),"")</f>
         <v>37</v>
       </c>
-      <c r="N179" t="str">
+      <c r="N179">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A179)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A179)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A179&lt;&gt;""),IFERROR(MAX($N$4:N178),0)+1,"")</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="O179" t="str">
         <f>IF(AND(D178&gt;0,F178="أحد الشركاء"),COUNTIFS($D$4:D178,"&gt;"&amp;0,$F$4:F178,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P179" t="str">
+      <c r="P179">
         <f>IF(OR($A179="",$F179="أحد الشركاء",AND($D179="",$E179="")),"",SUMPRODUCT(($A$4:$A179&lt;&gt;"")*($F$4:$F179&lt;&gt;"أحد الشركاء")*((($D$4:$D179&lt;&gt;"")+($E$4:$E179&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>155</v>
       </c>
       <c r="Q179" t="str">
         <f>IF(OR($A179="",$F179&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A179,"&lt;&gt;",$F$4:F179,"أحد الشركاء"))</f>
@@ -19676,9 +19692,9 @@
         <f>IF(E179&gt;0,COUNTIF($E$4:E179,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M180" t="str">
+      <c r="M180">
         <f>IF(AND(D179&gt;0,G179="المحفظة"),COUNTIFS($D$4:D179,"&gt;"&amp;0,$G$4:G179,"المحفظة"),"")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="N180" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A180)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A180)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A180&lt;&gt;""),IFERROR(MAX($N$4:N179),0)+1,"")</f>
@@ -20618,14 +20634,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="163"/>
-      <c r="B204" s="157"/>
-      <c r="C204" s="158"/>
+      <c r="A204" s="164"/>
+      <c r="B204" s="158"/>
+      <c r="C204" s="159"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="156"/>
-      <c r="G204" s="157"/>
-      <c r="H204" s="158"/>
+      <c r="F204" s="157"/>
+      <c r="G204" s="158"/>
+      <c r="H204" s="159"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -20665,7 +20681,7 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>3435.2450000000003</v>
+        <v>3497.7450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
@@ -20760,11 +20776,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="165" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -20922,16 +20938,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="167" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="157"/>
+      <c r="B1" s="158"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="166" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="157"/>
+      <c r="B2" s="158"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -20950,10 +20966,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="166" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="157"/>
+      <c r="B5" s="158"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -20996,10 +21012,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="165" t="s">
+      <c r="A11" s="166" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="157"/>
+      <c r="B11" s="158"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -21064,47 +21080,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="167"/>
-      <c r="B2" s="157"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="158"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="167">
+      <c r="D2" s="168">
         <v>2026</v>
       </c>
-      <c r="E2" s="157"/>
+      <c r="E2" s="158"/>
       <c r="F2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="171" t="s">
         <v>257</v>
       </c>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="172" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -23069,49 +23085,49 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="str">
+      <c r="A47" s="63">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="64" t="str">
+        <v>46265</v>
+      </c>
+      <c r="B47" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C47" s="65" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="66" t="str">
+        <v>نصف قيمه فلتر المالج</v>
+      </c>
+      <c r="D47" s="66">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="67" t="str">
+        <v>62.5</v>
+      </c>
+      <c r="E47" s="67">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="64" t="str">
+        <v>0</v>
+      </c>
+      <c r="F47" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>المحفظة</v>
       </c>
       <c r="H47" s="64" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="64" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I47" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J47" s="68">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="64" t="str">
+        <v>35.44500000000005</v>
+      </c>
+      <c r="K47" s="64">
         <f>IFERROR(IF(IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(43,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28037,29 +28053,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="168" t="s">
+      <c r="A155" s="169" t="s">
         <v>265</v>
       </c>
-      <c r="B155" s="157"/>
-      <c r="C155" s="157"/>
+      <c r="B155" s="158"/>
+      <c r="C155" s="158"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
-        <v>1301.95</v>
+        <v>1364.45</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
         <v>600.5</v>
       </c>
-      <c r="F155" s="169">
+      <c r="F155" s="170">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="157"/>
-      <c r="H155" s="157"/>
+      <c r="G155" s="158"/>
+      <c r="H155" s="158"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-701.45</v>
+        <v>-763.95</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -28138,45 +28154,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="163" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="168" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="157"/>
+      <c r="B2" s="158"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="167" t="s">
+      <c r="D2" s="168" t="s">
         <v>270</v>
       </c>
-      <c r="E2" s="157"/>
+      <c r="E2" s="158"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="172" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="157"/>
+      <c r="B3" s="158"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="171" t="s">
+      <c r="D3" s="172" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="157"/>
+      <c r="E3" s="158"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
@@ -28186,12 +28202,12 @@
       <c r="A4" s="173" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -29497,9 +29513,9 @@
       <c r="A55" s="173" t="s">
         <v>266</v>
       </c>
-      <c r="B55" s="157"/>
-      <c r="C55" s="157"/>
-      <c r="D55" s="157"/>
+      <c r="B55" s="158"/>
+      <c r="C55" s="158"/>
+      <c r="D55" s="158"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -29508,15 +29524,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="172" t="s">
+      <c r="A56" s="175" t="s">
         <v>275</v>
       </c>
-      <c r="B56" s="157"/>
-      <c r="C56" s="157"/>
-      <c r="D56" s="157"/>
-      <c r="E56" s="157"/>
-      <c r="F56" s="157"/>
-      <c r="G56" s="157"/>
+      <c r="B56" s="158"/>
+      <c r="C56" s="158"/>
+      <c r="D56" s="158"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="158"/>
+      <c r="G56" s="158"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -30819,11 +30835,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="172" t="s">
+      <c r="A107" s="175" t="s">
         <v>276</v>
       </c>
-      <c r="B107" s="157"/>
-      <c r="C107" s="157"/>
+      <c r="B107" s="158"/>
+      <c r="C107" s="158"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -30833,11 +30849,11 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="168" t="s">
+      <c r="A108" s="169" t="s">
         <v>277</v>
       </c>
-      <c r="B108" s="157"/>
-      <c r="C108" s="157"/>
+      <c r="B108" s="158"/>
+      <c r="C108" s="158"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
@@ -30846,22 +30862,22 @@
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="157"/>
-      <c r="G108" s="158"/>
+      <c r="F108" s="158"/>
+      <c r="G108" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DB5B8E-9109-4CE9-9AE1-A405403A964F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36935F-A8B7-4CD9-A5DF-2C98504C78FF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="398">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1233,6 +1233,9 @@
   </si>
   <si>
     <t>نصف قيمه فلتر المالج</t>
+  </si>
+  <si>
+    <t>Inv-132</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2360,6 +2363,9 @@
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="46" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -2419,14 +2425,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2770,45 +2776,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="154" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="152"/>
+      <c r="A1" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="153"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="152"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>35.44500000000005</v>
+        <v>37.44500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="156"/>
-      <c r="B3" s="151"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="152"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="152"/>
+      <c r="F3" s="153"/>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="152"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="153"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="120" t="s">
@@ -6861,29 +6867,29 @@
       </c>
     </row>
     <row r="161" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="142" t="str">
+      <c r="A161" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(156,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46265</v>
       </c>
       <c r="B161" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(156,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-132</v>
       </c>
       <c r="C161" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(156,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D161" s="123" t="str">
+        <v>ودليه عدد 2 الحبه 1</v>
+      </c>
+      <c r="D161" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(156,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E161" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E161" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(156,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F161" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F161" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>37.44500000000005</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8038,7 +8044,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>1751.69</v>
+        <v>1753.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8046,18 +8052,18 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>35.44500000000005</v>
+        <v>37.44500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="150" t="s">
+      <c r="A208" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="151"/>
-      <c r="C208" s="151"/>
-      <c r="D208" s="151"/>
-      <c r="E208" s="151"/>
-      <c r="F208" s="152"/>
+      <c r="B208" s="152"/>
+      <c r="C208" s="152"/>
+      <c r="D208" s="152"/>
+      <c r="E208" s="152"/>
+      <c r="F208" s="153"/>
     </row>
     <row r="209" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="131" t="s">
@@ -10455,38 +10461,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="161" t="s">
+      <c r="E2" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -19674,18 +19680,30 @@
       </c>
     </row>
     <row r="180" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="139"/>
-      <c r="B180" s="36"/>
-      <c r="C180" s="37"/>
+      <c r="A180" s="150">
+        <v>46265</v>
+      </c>
+      <c r="B180" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="C180" s="37" t="s">
+        <v>121</v>
+      </c>
       <c r="D180" s="38"/>
-      <c r="E180" s="39"/>
-      <c r="F180" s="136"/>
+      <c r="E180" s="39">
+        <v>2</v>
+      </c>
+      <c r="F180" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G180" s="40"/>
-      <c r="H180" s="41"/>
+      <c r="H180" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I180" s="42"/>
-      <c r="J180" s="43" t="str">
+      <c r="J180" s="43">
         <f>IF(AND(D180="",E180="",A180="",B180="",C180=""),"", IFERROR(IF(J179="",D2,J179),D2)+IF(E180="",0,E180)-IF(OR(G180="أبو اسحاق",G180="أبو آدم",G180="أبو اسحاق ",G180="أبو آدم "),0,IF(D180="",0,D180)))</f>
-        <v/>
+        <v>37.44500000000005</v>
       </c>
       <c r="K180" s="44"/>
       <c r="L180" t="str">
@@ -19696,17 +19714,17 @@
         <f>IF(AND(D179&gt;0,G179="المحفظة"),COUNTIFS($D$4:D179,"&gt;"&amp;0,$G$4:G179,"المحفظة"),"")</f>
         <v>38</v>
       </c>
-      <c r="N180" t="str">
+      <c r="N180">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A180)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A180)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A180&lt;&gt;""),IFERROR(MAX($N$4:N179),0)+1,"")</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="O180" t="str">
         <f>IF(AND(D179&gt;0,F179="أحد الشركاء"),COUNTIFS($D$4:D179,"&gt;"&amp;0,$F$4:F179,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P180" t="str">
+      <c r="P180">
         <f>IF(OR($A180="",$F180="أحد الشركاء",AND($D180="",$E180="")),"",SUMPRODUCT(($A$4:$A180&lt;&gt;"")*($F$4:$F180&lt;&gt;"أحد الشركاء")*((($D$4:$D180&lt;&gt;"")+($E$4:$E180&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>156</v>
       </c>
       <c r="Q180" t="str">
         <f>IF(OR($A180="",$F180&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A180,"&lt;&gt;",$F$4:F180,"أحد الشركاء"))</f>
@@ -19728,9 +19746,9 @@
         <v/>
       </c>
       <c r="K181" s="35"/>
-      <c r="L181" t="str">
+      <c r="L181">
         <f>IF(E180&gt;0,COUNTIF($E$4:E180,"&gt;0"),"")</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="M181" t="str">
         <f>IF(AND(D180&gt;0,G180="المحفظة"),COUNTIFS($D$4:D180,"&gt;"&amp;0,$G$4:G180,"المحفظة"),"")</f>
@@ -20634,14 +20652,14 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="164"/>
-      <c r="B204" s="158"/>
-      <c r="C204" s="159"/>
+      <c r="A204" s="165"/>
+      <c r="B204" s="159"/>
+      <c r="C204" s="160"/>
       <c r="D204" s="38"/>
       <c r="E204" s="39"/>
-      <c r="F204" s="157"/>
-      <c r="G204" s="158"/>
-      <c r="H204" s="159"/>
+      <c r="F204" s="158"/>
+      <c r="G204" s="159"/>
+      <c r="H204" s="160"/>
       <c r="I204" s="42"/>
       <c r="J204" s="43" t="str">
         <f>IF(AND(D203="",E203="",A203="",B203="",C203=""),"", IFERROR(IF(J202="",D2,J202),D2)+IF(E203="",0,E203)-IF(D203="",0,D203))</f>
@@ -20685,7 +20703,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>1751.69</v>
+        <v>1753.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -20776,11 +20794,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="166" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -20938,16 +20956,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="168" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="158"/>
+      <c r="B1" s="159"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="167" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="158"/>
+      <c r="B2" s="159"/>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
@@ -20966,10 +20984,10 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="166" t="s">
+      <c r="A5" s="167" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -21012,10 +21030,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="166" t="s">
+      <c r="A11" s="167" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="158"/>
+      <c r="B11" s="159"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
@@ -21080,47 +21098,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168"/>
-      <c r="B2" s="158"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="159"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="168">
+      <c r="D2" s="169">
         <v>2026</v>
       </c>
-      <c r="E2" s="158"/>
+      <c r="E2" s="159"/>
       <c r="F2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="171" t="s">
+      <c r="G2" s="172" t="s">
         <v>257</v>
       </c>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="172" t="s">
+      <c r="A3" s="173" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
       <c r="D3" s="57">
         <f>'كشف الحساب'!$D$2</f>
         <v>0</v>
@@ -23131,49 +23149,49 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="69" t="str">
+      <c r="A48" s="69">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$A$4:$A$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>46265</v>
       </c>
       <c r="B48" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$B$4:$B$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>Inv-132</v>
       </c>
       <c r="C48" s="71" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$C$4:$C$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="72" t="str">
+        <v>ودليه عدد 2 الحبه 1</v>
+      </c>
+      <c r="D48" s="72">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$D$4:$D$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="73" t="str">
+        <v>0</v>
+      </c>
+      <c r="E48" s="73">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$E$4:$E$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F48" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$F$4:$F$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="70" t="str">
+        <v>أون لاين</v>
+      </c>
+      <c r="G48" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$G$4:$G$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="70" t="str">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$H$4:$H$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="70" t="str">
+        <v>تم الدفع</v>
+      </c>
+      <c r="I48" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$I$4:$I$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J48" s="74">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$J$4:$J$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="70" t="str">
+        <v>37.44500000000005</v>
+      </c>
+      <c r="K48" s="70">
         <f>IFERROR(IF(IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0)=0,"",INDEX('كشف الحساب'!$K$4:$K$203,IFERROR(MATCH(44,'كشف الحساب'!$N$4:$N$203,0),0))),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28053,29 +28071,29 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="169" t="s">
+      <c r="A155" s="170" t="s">
         <v>265</v>
       </c>
-      <c r="B155" s="158"/>
-      <c r="C155" s="158"/>
+      <c r="B155" s="159"/>
+      <c r="C155" s="159"/>
       <c r="D155" s="75">
         <f>SUM(D5:D154)</f>
         <v>1364.45</v>
       </c>
       <c r="E155" s="75">
         <f>SUM(E5:E154)</f>
-        <v>600.5</v>
-      </c>
-      <c r="F155" s="170">
+        <v>602.5</v>
+      </c>
+      <c r="F155" s="171">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
-      <c r="G155" s="158"/>
-      <c r="H155" s="158"/>
+      <c r="G155" s="159"/>
+      <c r="H155" s="159"/>
       <c r="I155" s="76"/>
       <c r="J155" s="75">
         <f>E155-D155</f>
-        <v>-763.95</v>
+        <v>-761.95</v>
       </c>
       <c r="K155" s="76"/>
     </row>
@@ -28154,60 +28172,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="169" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="158"/>
+      <c r="B2" s="159"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="168" t="s">
+      <c r="D2" s="169" t="s">
         <v>270</v>
       </c>
-      <c r="E2" s="158"/>
+      <c r="E2" s="159"/>
       <c r="F2" s="56">
         <v>2026</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="172" t="s">
+      <c r="A3" s="173" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="158"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="57">
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="172" t="s">
+      <c r="D3" s="173" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="158"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="78">
         <f>المحفظة!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="175" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -29510,12 +29528,12 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="173" t="s">
+      <c r="A55" s="175" t="s">
         <v>266</v>
       </c>
-      <c r="B55" s="158"/>
-      <c r="C55" s="158"/>
-      <c r="D55" s="158"/>
+      <c r="B55" s="159"/>
+      <c r="C55" s="159"/>
+      <c r="D55" s="159"/>
       <c r="E55" s="141">
         <f>SUMIF(المحفظة!$H$5:$H$104,"&gt;0",المحفظة!$E$5:$E$104)</f>
         <v>0</v>
@@ -29524,15 +29542,15 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="175" t="s">
+      <c r="A56" s="174" t="s">
         <v>275</v>
       </c>
-      <c r="B56" s="158"/>
-      <c r="C56" s="158"/>
-      <c r="D56" s="158"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="158"/>
-      <c r="G56" s="158"/>
+      <c r="B56" s="159"/>
+      <c r="C56" s="159"/>
+      <c r="D56" s="159"/>
+      <c r="E56" s="159"/>
+      <c r="F56" s="159"/>
+      <c r="G56" s="159"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="str">
@@ -30835,11 +30853,11 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="175" t="s">
+      <c r="A107" s="174" t="s">
         <v>276</v>
       </c>
-      <c r="B107" s="158"/>
-      <c r="C107" s="158"/>
+      <c r="B107" s="159"/>
+      <c r="C107" s="159"/>
       <c r="D107" s="107">
         <f>SUMIF(المحفظة!$H$107:$H$206,"&gt;0",المحفظة!$D$107:$D$206)</f>
         <v>0</v>
@@ -30849,35 +30867,35 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="169" t="s">
+      <c r="A108" s="170" t="s">
         <v>277</v>
       </c>
-      <c r="B108" s="158"/>
-      <c r="C108" s="158"/>
+      <c r="B108" s="159"/>
+      <c r="C108" s="159"/>
       <c r="D108" s="75">
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="174">
+      <c r="E108" s="176">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
-      <c r="F108" s="158"/>
-      <c r="G108" s="159"/>
+      <c r="F108" s="159"/>
+      <c r="G108" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36935F-A8B7-4CD9-A5DF-2C98504C78FF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEECEF02-8767-4259-A391-6F2BDE66A5F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="401">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1236,6 +1236,15 @@
   </si>
   <si>
     <t>Inv-132</t>
+  </si>
+  <si>
+    <t>Inv-133</t>
+  </si>
+  <si>
+    <t>زهور التهاني</t>
+  </si>
+  <si>
+    <t>يوريا  عدد1 (12.250) + مقص عدد1(1.250)</t>
   </si>
 </sst>
 </file>
@@ -2425,14 +2434,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2795,7 +2804,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>37.44500000000005</v>
+        <v>293.94500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6893,55 +6902,55 @@
       </c>
     </row>
     <row r="162" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="142" t="str">
+      <c r="A162" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(157,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46268</v>
       </c>
       <c r="B162" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(157,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-133</v>
       </c>
       <c r="C162" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(157,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D162" s="123" t="str">
+        <v>زهور التهاني</v>
+      </c>
+      <c r="D162" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(157,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E162" s="124" t="str">
+        <v>270</v>
+      </c>
+      <c r="E162" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(157,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F162" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F162" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>307.44500000000005</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="142" t="str">
+      <c r="A163" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(158,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B163" s="122" t="str">
+        <v>46269</v>
+      </c>
+      <c r="B163" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(158,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C163" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(158,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D163" s="123" t="str">
+        <v>يوريا  عدد1 (12.250) + مقص عدد1(1.250)</v>
+      </c>
+      <c r="D163" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(158,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E163" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E163" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(158,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F163" s="125" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="F163" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>293.94500000000005</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8044,15 +8053,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>1753.69</v>
+        <v>2023.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1716.2449999999999</v>
+        <v>1729.7449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>37.44500000000005</v>
+        <v>293.94500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19732,18 +19741,30 @@
       </c>
     </row>
     <row r="181" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="25"/>
-      <c r="B181" s="26"/>
-      <c r="C181" s="27"/>
+      <c r="A181" s="25">
+        <v>46268</v>
+      </c>
+      <c r="B181" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="C181" s="27" t="s">
+        <v>399</v>
+      </c>
       <c r="D181" s="28"/>
-      <c r="E181" s="29"/>
-      <c r="F181" s="30"/>
+      <c r="E181" s="29">
+        <v>270</v>
+      </c>
+      <c r="F181" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G181" s="31"/>
-      <c r="H181" s="32"/>
+      <c r="H181" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I181" s="33"/>
-      <c r="J181" s="34" t="str">
+      <c r="J181" s="34">
         <f>IF(AND(D181="",E181="",A181="",B181="",C181=""),"", IFERROR(IF(J180="",D2,J180),D2)+IF(E181="",0,E181)-IF(OR(G181="أبو اسحاق",G181="أبو آدم",G181="أبو اسحاق ",G181="أبو آدم "),0,IF(D181="",0,D181)))</f>
-        <v/>
+        <v>307.44500000000005</v>
       </c>
       <c r="K181" s="35"/>
       <c r="L181">
@@ -19762,9 +19783,9 @@
         <f>IF(AND(D180&gt;0,F180="أحد الشركاء"),COUNTIFS($D$4:D180,"&gt;"&amp;0,$F$4:F180,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P181" t="str">
+      <c r="P181">
         <f>IF(OR($A181="",$F181="أحد الشركاء",AND($D181="",$E181="")),"",SUMPRODUCT(($A$4:$A181&lt;&gt;"")*($F$4:$F181&lt;&gt;"أحد الشركاء")*((($D$4:$D181&lt;&gt;"")+($E$4:$E181&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>157</v>
       </c>
       <c r="Q181" t="str">
         <f>IF(OR($A181="",$F181&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A181,"&lt;&gt;",$F$4:F181,"أحد الشركاء"))</f>
@@ -19772,23 +19793,35 @@
       </c>
     </row>
     <row r="182" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="139"/>
+      <c r="A182" s="139">
+        <v>46269</v>
+      </c>
       <c r="B182" s="36"/>
-      <c r="C182" s="37"/>
-      <c r="D182" s="38"/>
+      <c r="C182" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="D182" s="38">
+        <v>13.5</v>
+      </c>
       <c r="E182" s="39"/>
-      <c r="F182" s="136"/>
-      <c r="G182" s="40"/>
-      <c r="H182" s="41"/>
+      <c r="F182" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G182" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H182" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I182" s="42"/>
-      <c r="J182" s="43" t="str">
+      <c r="J182" s="43">
         <f>IF(AND(D182="",E182="",A182="",B182="",C182=""),"", IFERROR(IF(J181="",D2,J181),D2)+IF(E182="",0,E182)-IF(OR(G182="أبو اسحاق",G182="أبو آدم",G182="أبو اسحاق ",G182="أبو آدم "),0,IF(D182="",0,D182)))</f>
-        <v/>
+        <v>293.94500000000005</v>
       </c>
       <c r="K182" s="44"/>
-      <c r="L182" t="str">
+      <c r="L182">
         <f>IF(E181&gt;0,COUNTIF($E$4:E181,"&gt;0"),"")</f>
-        <v/>
+        <v>119</v>
       </c>
       <c r="M182" t="str">
         <f>IF(AND(D181&gt;0,G181="المحفظة"),COUNTIFS($D$4:D181,"&gt;"&amp;0,$G$4:G181,"المحفظة"),"")</f>
@@ -19802,9 +19835,9 @@
         <f>IF(AND(D181&gt;0,F181="أحد الشركاء"),COUNTIFS($D$4:D181,"&gt;"&amp;0,$F$4:F181,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P182" t="str">
+      <c r="P182">
         <f>IF(OR($A182="",$F182="أحد الشركاء",AND($D182="",$E182="")),"",SUMPRODUCT(($A$4:$A182&lt;&gt;"")*($F$4:$F182&lt;&gt;"أحد الشركاء")*((($D$4:$D182&lt;&gt;"")+($E$4:$E182&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>158</v>
       </c>
       <c r="Q182" t="str">
         <f>IF(OR($A182="",$F182&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A182,"&lt;&gt;",$F$4:F182,"أحد الشركاء"))</f>
@@ -19830,9 +19863,9 @@
         <f>IF(E182&gt;0,COUNTIF($E$4:E182,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M183" t="str">
+      <c r="M183">
         <f>IF(AND(D182&gt;0,G182="المحفظة"),COUNTIFS($D$4:D182,"&gt;"&amp;0,$G$4:G182,"المحفظة"),"")</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="N183" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A183)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A183)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A183&lt;&gt;""),IFERROR(MAX($N$4:N182),0)+1,"")</f>
@@ -20699,11 +20732,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>3497.7450000000003</v>
+        <v>3511.2450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>1753.69</v>
+        <v>2023.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -28217,7 +28250,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
+      <c r="A4" s="174" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="159"/>
@@ -29528,7 +29561,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="159"/>
@@ -29542,7 +29575,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="174" t="s">
+      <c r="A56" s="176" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="159"/>
@@ -30853,7 +30886,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="174" t="s">
+      <c r="A107" s="176" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="159"/>
@@ -30876,7 +30909,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="176">
+      <c r="E108" s="175">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30885,17 +30918,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEECEF02-8767-4259-A391-6F2BDE66A5F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45980C0-50A5-4F0B-86E8-CFE4F27ADACC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,12 +26,12 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'طباعة المحفظة'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'طباعة كشف الحساب'!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="408">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1245,6 +1245,27 @@
   </si>
   <si>
     <t>يوريا  عدد1 (12.250) + مقص عدد1(1.250)</t>
+  </si>
+  <si>
+    <t>Inv-134</t>
+  </si>
+  <si>
+    <t>ليمون جراس عدد 4 الحبه 3</t>
+  </si>
+  <si>
+    <t>Inv-135</t>
+  </si>
+  <si>
+    <t>Inv-136</t>
+  </si>
+  <si>
+    <t>متنوع عدد 7 الحبه 1</t>
+  </si>
+  <si>
+    <t>احواض  عدد 1000 الحجم 25 سم</t>
+  </si>
+  <si>
+    <t>من المحفظة</t>
   </si>
 </sst>
 </file>
@@ -2434,14 +2455,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2804,7 +2825,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>293.94500000000005</v>
+        <v>230.94500000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6954,107 +6975,107 @@
       </c>
     </row>
     <row r="164" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="142" t="str">
+      <c r="A164" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(159,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46271</v>
       </c>
       <c r="B164" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(159,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-134</v>
       </c>
       <c r="C164" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(159,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D164" s="123" t="str">
+        <v>ليمون جراس عدد 4 الحبه 3</v>
+      </c>
+      <c r="D164" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(159,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E164" s="124" t="str">
+        <v>12</v>
+      </c>
+      <c r="E164" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(159,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F164" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F164" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>305.94500000000005</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="142" t="str">
+      <c r="A165" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(160,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46271</v>
       </c>
       <c r="B165" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(160,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-135</v>
       </c>
       <c r="C165" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(160,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D165" s="123" t="str">
+        <v>ربل عدد 2 الحبه 1.500</v>
+      </c>
+      <c r="D165" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(160,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E165" s="124" t="str">
+        <v>3</v>
+      </c>
+      <c r="E165" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(160,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F165" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F165" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>308.94500000000005</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="142" t="str">
+      <c r="A166" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(161,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46271</v>
       </c>
       <c r="B166" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(161,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-136</v>
       </c>
       <c r="C166" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(161,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D166" s="123" t="str">
+        <v>متنوع عدد 7 الحبه 1</v>
+      </c>
+      <c r="D166" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(161,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E166" s="124" t="str">
+        <v>7</v>
+      </c>
+      <c r="E166" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(161,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F166" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F166" s="125">
         <f t="shared" si="4"/>
-        <v/>
+        <v>315.94500000000005</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="142" t="str">
+      <c r="A167" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(162,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B167" s="122" t="str">
+        <v>46271</v>
+      </c>
+      <c r="B167" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(162,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C167" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(162,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D167" s="123" t="str">
+        <v>احواض  عدد 1000 الحجم 25 سم</v>
+      </c>
+      <c r="D167" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(162,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E167" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E167" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(162,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F167" s="125" t="str">
+        <v>85</v>
+      </c>
+      <c r="F167" s="125">
         <f t="shared" ref="F167:F198" si="5">IF($A167="","",IF($F166="",0,$F166)+IF($D167="",0,$D167)-IF($E167="",0,$E167))</f>
-        <v/>
+        <v>230.94500000000005</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8053,15 +8074,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2023.69</v>
+        <v>2045.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1729.7449999999999</v>
+        <v>1814.7449999999999</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>293.94500000000005</v>
+        <v>230.94500000000005</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -19845,18 +19866,30 @@
       </c>
     </row>
     <row r="183" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="25"/>
-      <c r="B183" s="26"/>
-      <c r="C183" s="27"/>
+      <c r="A183" s="25">
+        <v>46271</v>
+      </c>
+      <c r="B183" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="C183" s="27" t="s">
+        <v>402</v>
+      </c>
       <c r="D183" s="28"/>
-      <c r="E183" s="29"/>
-      <c r="F183" s="30"/>
+      <c r="E183" s="29">
+        <v>12</v>
+      </c>
+      <c r="F183" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G183" s="31"/>
-      <c r="H183" s="32"/>
+      <c r="H183" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I183" s="33"/>
-      <c r="J183" s="34" t="str">
+      <c r="J183" s="34">
         <f>IF(AND(D183="",E183="",A183="",B183="",C183=""),"", IFERROR(IF(J182="",D2,J182),D2)+IF(E183="",0,E183)-IF(OR(G183="أبو اسحاق",G183="أبو آدم",G183="أبو اسحاق ",G183="أبو آدم "),0,IF(D183="",0,D183)))</f>
-        <v/>
+        <v>305.94500000000005</v>
       </c>
       <c r="K183" s="35"/>
       <c r="L183" t="str">
@@ -19875,9 +19908,9 @@
         <f>IF(AND(D182&gt;0,F182="أحد الشركاء"),COUNTIFS($D$4:D182,"&gt;"&amp;0,$F$4:F182,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P183" t="str">
+      <c r="P183">
         <f>IF(OR($A183="",$F183="أحد الشركاء",AND($D183="",$E183="")),"",SUMPRODUCT(($A$4:$A183&lt;&gt;"")*($F$4:$F183&lt;&gt;"أحد الشركاء")*((($D$4:$D183&lt;&gt;"")+($E$4:$E183&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>159</v>
       </c>
       <c r="Q183" t="str">
         <f>IF(OR($A183="",$F183&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A183,"&lt;&gt;",$F$4:F183,"أحد الشركاء"))</f>
@@ -19885,23 +19918,35 @@
       </c>
     </row>
     <row r="184" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="139"/>
-      <c r="B184" s="36"/>
-      <c r="C184" s="37"/>
+      <c r="A184" s="25">
+        <v>46271</v>
+      </c>
+      <c r="B184" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="C184" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="D184" s="38"/>
-      <c r="E184" s="39"/>
-      <c r="F184" s="136"/>
+      <c r="E184" s="39">
+        <v>3</v>
+      </c>
+      <c r="F184" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G184" s="40"/>
-      <c r="H184" s="41"/>
+      <c r="H184" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I184" s="42"/>
-      <c r="J184" s="43" t="str">
+      <c r="J184" s="43">
         <f>IF(AND(D184="",E184="",A184="",B184="",C184=""),"", IFERROR(IF(J183="",D2,J183),D2)+IF(E184="",0,E184)-IF(OR(G184="أبو اسحاق",G184="أبو آدم",G184="أبو اسحاق ",G184="أبو آدم "),0,IF(D184="",0,D184)))</f>
-        <v/>
+        <v>308.94500000000005</v>
       </c>
       <c r="K184" s="44"/>
-      <c r="L184" t="str">
+      <c r="L184">
         <f>IF(E183&gt;0,COUNTIF($E$4:E183,"&gt;0"),"")</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="M184" t="str">
         <f>IF(AND(D183&gt;0,G183="المحفظة"),COUNTIFS($D$4:D183,"&gt;"&amp;0,$G$4:G183,"المحفظة"),"")</f>
@@ -19915,9 +19960,9 @@
         <f>IF(AND(D183&gt;0,F183="أحد الشركاء"),COUNTIFS($D$4:D183,"&gt;"&amp;0,$F$4:F183,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P184" t="str">
+      <c r="P184">
         <f>IF(OR($A184="",$F184="أحد الشركاء",AND($D184="",$E184="")),"",SUMPRODUCT(($A$4:$A184&lt;&gt;"")*($F$4:$F184&lt;&gt;"أحد الشركاء")*((($D$4:$D184&lt;&gt;"")+($E$4:$E184&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="Q184" t="str">
         <f>IF(OR($A184="",$F184&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A184,"&lt;&gt;",$F$4:F184,"أحد الشركاء"))</f>
@@ -19925,23 +19970,35 @@
       </c>
     </row>
     <row r="185" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="25"/>
-      <c r="B185" s="26"/>
-      <c r="C185" s="27"/>
+      <c r="A185" s="25">
+        <v>46271</v>
+      </c>
+      <c r="B185" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="C185" s="27" t="s">
+        <v>405</v>
+      </c>
       <c r="D185" s="28"/>
-      <c r="E185" s="29"/>
-      <c r="F185" s="30"/>
+      <c r="E185" s="29">
+        <v>7</v>
+      </c>
+      <c r="F185" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G185" s="31"/>
-      <c r="H185" s="32"/>
+      <c r="H185" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I185" s="33"/>
-      <c r="J185" s="34" t="str">
+      <c r="J185" s="34">
         <f>IF(AND(D185="",E185="",A185="",B185="",C185=""),"", IFERROR(IF(J184="",D2,J184),D2)+IF(E185="",0,E185)-IF(OR(G185="أبو اسحاق",G185="أبو آدم",G185="أبو اسحاق ",G185="أبو آدم "),0,IF(D185="",0,D185)))</f>
-        <v/>
+        <v>315.94500000000005</v>
       </c>
       <c r="K185" s="35"/>
-      <c r="L185" t="str">
+      <c r="L185">
         <f>IF(E184&gt;0,COUNTIF($E$4:E184,"&gt;0"),"")</f>
-        <v/>
+        <v>121</v>
       </c>
       <c r="M185" t="str">
         <f>IF(AND(D184&gt;0,G184="المحفظة"),COUNTIFS($D$4:D184,"&gt;"&amp;0,$G$4:G184,"المحفظة"),"")</f>
@@ -19955,9 +20012,9 @@
         <f>IF(AND(D184&gt;0,F184="أحد الشركاء"),COUNTIFS($D$4:D184,"&gt;"&amp;0,$F$4:F184,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P185" t="str">
+      <c r="P185">
         <f>IF(OR($A185="",$F185="أحد الشركاء",AND($D185="",$E185="")),"",SUMPRODUCT(($A$4:$A185&lt;&gt;"")*($F$4:$F185&lt;&gt;"أحد الشركاء")*((($D$4:$D185&lt;&gt;"")+($E$4:$E185&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>161</v>
       </c>
       <c r="Q185" t="str">
         <f>IF(OR($A185="",$F185&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A185,"&lt;&gt;",$F$4:F185,"أحد الشركاء"))</f>
@@ -19965,23 +20022,33 @@
       </c>
     </row>
     <row r="186" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="139"/>
+      <c r="A186" s="25">
+        <v>46271</v>
+      </c>
       <c r="B186" s="36"/>
-      <c r="C186" s="37"/>
-      <c r="D186" s="38"/>
+      <c r="C186" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="D186" s="38">
+        <v>85</v>
+      </c>
       <c r="E186" s="39"/>
-      <c r="F186" s="136"/>
+      <c r="F186" s="136" t="s">
+        <v>407</v>
+      </c>
       <c r="G186" s="40"/>
-      <c r="H186" s="41"/>
+      <c r="H186" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I186" s="42"/>
-      <c r="J186" s="43" t="str">
+      <c r="J186" s="43">
         <f>IF(AND(D186="",E186="",A186="",B186="",C186=""),"", IFERROR(IF(J185="",D2,J185),D2)+IF(E186="",0,E186)-IF(OR(G186="أبو اسحاق",G186="أبو آدم",G186="أبو اسحاق ",G186="أبو آدم "),0,IF(D186="",0,D186)))</f>
-        <v/>
+        <v>230.94500000000005</v>
       </c>
       <c r="K186" s="44"/>
-      <c r="L186" t="str">
+      <c r="L186">
         <f>IF(E185&gt;0,COUNTIF($E$4:E185,"&gt;0"),"")</f>
-        <v/>
+        <v>122</v>
       </c>
       <c r="M186" t="str">
         <f>IF(AND(D185&gt;0,G185="المحفظة"),COUNTIFS($D$4:D185,"&gt;"&amp;0,$G$4:G185,"المحفظة"),"")</f>
@@ -19995,9 +20062,9 @@
         <f>IF(AND(D185&gt;0,F185="أحد الشركاء"),COUNTIFS($D$4:D185,"&gt;"&amp;0,$F$4:F185,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P186" t="str">
+      <c r="P186">
         <f>IF(OR($A186="",$F186="أحد الشركاء",AND($D186="",$E186="")),"",SUMPRODUCT(($A$4:$A186&lt;&gt;"")*($F$4:$F186&lt;&gt;"أحد الشركاء")*((($D$4:$D186&lt;&gt;"")+($E$4:$E186&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>162</v>
       </c>
       <c r="Q186" t="str">
         <f>IF(OR($A186="",$F186&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A186,"&lt;&gt;",$F$4:F186,"أحد الشركاء"))</f>
@@ -20732,11 +20799,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>3511.2450000000003</v>
+        <v>3596.2450000000003</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>2023.69</v>
+        <v>2045.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -28250,7 +28317,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="174" t="s">
+      <c r="A4" s="175" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="159"/>
@@ -29561,7 +29628,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="175" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="159"/>
@@ -29575,7 +29642,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="176" t="s">
+      <c r="A56" s="174" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="159"/>
@@ -30886,7 +30953,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="176" t="s">
+      <c r="A107" s="174" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="159"/>
@@ -30909,7 +30976,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="175">
+      <c r="E108" s="176">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -30918,17 +30985,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45980C0-50A5-4F0B-86E8-CFE4F27ADACC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925F362B-1040-48E6-96FE-10CBF53F6D09}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="409">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1265,7 +1265,10 @@
     <t>احواض  عدد 1000 الحجم 25 سم</t>
   </si>
   <si>
-    <t>من المحفظة</t>
+    <t>Inv-137</t>
+  </si>
+  <si>
+    <t>صبار عدد 5 الحبه 1</t>
   </si>
 </sst>
 </file>
@@ -2825,7 +2828,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>230.94500000000005</v>
+        <v>233.79500000000004</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,55 +7082,55 @@
       </c>
     </row>
     <row r="168" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="142" t="str">
+      <c r="A168" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(163,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B168" s="122" t="str">
+        <v>46272</v>
+      </c>
+      <c r="B168" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(163,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C168" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(163,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D168" s="123" t="str">
+        <v>وصلات</v>
+      </c>
+      <c r="D168" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(163,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E168" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E168" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(163,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F168" s="125" t="str">
+        <v>2.15</v>
+      </c>
+      <c r="F168" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>228.79500000000004</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="142" t="str">
+      <c r="A169" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(164,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46275</v>
       </c>
       <c r="B169" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(164,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-137</v>
       </c>
       <c r="C169" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(164,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D169" s="123" t="str">
+        <v>صبار عدد 5 الحبه 1</v>
+      </c>
+      <c r="D169" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(164,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E169" s="124" t="str">
+        <v>5</v>
+      </c>
+      <c r="E169" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(164,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F169" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F169" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>233.79500000000004</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8074,15 +8077,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2045.69</v>
+        <v>2050.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1814.7449999999999</v>
+        <v>1816.895</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>230.94500000000005</v>
+        <v>233.79500000000004</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20034,9 +20037,11 @@
       </c>
       <c r="E186" s="39"/>
       <c r="F186" s="136" t="s">
-        <v>407</v>
-      </c>
-      <c r="G186" s="40"/>
+        <v>38</v>
+      </c>
+      <c r="G186" s="40" t="s">
+        <v>39</v>
+      </c>
       <c r="H186" s="41" t="s">
         <v>40</v>
       </c>
@@ -20072,27 +20077,37 @@
       </c>
     </row>
     <row r="187" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="25"/>
+      <c r="A187" s="25">
+        <v>46272</v>
+      </c>
       <c r="B187" s="26"/>
-      <c r="C187" s="27"/>
-      <c r="D187" s="28"/>
+      <c r="C187" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="D187" s="28">
+        <v>2.15</v>
+      </c>
       <c r="E187" s="29"/>
-      <c r="F187" s="30"/>
+      <c r="F187" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G187" s="31"/>
-      <c r="H187" s="32"/>
+      <c r="H187" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I187" s="33"/>
-      <c r="J187" s="34" t="str">
+      <c r="J187" s="34">
         <f>IF(AND(D187="",E187="",A187="",B187="",C187=""),"", IFERROR(IF(J186="",D2,J186),D2)+IF(E187="",0,E187)-IF(OR(G187="أبو اسحاق",G187="أبو آدم",G187="أبو اسحاق ",G187="أبو آدم "),0,IF(D187="",0,D187)))</f>
-        <v/>
+        <v>228.79500000000004</v>
       </c>
       <c r="K187" s="35"/>
       <c r="L187" t="str">
         <f>IF(E186&gt;0,COUNTIF($E$4:E186,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M187" t="str">
+      <c r="M187">
         <f>IF(AND(D186&gt;0,G186="المحفظة"),COUNTIFS($D$4:D186,"&gt;"&amp;0,$G$4:G186,"المحفظة"),"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="N187" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A187)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A187)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A187&lt;&gt;""),IFERROR(MAX($N$4:N186),0)+1,"")</f>
@@ -20102,9 +20117,9 @@
         <f>IF(AND(D186&gt;0,F186="أحد الشركاء"),COUNTIFS($D$4:D186,"&gt;"&amp;0,$F$4:F186,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P187" t="str">
+      <c r="P187">
         <f>IF(OR($A187="",$F187="أحد الشركاء",AND($D187="",$E187="")),"",SUMPRODUCT(($A$4:$A187&lt;&gt;"")*($F$4:$F187&lt;&gt;"أحد الشركاء")*((($D$4:$D187&lt;&gt;"")+($E$4:$E187&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>163</v>
       </c>
       <c r="Q187" t="str">
         <f>IF(OR($A187="",$F187&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A187,"&lt;&gt;",$F$4:F187,"أحد الشركاء"))</f>
@@ -20112,18 +20127,30 @@
       </c>
     </row>
     <row r="188" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="139"/>
-      <c r="B188" s="36"/>
-      <c r="C188" s="37"/>
+      <c r="A188" s="139">
+        <v>46275</v>
+      </c>
+      <c r="B188" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="C188" s="37" t="s">
+        <v>408</v>
+      </c>
       <c r="D188" s="38"/>
-      <c r="E188" s="39"/>
-      <c r="F188" s="136"/>
+      <c r="E188" s="39">
+        <v>5</v>
+      </c>
+      <c r="F188" s="136" t="s">
+        <v>172</v>
+      </c>
       <c r="G188" s="40"/>
-      <c r="H188" s="41"/>
+      <c r="H188" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I188" s="42"/>
-      <c r="J188" s="43" t="str">
+      <c r="J188" s="43">
         <f>IF(AND(D188="",E188="",A188="",B188="",C188=""),"", IFERROR(IF(J187="",D2,J187),D2)+IF(E188="",0,E188)-IF(OR(G188="أبو اسحاق",G188="أبو آدم",G188="أبو اسحاق ",G188="أبو آدم "),0,IF(D188="",0,D188)))</f>
-        <v/>
+        <v>233.79500000000004</v>
       </c>
       <c r="K188" s="44"/>
       <c r="L188" t="str">
@@ -20142,9 +20169,9 @@
         <f>IF(AND(D187&gt;0,F187="أحد الشركاء"),COUNTIFS($D$4:D187,"&gt;"&amp;0,$F$4:F187,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P188" t="str">
+      <c r="P188">
         <f>IF(OR($A188="",$F188="أحد الشركاء",AND($D188="",$E188="")),"",SUMPRODUCT(($A$4:$A188&lt;&gt;"")*($F$4:$F188&lt;&gt;"أحد الشركاء")*((($D$4:$D188&lt;&gt;"")+($E$4:$E188&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="Q188" t="str">
         <f>IF(OR($A188="",$F188&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A188,"&lt;&gt;",$F$4:F188,"أحد الشركاء"))</f>
@@ -20166,9 +20193,9 @@
         <v/>
       </c>
       <c r="K189" s="35"/>
-      <c r="L189" t="str">
+      <c r="L189">
         <f>IF(E188&gt;0,COUNTIF($E$4:E188,"&gt;0"),"")</f>
-        <v/>
+        <v>123</v>
       </c>
       <c r="M189" t="str">
         <f>IF(AND(D188&gt;0,G188="المحفظة"),COUNTIFS($D$4:D188,"&gt;"&amp;0,$G$4:G188,"المحفظة"),"")</f>
@@ -20799,11 +20826,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>3596.2450000000003</v>
+        <v>3598.3950000000004</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>2045.69</v>
+        <v>2050.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925F362B-1040-48E6-96FE-10CBF53F6D09}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4FD901-E1DF-4474-A3E4-41982E58D36A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="431">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1269,6 +1269,72 @@
   </si>
   <si>
     <t>صبار عدد 5 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-138</t>
+  </si>
+  <si>
+    <t>متنوع عدد 10 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>Inv-139</t>
+  </si>
+  <si>
+    <t>متنوع عدد 20 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-140</t>
+  </si>
+  <si>
+    <t>صبار عدد 35 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-141</t>
+  </si>
+  <si>
+    <t>متنوع عدد 5 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-142</t>
+  </si>
+  <si>
+    <t>عطره العدد 10 الحبه .750</t>
+  </si>
+  <si>
+    <t>لم يدفع</t>
+  </si>
+  <si>
+    <t>Inv-143</t>
+  </si>
+  <si>
+    <t>دارسينا متنوع عدد 2  الحبه 3</t>
+  </si>
+  <si>
+    <t>Inv-144</t>
+  </si>
+  <si>
+    <t>معلقات عدد 2 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-145</t>
+  </si>
+  <si>
+    <t>دارسينا اسود عدد 2 الحبه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-146</t>
+  </si>
+  <si>
+    <t>متنوع عدد 2 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-147</t>
+  </si>
+  <si>
+    <t>متنوع عدد 2 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>Inv-148</t>
   </si>
 </sst>
 </file>
@@ -1870,7 +1936,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1969,11 +2035,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2458,14 +2561,23 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2828,7 +2940,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>233.79500000000004</v>
+        <v>336.29500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7134,289 +7246,289 @@
       </c>
     </row>
     <row r="170" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="142" t="str">
+      <c r="A170" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(165,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B170" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(165,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-138</v>
       </c>
       <c r="C170" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(165,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D170" s="123" t="str">
+        <v>متنوع عدد 10 الحبه 1.500</v>
+      </c>
+      <c r="D170" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(165,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E170" s="124" t="str">
+        <v>15</v>
+      </c>
+      <c r="E170" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(165,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F170" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F170" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>248.79500000000004</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="142" t="str">
+      <c r="A171" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(166,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B171" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(166,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-139</v>
       </c>
       <c r="C171" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(166,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D171" s="123" t="str">
+        <v>متنوع عدد 20 الحبه 1</v>
+      </c>
+      <c r="D171" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(166,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E171" s="124" t="str">
+        <v>20</v>
+      </c>
+      <c r="E171" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(166,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F171" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F171" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>268.79500000000007</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="142" t="str">
+      <c r="A172" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(167,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B172" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(167,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-140</v>
       </c>
       <c r="C172" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(167,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D172" s="123" t="str">
+        <v>صبار عدد 35 الحبه 1</v>
+      </c>
+      <c r="D172" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(167,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E172" s="124" t="str">
+        <v>35</v>
+      </c>
+      <c r="E172" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(167,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F172" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F172" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>303.79500000000007</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="142" t="str">
+      <c r="A173" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(168,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B173" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(168,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-141</v>
       </c>
       <c r="C173" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(168,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D173" s="123" t="str">
+        <v>متنوع عدد 5 الحبه 1</v>
+      </c>
+      <c r="D173" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(168,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E173" s="124" t="str">
+        <v>5</v>
+      </c>
+      <c r="E173" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(168,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F173" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F173" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>308.79500000000007</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="142" t="str">
+      <c r="A174" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B174" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-142</v>
       </c>
       <c r="C174" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D174" s="123" t="str">
+        <v>عطره العدد 10 الحبه .750</v>
+      </c>
+      <c r="D174" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E174" s="124" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="E174" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F174" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F174" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>316.29500000000007</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="142" t="str">
+      <c r="A175" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(170,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B175" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(170,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-143</v>
       </c>
       <c r="C175" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(170,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D175" s="123" t="str">
+        <v>دارسينا متنوع عدد 2  الحبه 3</v>
+      </c>
+      <c r="D175" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(170,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E175" s="124" t="str">
+        <v>6</v>
+      </c>
+      <c r="E175" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(170,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F175" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F175" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>322.29500000000007</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="142" t="str">
+      <c r="A176" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(171,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B176" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(171,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-144</v>
       </c>
       <c r="C176" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(171,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D176" s="123" t="str">
+        <v>معلقات عدد 2 الحبه 1</v>
+      </c>
+      <c r="D176" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(171,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E176" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E176" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(171,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F176" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F176" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>324.29500000000007</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="142" t="str">
+      <c r="A177" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(172,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B177" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(172,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-145</v>
       </c>
       <c r="C177" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(172,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D177" s="123" t="str">
+        <v>دارسينا اسود عدد 2 الحبه 2.500</v>
+      </c>
+      <c r="D177" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(172,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E177" s="124" t="str">
+        <v>5</v>
+      </c>
+      <c r="E177" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(172,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F177" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F177" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>329.29500000000007</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="142" t="str">
+      <c r="A178" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(173,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B178" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(173,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-146</v>
       </c>
       <c r="C178" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(173,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D178" s="123" t="str">
+        <v>متنوع عدد 2 الحبه 1</v>
+      </c>
+      <c r="D178" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(173,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E178" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E178" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(173,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F178" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F178" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>331.29500000000007</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="142" t="str">
+      <c r="A179" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(174,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B179" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(174,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-147</v>
       </c>
       <c r="C179" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(174,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D179" s="123" t="str">
+        <v>متنوع عدد 2 الحبه 1.500</v>
+      </c>
+      <c r="D179" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(174,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E179" s="124" t="str">
+        <v>3</v>
+      </c>
+      <c r="E179" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(174,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F179" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F179" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>334.29500000000007</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="142" t="str">
+      <c r="A180" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(175,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46276</v>
       </c>
       <c r="B180" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(175,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-148</v>
       </c>
       <c r="C180" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(175,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D180" s="123" t="str">
+        <v>متنوع عدد 2 الحبه 1</v>
+      </c>
+      <c r="D180" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(175,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E180" s="124" t="str">
+        <v>2</v>
+      </c>
+      <c r="E180" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(175,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F180" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F180" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>336.29500000000007</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8077,7 +8189,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2050.69</v>
+        <v>2153.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8085,7 +8197,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>233.79500000000004</v>
+        <v>336.29500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20179,20 +20291,34 @@
       </c>
     </row>
     <row r="189" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="25"/>
-      <c r="B189" s="26"/>
-      <c r="C189" s="27"/>
+      <c r="A189" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B189" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="C189" s="27" t="s">
+        <v>410</v>
+      </c>
       <c r="D189" s="28"/>
-      <c r="E189" s="29"/>
-      <c r="F189" s="30"/>
+      <c r="E189" s="29">
+        <v>15</v>
+      </c>
+      <c r="F189" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G189" s="31"/>
-      <c r="H189" s="32"/>
+      <c r="H189" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I189" s="33"/>
-      <c r="J189" s="34" t="str">
+      <c r="J189" s="34">
         <f>IF(AND(D189="",E189="",A189="",B189="",C189=""),"", IFERROR(IF(J188="",D2,J188),D2)+IF(E189="",0,E189)-IF(OR(G189="أبو اسحاق",G189="أبو آدم",G189="أبو اسحاق ",G189="أبو آدم "),0,IF(D189="",0,D189)))</f>
-        <v/>
-      </c>
-      <c r="K189" s="35"/>
+        <v>248.79500000000004</v>
+      </c>
+      <c r="K189" s="177" t="s">
+        <v>419</v>
+      </c>
       <c r="L189">
         <f>IF(E188&gt;0,COUNTIF($E$4:E188,"&gt;0"),"")</f>
         <v>123</v>
@@ -20209,9 +20335,9 @@
         <f>IF(AND(D188&gt;0,F188="أحد الشركاء"),COUNTIFS($D$4:D188,"&gt;"&amp;0,$F$4:F188,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P189" t="str">
+      <c r="P189">
         <f>IF(OR($A189="",$F189="أحد الشركاء",AND($D189="",$E189="")),"",SUMPRODUCT(($A$4:$A189&lt;&gt;"")*($F$4:$F189&lt;&gt;"أحد الشركاء")*((($D$4:$D189&lt;&gt;"")+($E$4:$E189&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>165</v>
       </c>
       <c r="Q189" t="str">
         <f>IF(OR($A189="",$F189&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A189,"&lt;&gt;",$F$4:F189,"أحد الشركاء"))</f>
@@ -20219,23 +20345,35 @@
       </c>
     </row>
     <row r="190" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="139"/>
-      <c r="B190" s="36"/>
-      <c r="C190" s="37"/>
+      <c r="A190" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B190" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="C190" s="37" t="s">
+        <v>412</v>
+      </c>
       <c r="D190" s="38"/>
-      <c r="E190" s="39"/>
-      <c r="F190" s="136"/>
+      <c r="E190" s="39">
+        <v>20</v>
+      </c>
+      <c r="F190" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G190" s="40"/>
-      <c r="H190" s="41"/>
+      <c r="H190" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I190" s="42"/>
-      <c r="J190" s="43" t="str">
+      <c r="J190" s="43">
         <f>IF(AND(D190="",E190="",A190="",B190="",C190=""),"", IFERROR(IF(J189="",D2,J189),D2)+IF(E190="",0,E190)-IF(OR(G190="أبو اسحاق",G190="أبو آدم",G190="أبو اسحاق ",G190="أبو آدم "),0,IF(D190="",0,D190)))</f>
-        <v/>
-      </c>
-      <c r="K190" s="44"/>
-      <c r="L190" t="str">
+        <v>268.79500000000007</v>
+      </c>
+      <c r="K190" s="178"/>
+      <c r="L190">
         <f>IF(E189&gt;0,COUNTIF($E$4:E189,"&gt;0"),"")</f>
-        <v/>
+        <v>124</v>
       </c>
       <c r="M190" t="str">
         <f>IF(AND(D189&gt;0,G189="المحفظة"),COUNTIFS($D$4:D189,"&gt;"&amp;0,$G$4:G189,"المحفظة"),"")</f>
@@ -20249,9 +20387,9 @@
         <f>IF(AND(D189&gt;0,F189="أحد الشركاء"),COUNTIFS($D$4:D189,"&gt;"&amp;0,$F$4:F189,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P190" t="str">
+      <c r="P190">
         <f>IF(OR($A190="",$F190="أحد الشركاء",AND($D190="",$E190="")),"",SUMPRODUCT(($A$4:$A190&lt;&gt;"")*($F$4:$F190&lt;&gt;"أحد الشركاء")*((($D$4:$D190&lt;&gt;"")+($E$4:$E190&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>166</v>
       </c>
       <c r="Q190" t="str">
         <f>IF(OR($A190="",$F190&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A190,"&lt;&gt;",$F$4:F190,"أحد الشركاء"))</f>
@@ -20259,23 +20397,35 @@
       </c>
     </row>
     <row r="191" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="25"/>
-      <c r="B191" s="26"/>
-      <c r="C191" s="27"/>
+      <c r="A191" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B191" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="C191" s="27" t="s">
+        <v>414</v>
+      </c>
       <c r="D191" s="28"/>
-      <c r="E191" s="29"/>
-      <c r="F191" s="30"/>
+      <c r="E191" s="29">
+        <v>35</v>
+      </c>
+      <c r="F191" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G191" s="31"/>
-      <c r="H191" s="32"/>
+      <c r="H191" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I191" s="33"/>
-      <c r="J191" s="34" t="str">
+      <c r="J191" s="34">
         <f>IF(AND(D191="",E191="",A191="",B191="",C191=""),"", IFERROR(IF(J190="",D2,J190),D2)+IF(E191="",0,E191)-IF(OR(G191="أبو اسحاق",G191="أبو آدم",G191="أبو اسحاق ",G191="أبو آدم "),0,IF(D191="",0,D191)))</f>
-        <v/>
-      </c>
-      <c r="K191" s="35"/>
-      <c r="L191" t="str">
+        <v>303.79500000000007</v>
+      </c>
+      <c r="K191" s="178"/>
+      <c r="L191">
         <f>IF(E190&gt;0,COUNTIF($E$4:E190,"&gt;0"),"")</f>
-        <v/>
+        <v>125</v>
       </c>
       <c r="M191" t="str">
         <f>IF(AND(D190&gt;0,G190="المحفظة"),COUNTIFS($D$4:D190,"&gt;"&amp;0,$G$4:G190,"المحفظة"),"")</f>
@@ -20289,9 +20439,9 @@
         <f>IF(AND(D190&gt;0,F190="أحد الشركاء"),COUNTIFS($D$4:D190,"&gt;"&amp;0,$F$4:F190,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P191" t="str">
+      <c r="P191">
         <f>IF(OR($A191="",$F191="أحد الشركاء",AND($D191="",$E191="")),"",SUMPRODUCT(($A$4:$A191&lt;&gt;"")*($F$4:$F191&lt;&gt;"أحد الشركاء")*((($D$4:$D191&lt;&gt;"")+($E$4:$E191&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>167</v>
       </c>
       <c r="Q191" t="str">
         <f>IF(OR($A191="",$F191&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A191,"&lt;&gt;",$F$4:F191,"أحد الشركاء"))</f>
@@ -20299,23 +20449,35 @@
       </c>
     </row>
     <row r="192" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="139"/>
-      <c r="B192" s="36"/>
-      <c r="C192" s="37"/>
+      <c r="A192" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B192" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="C192" s="37" t="s">
+        <v>416</v>
+      </c>
       <c r="D192" s="38"/>
-      <c r="E192" s="39"/>
-      <c r="F192" s="136"/>
+      <c r="E192" s="39">
+        <v>5</v>
+      </c>
+      <c r="F192" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G192" s="40"/>
-      <c r="H192" s="41"/>
+      <c r="H192" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I192" s="42"/>
-      <c r="J192" s="43" t="str">
+      <c r="J192" s="43">
         <f>IF(AND(D192="",E192="",A192="",B192="",C192=""),"", IFERROR(IF(J191="",D2,J191),D2)+IF(E192="",0,E192)-IF(OR(G192="أبو اسحاق",G192="أبو آدم",G192="أبو اسحاق ",G192="أبو آدم "),0,IF(D192="",0,D192)))</f>
-        <v/>
-      </c>
-      <c r="K192" s="44"/>
-      <c r="L192" t="str">
+        <v>308.79500000000007</v>
+      </c>
+      <c r="K192" s="178"/>
+      <c r="L192">
         <f>IF(E191&gt;0,COUNTIF($E$4:E191,"&gt;0"),"")</f>
-        <v/>
+        <v>126</v>
       </c>
       <c r="M192" t="str">
         <f>IF(AND(D191&gt;0,G191="المحفظة"),COUNTIFS($D$4:D191,"&gt;"&amp;0,$G$4:G191,"المحفظة"),"")</f>
@@ -20329,9 +20491,9 @@
         <f>IF(AND(D191&gt;0,F191="أحد الشركاء"),COUNTIFS($D$4:D191,"&gt;"&amp;0,$F$4:F191,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P192" t="str">
+      <c r="P192">
         <f>IF(OR($A192="",$F192="أحد الشركاء",AND($D192="",$E192="")),"",SUMPRODUCT(($A$4:$A192&lt;&gt;"")*($F$4:$F192&lt;&gt;"أحد الشركاء")*((($D$4:$D192&lt;&gt;"")+($E$4:$E192&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>168</v>
       </c>
       <c r="Q192" t="str">
         <f>IF(OR($A192="",$F192&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A192,"&lt;&gt;",$F$4:F192,"أحد الشركاء"))</f>
@@ -20339,23 +20501,35 @@
       </c>
     </row>
     <row r="193" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="25"/>
-      <c r="B193" s="26"/>
-      <c r="C193" s="27"/>
+      <c r="A193" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B193" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="C193" s="27" t="s">
+        <v>418</v>
+      </c>
       <c r="D193" s="28"/>
-      <c r="E193" s="29"/>
-      <c r="F193" s="30"/>
+      <c r="E193" s="29">
+        <v>7.5</v>
+      </c>
+      <c r="F193" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G193" s="31"/>
-      <c r="H193" s="32"/>
+      <c r="H193" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I193" s="33"/>
-      <c r="J193" s="34" t="str">
+      <c r="J193" s="34">
         <f>IF(AND(D193="",E193="",A193="",B193="",C193=""),"", IFERROR(IF(J192="",D2,J192),D2)+IF(E193="",0,E193)-IF(OR(G193="أبو اسحاق",G193="أبو آدم",G193="أبو اسحاق ",G193="أبو آدم "),0,IF(D193="",0,D193)))</f>
-        <v/>
-      </c>
-      <c r="K193" s="35"/>
-      <c r="L193" t="str">
+        <v>316.29500000000007</v>
+      </c>
+      <c r="K193" s="179"/>
+      <c r="L193">
         <f>IF(E192&gt;0,COUNTIF($E$4:E192,"&gt;0"),"")</f>
-        <v/>
+        <v>127</v>
       </c>
       <c r="M193" t="str">
         <f>IF(AND(D192&gt;0,G192="المحفظة"),COUNTIFS($D$4:D192,"&gt;"&amp;0,$G$4:G192,"المحفظة"),"")</f>
@@ -20369,9 +20543,9 @@
         <f>IF(AND(D192&gt;0,F192="أحد الشركاء"),COUNTIFS($D$4:D192,"&gt;"&amp;0,$F$4:F192,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P193" t="str">
+      <c r="P193">
         <f>IF(OR($A193="",$F193="أحد الشركاء",AND($D193="",$E193="")),"",SUMPRODUCT(($A$4:$A193&lt;&gt;"")*($F$4:$F193&lt;&gt;"أحد الشركاء")*((($D$4:$D193&lt;&gt;"")+($E$4:$E193&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>169</v>
       </c>
       <c r="Q193" t="str">
         <f>IF(OR($A193="",$F193&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A193,"&lt;&gt;",$F$4:F193,"أحد الشركاء"))</f>
@@ -20379,23 +20553,35 @@
       </c>
     </row>
     <row r="194" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="139"/>
-      <c r="B194" s="36"/>
-      <c r="C194" s="37"/>
+      <c r="A194" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B194" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="C194" s="37" t="s">
+        <v>421</v>
+      </c>
       <c r="D194" s="38"/>
-      <c r="E194" s="39"/>
-      <c r="F194" s="136"/>
+      <c r="E194" s="39">
+        <v>6</v>
+      </c>
+      <c r="F194" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G194" s="40"/>
-      <c r="H194" s="41"/>
+      <c r="H194" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I194" s="42"/>
-      <c r="J194" s="43" t="str">
+      <c r="J194" s="43">
         <f>IF(AND(D194="",E194="",A194="",B194="",C194=""),"", IFERROR(IF(J193="",D2,J193),D2)+IF(E194="",0,E194)-IF(OR(G194="أبو اسحاق",G194="أبو آدم",G194="أبو اسحاق ",G194="أبو آدم "),0,IF(D194="",0,D194)))</f>
-        <v/>
+        <v>322.29500000000007</v>
       </c>
       <c r="K194" s="44"/>
-      <c r="L194" t="str">
+      <c r="L194">
         <f>IF(E193&gt;0,COUNTIF($E$4:E193,"&gt;0"),"")</f>
-        <v/>
+        <v>128</v>
       </c>
       <c r="M194" t="str">
         <f>IF(AND(D193&gt;0,G193="المحفظة"),COUNTIFS($D$4:D193,"&gt;"&amp;0,$G$4:G193,"المحفظة"),"")</f>
@@ -20409,9 +20595,9 @@
         <f>IF(AND(D193&gt;0,F193="أحد الشركاء"),COUNTIFS($D$4:D193,"&gt;"&amp;0,$F$4:F193,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P194" t="str">
+      <c r="P194">
         <f>IF(OR($A194="",$F194="أحد الشركاء",AND($D194="",$E194="")),"",SUMPRODUCT(($A$4:$A194&lt;&gt;"")*($F$4:$F194&lt;&gt;"أحد الشركاء")*((($D$4:$D194&lt;&gt;"")+($E$4:$E194&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>170</v>
       </c>
       <c r="Q194" t="str">
         <f>IF(OR($A194="",$F194&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A194,"&lt;&gt;",$F$4:F194,"أحد الشركاء"))</f>
@@ -20419,23 +20605,35 @@
       </c>
     </row>
     <row r="195" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="25"/>
-      <c r="B195" s="26"/>
-      <c r="C195" s="27"/>
+      <c r="A195" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B195" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="C195" s="27" t="s">
+        <v>423</v>
+      </c>
       <c r="D195" s="28"/>
-      <c r="E195" s="29"/>
-      <c r="F195" s="30"/>
+      <c r="E195" s="29">
+        <v>2</v>
+      </c>
+      <c r="F195" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G195" s="31"/>
-      <c r="H195" s="32"/>
+      <c r="H195" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I195" s="33"/>
-      <c r="J195" s="34" t="str">
+      <c r="J195" s="34">
         <f>IF(AND(D195="",E195="",A195="",B195="",C195=""),"", IFERROR(IF(J194="",D2,J194),D2)+IF(E195="",0,E195)-IF(OR(G195="أبو اسحاق",G195="أبو آدم",G195="أبو اسحاق ",G195="أبو آدم "),0,IF(D195="",0,D195)))</f>
-        <v/>
+        <v>324.29500000000007</v>
       </c>
       <c r="K195" s="35"/>
-      <c r="L195" t="str">
+      <c r="L195">
         <f>IF(E194&gt;0,COUNTIF($E$4:E194,"&gt;0"),"")</f>
-        <v/>
+        <v>129</v>
       </c>
       <c r="M195" t="str">
         <f>IF(AND(D194&gt;0,G194="المحفظة"),COUNTIFS($D$4:D194,"&gt;"&amp;0,$G$4:G194,"المحفظة"),"")</f>
@@ -20449,9 +20647,9 @@
         <f>IF(AND(D194&gt;0,F194="أحد الشركاء"),COUNTIFS($D$4:D194,"&gt;"&amp;0,$F$4:F194,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P195" t="str">
+      <c r="P195">
         <f>IF(OR($A195="",$F195="أحد الشركاء",AND($D195="",$E195="")),"",SUMPRODUCT(($A$4:$A195&lt;&gt;"")*($F$4:$F195&lt;&gt;"أحد الشركاء")*((($D$4:$D195&lt;&gt;"")+($E$4:$E195&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>171</v>
       </c>
       <c r="Q195" t="str">
         <f>IF(OR($A195="",$F195&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A195,"&lt;&gt;",$F$4:F195,"أحد الشركاء"))</f>
@@ -20459,23 +20657,35 @@
       </c>
     </row>
     <row r="196" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="139"/>
-      <c r="B196" s="36"/>
-      <c r="C196" s="37"/>
+      <c r="A196" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B196" s="36" t="s">
+        <v>424</v>
+      </c>
+      <c r="C196" s="37" t="s">
+        <v>425</v>
+      </c>
       <c r="D196" s="38"/>
-      <c r="E196" s="39"/>
-      <c r="F196" s="136"/>
+      <c r="E196" s="39">
+        <v>5</v>
+      </c>
+      <c r="F196" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G196" s="40"/>
-      <c r="H196" s="41"/>
+      <c r="H196" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I196" s="42"/>
-      <c r="J196" s="43" t="str">
+      <c r="J196" s="43">
         <f>IF(AND(D196="",E196="",A196="",B196="",C196=""),"", IFERROR(IF(J195="",D2,J195),D2)+IF(E196="",0,E196)-IF(OR(G196="أبو اسحاق",G196="أبو آدم",G196="أبو اسحاق ",G196="أبو آدم "),0,IF(D196="",0,D196)))</f>
-        <v/>
+        <v>329.29500000000007</v>
       </c>
       <c r="K196" s="44"/>
-      <c r="L196" t="str">
+      <c r="L196">
         <f>IF(E195&gt;0,COUNTIF($E$4:E195,"&gt;0"),"")</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="M196" t="str">
         <f>IF(AND(D195&gt;0,G195="المحفظة"),COUNTIFS($D$4:D195,"&gt;"&amp;0,$G$4:G195,"المحفظة"),"")</f>
@@ -20489,9 +20699,9 @@
         <f>IF(AND(D195&gt;0,F195="أحد الشركاء"),COUNTIFS($D$4:D195,"&gt;"&amp;0,$F$4:F195,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P196" t="str">
+      <c r="P196">
         <f>IF(OR($A196="",$F196="أحد الشركاء",AND($D196="",$E196="")),"",SUMPRODUCT(($A$4:$A196&lt;&gt;"")*($F$4:$F196&lt;&gt;"أحد الشركاء")*((($D$4:$D196&lt;&gt;"")+($E$4:$E196&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>172</v>
       </c>
       <c r="Q196" t="str">
         <f>IF(OR($A196="",$F196&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A196,"&lt;&gt;",$F$4:F196,"أحد الشركاء"))</f>
@@ -20499,23 +20709,35 @@
       </c>
     </row>
     <row r="197" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="25"/>
-      <c r="B197" s="26"/>
-      <c r="C197" s="27"/>
+      <c r="A197" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B197" s="36" t="s">
+        <v>426</v>
+      </c>
+      <c r="C197" s="27" t="s">
+        <v>427</v>
+      </c>
       <c r="D197" s="28"/>
-      <c r="E197" s="29"/>
-      <c r="F197" s="30"/>
+      <c r="E197" s="29">
+        <v>2</v>
+      </c>
+      <c r="F197" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G197" s="31"/>
-      <c r="H197" s="32"/>
+      <c r="H197" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I197" s="33"/>
-      <c r="J197" s="34" t="str">
+      <c r="J197" s="34">
         <f>IF(AND(D197="",E197="",A197="",B197="",C197=""),"", IFERROR(IF(J196="",D2,J196),D2)+IF(E197="",0,E197)-IF(OR(G197="أبو اسحاق",G197="أبو آدم",G197="أبو اسحاق ",G197="أبو آدم "),0,IF(D197="",0,D197)))</f>
-        <v/>
+        <v>331.29500000000007</v>
       </c>
       <c r="K197" s="35"/>
-      <c r="L197" t="str">
+      <c r="L197">
         <f>IF(E196&gt;0,COUNTIF($E$4:E196,"&gt;0"),"")</f>
-        <v/>
+        <v>131</v>
       </c>
       <c r="M197" t="str">
         <f>IF(AND(D196&gt;0,G196="المحفظة"),COUNTIFS($D$4:D196,"&gt;"&amp;0,$G$4:G196,"المحفظة"),"")</f>
@@ -20529,9 +20751,9 @@
         <f>IF(AND(D196&gt;0,F196="أحد الشركاء"),COUNTIFS($D$4:D196,"&gt;"&amp;0,$F$4:F196,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P197" t="str">
+      <c r="P197">
         <f>IF(OR($A197="",$F197="أحد الشركاء",AND($D197="",$E197="")),"",SUMPRODUCT(($A$4:$A197&lt;&gt;"")*($F$4:$F197&lt;&gt;"أحد الشركاء")*((($D$4:$D197&lt;&gt;"")+($E$4:$E197&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>173</v>
       </c>
       <c r="Q197" t="str">
         <f>IF(OR($A197="",$F197&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A197,"&lt;&gt;",$F$4:F197,"أحد الشركاء"))</f>
@@ -20539,23 +20761,35 @@
       </c>
     </row>
     <row r="198" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="139"/>
-      <c r="B198" s="36"/>
-      <c r="C198" s="37"/>
+      <c r="A198" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B198" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="C198" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="D198" s="38"/>
-      <c r="E198" s="39"/>
-      <c r="F198" s="136"/>
+      <c r="E198" s="39">
+        <v>3</v>
+      </c>
+      <c r="F198" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G198" s="40"/>
-      <c r="H198" s="41"/>
+      <c r="H198" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I198" s="42"/>
-      <c r="J198" s="43" t="str">
+      <c r="J198" s="43">
         <f>IF(AND(D198="",E198="",A198="",B198="",C198=""),"", IFERROR(IF(J197="",D2,J197),D2)+IF(E198="",0,E198)-IF(OR(G198="أبو اسحاق",G198="أبو آدم",G198="أبو اسحاق ",G198="أبو آدم "),0,IF(D198="",0,D198)))</f>
-        <v/>
+        <v>334.29500000000007</v>
       </c>
       <c r="K198" s="44"/>
-      <c r="L198" t="str">
+      <c r="L198">
         <f>IF(E197&gt;0,COUNTIF($E$4:E197,"&gt;0"),"")</f>
-        <v/>
+        <v>132</v>
       </c>
       <c r="M198" t="str">
         <f>IF(AND(D197&gt;0,G197="المحفظة"),COUNTIFS($D$4:D197,"&gt;"&amp;0,$G$4:G197,"المحفظة"),"")</f>
@@ -20569,9 +20803,9 @@
         <f>IF(AND(D197&gt;0,F197="أحد الشركاء"),COUNTIFS($D$4:D197,"&gt;"&amp;0,$F$4:F197,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P198" t="str">
+      <c r="P198">
         <f>IF(OR($A198="",$F198="أحد الشركاء",AND($D198="",$E198="")),"",SUMPRODUCT(($A$4:$A198&lt;&gt;"")*($F$4:$F198&lt;&gt;"أحد الشركاء")*((($D$4:$D198&lt;&gt;"")+($E$4:$E198&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="Q198" t="str">
         <f>IF(OR($A198="",$F198&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A198,"&lt;&gt;",$F$4:F198,"أحد الشركاء"))</f>
@@ -20579,23 +20813,35 @@
       </c>
     </row>
     <row r="199" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="25"/>
-      <c r="B199" s="26"/>
-      <c r="C199" s="27"/>
+      <c r="A199" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B199" s="36" t="s">
+        <v>430</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>427</v>
+      </c>
       <c r="D199" s="28"/>
-      <c r="E199" s="29"/>
-      <c r="F199" s="30"/>
+      <c r="E199" s="29">
+        <v>2</v>
+      </c>
+      <c r="F199" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G199" s="31"/>
-      <c r="H199" s="32"/>
+      <c r="H199" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I199" s="33"/>
-      <c r="J199" s="34" t="str">
+      <c r="J199" s="34">
         <f>IF(AND(D199="",E199="",A199="",B199="",C199=""),"", IFERROR(IF(J198="",D2,J198),D2)+IF(E199="",0,E199)-IF(OR(G199="أبو اسحاق",G199="أبو آدم",G199="أبو اسحاق ",G199="أبو آدم "),0,IF(D199="",0,D199)))</f>
-        <v/>
+        <v>336.29500000000007</v>
       </c>
       <c r="K199" s="35"/>
-      <c r="L199" t="str">
+      <c r="L199">
         <f>IF(E198&gt;0,COUNTIF($E$4:E198,"&gt;0"),"")</f>
-        <v/>
+        <v>133</v>
       </c>
       <c r="M199" t="str">
         <f>IF(AND(D198&gt;0,G198="المحفظة"),COUNTIFS($D$4:D198,"&gt;"&amp;0,$G$4:G198,"المحفظة"),"")</f>
@@ -20609,9 +20855,9 @@
         <f>IF(AND(D198&gt;0,F198="أحد الشركاء"),COUNTIFS($D$4:D198,"&gt;"&amp;0,$F$4:F198,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P199" t="str">
+      <c r="P199">
         <f>IF(OR($A199="",$F199="أحد الشركاء",AND($D199="",$E199="")),"",SUMPRODUCT(($A$4:$A199&lt;&gt;"")*($F$4:$F199&lt;&gt;"أحد الشركاء")*((($D$4:$D199&lt;&gt;"")+($E$4:$E199&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="Q199" t="str">
         <f>IF(OR($A199="",$F199&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A199,"&lt;&gt;",$F$4:F199,"أحد الشركاء"))</f>
@@ -20633,9 +20879,9 @@
         <v/>
       </c>
       <c r="K200" s="44"/>
-      <c r="L200" t="str">
+      <c r="L200">
         <f>IF(E199&gt;0,COUNTIF($E$4:E199,"&gt;0"),"")</f>
-        <v/>
+        <v>134</v>
       </c>
       <c r="M200" t="str">
         <f>IF(AND(D199&gt;0,G199="المحفظة"),COUNTIFS($D$4:D199,"&gt;"&amp;0,$G$4:G199,"المحفظة"),"")</f>
@@ -20830,7 +21076,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>2050.69</v>
+        <v>2153.19</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -20862,12 +21108,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="F204:H204"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A204:C204"/>
+    <mergeCell ref="K189:K193"/>
   </mergeCells>
   <conditionalFormatting sqref="J4:J203">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
@@ -28344,7 +28591,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
+      <c r="A4" s="174" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="159"/>
@@ -29655,7 +29902,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="175" t="s">
+      <c r="A55" s="174" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="159"/>
@@ -29669,7 +29916,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="174" t="s">
+      <c r="A56" s="176" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="159"/>
@@ -30980,7 +31227,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="174" t="s">
+      <c r="A107" s="176" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="159"/>
@@ -31003,7 +31250,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="176">
+      <c r="E108" s="175">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -31012,17 +31259,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">
